--- a/assets/data/world-bank/excel/ove_banco_mundial_venezuela_pobreza_y_desigualdad.xlsx
+++ b/assets/data/world-bank/excel/ove_banco_mundial_venezuela_pobreza_y_desigualdad.xlsx
@@ -715,7 +715,7 @@
       </c>
       <c r="P7" s="4" t="inlineStr">
         <is>
-          <t>2026-09-07</t>
+          <t>2026-09-14</t>
         </is>
       </c>
       <c r="Q7" s="4" t="n"/>
@@ -792,7 +792,7 @@
       </c>
       <c r="P8" s="4" t="inlineStr">
         <is>
-          <t>2026-09-07</t>
+          <t>2026-09-14</t>
         </is>
       </c>
       <c r="Q8" s="4" t="n"/>
@@ -869,7 +869,7 @@
       </c>
       <c r="P9" s="4" t="inlineStr">
         <is>
-          <t>2026-09-07</t>
+          <t>2026-09-14</t>
         </is>
       </c>
       <c r="Q9" s="4" t="n"/>
@@ -946,7 +946,7 @@
       </c>
       <c r="P10" s="4" t="inlineStr">
         <is>
-          <t>2026-09-07</t>
+          <t>2026-09-14</t>
         </is>
       </c>
       <c r="Q10" s="4" t="n"/>
@@ -1023,7 +1023,7 @@
       </c>
       <c r="P11" s="4" t="inlineStr">
         <is>
-          <t>2026-09-07</t>
+          <t>2026-09-14</t>
         </is>
       </c>
       <c r="Q11" s="4" t="n"/>
@@ -1100,7 +1100,7 @@
       </c>
       <c r="P12" s="4" t="inlineStr">
         <is>
-          <t>2026-09-07</t>
+          <t>2026-09-14</t>
         </is>
       </c>
       <c r="Q12" s="4" t="n"/>
@@ -1177,7 +1177,7 @@
       </c>
       <c r="P13" s="4" t="inlineStr">
         <is>
-          <t>2026-09-07</t>
+          <t>2026-09-14</t>
         </is>
       </c>
       <c r="Q13" s="4" t="n"/>
@@ -1254,7 +1254,7 @@
       </c>
       <c r="P14" s="4" t="inlineStr">
         <is>
-          <t>2026-09-07</t>
+          <t>2026-09-14</t>
         </is>
       </c>
       <c r="Q14" s="4" t="n"/>
@@ -1331,7 +1331,7 @@
       </c>
       <c r="P15" s="4" t="inlineStr">
         <is>
-          <t>2026-09-07</t>
+          <t>2026-09-14</t>
         </is>
       </c>
       <c r="Q15" s="4" t="n"/>
@@ -1408,7 +1408,7 @@
       </c>
       <c r="P16" s="4" t="inlineStr">
         <is>
-          <t>2026-09-07</t>
+          <t>2026-09-14</t>
         </is>
       </c>
       <c r="Q16" s="4" t="n"/>
@@ -1485,7 +1485,7 @@
       </c>
       <c r="P17" s="4" t="inlineStr">
         <is>
-          <t>2026-09-07</t>
+          <t>2026-09-14</t>
         </is>
       </c>
       <c r="Q17" s="4" t="n"/>
@@ -1562,7 +1562,7 @@
       </c>
       <c r="P18" s="4" t="inlineStr">
         <is>
-          <t>2026-09-07</t>
+          <t>2026-09-14</t>
         </is>
       </c>
       <c r="Q18" s="4" t="n"/>
@@ -1639,7 +1639,7 @@
       </c>
       <c r="P19" s="4" t="inlineStr">
         <is>
-          <t>2026-09-07</t>
+          <t>2026-09-14</t>
         </is>
       </c>
       <c r="Q19" s="4" t="n"/>
@@ -1716,7 +1716,7 @@
       </c>
       <c r="P20" s="4" t="inlineStr">
         <is>
-          <t>2026-09-07</t>
+          <t>2026-09-14</t>
         </is>
       </c>
       <c r="Q20" s="4" t="n"/>
@@ -1793,7 +1793,7 @@
       </c>
       <c r="P21" s="4" t="inlineStr">
         <is>
-          <t>2026-09-07</t>
+          <t>2026-09-14</t>
         </is>
       </c>
       <c r="Q21" s="4" t="n"/>
@@ -1870,7 +1870,7 @@
       </c>
       <c r="P22" s="4" t="inlineStr">
         <is>
-          <t>2026-09-07</t>
+          <t>2026-09-14</t>
         </is>
       </c>
       <c r="Q22" s="4" t="n"/>
@@ -1947,7 +1947,7 @@
       </c>
       <c r="P23" s="4" t="inlineStr">
         <is>
-          <t>2026-09-07</t>
+          <t>2026-09-14</t>
         </is>
       </c>
       <c r="Q23" s="4" t="n"/>
@@ -2024,7 +2024,7 @@
       </c>
       <c r="P24" s="4" t="inlineStr">
         <is>
-          <t>2026-09-07</t>
+          <t>2026-09-14</t>
         </is>
       </c>
       <c r="Q24" s="4" t="n"/>
@@ -2101,7 +2101,7 @@
       </c>
       <c r="P25" s="4" t="inlineStr">
         <is>
-          <t>2026-09-07</t>
+          <t>2026-09-14</t>
         </is>
       </c>
       <c r="Q25" s="4" t="n"/>
@@ -2178,7 +2178,7 @@
       </c>
       <c r="P26" s="4" t="inlineStr">
         <is>
-          <t>2026-09-07</t>
+          <t>2026-09-14</t>
         </is>
       </c>
       <c r="Q26" s="4" t="n"/>
@@ -2255,7 +2255,7 @@
       </c>
       <c r="P27" s="4" t="inlineStr">
         <is>
-          <t>2026-09-07</t>
+          <t>2026-09-14</t>
         </is>
       </c>
       <c r="Q27" s="4" t="n"/>
@@ -2334,7 +2334,7 @@
       </c>
       <c r="P28" s="4" t="inlineStr">
         <is>
-          <t>2026-09-07</t>
+          <t>2026-09-14</t>
         </is>
       </c>
       <c r="Q28" s="4" t="n"/>
@@ -2411,7 +2411,7 @@
       </c>
       <c r="P29" s="4" t="inlineStr">
         <is>
-          <t>2026-09-07</t>
+          <t>2026-09-14</t>
         </is>
       </c>
       <c r="Q29" s="4" t="n"/>
@@ -2488,7 +2488,7 @@
       </c>
       <c r="P30" s="4" t="inlineStr">
         <is>
-          <t>2026-09-07</t>
+          <t>2026-09-14</t>
         </is>
       </c>
       <c r="Q30" s="4" t="n"/>
@@ -2565,7 +2565,7 @@
       </c>
       <c r="P31" s="4" t="inlineStr">
         <is>
-          <t>2026-09-07</t>
+          <t>2026-09-14</t>
         </is>
       </c>
       <c r="Q31" s="4" t="n"/>
@@ -2642,7 +2642,7 @@
       </c>
       <c r="P32" s="4" t="inlineStr">
         <is>
-          <t>2026-09-07</t>
+          <t>2026-09-14</t>
         </is>
       </c>
       <c r="Q32" s="4" t="n"/>
@@ -2719,7 +2719,7 @@
       </c>
       <c r="P33" s="4" t="inlineStr">
         <is>
-          <t>2026-09-07</t>
+          <t>2026-09-14</t>
         </is>
       </c>
       <c r="Q33" s="4" t="n"/>
@@ -2798,7 +2798,7 @@
       </c>
       <c r="P34" s="4" t="inlineStr">
         <is>
-          <t>2026-09-07</t>
+          <t>2026-09-14</t>
         </is>
       </c>
       <c r="Q34" s="4" t="n"/>
@@ -2875,7 +2875,7 @@
       </c>
       <c r="P35" s="4" t="inlineStr">
         <is>
-          <t>2026-09-07</t>
+          <t>2026-09-14</t>
         </is>
       </c>
       <c r="Q35" s="4" t="n"/>
@@ -2954,7 +2954,7 @@
       </c>
       <c r="P36" s="4" t="inlineStr">
         <is>
-          <t>2026-09-07</t>
+          <t>2026-09-14</t>
         </is>
       </c>
       <c r="Q36" s="4" t="n"/>
@@ -3031,7 +3031,7 @@
       </c>
       <c r="P37" s="4" t="inlineStr">
         <is>
-          <t>2026-09-07</t>
+          <t>2026-09-14</t>
         </is>
       </c>
       <c r="Q37" s="4" t="n"/>
@@ -3108,7 +3108,7 @@
       </c>
       <c r="P38" s="4" t="inlineStr">
         <is>
-          <t>2026-09-07</t>
+          <t>2026-09-14</t>
         </is>
       </c>
       <c r="Q38" s="4" t="n"/>
@@ -3187,7 +3187,7 @@
       </c>
       <c r="P39" s="4" t="inlineStr">
         <is>
-          <t>2026-09-07</t>
+          <t>2026-09-14</t>
         </is>
       </c>
       <c r="Q39" s="4" t="n"/>
@@ -3264,7 +3264,7 @@
       </c>
       <c r="P40" s="4" t="inlineStr">
         <is>
-          <t>2026-09-07</t>
+          <t>2026-09-14</t>
         </is>
       </c>
       <c r="Q40" s="4" t="n"/>
@@ -3341,7 +3341,7 @@
       </c>
       <c r="P41" s="4" t="inlineStr">
         <is>
-          <t>2026-09-07</t>
+          <t>2026-09-14</t>
         </is>
       </c>
       <c r="Q41" s="4" t="n"/>
@@ -3420,7 +3420,7 @@
       </c>
       <c r="P42" s="4" t="inlineStr">
         <is>
-          <t>2026-09-07</t>
+          <t>2026-09-14</t>
         </is>
       </c>
       <c r="Q42" s="4" t="n"/>
@@ -3497,7 +3497,7 @@
       </c>
       <c r="P43" s="4" t="inlineStr">
         <is>
-          <t>2026-09-07</t>
+          <t>2026-09-14</t>
         </is>
       </c>
       <c r="Q43" s="4" t="n"/>
@@ -3574,7 +3574,7 @@
       </c>
       <c r="P44" s="4" t="inlineStr">
         <is>
-          <t>2026-09-07</t>
+          <t>2026-09-14</t>
         </is>
       </c>
       <c r="Q44" s="4" t="n"/>
@@ -3653,7 +3653,7 @@
       </c>
       <c r="P45" s="4" t="inlineStr">
         <is>
-          <t>2026-09-07</t>
+          <t>2026-09-14</t>
         </is>
       </c>
       <c r="Q45" s="4" t="n"/>
@@ -3732,7 +3732,7 @@
       </c>
       <c r="P46" s="4" t="inlineStr">
         <is>
-          <t>2026-09-07</t>
+          <t>2026-09-14</t>
         </is>
       </c>
       <c r="Q46" s="4" t="n"/>
@@ -3809,7 +3809,7 @@
       </c>
       <c r="P47" s="4" t="inlineStr">
         <is>
-          <t>2026-09-07</t>
+          <t>2026-09-14</t>
         </is>
       </c>
       <c r="Q47" s="4" t="n"/>
@@ -3888,7 +3888,7 @@
       </c>
       <c r="P48" s="4" t="inlineStr">
         <is>
-          <t>2026-09-07</t>
+          <t>2026-09-14</t>
         </is>
       </c>
       <c r="Q48" s="4" t="n"/>
@@ -3967,7 +3967,7 @@
       </c>
       <c r="P49" s="4" t="inlineStr">
         <is>
-          <t>2026-09-07</t>
+          <t>2026-09-14</t>
         </is>
       </c>
       <c r="Q49" s="4" t="n"/>
@@ -4046,7 +4046,7 @@
       </c>
       <c r="P50" s="4" t="inlineStr">
         <is>
-          <t>2026-09-07</t>
+          <t>2026-09-14</t>
         </is>
       </c>
       <c r="Q50" s="4" t="n"/>
@@ -4125,7 +4125,7 @@
       </c>
       <c r="P51" s="4" t="inlineStr">
         <is>
-          <t>2026-09-07</t>
+          <t>2026-09-14</t>
         </is>
       </c>
       <c r="Q51" s="4" t="n"/>
@@ -4204,7 +4204,7 @@
       </c>
       <c r="P52" s="4" t="inlineStr">
         <is>
-          <t>2026-09-07</t>
+          <t>2026-09-14</t>
         </is>
       </c>
       <c r="Q52" s="4" t="n"/>
@@ -4283,7 +4283,7 @@
       </c>
       <c r="P53" s="4" t="inlineStr">
         <is>
-          <t>2026-09-07</t>
+          <t>2026-09-14</t>
         </is>
       </c>
       <c r="Q53" s="4" t="n"/>
@@ -4360,7 +4360,7 @@
       </c>
       <c r="P54" s="4" t="inlineStr">
         <is>
-          <t>2026-09-07</t>
+          <t>2026-09-14</t>
         </is>
       </c>
       <c r="Q54" s="4" t="n"/>
@@ -4437,7 +4437,7 @@
       </c>
       <c r="P55" s="4" t="inlineStr">
         <is>
-          <t>2026-09-07</t>
+          <t>2026-09-14</t>
         </is>
       </c>
       <c r="Q55" s="4" t="n"/>
@@ -4514,7 +4514,7 @@
       </c>
       <c r="P56" s="4" t="inlineStr">
         <is>
-          <t>2026-09-07</t>
+          <t>2026-09-14</t>
         </is>
       </c>
       <c r="Q56" s="4" t="n"/>
@@ -4591,7 +4591,7 @@
       </c>
       <c r="P57" s="4" t="inlineStr">
         <is>
-          <t>2026-09-07</t>
+          <t>2026-09-14</t>
         </is>
       </c>
       <c r="Q57" s="4" t="n"/>
@@ -4668,7 +4668,7 @@
       </c>
       <c r="P58" s="4" t="inlineStr">
         <is>
-          <t>2026-09-07</t>
+          <t>2026-09-14</t>
         </is>
       </c>
       <c r="Q58" s="4" t="n"/>
@@ -4745,7 +4745,7 @@
       </c>
       <c r="P59" s="4" t="inlineStr">
         <is>
-          <t>2026-09-07</t>
+          <t>2026-09-14</t>
         </is>
       </c>
       <c r="Q59" s="4" t="n"/>
@@ -4822,7 +4822,7 @@
       </c>
       <c r="P60" s="4" t="inlineStr">
         <is>
-          <t>2026-09-07</t>
+          <t>2026-09-14</t>
         </is>
       </c>
       <c r="Q60" s="4" t="n"/>
@@ -4899,7 +4899,7 @@
       </c>
       <c r="P61" s="4" t="inlineStr">
         <is>
-          <t>2026-09-07</t>
+          <t>2026-09-14</t>
         </is>
       </c>
       <c r="Q61" s="4" t="n"/>
@@ -4976,7 +4976,7 @@
       </c>
       <c r="P62" s="4" t="inlineStr">
         <is>
-          <t>2026-09-07</t>
+          <t>2026-09-14</t>
         </is>
       </c>
       <c r="Q62" s="4" t="n"/>
@@ -5053,7 +5053,7 @@
       </c>
       <c r="P63" s="4" t="inlineStr">
         <is>
-          <t>2026-09-07</t>
+          <t>2026-09-14</t>
         </is>
       </c>
       <c r="Q63" s="4" t="n"/>
@@ -5130,7 +5130,7 @@
       </c>
       <c r="P64" s="4" t="inlineStr">
         <is>
-          <t>2026-09-07</t>
+          <t>2026-09-14</t>
         </is>
       </c>
       <c r="Q64" s="4" t="n"/>
@@ -5207,7 +5207,7 @@
       </c>
       <c r="P65" s="4" t="inlineStr">
         <is>
-          <t>2026-09-07</t>
+          <t>2026-09-14</t>
         </is>
       </c>
       <c r="Q65" s="4" t="n"/>
@@ -5284,7 +5284,7 @@
       </c>
       <c r="P66" s="4" t="inlineStr">
         <is>
-          <t>2026-09-07</t>
+          <t>2026-09-14</t>
         </is>
       </c>
       <c r="Q66" s="4" t="n"/>
@@ -5361,7 +5361,7 @@
       </c>
       <c r="P67" s="4" t="inlineStr">
         <is>
-          <t>2026-09-07</t>
+          <t>2026-09-14</t>
         </is>
       </c>
       <c r="Q67" s="4" t="n"/>
@@ -5438,7 +5438,7 @@
       </c>
       <c r="P68" s="4" t="inlineStr">
         <is>
-          <t>2026-09-07</t>
+          <t>2026-09-14</t>
         </is>
       </c>
       <c r="Q68" s="4" t="n"/>
@@ -5515,7 +5515,7 @@
       </c>
       <c r="P69" s="4" t="inlineStr">
         <is>
-          <t>2026-09-07</t>
+          <t>2026-09-14</t>
         </is>
       </c>
       <c r="Q69" s="4" t="n"/>
@@ -5592,7 +5592,7 @@
       </c>
       <c r="P70" s="4" t="inlineStr">
         <is>
-          <t>2026-09-07</t>
+          <t>2026-09-14</t>
         </is>
       </c>
       <c r="Q70" s="4" t="n"/>
@@ -5669,7 +5669,7 @@
       </c>
       <c r="P71" s="4" t="inlineStr">
         <is>
-          <t>2026-09-07</t>
+          <t>2026-09-14</t>
         </is>
       </c>
       <c r="Q71" s="4" t="n"/>
@@ -5746,7 +5746,7 @@
       </c>
       <c r="P72" s="4" t="inlineStr">
         <is>
-          <t>2026-09-07</t>
+          <t>2026-09-14</t>
         </is>
       </c>
       <c r="Q72" s="4" t="n"/>
@@ -5823,7 +5823,7 @@
       </c>
       <c r="P73" s="4" t="inlineStr">
         <is>
-          <t>2026-09-07</t>
+          <t>2026-09-14</t>
         </is>
       </c>
       <c r="Q73" s="4" t="n"/>
@@ -5900,7 +5900,7 @@
       </c>
       <c r="P74" s="4" t="inlineStr">
         <is>
-          <t>2026-09-07</t>
+          <t>2026-09-14</t>
         </is>
       </c>
       <c r="Q74" s="4" t="n"/>
@@ -5977,7 +5977,7 @@
       </c>
       <c r="P75" s="4" t="inlineStr">
         <is>
-          <t>2026-09-07</t>
+          <t>2026-09-14</t>
         </is>
       </c>
       <c r="Q75" s="4" t="n"/>
@@ -6054,7 +6054,7 @@
       </c>
       <c r="P76" s="4" t="inlineStr">
         <is>
-          <t>2026-09-07</t>
+          <t>2026-09-14</t>
         </is>
       </c>
       <c r="Q76" s="4" t="n"/>
@@ -6131,7 +6131,7 @@
       </c>
       <c r="P77" s="4" t="inlineStr">
         <is>
-          <t>2026-09-07</t>
+          <t>2026-09-14</t>
         </is>
       </c>
       <c r="Q77" s="4" t="n"/>
@@ -6208,7 +6208,7 @@
       </c>
       <c r="P78" s="4" t="inlineStr">
         <is>
-          <t>2026-09-07</t>
+          <t>2026-09-14</t>
         </is>
       </c>
       <c r="Q78" s="4" t="n"/>
@@ -6285,7 +6285,7 @@
       </c>
       <c r="P79" s="4" t="inlineStr">
         <is>
-          <t>2026-09-07</t>
+          <t>2026-09-14</t>
         </is>
       </c>
       <c r="Q79" s="4" t="n"/>
@@ -6362,7 +6362,7 @@
       </c>
       <c r="P80" s="4" t="inlineStr">
         <is>
-          <t>2026-09-07</t>
+          <t>2026-09-14</t>
         </is>
       </c>
       <c r="Q80" s="4" t="n"/>
@@ -6439,7 +6439,7 @@
       </c>
       <c r="P81" s="4" t="inlineStr">
         <is>
-          <t>2026-09-07</t>
+          <t>2026-09-14</t>
         </is>
       </c>
       <c r="Q81" s="4" t="n"/>
@@ -6516,7 +6516,7 @@
       </c>
       <c r="P82" s="4" t="inlineStr">
         <is>
-          <t>2026-09-07</t>
+          <t>2026-09-14</t>
         </is>
       </c>
       <c r="Q82" s="4" t="n"/>
@@ -6593,7 +6593,7 @@
       </c>
       <c r="P83" s="4" t="inlineStr">
         <is>
-          <t>2026-09-07</t>
+          <t>2026-09-14</t>
         </is>
       </c>
       <c r="Q83" s="4" t="n"/>
@@ -6670,7 +6670,7 @@
       </c>
       <c r="P84" s="4" t="inlineStr">
         <is>
-          <t>2026-09-07</t>
+          <t>2026-09-14</t>
         </is>
       </c>
       <c r="Q84" s="4" t="n"/>
@@ -6747,7 +6747,7 @@
       </c>
       <c r="P85" s="4" t="inlineStr">
         <is>
-          <t>2026-09-07</t>
+          <t>2026-09-14</t>
         </is>
       </c>
       <c r="Q85" s="4" t="n"/>
@@ -6824,7 +6824,7 @@
       </c>
       <c r="P86" s="4" t="inlineStr">
         <is>
-          <t>2026-09-07</t>
+          <t>2026-09-14</t>
         </is>
       </c>
       <c r="Q86" s="4" t="n"/>
@@ -6901,7 +6901,7 @@
       </c>
       <c r="P87" s="4" t="inlineStr">
         <is>
-          <t>2026-09-07</t>
+          <t>2026-09-14</t>
         </is>
       </c>
       <c r="Q87" s="4" t="n"/>
@@ -6978,7 +6978,7 @@
       </c>
       <c r="P88" s="4" t="inlineStr">
         <is>
-          <t>2026-09-07</t>
+          <t>2026-09-14</t>
         </is>
       </c>
       <c r="Q88" s="4" t="n"/>
@@ -7055,7 +7055,7 @@
       </c>
       <c r="P89" s="4" t="inlineStr">
         <is>
-          <t>2026-09-07</t>
+          <t>2026-09-14</t>
         </is>
       </c>
       <c r="Q89" s="4" t="n"/>
@@ -7132,7 +7132,7 @@
       </c>
       <c r="P90" s="4" t="inlineStr">
         <is>
-          <t>2026-09-07</t>
+          <t>2026-09-14</t>
         </is>
       </c>
       <c r="Q90" s="4" t="n"/>
@@ -7209,7 +7209,7 @@
       </c>
       <c r="P91" s="4" t="inlineStr">
         <is>
-          <t>2026-09-07</t>
+          <t>2026-09-14</t>
         </is>
       </c>
       <c r="Q91" s="4" t="n"/>
@@ -7286,7 +7286,7 @@
       </c>
       <c r="P92" s="4" t="inlineStr">
         <is>
-          <t>2026-09-07</t>
+          <t>2026-09-14</t>
         </is>
       </c>
       <c r="Q92" s="4" t="n"/>
@@ -7363,7 +7363,7 @@
       </c>
       <c r="P93" s="4" t="inlineStr">
         <is>
-          <t>2026-09-07</t>
+          <t>2026-09-14</t>
         </is>
       </c>
       <c r="Q93" s="4" t="n"/>
@@ -7442,7 +7442,7 @@
       </c>
       <c r="P94" s="4" t="inlineStr">
         <is>
-          <t>2026-09-07</t>
+          <t>2026-09-14</t>
         </is>
       </c>
       <c r="Q94" s="4" t="n"/>
@@ -7519,7 +7519,7 @@
       </c>
       <c r="P95" s="4" t="inlineStr">
         <is>
-          <t>2026-09-07</t>
+          <t>2026-09-14</t>
         </is>
       </c>
       <c r="Q95" s="4" t="n"/>
@@ -7596,7 +7596,7 @@
       </c>
       <c r="P96" s="4" t="inlineStr">
         <is>
-          <t>2026-09-07</t>
+          <t>2026-09-14</t>
         </is>
       </c>
       <c r="Q96" s="4" t="n"/>
@@ -7673,7 +7673,7 @@
       </c>
       <c r="P97" s="4" t="inlineStr">
         <is>
-          <t>2026-09-07</t>
+          <t>2026-09-14</t>
         </is>
       </c>
       <c r="Q97" s="4" t="n"/>
@@ -7750,7 +7750,7 @@
       </c>
       <c r="P98" s="4" t="inlineStr">
         <is>
-          <t>2026-09-07</t>
+          <t>2026-09-14</t>
         </is>
       </c>
       <c r="Q98" s="4" t="n"/>
@@ -7827,7 +7827,7 @@
       </c>
       <c r="P99" s="4" t="inlineStr">
         <is>
-          <t>2026-09-07</t>
+          <t>2026-09-14</t>
         </is>
       </c>
       <c r="Q99" s="4" t="n"/>
@@ -7906,7 +7906,7 @@
       </c>
       <c r="P100" s="4" t="inlineStr">
         <is>
-          <t>2026-09-07</t>
+          <t>2026-09-14</t>
         </is>
       </c>
       <c r="Q100" s="4" t="n"/>
@@ -7983,7 +7983,7 @@
       </c>
       <c r="P101" s="4" t="inlineStr">
         <is>
-          <t>2026-09-07</t>
+          <t>2026-09-14</t>
         </is>
       </c>
       <c r="Q101" s="4" t="n"/>
@@ -8062,7 +8062,7 @@
       </c>
       <c r="P102" s="4" t="inlineStr">
         <is>
-          <t>2026-09-07</t>
+          <t>2026-09-14</t>
         </is>
       </c>
       <c r="Q102" s="4" t="n"/>
@@ -8139,7 +8139,7 @@
       </c>
       <c r="P103" s="4" t="inlineStr">
         <is>
-          <t>2026-09-07</t>
+          <t>2026-09-14</t>
         </is>
       </c>
       <c r="Q103" s="4" t="n"/>
@@ -8216,7 +8216,7 @@
       </c>
       <c r="P104" s="4" t="inlineStr">
         <is>
-          <t>2026-09-07</t>
+          <t>2026-09-14</t>
         </is>
       </c>
       <c r="Q104" s="4" t="n"/>
@@ -8295,7 +8295,7 @@
       </c>
       <c r="P105" s="4" t="inlineStr">
         <is>
-          <t>2026-09-07</t>
+          <t>2026-09-14</t>
         </is>
       </c>
       <c r="Q105" s="4" t="n"/>
@@ -8372,7 +8372,7 @@
       </c>
       <c r="P106" s="4" t="inlineStr">
         <is>
-          <t>2026-09-07</t>
+          <t>2026-09-14</t>
         </is>
       </c>
       <c r="Q106" s="4" t="n"/>
@@ -8449,7 +8449,7 @@
       </c>
       <c r="P107" s="4" t="inlineStr">
         <is>
-          <t>2026-09-07</t>
+          <t>2026-09-14</t>
         </is>
       </c>
       <c r="Q107" s="4" t="n"/>
@@ -8528,7 +8528,7 @@
       </c>
       <c r="P108" s="4" t="inlineStr">
         <is>
-          <t>2026-09-07</t>
+          <t>2026-09-14</t>
         </is>
       </c>
       <c r="Q108" s="4" t="n"/>
@@ -8605,7 +8605,7 @@
       </c>
       <c r="P109" s="4" t="inlineStr">
         <is>
-          <t>2026-09-07</t>
+          <t>2026-09-14</t>
         </is>
       </c>
       <c r="Q109" s="4" t="n"/>
@@ -8682,7 +8682,7 @@
       </c>
       <c r="P110" s="4" t="inlineStr">
         <is>
-          <t>2026-09-07</t>
+          <t>2026-09-14</t>
         </is>
       </c>
       <c r="Q110" s="4" t="n"/>
@@ -8761,7 +8761,7 @@
       </c>
       <c r="P111" s="4" t="inlineStr">
         <is>
-          <t>2026-09-07</t>
+          <t>2026-09-14</t>
         </is>
       </c>
       <c r="Q111" s="4" t="n"/>
@@ -8840,7 +8840,7 @@
       </c>
       <c r="P112" s="4" t="inlineStr">
         <is>
-          <t>2026-09-07</t>
+          <t>2026-09-14</t>
         </is>
       </c>
       <c r="Q112" s="4" t="n"/>
@@ -8917,7 +8917,7 @@
       </c>
       <c r="P113" s="4" t="inlineStr">
         <is>
-          <t>2026-09-07</t>
+          <t>2026-09-14</t>
         </is>
       </c>
       <c r="Q113" s="4" t="n"/>
@@ -8996,7 +8996,7 @@
       </c>
       <c r="P114" s="4" t="inlineStr">
         <is>
-          <t>2026-09-07</t>
+          <t>2026-09-14</t>
         </is>
       </c>
       <c r="Q114" s="4" t="n"/>
@@ -9075,7 +9075,7 @@
       </c>
       <c r="P115" s="4" t="inlineStr">
         <is>
-          <t>2026-09-07</t>
+          <t>2026-09-14</t>
         </is>
       </c>
       <c r="Q115" s="4" t="n"/>
@@ -9154,7 +9154,7 @@
       </c>
       <c r="P116" s="4" t="inlineStr">
         <is>
-          <t>2026-09-07</t>
+          <t>2026-09-14</t>
         </is>
       </c>
       <c r="Q116" s="4" t="n"/>
@@ -9233,7 +9233,7 @@
       </c>
       <c r="P117" s="4" t="inlineStr">
         <is>
-          <t>2026-09-07</t>
+          <t>2026-09-14</t>
         </is>
       </c>
       <c r="Q117" s="4" t="n"/>
@@ -9312,7 +9312,7 @@
       </c>
       <c r="P118" s="4" t="inlineStr">
         <is>
-          <t>2026-09-07</t>
+          <t>2026-09-14</t>
         </is>
       </c>
       <c r="Q118" s="4" t="n"/>
@@ -9391,7 +9391,7 @@
       </c>
       <c r="P119" s="4" t="inlineStr">
         <is>
-          <t>2026-09-07</t>
+          <t>2026-09-14</t>
         </is>
       </c>
       <c r="Q119" s="4" t="n"/>
@@ -9468,7 +9468,7 @@
       </c>
       <c r="P120" s="4" t="inlineStr">
         <is>
-          <t>2026-09-07</t>
+          <t>2026-09-14</t>
         </is>
       </c>
       <c r="Q120" s="4" t="n"/>
@@ -9545,7 +9545,7 @@
       </c>
       <c r="P121" s="4" t="inlineStr">
         <is>
-          <t>2026-09-07</t>
+          <t>2026-09-14</t>
         </is>
       </c>
       <c r="Q121" s="4" t="n"/>
@@ -9622,7 +9622,7 @@
       </c>
       <c r="P122" s="4" t="inlineStr">
         <is>
-          <t>2026-09-07</t>
+          <t>2026-09-14</t>
         </is>
       </c>
       <c r="Q122" s="4" t="n"/>
@@ -9699,7 +9699,7 @@
       </c>
       <c r="P123" s="4" t="inlineStr">
         <is>
-          <t>2026-09-07</t>
+          <t>2026-09-14</t>
         </is>
       </c>
       <c r="Q123" s="4" t="n"/>
@@ -9776,7 +9776,7 @@
       </c>
       <c r="P124" s="4" t="inlineStr">
         <is>
-          <t>2026-09-07</t>
+          <t>2026-09-14</t>
         </is>
       </c>
       <c r="Q124" s="4" t="n"/>
@@ -9853,7 +9853,7 @@
       </c>
       <c r="P125" s="4" t="inlineStr">
         <is>
-          <t>2026-09-07</t>
+          <t>2026-09-14</t>
         </is>
       </c>
       <c r="Q125" s="4" t="n"/>
@@ -9930,7 +9930,7 @@
       </c>
       <c r="P126" s="4" t="inlineStr">
         <is>
-          <t>2026-09-07</t>
+          <t>2026-09-14</t>
         </is>
       </c>
       <c r="Q126" s="4" t="n"/>
@@ -10007,7 +10007,7 @@
       </c>
       <c r="P127" s="4" t="inlineStr">
         <is>
-          <t>2026-09-07</t>
+          <t>2026-09-14</t>
         </is>
       </c>
       <c r="Q127" s="4" t="n"/>
@@ -10084,7 +10084,7 @@
       </c>
       <c r="P128" s="4" t="inlineStr">
         <is>
-          <t>2026-09-07</t>
+          <t>2026-09-14</t>
         </is>
       </c>
       <c r="Q128" s="4" t="n"/>
@@ -10161,7 +10161,7 @@
       </c>
       <c r="P129" s="4" t="inlineStr">
         <is>
-          <t>2026-09-07</t>
+          <t>2026-09-14</t>
         </is>
       </c>
       <c r="Q129" s="4" t="n"/>
@@ -10238,7 +10238,7 @@
       </c>
       <c r="P130" s="4" t="inlineStr">
         <is>
-          <t>2026-09-07</t>
+          <t>2026-09-14</t>
         </is>
       </c>
       <c r="Q130" s="4" t="n"/>
@@ -10315,7 +10315,7 @@
       </c>
       <c r="P131" s="4" t="inlineStr">
         <is>
-          <t>2026-09-07</t>
+          <t>2026-09-14</t>
         </is>
       </c>
       <c r="Q131" s="4" t="n"/>
@@ -10392,7 +10392,7 @@
       </c>
       <c r="P132" s="4" t="inlineStr">
         <is>
-          <t>2026-09-07</t>
+          <t>2026-09-14</t>
         </is>
       </c>
       <c r="Q132" s="4" t="n"/>
@@ -10469,7 +10469,7 @@
       </c>
       <c r="P133" s="4" t="inlineStr">
         <is>
-          <t>2026-09-07</t>
+          <t>2026-09-14</t>
         </is>
       </c>
       <c r="Q133" s="4" t="n"/>
@@ -10546,7 +10546,7 @@
       </c>
       <c r="P134" s="4" t="inlineStr">
         <is>
-          <t>2026-09-07</t>
+          <t>2026-09-14</t>
         </is>
       </c>
       <c r="Q134" s="4" t="n"/>
@@ -10623,7 +10623,7 @@
       </c>
       <c r="P135" s="4" t="inlineStr">
         <is>
-          <t>2026-09-07</t>
+          <t>2026-09-14</t>
         </is>
       </c>
       <c r="Q135" s="4" t="n"/>
@@ -10700,7 +10700,7 @@
       </c>
       <c r="P136" s="4" t="inlineStr">
         <is>
-          <t>2026-09-07</t>
+          <t>2026-09-14</t>
         </is>
       </c>
       <c r="Q136" s="4" t="n"/>
@@ -10777,7 +10777,7 @@
       </c>
       <c r="P137" s="4" t="inlineStr">
         <is>
-          <t>2026-09-07</t>
+          <t>2026-09-14</t>
         </is>
       </c>
       <c r="Q137" s="4" t="n"/>
@@ -10854,7 +10854,7 @@
       </c>
       <c r="P138" s="4" t="inlineStr">
         <is>
-          <t>2026-09-07</t>
+          <t>2026-09-14</t>
         </is>
       </c>
       <c r="Q138" s="4" t="n"/>
@@ -10931,7 +10931,7 @@
       </c>
       <c r="P139" s="4" t="inlineStr">
         <is>
-          <t>2026-09-07</t>
+          <t>2026-09-14</t>
         </is>
       </c>
       <c r="Q139" s="4" t="n"/>
@@ -11008,7 +11008,7 @@
       </c>
       <c r="P140" s="4" t="inlineStr">
         <is>
-          <t>2026-09-07</t>
+          <t>2026-09-14</t>
         </is>
       </c>
       <c r="Q140" s="4" t="n"/>
@@ -11085,7 +11085,7 @@
       </c>
       <c r="P141" s="4" t="inlineStr">
         <is>
-          <t>2026-09-07</t>
+          <t>2026-09-14</t>
         </is>
       </c>
       <c r="Q141" s="4" t="n"/>
@@ -11162,7 +11162,7 @@
       </c>
       <c r="P142" s="4" t="inlineStr">
         <is>
-          <t>2026-09-07</t>
+          <t>2026-09-14</t>
         </is>
       </c>
       <c r="Q142" s="4" t="n"/>
@@ -11239,7 +11239,7 @@
       </c>
       <c r="P143" s="4" t="inlineStr">
         <is>
-          <t>2026-09-07</t>
+          <t>2026-09-14</t>
         </is>
       </c>
       <c r="Q143" s="4" t="n"/>
@@ -11316,7 +11316,7 @@
       </c>
       <c r="P144" s="4" t="inlineStr">
         <is>
-          <t>2026-09-07</t>
+          <t>2026-09-14</t>
         </is>
       </c>
       <c r="Q144" s="4" t="n"/>
@@ -11393,7 +11393,7 @@
       </c>
       <c r="P145" s="4" t="inlineStr">
         <is>
-          <t>2026-09-07</t>
+          <t>2026-09-14</t>
         </is>
       </c>
       <c r="Q145" s="4" t="n"/>
@@ -11470,7 +11470,7 @@
       </c>
       <c r="P146" s="4" t="inlineStr">
         <is>
-          <t>2026-09-07</t>
+          <t>2026-09-14</t>
         </is>
       </c>
       <c r="Q146" s="4" t="n"/>
@@ -11547,7 +11547,7 @@
       </c>
       <c r="P147" s="4" t="inlineStr">
         <is>
-          <t>2026-09-07</t>
+          <t>2026-09-14</t>
         </is>
       </c>
       <c r="Q147" s="4" t="n"/>
@@ -11624,7 +11624,7 @@
       </c>
       <c r="P148" s="4" t="inlineStr">
         <is>
-          <t>2026-09-07</t>
+          <t>2026-09-14</t>
         </is>
       </c>
       <c r="Q148" s="4" t="n"/>
@@ -11701,7 +11701,7 @@
       </c>
       <c r="P149" s="4" t="inlineStr">
         <is>
-          <t>2026-09-07</t>
+          <t>2026-09-14</t>
         </is>
       </c>
       <c r="Q149" s="4" t="n"/>
@@ -11778,7 +11778,7 @@
       </c>
       <c r="P150" s="4" t="inlineStr">
         <is>
-          <t>2026-09-07</t>
+          <t>2026-09-14</t>
         </is>
       </c>
       <c r="Q150" s="4" t="n"/>
@@ -11855,7 +11855,7 @@
       </c>
       <c r="P151" s="4" t="inlineStr">
         <is>
-          <t>2026-09-07</t>
+          <t>2026-09-14</t>
         </is>
       </c>
       <c r="Q151" s="4" t="n"/>
@@ -11932,7 +11932,7 @@
       </c>
       <c r="P152" s="4" t="inlineStr">
         <is>
-          <t>2026-09-07</t>
+          <t>2026-09-14</t>
         </is>
       </c>
       <c r="Q152" s="4" t="n"/>
@@ -12009,7 +12009,7 @@
       </c>
       <c r="P153" s="4" t="inlineStr">
         <is>
-          <t>2026-09-07</t>
+          <t>2026-09-14</t>
         </is>
       </c>
       <c r="Q153" s="4" t="n"/>
@@ -12086,7 +12086,7 @@
       </c>
       <c r="P154" s="4" t="inlineStr">
         <is>
-          <t>2026-09-07</t>
+          <t>2026-09-14</t>
         </is>
       </c>
       <c r="Q154" s="4" t="n"/>
@@ -12163,7 +12163,7 @@
       </c>
       <c r="P155" s="4" t="inlineStr">
         <is>
-          <t>2026-09-07</t>
+          <t>2026-09-14</t>
         </is>
       </c>
       <c r="Q155" s="4" t="n"/>
@@ -12240,7 +12240,7 @@
       </c>
       <c r="P156" s="4" t="inlineStr">
         <is>
-          <t>2026-09-07</t>
+          <t>2026-09-14</t>
         </is>
       </c>
       <c r="Q156" s="4" t="n"/>
@@ -12317,7 +12317,7 @@
       </c>
       <c r="P157" s="4" t="inlineStr">
         <is>
-          <t>2026-09-07</t>
+          <t>2026-09-14</t>
         </is>
       </c>
       <c r="Q157" s="4" t="n"/>
@@ -12394,7 +12394,7 @@
       </c>
       <c r="P158" s="4" t="inlineStr">
         <is>
-          <t>2026-09-07</t>
+          <t>2026-09-14</t>
         </is>
       </c>
       <c r="Q158" s="4" t="n"/>
@@ -12471,7 +12471,7 @@
       </c>
       <c r="P159" s="4" t="inlineStr">
         <is>
-          <t>2026-09-07</t>
+          <t>2026-09-14</t>
         </is>
       </c>
       <c r="Q159" s="4" t="n"/>
@@ -12550,7 +12550,7 @@
       </c>
       <c r="P160" s="4" t="inlineStr">
         <is>
-          <t>2026-09-07</t>
+          <t>2026-09-14</t>
         </is>
       </c>
       <c r="Q160" s="4" t="n"/>
@@ -12627,7 +12627,7 @@
       </c>
       <c r="P161" s="4" t="inlineStr">
         <is>
-          <t>2026-09-07</t>
+          <t>2026-09-14</t>
         </is>
       </c>
       <c r="Q161" s="4" t="n"/>
@@ -12704,7 +12704,7 @@
       </c>
       <c r="P162" s="4" t="inlineStr">
         <is>
-          <t>2026-09-07</t>
+          <t>2026-09-14</t>
         </is>
       </c>
       <c r="Q162" s="4" t="n"/>
@@ -12781,7 +12781,7 @@
       </c>
       <c r="P163" s="4" t="inlineStr">
         <is>
-          <t>2026-09-07</t>
+          <t>2026-09-14</t>
         </is>
       </c>
       <c r="Q163" s="4" t="n"/>
@@ -12858,7 +12858,7 @@
       </c>
       <c r="P164" s="4" t="inlineStr">
         <is>
-          <t>2026-09-07</t>
+          <t>2026-09-14</t>
         </is>
       </c>
       <c r="Q164" s="4" t="n"/>
@@ -12935,7 +12935,7 @@
       </c>
       <c r="P165" s="4" t="inlineStr">
         <is>
-          <t>2026-09-07</t>
+          <t>2026-09-14</t>
         </is>
       </c>
       <c r="Q165" s="4" t="n"/>
@@ -13014,7 +13014,7 @@
       </c>
       <c r="P166" s="4" t="inlineStr">
         <is>
-          <t>2026-09-07</t>
+          <t>2026-09-14</t>
         </is>
       </c>
       <c r="Q166" s="4" t="n"/>
@@ -13091,7 +13091,7 @@
       </c>
       <c r="P167" s="4" t="inlineStr">
         <is>
-          <t>2026-09-07</t>
+          <t>2026-09-14</t>
         </is>
       </c>
       <c r="Q167" s="4" t="n"/>
@@ -13170,7 +13170,7 @@
       </c>
       <c r="P168" s="4" t="inlineStr">
         <is>
-          <t>2026-09-07</t>
+          <t>2026-09-14</t>
         </is>
       </c>
       <c r="Q168" s="4" t="n"/>
@@ -13247,7 +13247,7 @@
       </c>
       <c r="P169" s="4" t="inlineStr">
         <is>
-          <t>2026-09-07</t>
+          <t>2026-09-14</t>
         </is>
       </c>
       <c r="Q169" s="4" t="n"/>
@@ -13324,7 +13324,7 @@
       </c>
       <c r="P170" s="4" t="inlineStr">
         <is>
-          <t>2026-09-07</t>
+          <t>2026-09-14</t>
         </is>
       </c>
       <c r="Q170" s="4" t="n"/>
@@ -13403,7 +13403,7 @@
       </c>
       <c r="P171" s="4" t="inlineStr">
         <is>
-          <t>2026-09-07</t>
+          <t>2026-09-14</t>
         </is>
       </c>
       <c r="Q171" s="4" t="n"/>
@@ -13480,7 +13480,7 @@
       </c>
       <c r="P172" s="4" t="inlineStr">
         <is>
-          <t>2026-09-07</t>
+          <t>2026-09-14</t>
         </is>
       </c>
       <c r="Q172" s="4" t="n"/>
@@ -13557,7 +13557,7 @@
       </c>
       <c r="P173" s="4" t="inlineStr">
         <is>
-          <t>2026-09-07</t>
+          <t>2026-09-14</t>
         </is>
       </c>
       <c r="Q173" s="4" t="n"/>
@@ -13636,7 +13636,7 @@
       </c>
       <c r="P174" s="4" t="inlineStr">
         <is>
-          <t>2026-09-07</t>
+          <t>2026-09-14</t>
         </is>
       </c>
       <c r="Q174" s="4" t="n"/>
@@ -13713,7 +13713,7 @@
       </c>
       <c r="P175" s="4" t="inlineStr">
         <is>
-          <t>2026-09-07</t>
+          <t>2026-09-14</t>
         </is>
       </c>
       <c r="Q175" s="4" t="n"/>
@@ -13790,7 +13790,7 @@
       </c>
       <c r="P176" s="4" t="inlineStr">
         <is>
-          <t>2026-09-07</t>
+          <t>2026-09-14</t>
         </is>
       </c>
       <c r="Q176" s="4" t="n"/>
@@ -13869,7 +13869,7 @@
       </c>
       <c r="P177" s="4" t="inlineStr">
         <is>
-          <t>2026-09-07</t>
+          <t>2026-09-14</t>
         </is>
       </c>
       <c r="Q177" s="4" t="n"/>
@@ -13948,7 +13948,7 @@
       </c>
       <c r="P178" s="4" t="inlineStr">
         <is>
-          <t>2026-09-07</t>
+          <t>2026-09-14</t>
         </is>
       </c>
       <c r="Q178" s="4" t="n"/>
@@ -14025,7 +14025,7 @@
       </c>
       <c r="P179" s="4" t="inlineStr">
         <is>
-          <t>2026-09-07</t>
+          <t>2026-09-14</t>
         </is>
       </c>
       <c r="Q179" s="4" t="n"/>
@@ -14104,7 +14104,7 @@
       </c>
       <c r="P180" s="4" t="inlineStr">
         <is>
-          <t>2026-09-07</t>
+          <t>2026-09-14</t>
         </is>
       </c>
       <c r="Q180" s="4" t="n"/>
@@ -14183,7 +14183,7 @@
       </c>
       <c r="P181" s="4" t="inlineStr">
         <is>
-          <t>2026-09-07</t>
+          <t>2026-09-14</t>
         </is>
       </c>
       <c r="Q181" s="4" t="n"/>
@@ -14262,7 +14262,7 @@
       </c>
       <c r="P182" s="4" t="inlineStr">
         <is>
-          <t>2026-09-07</t>
+          <t>2026-09-14</t>
         </is>
       </c>
       <c r="Q182" s="4" t="n"/>
@@ -14341,7 +14341,7 @@
       </c>
       <c r="P183" s="4" t="inlineStr">
         <is>
-          <t>2026-09-07</t>
+          <t>2026-09-14</t>
         </is>
       </c>
       <c r="Q183" s="4" t="n"/>
@@ -14420,7 +14420,7 @@
       </c>
       <c r="P184" s="4" t="inlineStr">
         <is>
-          <t>2026-09-07</t>
+          <t>2026-09-14</t>
         </is>
       </c>
       <c r="Q184" s="4" t="n"/>
@@ -14499,7 +14499,7 @@
       </c>
       <c r="P185" s="4" t="inlineStr">
         <is>
-          <t>2026-09-07</t>
+          <t>2026-09-14</t>
         </is>
       </c>
       <c r="Q185" s="4" t="n"/>
@@ -14576,7 +14576,7 @@
       </c>
       <c r="P186" s="4" t="inlineStr">
         <is>
-          <t>2026-09-07</t>
+          <t>2026-09-14</t>
         </is>
       </c>
       <c r="Q186" s="4" t="n"/>
@@ -14653,7 +14653,7 @@
       </c>
       <c r="P187" s="4" t="inlineStr">
         <is>
-          <t>2026-09-07</t>
+          <t>2026-09-14</t>
         </is>
       </c>
       <c r="Q187" s="4" t="n"/>
@@ -14730,7 +14730,7 @@
       </c>
       <c r="P188" s="4" t="inlineStr">
         <is>
-          <t>2026-09-07</t>
+          <t>2026-09-14</t>
         </is>
       </c>
       <c r="Q188" s="4" t="n"/>
@@ -14807,7 +14807,7 @@
       </c>
       <c r="P189" s="4" t="inlineStr">
         <is>
-          <t>2026-09-07</t>
+          <t>2026-09-14</t>
         </is>
       </c>
       <c r="Q189" s="4" t="n"/>
@@ -14884,7 +14884,7 @@
       </c>
       <c r="P190" s="4" t="inlineStr">
         <is>
-          <t>2026-09-07</t>
+          <t>2026-09-14</t>
         </is>
       </c>
       <c r="Q190" s="4" t="n"/>
@@ -14961,7 +14961,7 @@
       </c>
       <c r="P191" s="4" t="inlineStr">
         <is>
-          <t>2026-09-07</t>
+          <t>2026-09-14</t>
         </is>
       </c>
       <c r="Q191" s="4" t="n"/>
@@ -15038,7 +15038,7 @@
       </c>
       <c r="P192" s="4" t="inlineStr">
         <is>
-          <t>2026-09-07</t>
+          <t>2026-09-14</t>
         </is>
       </c>
       <c r="Q192" s="4" t="n"/>
@@ -15115,7 +15115,7 @@
       </c>
       <c r="P193" s="4" t="inlineStr">
         <is>
-          <t>2026-09-07</t>
+          <t>2026-09-14</t>
         </is>
       </c>
       <c r="Q193" s="4" t="n"/>
@@ -15192,7 +15192,7 @@
       </c>
       <c r="P194" s="4" t="inlineStr">
         <is>
-          <t>2026-09-07</t>
+          <t>2026-09-14</t>
         </is>
       </c>
       <c r="Q194" s="4" t="n"/>
@@ -15269,7 +15269,7 @@
       </c>
       <c r="P195" s="4" t="inlineStr">
         <is>
-          <t>2026-09-07</t>
+          <t>2026-09-14</t>
         </is>
       </c>
       <c r="Q195" s="4" t="n"/>
@@ -15346,7 +15346,7 @@
       </c>
       <c r="P196" s="4" t="inlineStr">
         <is>
-          <t>2026-09-07</t>
+          <t>2026-09-14</t>
         </is>
       </c>
       <c r="Q196" s="4" t="n"/>
@@ -15423,7 +15423,7 @@
       </c>
       <c r="P197" s="4" t="inlineStr">
         <is>
-          <t>2026-09-07</t>
+          <t>2026-09-14</t>
         </is>
       </c>
       <c r="Q197" s="4" t="n"/>
@@ -15500,7 +15500,7 @@
       </c>
       <c r="P198" s="4" t="inlineStr">
         <is>
-          <t>2026-09-07</t>
+          <t>2026-09-14</t>
         </is>
       </c>
       <c r="Q198" s="4" t="n"/>
@@ -15577,7 +15577,7 @@
       </c>
       <c r="P199" s="4" t="inlineStr">
         <is>
-          <t>2026-09-07</t>
+          <t>2026-09-14</t>
         </is>
       </c>
       <c r="Q199" s="4" t="n"/>
@@ -15654,7 +15654,7 @@
       </c>
       <c r="P200" s="4" t="inlineStr">
         <is>
-          <t>2026-09-07</t>
+          <t>2026-09-14</t>
         </is>
       </c>
       <c r="Q200" s="4" t="n"/>
@@ -15731,7 +15731,7 @@
       </c>
       <c r="P201" s="4" t="inlineStr">
         <is>
-          <t>2026-09-07</t>
+          <t>2026-09-14</t>
         </is>
       </c>
       <c r="Q201" s="4" t="n"/>
@@ -15808,7 +15808,7 @@
       </c>
       <c r="P202" s="4" t="inlineStr">
         <is>
-          <t>2026-09-07</t>
+          <t>2026-09-14</t>
         </is>
       </c>
       <c r="Q202" s="4" t="n"/>
@@ -15885,7 +15885,7 @@
       </c>
       <c r="P203" s="4" t="inlineStr">
         <is>
-          <t>2026-09-07</t>
+          <t>2026-09-14</t>
         </is>
       </c>
       <c r="Q203" s="4" t="n"/>
@@ -15962,7 +15962,7 @@
       </c>
       <c r="P204" s="4" t="inlineStr">
         <is>
-          <t>2026-09-07</t>
+          <t>2026-09-14</t>
         </is>
       </c>
       <c r="Q204" s="4" t="n"/>
@@ -16039,7 +16039,7 @@
       </c>
       <c r="P205" s="4" t="inlineStr">
         <is>
-          <t>2026-09-07</t>
+          <t>2026-09-14</t>
         </is>
       </c>
       <c r="Q205" s="4" t="n"/>
@@ -16116,7 +16116,7 @@
       </c>
       <c r="P206" s="4" t="inlineStr">
         <is>
-          <t>2026-09-07</t>
+          <t>2026-09-14</t>
         </is>
       </c>
       <c r="Q206" s="4" t="n"/>
@@ -16193,7 +16193,7 @@
       </c>
       <c r="P207" s="4" t="inlineStr">
         <is>
-          <t>2026-09-07</t>
+          <t>2026-09-14</t>
         </is>
       </c>
       <c r="Q207" s="4" t="n"/>
@@ -16270,7 +16270,7 @@
       </c>
       <c r="P208" s="4" t="inlineStr">
         <is>
-          <t>2026-09-07</t>
+          <t>2026-09-14</t>
         </is>
       </c>
       <c r="Q208" s="4" t="n"/>
@@ -16347,7 +16347,7 @@
       </c>
       <c r="P209" s="4" t="inlineStr">
         <is>
-          <t>2026-09-07</t>
+          <t>2026-09-14</t>
         </is>
       </c>
       <c r="Q209" s="4" t="n"/>
@@ -16424,7 +16424,7 @@
       </c>
       <c r="P210" s="4" t="inlineStr">
         <is>
-          <t>2026-09-07</t>
+          <t>2026-09-14</t>
         </is>
       </c>
       <c r="Q210" s="4" t="n"/>
@@ -16501,7 +16501,7 @@
       </c>
       <c r="P211" s="4" t="inlineStr">
         <is>
-          <t>2026-09-07</t>
+          <t>2026-09-14</t>
         </is>
       </c>
       <c r="Q211" s="4" t="n"/>
@@ -16578,7 +16578,7 @@
       </c>
       <c r="P212" s="4" t="inlineStr">
         <is>
-          <t>2026-09-07</t>
+          <t>2026-09-14</t>
         </is>
       </c>
       <c r="Q212" s="4" t="n"/>
@@ -16655,7 +16655,7 @@
       </c>
       <c r="P213" s="4" t="inlineStr">
         <is>
-          <t>2026-09-07</t>
+          <t>2026-09-14</t>
         </is>
       </c>
       <c r="Q213" s="4" t="n"/>
@@ -16732,7 +16732,7 @@
       </c>
       <c r="P214" s="4" t="inlineStr">
         <is>
-          <t>2026-09-07</t>
+          <t>2026-09-14</t>
         </is>
       </c>
       <c r="Q214" s="4" t="n"/>
@@ -16809,7 +16809,7 @@
       </c>
       <c r="P215" s="4" t="inlineStr">
         <is>
-          <t>2026-09-07</t>
+          <t>2026-09-14</t>
         </is>
       </c>
       <c r="Q215" s="4" t="n"/>
@@ -16886,7 +16886,7 @@
       </c>
       <c r="P216" s="4" t="inlineStr">
         <is>
-          <t>2026-09-07</t>
+          <t>2026-09-14</t>
         </is>
       </c>
       <c r="Q216" s="4" t="n"/>
@@ -16963,7 +16963,7 @@
       </c>
       <c r="P217" s="4" t="inlineStr">
         <is>
-          <t>2026-09-07</t>
+          <t>2026-09-14</t>
         </is>
       </c>
       <c r="Q217" s="4" t="n"/>
@@ -17040,7 +17040,7 @@
       </c>
       <c r="P218" s="4" t="inlineStr">
         <is>
-          <t>2026-09-07</t>
+          <t>2026-09-14</t>
         </is>
       </c>
       <c r="Q218" s="4" t="n"/>
@@ -17117,7 +17117,7 @@
       </c>
       <c r="P219" s="4" t="inlineStr">
         <is>
-          <t>2026-09-07</t>
+          <t>2026-09-14</t>
         </is>
       </c>
       <c r="Q219" s="4" t="n"/>
@@ -17194,7 +17194,7 @@
       </c>
       <c r="P220" s="4" t="inlineStr">
         <is>
-          <t>2026-09-07</t>
+          <t>2026-09-14</t>
         </is>
       </c>
       <c r="Q220" s="4" t="n"/>
@@ -17271,7 +17271,7 @@
       </c>
       <c r="P221" s="4" t="inlineStr">
         <is>
-          <t>2026-09-07</t>
+          <t>2026-09-14</t>
         </is>
       </c>
       <c r="Q221" s="4" t="n"/>
@@ -17348,7 +17348,7 @@
       </c>
       <c r="P222" s="4" t="inlineStr">
         <is>
-          <t>2026-09-07</t>
+          <t>2026-09-14</t>
         </is>
       </c>
       <c r="Q222" s="4" t="n"/>
@@ -17425,7 +17425,7 @@
       </c>
       <c r="P223" s="4" t="inlineStr">
         <is>
-          <t>2026-09-07</t>
+          <t>2026-09-14</t>
         </is>
       </c>
       <c r="Q223" s="4" t="n"/>
@@ -17502,7 +17502,7 @@
       </c>
       <c r="P224" s="4" t="inlineStr">
         <is>
-          <t>2026-09-07</t>
+          <t>2026-09-14</t>
         </is>
       </c>
       <c r="Q224" s="4" t="n"/>
@@ -17579,7 +17579,7 @@
       </c>
       <c r="P225" s="4" t="inlineStr">
         <is>
-          <t>2026-09-07</t>
+          <t>2026-09-14</t>
         </is>
       </c>
       <c r="Q225" s="4" t="n"/>
@@ -17658,7 +17658,7 @@
       </c>
       <c r="P226" s="4" t="inlineStr">
         <is>
-          <t>2026-09-07</t>
+          <t>2026-09-14</t>
         </is>
       </c>
       <c r="Q226" s="4" t="n"/>
@@ -17735,7 +17735,7 @@
       </c>
       <c r="P227" s="4" t="inlineStr">
         <is>
-          <t>2026-09-07</t>
+          <t>2026-09-14</t>
         </is>
       </c>
       <c r="Q227" s="4" t="n"/>
@@ -17812,7 +17812,7 @@
       </c>
       <c r="P228" s="4" t="inlineStr">
         <is>
-          <t>2026-09-07</t>
+          <t>2026-09-14</t>
         </is>
       </c>
       <c r="Q228" s="4" t="n"/>
@@ -17889,7 +17889,7 @@
       </c>
       <c r="P229" s="4" t="inlineStr">
         <is>
-          <t>2026-09-07</t>
+          <t>2026-09-14</t>
         </is>
       </c>
       <c r="Q229" s="4" t="n"/>
@@ -17966,7 +17966,7 @@
       </c>
       <c r="P230" s="4" t="inlineStr">
         <is>
-          <t>2026-09-07</t>
+          <t>2026-09-14</t>
         </is>
       </c>
       <c r="Q230" s="4" t="n"/>
@@ -18043,7 +18043,7 @@
       </c>
       <c r="P231" s="4" t="inlineStr">
         <is>
-          <t>2026-09-07</t>
+          <t>2026-09-14</t>
         </is>
       </c>
       <c r="Q231" s="4" t="n"/>
@@ -18122,7 +18122,7 @@
       </c>
       <c r="P232" s="4" t="inlineStr">
         <is>
-          <t>2026-09-07</t>
+          <t>2026-09-14</t>
         </is>
       </c>
       <c r="Q232" s="4" t="n"/>
@@ -18199,7 +18199,7 @@
       </c>
       <c r="P233" s="4" t="inlineStr">
         <is>
-          <t>2026-09-07</t>
+          <t>2026-09-14</t>
         </is>
       </c>
       <c r="Q233" s="4" t="n"/>
@@ -18278,7 +18278,7 @@
       </c>
       <c r="P234" s="4" t="inlineStr">
         <is>
-          <t>2026-09-07</t>
+          <t>2026-09-14</t>
         </is>
       </c>
       <c r="Q234" s="4" t="n"/>
@@ -18355,7 +18355,7 @@
       </c>
       <c r="P235" s="4" t="inlineStr">
         <is>
-          <t>2026-09-07</t>
+          <t>2026-09-14</t>
         </is>
       </c>
       <c r="Q235" s="4" t="n"/>
@@ -18432,7 +18432,7 @@
       </c>
       <c r="P236" s="4" t="inlineStr">
         <is>
-          <t>2026-09-07</t>
+          <t>2026-09-14</t>
         </is>
       </c>
       <c r="Q236" s="4" t="n"/>
@@ -18511,7 +18511,7 @@
       </c>
       <c r="P237" s="4" t="inlineStr">
         <is>
-          <t>2026-09-07</t>
+          <t>2026-09-14</t>
         </is>
       </c>
       <c r="Q237" s="4" t="n"/>
@@ -18588,7 +18588,7 @@
       </c>
       <c r="P238" s="4" t="inlineStr">
         <is>
-          <t>2026-09-07</t>
+          <t>2026-09-14</t>
         </is>
       </c>
       <c r="Q238" s="4" t="n"/>
@@ -18665,7 +18665,7 @@
       </c>
       <c r="P239" s="4" t="inlineStr">
         <is>
-          <t>2026-09-07</t>
+          <t>2026-09-14</t>
         </is>
       </c>
       <c r="Q239" s="4" t="n"/>
@@ -18744,7 +18744,7 @@
       </c>
       <c r="P240" s="4" t="inlineStr">
         <is>
-          <t>2026-09-07</t>
+          <t>2026-09-14</t>
         </is>
       </c>
       <c r="Q240" s="4" t="n"/>
@@ -18821,7 +18821,7 @@
       </c>
       <c r="P241" s="4" t="inlineStr">
         <is>
-          <t>2026-09-07</t>
+          <t>2026-09-14</t>
         </is>
       </c>
       <c r="Q241" s="4" t="n"/>
@@ -18898,7 +18898,7 @@
       </c>
       <c r="P242" s="4" t="inlineStr">
         <is>
-          <t>2026-09-07</t>
+          <t>2026-09-14</t>
         </is>
       </c>
       <c r="Q242" s="4" t="n"/>
@@ -18977,7 +18977,7 @@
       </c>
       <c r="P243" s="4" t="inlineStr">
         <is>
-          <t>2026-09-07</t>
+          <t>2026-09-14</t>
         </is>
       </c>
       <c r="Q243" s="4" t="n"/>
@@ -19056,7 +19056,7 @@
       </c>
       <c r="P244" s="4" t="inlineStr">
         <is>
-          <t>2026-09-07</t>
+          <t>2026-09-14</t>
         </is>
       </c>
       <c r="Q244" s="4" t="n"/>
@@ -19133,7 +19133,7 @@
       </c>
       <c r="P245" s="4" t="inlineStr">
         <is>
-          <t>2026-09-07</t>
+          <t>2026-09-14</t>
         </is>
       </c>
       <c r="Q245" s="4" t="n"/>
@@ -19212,7 +19212,7 @@
       </c>
       <c r="P246" s="4" t="inlineStr">
         <is>
-          <t>2026-09-07</t>
+          <t>2026-09-14</t>
         </is>
       </c>
       <c r="Q246" s="4" t="n"/>
@@ -19291,7 +19291,7 @@
       </c>
       <c r="P247" s="4" t="inlineStr">
         <is>
-          <t>2026-09-07</t>
+          <t>2026-09-14</t>
         </is>
       </c>
       <c r="Q247" s="4" t="n"/>
@@ -19370,7 +19370,7 @@
       </c>
       <c r="P248" s="4" t="inlineStr">
         <is>
-          <t>2026-09-07</t>
+          <t>2026-09-14</t>
         </is>
       </c>
       <c r="Q248" s="4" t="n"/>
@@ -19449,7 +19449,7 @@
       </c>
       <c r="P249" s="4" t="inlineStr">
         <is>
-          <t>2026-09-07</t>
+          <t>2026-09-14</t>
         </is>
       </c>
       <c r="Q249" s="4" t="n"/>
@@ -19528,7 +19528,7 @@
       </c>
       <c r="P250" s="4" t="inlineStr">
         <is>
-          <t>2026-09-07</t>
+          <t>2026-09-14</t>
         </is>
       </c>
       <c r="Q250" s="4" t="n"/>
@@ -19607,7 +19607,7 @@
       </c>
       <c r="P251" s="4" t="inlineStr">
         <is>
-          <t>2026-09-07</t>
+          <t>2026-09-14</t>
         </is>
       </c>
       <c r="Q251" s="4" t="n"/>
@@ -19684,7 +19684,7 @@
       </c>
       <c r="P252" s="4" t="inlineStr">
         <is>
-          <t>2026-09-07</t>
+          <t>2026-09-14</t>
         </is>
       </c>
       <c r="Q252" s="4" t="n"/>
@@ -19761,7 +19761,7 @@
       </c>
       <c r="P253" s="4" t="inlineStr">
         <is>
-          <t>2026-09-07</t>
+          <t>2026-09-14</t>
         </is>
       </c>
       <c r="Q253" s="4" t="n"/>
@@ -19838,7 +19838,7 @@
       </c>
       <c r="P254" s="4" t="inlineStr">
         <is>
-          <t>2026-09-07</t>
+          <t>2026-09-14</t>
         </is>
       </c>
       <c r="Q254" s="4" t="n"/>
@@ -19915,7 +19915,7 @@
       </c>
       <c r="P255" s="4" t="inlineStr">
         <is>
-          <t>2026-09-07</t>
+          <t>2026-09-14</t>
         </is>
       </c>
       <c r="Q255" s="4" t="n"/>
@@ -19992,7 +19992,7 @@
       </c>
       <c r="P256" s="4" t="inlineStr">
         <is>
-          <t>2026-09-07</t>
+          <t>2026-09-14</t>
         </is>
       </c>
       <c r="Q256" s="4" t="n"/>
@@ -20069,7 +20069,7 @@
       </c>
       <c r="P257" s="4" t="inlineStr">
         <is>
-          <t>2026-09-07</t>
+          <t>2026-09-14</t>
         </is>
       </c>
       <c r="Q257" s="4" t="n"/>
@@ -20146,7 +20146,7 @@
       </c>
       <c r="P258" s="4" t="inlineStr">
         <is>
-          <t>2026-09-07</t>
+          <t>2026-09-14</t>
         </is>
       </c>
       <c r="Q258" s="4" t="n"/>
@@ -20223,7 +20223,7 @@
       </c>
       <c r="P259" s="4" t="inlineStr">
         <is>
-          <t>2026-09-07</t>
+          <t>2026-09-14</t>
         </is>
       </c>
       <c r="Q259" s="4" t="n"/>
@@ -20300,7 +20300,7 @@
       </c>
       <c r="P260" s="4" t="inlineStr">
         <is>
-          <t>2026-09-07</t>
+          <t>2026-09-14</t>
         </is>
       </c>
       <c r="Q260" s="4" t="n"/>
@@ -20377,7 +20377,7 @@
       </c>
       <c r="P261" s="4" t="inlineStr">
         <is>
-          <t>2026-09-07</t>
+          <t>2026-09-14</t>
         </is>
       </c>
       <c r="Q261" s="4" t="n"/>
@@ -20454,7 +20454,7 @@
       </c>
       <c r="P262" s="4" t="inlineStr">
         <is>
-          <t>2026-09-07</t>
+          <t>2026-09-14</t>
         </is>
       </c>
       <c r="Q262" s="4" t="n"/>
@@ -20531,7 +20531,7 @@
       </c>
       <c r="P263" s="4" t="inlineStr">
         <is>
-          <t>2026-09-07</t>
+          <t>2026-09-14</t>
         </is>
       </c>
       <c r="Q263" s="4" t="n"/>
@@ -20608,7 +20608,7 @@
       </c>
       <c r="P264" s="4" t="inlineStr">
         <is>
-          <t>2026-09-07</t>
+          <t>2026-09-14</t>
         </is>
       </c>
       <c r="Q264" s="4" t="n"/>
@@ -20685,7 +20685,7 @@
       </c>
       <c r="P265" s="4" t="inlineStr">
         <is>
-          <t>2026-09-07</t>
+          <t>2026-09-14</t>
         </is>
       </c>
       <c r="Q265" s="4" t="n"/>
@@ -20762,7 +20762,7 @@
       </c>
       <c r="P266" s="4" t="inlineStr">
         <is>
-          <t>2026-09-07</t>
+          <t>2026-09-14</t>
         </is>
       </c>
       <c r="Q266" s="4" t="n"/>
@@ -20839,7 +20839,7 @@
       </c>
       <c r="P267" s="4" t="inlineStr">
         <is>
-          <t>2026-09-07</t>
+          <t>2026-09-14</t>
         </is>
       </c>
       <c r="Q267" s="4" t="n"/>
@@ -20916,7 +20916,7 @@
       </c>
       <c r="P268" s="4" t="inlineStr">
         <is>
-          <t>2026-09-07</t>
+          <t>2026-09-14</t>
         </is>
       </c>
       <c r="Q268" s="4" t="n"/>
@@ -20993,7 +20993,7 @@
       </c>
       <c r="P269" s="4" t="inlineStr">
         <is>
-          <t>2026-09-07</t>
+          <t>2026-09-14</t>
         </is>
       </c>
       <c r="Q269" s="4" t="n"/>
@@ -21070,7 +21070,7 @@
       </c>
       <c r="P270" s="4" t="inlineStr">
         <is>
-          <t>2026-09-07</t>
+          <t>2026-09-14</t>
         </is>
       </c>
       <c r="Q270" s="4" t="n"/>
@@ -21147,7 +21147,7 @@
       </c>
       <c r="P271" s="4" t="inlineStr">
         <is>
-          <t>2026-09-07</t>
+          <t>2026-09-14</t>
         </is>
       </c>
       <c r="Q271" s="4" t="n"/>
@@ -21224,7 +21224,7 @@
       </c>
       <c r="P272" s="4" t="inlineStr">
         <is>
-          <t>2026-09-07</t>
+          <t>2026-09-14</t>
         </is>
       </c>
       <c r="Q272" s="4" t="n"/>
@@ -21301,7 +21301,7 @@
       </c>
       <c r="P273" s="4" t="inlineStr">
         <is>
-          <t>2026-09-07</t>
+          <t>2026-09-14</t>
         </is>
       </c>
       <c r="Q273" s="4" t="n"/>
@@ -21378,7 +21378,7 @@
       </c>
       <c r="P274" s="4" t="inlineStr">
         <is>
-          <t>2026-09-07</t>
+          <t>2026-09-14</t>
         </is>
       </c>
       <c r="Q274" s="4" t="n"/>
@@ -21455,7 +21455,7 @@
       </c>
       <c r="P275" s="4" t="inlineStr">
         <is>
-          <t>2026-09-07</t>
+          <t>2026-09-14</t>
         </is>
       </c>
       <c r="Q275" s="4" t="n"/>
@@ -21532,7 +21532,7 @@
       </c>
       <c r="P276" s="4" t="inlineStr">
         <is>
-          <t>2026-09-07</t>
+          <t>2026-09-14</t>
         </is>
       </c>
       <c r="Q276" s="4" t="n"/>
@@ -21609,7 +21609,7 @@
       </c>
       <c r="P277" s="4" t="inlineStr">
         <is>
-          <t>2026-09-07</t>
+          <t>2026-09-14</t>
         </is>
       </c>
       <c r="Q277" s="4" t="n"/>
@@ -21686,7 +21686,7 @@
       </c>
       <c r="P278" s="4" t="inlineStr">
         <is>
-          <t>2026-09-07</t>
+          <t>2026-09-14</t>
         </is>
       </c>
       <c r="Q278" s="4" t="n"/>
@@ -21763,7 +21763,7 @@
       </c>
       <c r="P279" s="4" t="inlineStr">
         <is>
-          <t>2026-09-07</t>
+          <t>2026-09-14</t>
         </is>
       </c>
       <c r="Q279" s="4" t="n"/>
@@ -21840,7 +21840,7 @@
       </c>
       <c r="P280" s="4" t="inlineStr">
         <is>
-          <t>2026-09-07</t>
+          <t>2026-09-14</t>
         </is>
       </c>
       <c r="Q280" s="4" t="n"/>
@@ -21917,7 +21917,7 @@
       </c>
       <c r="P281" s="4" t="inlineStr">
         <is>
-          <t>2026-09-07</t>
+          <t>2026-09-14</t>
         </is>
       </c>
       <c r="Q281" s="4" t="n"/>
@@ -21994,7 +21994,7 @@
       </c>
       <c r="P282" s="4" t="inlineStr">
         <is>
-          <t>2026-09-07</t>
+          <t>2026-09-14</t>
         </is>
       </c>
       <c r="Q282" s="4" t="n"/>
@@ -22071,7 +22071,7 @@
       </c>
       <c r="P283" s="4" t="inlineStr">
         <is>
-          <t>2026-09-07</t>
+          <t>2026-09-14</t>
         </is>
       </c>
       <c r="Q283" s="4" t="n"/>
@@ -22148,7 +22148,7 @@
       </c>
       <c r="P284" s="4" t="inlineStr">
         <is>
-          <t>2026-09-07</t>
+          <t>2026-09-14</t>
         </is>
       </c>
       <c r="Q284" s="4" t="n"/>
@@ -22225,7 +22225,7 @@
       </c>
       <c r="P285" s="4" t="inlineStr">
         <is>
-          <t>2026-09-07</t>
+          <t>2026-09-14</t>
         </is>
       </c>
       <c r="Q285" s="4" t="n"/>
@@ -22302,7 +22302,7 @@
       </c>
       <c r="P286" s="4" t="inlineStr">
         <is>
-          <t>2026-09-07</t>
+          <t>2026-09-14</t>
         </is>
       </c>
       <c r="Q286" s="4" t="n"/>
@@ -22379,7 +22379,7 @@
       </c>
       <c r="P287" s="4" t="inlineStr">
         <is>
-          <t>2026-09-07</t>
+          <t>2026-09-14</t>
         </is>
       </c>
       <c r="Q287" s="4" t="n"/>
@@ -22456,7 +22456,7 @@
       </c>
       <c r="P288" s="4" t="inlineStr">
         <is>
-          <t>2026-09-07</t>
+          <t>2026-09-14</t>
         </is>
       </c>
       <c r="Q288" s="4" t="n"/>
@@ -22533,7 +22533,7 @@
       </c>
       <c r="P289" s="4" t="inlineStr">
         <is>
-          <t>2026-09-07</t>
+          <t>2026-09-14</t>
         </is>
       </c>
       <c r="Q289" s="4" t="n"/>
@@ -22610,7 +22610,7 @@
       </c>
       <c r="P290" s="4" t="inlineStr">
         <is>
-          <t>2026-09-07</t>
+          <t>2026-09-14</t>
         </is>
       </c>
       <c r="Q290" s="4" t="n"/>
@@ -22687,7 +22687,7 @@
       </c>
       <c r="P291" s="4" t="inlineStr">
         <is>
-          <t>2026-09-07</t>
+          <t>2026-09-14</t>
         </is>
       </c>
       <c r="Q291" s="4" t="n"/>
@@ -22764,7 +22764,7 @@
       </c>
       <c r="P292" s="4" t="inlineStr">
         <is>
-          <t>2026-09-07</t>
+          <t>2026-09-14</t>
         </is>
       </c>
       <c r="Q292" s="4" t="n"/>
@@ -22841,7 +22841,7 @@
       </c>
       <c r="P293" s="4" t="inlineStr">
         <is>
-          <t>2026-09-07</t>
+          <t>2026-09-14</t>
         </is>
       </c>
       <c r="Q293" s="4" t="n"/>
@@ -22918,7 +22918,7 @@
       </c>
       <c r="P294" s="4" t="inlineStr">
         <is>
-          <t>2026-09-07</t>
+          <t>2026-09-14</t>
         </is>
       </c>
       <c r="Q294" s="4" t="n"/>
@@ -22995,7 +22995,7 @@
       </c>
       <c r="P295" s="4" t="inlineStr">
         <is>
-          <t>2026-09-07</t>
+          <t>2026-09-14</t>
         </is>
       </c>
       <c r="Q295" s="4" t="n"/>
@@ -23072,7 +23072,7 @@
       </c>
       <c r="P296" s="4" t="inlineStr">
         <is>
-          <t>2026-09-07</t>
+          <t>2026-09-14</t>
         </is>
       </c>
       <c r="Q296" s="4" t="n"/>
@@ -23149,7 +23149,7 @@
       </c>
       <c r="P297" s="4" t="inlineStr">
         <is>
-          <t>2026-09-07</t>
+          <t>2026-09-14</t>
         </is>
       </c>
       <c r="Q297" s="4" t="n"/>
@@ -23226,7 +23226,7 @@
       </c>
       <c r="P298" s="4" t="inlineStr">
         <is>
-          <t>2026-09-07</t>
+          <t>2026-09-14</t>
         </is>
       </c>
       <c r="Q298" s="4" t="n"/>
@@ -23303,7 +23303,7 @@
       </c>
       <c r="P299" s="4" t="inlineStr">
         <is>
-          <t>2026-09-07</t>
+          <t>2026-09-14</t>
         </is>
       </c>
       <c r="Q299" s="4" t="n"/>
@@ -23380,7 +23380,7 @@
       </c>
       <c r="P300" s="4" t="inlineStr">
         <is>
-          <t>2026-09-07</t>
+          <t>2026-09-14</t>
         </is>
       </c>
       <c r="Q300" s="4" t="n"/>
@@ -23457,7 +23457,7 @@
       </c>
       <c r="P301" s="4" t="inlineStr">
         <is>
-          <t>2026-09-07</t>
+          <t>2026-09-14</t>
         </is>
       </c>
       <c r="Q301" s="4" t="n"/>
@@ -23534,7 +23534,7 @@
       </c>
       <c r="P302" s="4" t="inlineStr">
         <is>
-          <t>2026-09-07</t>
+          <t>2026-09-14</t>
         </is>
       </c>
       <c r="Q302" s="4" t="n"/>
@@ -23611,7 +23611,7 @@
       </c>
       <c r="P303" s="4" t="inlineStr">
         <is>
-          <t>2026-09-07</t>
+          <t>2026-09-14</t>
         </is>
       </c>
       <c r="Q303" s="4" t="n"/>
@@ -23688,7 +23688,7 @@
       </c>
       <c r="P304" s="4" t="inlineStr">
         <is>
-          <t>2026-09-07</t>
+          <t>2026-09-14</t>
         </is>
       </c>
       <c r="Q304" s="4" t="n"/>
@@ -23765,7 +23765,7 @@
       </c>
       <c r="P305" s="4" t="inlineStr">
         <is>
-          <t>2026-09-07</t>
+          <t>2026-09-14</t>
         </is>
       </c>
       <c r="Q305" s="4" t="n"/>
@@ -23842,7 +23842,7 @@
       </c>
       <c r="P306" s="4" t="inlineStr">
         <is>
-          <t>2026-09-07</t>
+          <t>2026-09-14</t>
         </is>
       </c>
       <c r="Q306" s="4" t="n"/>
@@ -23919,7 +23919,7 @@
       </c>
       <c r="P307" s="4" t="inlineStr">
         <is>
-          <t>2026-09-07</t>
+          <t>2026-09-14</t>
         </is>
       </c>
       <c r="Q307" s="4" t="n"/>
@@ -23998,7 +23998,7 @@
       </c>
       <c r="P308" s="4" t="inlineStr">
         <is>
-          <t>2026-09-07</t>
+          <t>2026-09-14</t>
         </is>
       </c>
       <c r="Q308" s="4" t="n"/>
@@ -24077,7 +24077,7 @@
       </c>
       <c r="P309" s="4" t="inlineStr">
         <is>
-          <t>2026-09-07</t>
+          <t>2026-09-14</t>
         </is>
       </c>
       <c r="Q309" s="4" t="n"/>
@@ -24156,7 +24156,7 @@
       </c>
       <c r="P310" s="4" t="inlineStr">
         <is>
-          <t>2026-09-07</t>
+          <t>2026-09-14</t>
         </is>
       </c>
       <c r="Q310" s="4" t="n"/>
@@ -24235,7 +24235,7 @@
       </c>
       <c r="P311" s="4" t="inlineStr">
         <is>
-          <t>2026-09-07</t>
+          <t>2026-09-14</t>
         </is>
       </c>
       <c r="Q311" s="4" t="n"/>
@@ -24314,7 +24314,7 @@
       </c>
       <c r="P312" s="4" t="inlineStr">
         <is>
-          <t>2026-09-07</t>
+          <t>2026-09-14</t>
         </is>
       </c>
       <c r="Q312" s="4" t="n"/>
@@ -24393,7 +24393,7 @@
       </c>
       <c r="P313" s="4" t="inlineStr">
         <is>
-          <t>2026-09-07</t>
+          <t>2026-09-14</t>
         </is>
       </c>
       <c r="Q313" s="4" t="n"/>
@@ -24472,7 +24472,7 @@
       </c>
       <c r="P314" s="4" t="inlineStr">
         <is>
-          <t>2026-09-07</t>
+          <t>2026-09-14</t>
         </is>
       </c>
       <c r="Q314" s="4" t="n"/>
@@ -24551,7 +24551,7 @@
       </c>
       <c r="P315" s="4" t="inlineStr">
         <is>
-          <t>2026-09-07</t>
+          <t>2026-09-14</t>
         </is>
       </c>
       <c r="Q315" s="4" t="n"/>
@@ -24630,7 +24630,7 @@
       </c>
       <c r="P316" s="4" t="inlineStr">
         <is>
-          <t>2026-09-07</t>
+          <t>2026-09-14</t>
         </is>
       </c>
       <c r="Q316" s="4" t="n"/>
@@ -24709,7 +24709,7 @@
       </c>
       <c r="P317" s="4" t="inlineStr">
         <is>
-          <t>2026-09-07</t>
+          <t>2026-09-14</t>
         </is>
       </c>
       <c r="Q317" s="4" t="n"/>
@@ -24788,7 +24788,7 @@
       </c>
       <c r="P318" s="4" t="inlineStr">
         <is>
-          <t>2026-09-07</t>
+          <t>2026-09-14</t>
         </is>
       </c>
       <c r="Q318" s="4" t="n"/>
@@ -24867,7 +24867,7 @@
       </c>
       <c r="P319" s="4" t="inlineStr">
         <is>
-          <t>2026-09-07</t>
+          <t>2026-09-14</t>
         </is>
       </c>
       <c r="Q319" s="4" t="n"/>
@@ -24946,7 +24946,7 @@
       </c>
       <c r="P320" s="4" t="inlineStr">
         <is>
-          <t>2026-09-07</t>
+          <t>2026-09-14</t>
         </is>
       </c>
       <c r="Q320" s="4" t="n"/>
@@ -25025,7 +25025,7 @@
       </c>
       <c r="P321" s="4" t="inlineStr">
         <is>
-          <t>2026-09-07</t>
+          <t>2026-09-14</t>
         </is>
       </c>
       <c r="Q321" s="4" t="n"/>
@@ -25104,7 +25104,7 @@
       </c>
       <c r="P322" s="4" t="inlineStr">
         <is>
-          <t>2026-09-07</t>
+          <t>2026-09-14</t>
         </is>
       </c>
       <c r="Q322" s="4" t="n"/>
@@ -25183,7 +25183,7 @@
       </c>
       <c r="P323" s="4" t="inlineStr">
         <is>
-          <t>2026-09-07</t>
+          <t>2026-09-14</t>
         </is>
       </c>
       <c r="Q323" s="4" t="n"/>
@@ -25262,7 +25262,7 @@
       </c>
       <c r="P324" s="4" t="inlineStr">
         <is>
-          <t>2026-09-07</t>
+          <t>2026-09-14</t>
         </is>
       </c>
       <c r="Q324" s="4" t="n"/>
@@ -25341,7 +25341,7 @@
       </c>
       <c r="P325" s="4" t="inlineStr">
         <is>
-          <t>2026-09-07</t>
+          <t>2026-09-14</t>
         </is>
       </c>
       <c r="Q325" s="4" t="n"/>
@@ -25420,7 +25420,7 @@
       </c>
       <c r="P326" s="4" t="inlineStr">
         <is>
-          <t>2026-09-07</t>
+          <t>2026-09-14</t>
         </is>
       </c>
       <c r="Q326" s="4" t="n"/>
@@ -25497,7 +25497,7 @@
       </c>
       <c r="P327" s="4" t="inlineStr">
         <is>
-          <t>2026-09-07</t>
+          <t>2026-09-14</t>
         </is>
       </c>
       <c r="Q327" s="4" t="n"/>
@@ -25574,7 +25574,7 @@
       </c>
       <c r="P328" s="4" t="inlineStr">
         <is>
-          <t>2026-09-07</t>
+          <t>2026-09-14</t>
         </is>
       </c>
       <c r="Q328" s="4" t="n"/>
@@ -25651,7 +25651,7 @@
       </c>
       <c r="P329" s="4" t="inlineStr">
         <is>
-          <t>2026-09-07</t>
+          <t>2026-09-14</t>
         </is>
       </c>
       <c r="Q329" s="4" t="n"/>
@@ -25728,7 +25728,7 @@
       </c>
       <c r="P330" s="4" t="inlineStr">
         <is>
-          <t>2026-09-07</t>
+          <t>2026-09-14</t>
         </is>
       </c>
       <c r="Q330" s="4" t="n"/>
@@ -25805,7 +25805,7 @@
       </c>
       <c r="P331" s="4" t="inlineStr">
         <is>
-          <t>2026-09-07</t>
+          <t>2026-09-14</t>
         </is>
       </c>
       <c r="Q331" s="4" t="n"/>
@@ -25882,7 +25882,7 @@
       </c>
       <c r="P332" s="4" t="inlineStr">
         <is>
-          <t>2026-09-07</t>
+          <t>2026-09-14</t>
         </is>
       </c>
       <c r="Q332" s="4" t="n"/>
@@ -25959,7 +25959,7 @@
       </c>
       <c r="P333" s="4" t="inlineStr">
         <is>
-          <t>2026-09-07</t>
+          <t>2026-09-14</t>
         </is>
       </c>
       <c r="Q333" s="4" t="n"/>
@@ -26036,7 +26036,7 @@
       </c>
       <c r="P334" s="4" t="inlineStr">
         <is>
-          <t>2026-09-07</t>
+          <t>2026-09-14</t>
         </is>
       </c>
       <c r="Q334" s="4" t="n"/>
@@ -26113,7 +26113,7 @@
       </c>
       <c r="P335" s="4" t="inlineStr">
         <is>
-          <t>2026-09-07</t>
+          <t>2026-09-14</t>
         </is>
       </c>
       <c r="Q335" s="4" t="n"/>
@@ -26190,7 +26190,7 @@
       </c>
       <c r="P336" s="4" t="inlineStr">
         <is>
-          <t>2026-09-07</t>
+          <t>2026-09-14</t>
         </is>
       </c>
       <c r="Q336" s="4" t="n"/>
@@ -26275,7 +26275,7 @@
       </c>
       <c r="B9" s="4" t="inlineStr">
         <is>
-          <t>2026-09-07</t>
+          <t>2026-09-14</t>
         </is>
       </c>
     </row>

--- a/assets/data/world-bank/excel/ove_banco_mundial_venezuela_pobreza_y_desigualdad.xlsx
+++ b/assets/data/world-bank/excel/ove_banco_mundial_venezuela_pobreza_y_desigualdad.xlsx
@@ -715,7 +715,7 @@
       </c>
       <c r="P7" s="4" t="inlineStr">
         <is>
-          <t>2026-09-14</t>
+          <t>2026-09-21</t>
         </is>
       </c>
       <c r="Q7" s="4" t="n"/>
@@ -792,7 +792,7 @@
       </c>
       <c r="P8" s="4" t="inlineStr">
         <is>
-          <t>2026-09-14</t>
+          <t>2026-09-21</t>
         </is>
       </c>
       <c r="Q8" s="4" t="n"/>
@@ -869,7 +869,7 @@
       </c>
       <c r="P9" s="4" t="inlineStr">
         <is>
-          <t>2026-09-14</t>
+          <t>2026-09-21</t>
         </is>
       </c>
       <c r="Q9" s="4" t="n"/>
@@ -946,7 +946,7 @@
       </c>
       <c r="P10" s="4" t="inlineStr">
         <is>
-          <t>2026-09-14</t>
+          <t>2026-09-21</t>
         </is>
       </c>
       <c r="Q10" s="4" t="n"/>
@@ -1023,7 +1023,7 @@
       </c>
       <c r="P11" s="4" t="inlineStr">
         <is>
-          <t>2026-09-14</t>
+          <t>2026-09-21</t>
         </is>
       </c>
       <c r="Q11" s="4" t="n"/>
@@ -1100,7 +1100,7 @@
       </c>
       <c r="P12" s="4" t="inlineStr">
         <is>
-          <t>2026-09-14</t>
+          <t>2026-09-21</t>
         </is>
       </c>
       <c r="Q12" s="4" t="n"/>
@@ -1177,7 +1177,7 @@
       </c>
       <c r="P13" s="4" t="inlineStr">
         <is>
-          <t>2026-09-14</t>
+          <t>2026-09-21</t>
         </is>
       </c>
       <c r="Q13" s="4" t="n"/>
@@ -1254,7 +1254,7 @@
       </c>
       <c r="P14" s="4" t="inlineStr">
         <is>
-          <t>2026-09-14</t>
+          <t>2026-09-21</t>
         </is>
       </c>
       <c r="Q14" s="4" t="n"/>
@@ -1331,7 +1331,7 @@
       </c>
       <c r="P15" s="4" t="inlineStr">
         <is>
-          <t>2026-09-14</t>
+          <t>2026-09-21</t>
         </is>
       </c>
       <c r="Q15" s="4" t="n"/>
@@ -1408,7 +1408,7 @@
       </c>
       <c r="P16" s="4" t="inlineStr">
         <is>
-          <t>2026-09-14</t>
+          <t>2026-09-21</t>
         </is>
       </c>
       <c r="Q16" s="4" t="n"/>
@@ -1485,7 +1485,7 @@
       </c>
       <c r="P17" s="4" t="inlineStr">
         <is>
-          <t>2026-09-14</t>
+          <t>2026-09-21</t>
         </is>
       </c>
       <c r="Q17" s="4" t="n"/>
@@ -1562,7 +1562,7 @@
       </c>
       <c r="P18" s="4" t="inlineStr">
         <is>
-          <t>2026-09-14</t>
+          <t>2026-09-21</t>
         </is>
       </c>
       <c r="Q18" s="4" t="n"/>
@@ -1639,7 +1639,7 @@
       </c>
       <c r="P19" s="4" t="inlineStr">
         <is>
-          <t>2026-09-14</t>
+          <t>2026-09-21</t>
         </is>
       </c>
       <c r="Q19" s="4" t="n"/>
@@ -1716,7 +1716,7 @@
       </c>
       <c r="P20" s="4" t="inlineStr">
         <is>
-          <t>2026-09-14</t>
+          <t>2026-09-21</t>
         </is>
       </c>
       <c r="Q20" s="4" t="n"/>
@@ -1793,7 +1793,7 @@
       </c>
       <c r="P21" s="4" t="inlineStr">
         <is>
-          <t>2026-09-14</t>
+          <t>2026-09-21</t>
         </is>
       </c>
       <c r="Q21" s="4" t="n"/>
@@ -1870,7 +1870,7 @@
       </c>
       <c r="P22" s="4" t="inlineStr">
         <is>
-          <t>2026-09-14</t>
+          <t>2026-09-21</t>
         </is>
       </c>
       <c r="Q22" s="4" t="n"/>
@@ -1947,7 +1947,7 @@
       </c>
       <c r="P23" s="4" t="inlineStr">
         <is>
-          <t>2026-09-14</t>
+          <t>2026-09-21</t>
         </is>
       </c>
       <c r="Q23" s="4" t="n"/>
@@ -2024,7 +2024,7 @@
       </c>
       <c r="P24" s="4" t="inlineStr">
         <is>
-          <t>2026-09-14</t>
+          <t>2026-09-21</t>
         </is>
       </c>
       <c r="Q24" s="4" t="n"/>
@@ -2101,7 +2101,7 @@
       </c>
       <c r="P25" s="4" t="inlineStr">
         <is>
-          <t>2026-09-14</t>
+          <t>2026-09-21</t>
         </is>
       </c>
       <c r="Q25" s="4" t="n"/>
@@ -2178,7 +2178,7 @@
       </c>
       <c r="P26" s="4" t="inlineStr">
         <is>
-          <t>2026-09-14</t>
+          <t>2026-09-21</t>
         </is>
       </c>
       <c r="Q26" s="4" t="n"/>
@@ -2255,7 +2255,7 @@
       </c>
       <c r="P27" s="4" t="inlineStr">
         <is>
-          <t>2026-09-14</t>
+          <t>2026-09-21</t>
         </is>
       </c>
       <c r="Q27" s="4" t="n"/>
@@ -2334,7 +2334,7 @@
       </c>
       <c r="P28" s="4" t="inlineStr">
         <is>
-          <t>2026-09-14</t>
+          <t>2026-09-21</t>
         </is>
       </c>
       <c r="Q28" s="4" t="n"/>
@@ -2411,7 +2411,7 @@
       </c>
       <c r="P29" s="4" t="inlineStr">
         <is>
-          <t>2026-09-14</t>
+          <t>2026-09-21</t>
         </is>
       </c>
       <c r="Q29" s="4" t="n"/>
@@ -2488,7 +2488,7 @@
       </c>
       <c r="P30" s="4" t="inlineStr">
         <is>
-          <t>2026-09-14</t>
+          <t>2026-09-21</t>
         </is>
       </c>
       <c r="Q30" s="4" t="n"/>
@@ -2565,7 +2565,7 @@
       </c>
       <c r="P31" s="4" t="inlineStr">
         <is>
-          <t>2026-09-14</t>
+          <t>2026-09-21</t>
         </is>
       </c>
       <c r="Q31" s="4" t="n"/>
@@ -2642,7 +2642,7 @@
       </c>
       <c r="P32" s="4" t="inlineStr">
         <is>
-          <t>2026-09-14</t>
+          <t>2026-09-21</t>
         </is>
       </c>
       <c r="Q32" s="4" t="n"/>
@@ -2719,7 +2719,7 @@
       </c>
       <c r="P33" s="4" t="inlineStr">
         <is>
-          <t>2026-09-14</t>
+          <t>2026-09-21</t>
         </is>
       </c>
       <c r="Q33" s="4" t="n"/>
@@ -2798,7 +2798,7 @@
       </c>
       <c r="P34" s="4" t="inlineStr">
         <is>
-          <t>2026-09-14</t>
+          <t>2026-09-21</t>
         </is>
       </c>
       <c r="Q34" s="4" t="n"/>
@@ -2875,7 +2875,7 @@
       </c>
       <c r="P35" s="4" t="inlineStr">
         <is>
-          <t>2026-09-14</t>
+          <t>2026-09-21</t>
         </is>
       </c>
       <c r="Q35" s="4" t="n"/>
@@ -2954,7 +2954,7 @@
       </c>
       <c r="P36" s="4" t="inlineStr">
         <is>
-          <t>2026-09-14</t>
+          <t>2026-09-21</t>
         </is>
       </c>
       <c r="Q36" s="4" t="n"/>
@@ -3031,7 +3031,7 @@
       </c>
       <c r="P37" s="4" t="inlineStr">
         <is>
-          <t>2026-09-14</t>
+          <t>2026-09-21</t>
         </is>
       </c>
       <c r="Q37" s="4" t="n"/>
@@ -3108,7 +3108,7 @@
       </c>
       <c r="P38" s="4" t="inlineStr">
         <is>
-          <t>2026-09-14</t>
+          <t>2026-09-21</t>
         </is>
       </c>
       <c r="Q38" s="4" t="n"/>
@@ -3187,7 +3187,7 @@
       </c>
       <c r="P39" s="4" t="inlineStr">
         <is>
-          <t>2026-09-14</t>
+          <t>2026-09-21</t>
         </is>
       </c>
       <c r="Q39" s="4" t="n"/>
@@ -3264,7 +3264,7 @@
       </c>
       <c r="P40" s="4" t="inlineStr">
         <is>
-          <t>2026-09-14</t>
+          <t>2026-09-21</t>
         </is>
       </c>
       <c r="Q40" s="4" t="n"/>
@@ -3341,7 +3341,7 @@
       </c>
       <c r="P41" s="4" t="inlineStr">
         <is>
-          <t>2026-09-14</t>
+          <t>2026-09-21</t>
         </is>
       </c>
       <c r="Q41" s="4" t="n"/>
@@ -3420,7 +3420,7 @@
       </c>
       <c r="P42" s="4" t="inlineStr">
         <is>
-          <t>2026-09-14</t>
+          <t>2026-09-21</t>
         </is>
       </c>
       <c r="Q42" s="4" t="n"/>
@@ -3497,7 +3497,7 @@
       </c>
       <c r="P43" s="4" t="inlineStr">
         <is>
-          <t>2026-09-14</t>
+          <t>2026-09-21</t>
         </is>
       </c>
       <c r="Q43" s="4" t="n"/>
@@ -3574,7 +3574,7 @@
       </c>
       <c r="P44" s="4" t="inlineStr">
         <is>
-          <t>2026-09-14</t>
+          <t>2026-09-21</t>
         </is>
       </c>
       <c r="Q44" s="4" t="n"/>
@@ -3653,7 +3653,7 @@
       </c>
       <c r="P45" s="4" t="inlineStr">
         <is>
-          <t>2026-09-14</t>
+          <t>2026-09-21</t>
         </is>
       </c>
       <c r="Q45" s="4" t="n"/>
@@ -3732,7 +3732,7 @@
       </c>
       <c r="P46" s="4" t="inlineStr">
         <is>
-          <t>2026-09-14</t>
+          <t>2026-09-21</t>
         </is>
       </c>
       <c r="Q46" s="4" t="n"/>
@@ -3809,7 +3809,7 @@
       </c>
       <c r="P47" s="4" t="inlineStr">
         <is>
-          <t>2026-09-14</t>
+          <t>2026-09-21</t>
         </is>
       </c>
       <c r="Q47" s="4" t="n"/>
@@ -3888,7 +3888,7 @@
       </c>
       <c r="P48" s="4" t="inlineStr">
         <is>
-          <t>2026-09-14</t>
+          <t>2026-09-21</t>
         </is>
       </c>
       <c r="Q48" s="4" t="n"/>
@@ -3967,7 +3967,7 @@
       </c>
       <c r="P49" s="4" t="inlineStr">
         <is>
-          <t>2026-09-14</t>
+          <t>2026-09-21</t>
         </is>
       </c>
       <c r="Q49" s="4" t="n"/>
@@ -4046,7 +4046,7 @@
       </c>
       <c r="P50" s="4" t="inlineStr">
         <is>
-          <t>2026-09-14</t>
+          <t>2026-09-21</t>
         </is>
       </c>
       <c r="Q50" s="4" t="n"/>
@@ -4125,7 +4125,7 @@
       </c>
       <c r="P51" s="4" t="inlineStr">
         <is>
-          <t>2026-09-14</t>
+          <t>2026-09-21</t>
         </is>
       </c>
       <c r="Q51" s="4" t="n"/>
@@ -4204,7 +4204,7 @@
       </c>
       <c r="P52" s="4" t="inlineStr">
         <is>
-          <t>2026-09-14</t>
+          <t>2026-09-21</t>
         </is>
       </c>
       <c r="Q52" s="4" t="n"/>
@@ -4283,7 +4283,7 @@
       </c>
       <c r="P53" s="4" t="inlineStr">
         <is>
-          <t>2026-09-14</t>
+          <t>2026-09-21</t>
         </is>
       </c>
       <c r="Q53" s="4" t="n"/>
@@ -4360,7 +4360,7 @@
       </c>
       <c r="P54" s="4" t="inlineStr">
         <is>
-          <t>2026-09-14</t>
+          <t>2026-09-21</t>
         </is>
       </c>
       <c r="Q54" s="4" t="n"/>
@@ -4437,7 +4437,7 @@
       </c>
       <c r="P55" s="4" t="inlineStr">
         <is>
-          <t>2026-09-14</t>
+          <t>2026-09-21</t>
         </is>
       </c>
       <c r="Q55" s="4" t="n"/>
@@ -4514,7 +4514,7 @@
       </c>
       <c r="P56" s="4" t="inlineStr">
         <is>
-          <t>2026-09-14</t>
+          <t>2026-09-21</t>
         </is>
       </c>
       <c r="Q56" s="4" t="n"/>
@@ -4591,7 +4591,7 @@
       </c>
       <c r="P57" s="4" t="inlineStr">
         <is>
-          <t>2026-09-14</t>
+          <t>2026-09-21</t>
         </is>
       </c>
       <c r="Q57" s="4" t="n"/>
@@ -4668,7 +4668,7 @@
       </c>
       <c r="P58" s="4" t="inlineStr">
         <is>
-          <t>2026-09-14</t>
+          <t>2026-09-21</t>
         </is>
       </c>
       <c r="Q58" s="4" t="n"/>
@@ -4745,7 +4745,7 @@
       </c>
       <c r="P59" s="4" t="inlineStr">
         <is>
-          <t>2026-09-14</t>
+          <t>2026-09-21</t>
         </is>
       </c>
       <c r="Q59" s="4" t="n"/>
@@ -4822,7 +4822,7 @@
       </c>
       <c r="P60" s="4" t="inlineStr">
         <is>
-          <t>2026-09-14</t>
+          <t>2026-09-21</t>
         </is>
       </c>
       <c r="Q60" s="4" t="n"/>
@@ -4899,7 +4899,7 @@
       </c>
       <c r="P61" s="4" t="inlineStr">
         <is>
-          <t>2026-09-14</t>
+          <t>2026-09-21</t>
         </is>
       </c>
       <c r="Q61" s="4" t="n"/>
@@ -4976,7 +4976,7 @@
       </c>
       <c r="P62" s="4" t="inlineStr">
         <is>
-          <t>2026-09-14</t>
+          <t>2026-09-21</t>
         </is>
       </c>
       <c r="Q62" s="4" t="n"/>
@@ -5053,7 +5053,7 @@
       </c>
       <c r="P63" s="4" t="inlineStr">
         <is>
-          <t>2026-09-14</t>
+          <t>2026-09-21</t>
         </is>
       </c>
       <c r="Q63" s="4" t="n"/>
@@ -5130,7 +5130,7 @@
       </c>
       <c r="P64" s="4" t="inlineStr">
         <is>
-          <t>2026-09-14</t>
+          <t>2026-09-21</t>
         </is>
       </c>
       <c r="Q64" s="4" t="n"/>
@@ -5207,7 +5207,7 @@
       </c>
       <c r="P65" s="4" t="inlineStr">
         <is>
-          <t>2026-09-14</t>
+          <t>2026-09-21</t>
         </is>
       </c>
       <c r="Q65" s="4" t="n"/>
@@ -5284,7 +5284,7 @@
       </c>
       <c r="P66" s="4" t="inlineStr">
         <is>
-          <t>2026-09-14</t>
+          <t>2026-09-21</t>
         </is>
       </c>
       <c r="Q66" s="4" t="n"/>
@@ -5361,7 +5361,7 @@
       </c>
       <c r="P67" s="4" t="inlineStr">
         <is>
-          <t>2026-09-14</t>
+          <t>2026-09-21</t>
         </is>
       </c>
       <c r="Q67" s="4" t="n"/>
@@ -5438,7 +5438,7 @@
       </c>
       <c r="P68" s="4" t="inlineStr">
         <is>
-          <t>2026-09-14</t>
+          <t>2026-09-21</t>
         </is>
       </c>
       <c r="Q68" s="4" t="n"/>
@@ -5515,7 +5515,7 @@
       </c>
       <c r="P69" s="4" t="inlineStr">
         <is>
-          <t>2026-09-14</t>
+          <t>2026-09-21</t>
         </is>
       </c>
       <c r="Q69" s="4" t="n"/>
@@ -5592,7 +5592,7 @@
       </c>
       <c r="P70" s="4" t="inlineStr">
         <is>
-          <t>2026-09-14</t>
+          <t>2026-09-21</t>
         </is>
       </c>
       <c r="Q70" s="4" t="n"/>
@@ -5669,7 +5669,7 @@
       </c>
       <c r="P71" s="4" t="inlineStr">
         <is>
-          <t>2026-09-14</t>
+          <t>2026-09-21</t>
         </is>
       </c>
       <c r="Q71" s="4" t="n"/>
@@ -5746,7 +5746,7 @@
       </c>
       <c r="P72" s="4" t="inlineStr">
         <is>
-          <t>2026-09-14</t>
+          <t>2026-09-21</t>
         </is>
       </c>
       <c r="Q72" s="4" t="n"/>
@@ -5823,7 +5823,7 @@
       </c>
       <c r="P73" s="4" t="inlineStr">
         <is>
-          <t>2026-09-14</t>
+          <t>2026-09-21</t>
         </is>
       </c>
       <c r="Q73" s="4" t="n"/>
@@ -5900,7 +5900,7 @@
       </c>
       <c r="P74" s="4" t="inlineStr">
         <is>
-          <t>2026-09-14</t>
+          <t>2026-09-21</t>
         </is>
       </c>
       <c r="Q74" s="4" t="n"/>
@@ -5977,7 +5977,7 @@
       </c>
       <c r="P75" s="4" t="inlineStr">
         <is>
-          <t>2026-09-14</t>
+          <t>2026-09-21</t>
         </is>
       </c>
       <c r="Q75" s="4" t="n"/>
@@ -6054,7 +6054,7 @@
       </c>
       <c r="P76" s="4" t="inlineStr">
         <is>
-          <t>2026-09-14</t>
+          <t>2026-09-21</t>
         </is>
       </c>
       <c r="Q76" s="4" t="n"/>
@@ -6131,7 +6131,7 @@
       </c>
       <c r="P77" s="4" t="inlineStr">
         <is>
-          <t>2026-09-14</t>
+          <t>2026-09-21</t>
         </is>
       </c>
       <c r="Q77" s="4" t="n"/>
@@ -6208,7 +6208,7 @@
       </c>
       <c r="P78" s="4" t="inlineStr">
         <is>
-          <t>2026-09-14</t>
+          <t>2026-09-21</t>
         </is>
       </c>
       <c r="Q78" s="4" t="n"/>
@@ -6285,7 +6285,7 @@
       </c>
       <c r="P79" s="4" t="inlineStr">
         <is>
-          <t>2026-09-14</t>
+          <t>2026-09-21</t>
         </is>
       </c>
       <c r="Q79" s="4" t="n"/>
@@ -6362,7 +6362,7 @@
       </c>
       <c r="P80" s="4" t="inlineStr">
         <is>
-          <t>2026-09-14</t>
+          <t>2026-09-21</t>
         </is>
       </c>
       <c r="Q80" s="4" t="n"/>
@@ -6439,7 +6439,7 @@
       </c>
       <c r="P81" s="4" t="inlineStr">
         <is>
-          <t>2026-09-14</t>
+          <t>2026-09-21</t>
         </is>
       </c>
       <c r="Q81" s="4" t="n"/>
@@ -6516,7 +6516,7 @@
       </c>
       <c r="P82" s="4" t="inlineStr">
         <is>
-          <t>2026-09-14</t>
+          <t>2026-09-21</t>
         </is>
       </c>
       <c r="Q82" s="4" t="n"/>
@@ -6593,7 +6593,7 @@
       </c>
       <c r="P83" s="4" t="inlineStr">
         <is>
-          <t>2026-09-14</t>
+          <t>2026-09-21</t>
         </is>
       </c>
       <c r="Q83" s="4" t="n"/>
@@ -6670,7 +6670,7 @@
       </c>
       <c r="P84" s="4" t="inlineStr">
         <is>
-          <t>2026-09-14</t>
+          <t>2026-09-21</t>
         </is>
       </c>
       <c r="Q84" s="4" t="n"/>
@@ -6747,7 +6747,7 @@
       </c>
       <c r="P85" s="4" t="inlineStr">
         <is>
-          <t>2026-09-14</t>
+          <t>2026-09-21</t>
         </is>
       </c>
       <c r="Q85" s="4" t="n"/>
@@ -6824,7 +6824,7 @@
       </c>
       <c r="P86" s="4" t="inlineStr">
         <is>
-          <t>2026-09-14</t>
+          <t>2026-09-21</t>
         </is>
       </c>
       <c r="Q86" s="4" t="n"/>
@@ -6901,7 +6901,7 @@
       </c>
       <c r="P87" s="4" t="inlineStr">
         <is>
-          <t>2026-09-14</t>
+          <t>2026-09-21</t>
         </is>
       </c>
       <c r="Q87" s="4" t="n"/>
@@ -6978,7 +6978,7 @@
       </c>
       <c r="P88" s="4" t="inlineStr">
         <is>
-          <t>2026-09-14</t>
+          <t>2026-09-21</t>
         </is>
       </c>
       <c r="Q88" s="4" t="n"/>
@@ -7055,7 +7055,7 @@
       </c>
       <c r="P89" s="4" t="inlineStr">
         <is>
-          <t>2026-09-14</t>
+          <t>2026-09-21</t>
         </is>
       </c>
       <c r="Q89" s="4" t="n"/>
@@ -7132,7 +7132,7 @@
       </c>
       <c r="P90" s="4" t="inlineStr">
         <is>
-          <t>2026-09-14</t>
+          <t>2026-09-21</t>
         </is>
       </c>
       <c r="Q90" s="4" t="n"/>
@@ -7209,7 +7209,7 @@
       </c>
       <c r="P91" s="4" t="inlineStr">
         <is>
-          <t>2026-09-14</t>
+          <t>2026-09-21</t>
         </is>
       </c>
       <c r="Q91" s="4" t="n"/>
@@ -7286,7 +7286,7 @@
       </c>
       <c r="P92" s="4" t="inlineStr">
         <is>
-          <t>2026-09-14</t>
+          <t>2026-09-21</t>
         </is>
       </c>
       <c r="Q92" s="4" t="n"/>
@@ -7363,7 +7363,7 @@
       </c>
       <c r="P93" s="4" t="inlineStr">
         <is>
-          <t>2026-09-14</t>
+          <t>2026-09-21</t>
         </is>
       </c>
       <c r="Q93" s="4" t="n"/>
@@ -7442,7 +7442,7 @@
       </c>
       <c r="P94" s="4" t="inlineStr">
         <is>
-          <t>2026-09-14</t>
+          <t>2026-09-21</t>
         </is>
       </c>
       <c r="Q94" s="4" t="n"/>
@@ -7519,7 +7519,7 @@
       </c>
       <c r="P95" s="4" t="inlineStr">
         <is>
-          <t>2026-09-14</t>
+          <t>2026-09-21</t>
         </is>
       </c>
       <c r="Q95" s="4" t="n"/>
@@ -7596,7 +7596,7 @@
       </c>
       <c r="P96" s="4" t="inlineStr">
         <is>
-          <t>2026-09-14</t>
+          <t>2026-09-21</t>
         </is>
       </c>
       <c r="Q96" s="4" t="n"/>
@@ -7673,7 +7673,7 @@
       </c>
       <c r="P97" s="4" t="inlineStr">
         <is>
-          <t>2026-09-14</t>
+          <t>2026-09-21</t>
         </is>
       </c>
       <c r="Q97" s="4" t="n"/>
@@ -7750,7 +7750,7 @@
       </c>
       <c r="P98" s="4" t="inlineStr">
         <is>
-          <t>2026-09-14</t>
+          <t>2026-09-21</t>
         </is>
       </c>
       <c r="Q98" s="4" t="n"/>
@@ -7827,7 +7827,7 @@
       </c>
       <c r="P99" s="4" t="inlineStr">
         <is>
-          <t>2026-09-14</t>
+          <t>2026-09-21</t>
         </is>
       </c>
       <c r="Q99" s="4" t="n"/>
@@ -7906,7 +7906,7 @@
       </c>
       <c r="P100" s="4" t="inlineStr">
         <is>
-          <t>2026-09-14</t>
+          <t>2026-09-21</t>
         </is>
       </c>
       <c r="Q100" s="4" t="n"/>
@@ -7983,7 +7983,7 @@
       </c>
       <c r="P101" s="4" t="inlineStr">
         <is>
-          <t>2026-09-14</t>
+          <t>2026-09-21</t>
         </is>
       </c>
       <c r="Q101" s="4" t="n"/>
@@ -8062,7 +8062,7 @@
       </c>
       <c r="P102" s="4" t="inlineStr">
         <is>
-          <t>2026-09-14</t>
+          <t>2026-09-21</t>
         </is>
       </c>
       <c r="Q102" s="4" t="n"/>
@@ -8139,7 +8139,7 @@
       </c>
       <c r="P103" s="4" t="inlineStr">
         <is>
-          <t>2026-09-14</t>
+          <t>2026-09-21</t>
         </is>
       </c>
       <c r="Q103" s="4" t="n"/>
@@ -8216,7 +8216,7 @@
       </c>
       <c r="P104" s="4" t="inlineStr">
         <is>
-          <t>2026-09-14</t>
+          <t>2026-09-21</t>
         </is>
       </c>
       <c r="Q104" s="4" t="n"/>
@@ -8295,7 +8295,7 @@
       </c>
       <c r="P105" s="4" t="inlineStr">
         <is>
-          <t>2026-09-14</t>
+          <t>2026-09-21</t>
         </is>
       </c>
       <c r="Q105" s="4" t="n"/>
@@ -8372,7 +8372,7 @@
       </c>
       <c r="P106" s="4" t="inlineStr">
         <is>
-          <t>2026-09-14</t>
+          <t>2026-09-21</t>
         </is>
       </c>
       <c r="Q106" s="4" t="n"/>
@@ -8449,7 +8449,7 @@
       </c>
       <c r="P107" s="4" t="inlineStr">
         <is>
-          <t>2026-09-14</t>
+          <t>2026-09-21</t>
         </is>
       </c>
       <c r="Q107" s="4" t="n"/>
@@ -8528,7 +8528,7 @@
       </c>
       <c r="P108" s="4" t="inlineStr">
         <is>
-          <t>2026-09-14</t>
+          <t>2026-09-21</t>
         </is>
       </c>
       <c r="Q108" s="4" t="n"/>
@@ -8605,7 +8605,7 @@
       </c>
       <c r="P109" s="4" t="inlineStr">
         <is>
-          <t>2026-09-14</t>
+          <t>2026-09-21</t>
         </is>
       </c>
       <c r="Q109" s="4" t="n"/>
@@ -8682,7 +8682,7 @@
       </c>
       <c r="P110" s="4" t="inlineStr">
         <is>
-          <t>2026-09-14</t>
+          <t>2026-09-21</t>
         </is>
       </c>
       <c r="Q110" s="4" t="n"/>
@@ -8761,7 +8761,7 @@
       </c>
       <c r="P111" s="4" t="inlineStr">
         <is>
-          <t>2026-09-14</t>
+          <t>2026-09-21</t>
         </is>
       </c>
       <c r="Q111" s="4" t="n"/>
@@ -8840,7 +8840,7 @@
       </c>
       <c r="P112" s="4" t="inlineStr">
         <is>
-          <t>2026-09-14</t>
+          <t>2026-09-21</t>
         </is>
       </c>
       <c r="Q112" s="4" t="n"/>
@@ -8917,7 +8917,7 @@
       </c>
       <c r="P113" s="4" t="inlineStr">
         <is>
-          <t>2026-09-14</t>
+          <t>2026-09-21</t>
         </is>
       </c>
       <c r="Q113" s="4" t="n"/>
@@ -8996,7 +8996,7 @@
       </c>
       <c r="P114" s="4" t="inlineStr">
         <is>
-          <t>2026-09-14</t>
+          <t>2026-09-21</t>
         </is>
       </c>
       <c r="Q114" s="4" t="n"/>
@@ -9075,7 +9075,7 @@
       </c>
       <c r="P115" s="4" t="inlineStr">
         <is>
-          <t>2026-09-14</t>
+          <t>2026-09-21</t>
         </is>
       </c>
       <c r="Q115" s="4" t="n"/>
@@ -9154,7 +9154,7 @@
       </c>
       <c r="P116" s="4" t="inlineStr">
         <is>
-          <t>2026-09-14</t>
+          <t>2026-09-21</t>
         </is>
       </c>
       <c r="Q116" s="4" t="n"/>
@@ -9233,7 +9233,7 @@
       </c>
       <c r="P117" s="4" t="inlineStr">
         <is>
-          <t>2026-09-14</t>
+          <t>2026-09-21</t>
         </is>
       </c>
       <c r="Q117" s="4" t="n"/>
@@ -9312,7 +9312,7 @@
       </c>
       <c r="P118" s="4" t="inlineStr">
         <is>
-          <t>2026-09-14</t>
+          <t>2026-09-21</t>
         </is>
       </c>
       <c r="Q118" s="4" t="n"/>
@@ -9391,7 +9391,7 @@
       </c>
       <c r="P119" s="4" t="inlineStr">
         <is>
-          <t>2026-09-14</t>
+          <t>2026-09-21</t>
         </is>
       </c>
       <c r="Q119" s="4" t="n"/>
@@ -9468,7 +9468,7 @@
       </c>
       <c r="P120" s="4" t="inlineStr">
         <is>
-          <t>2026-09-14</t>
+          <t>2026-09-21</t>
         </is>
       </c>
       <c r="Q120" s="4" t="n"/>
@@ -9545,7 +9545,7 @@
       </c>
       <c r="P121" s="4" t="inlineStr">
         <is>
-          <t>2026-09-14</t>
+          <t>2026-09-21</t>
         </is>
       </c>
       <c r="Q121" s="4" t="n"/>
@@ -9622,7 +9622,7 @@
       </c>
       <c r="P122" s="4" t="inlineStr">
         <is>
-          <t>2026-09-14</t>
+          <t>2026-09-21</t>
         </is>
       </c>
       <c r="Q122" s="4" t="n"/>
@@ -9699,7 +9699,7 @@
       </c>
       <c r="P123" s="4" t="inlineStr">
         <is>
-          <t>2026-09-14</t>
+          <t>2026-09-21</t>
         </is>
       </c>
       <c r="Q123" s="4" t="n"/>
@@ -9776,7 +9776,7 @@
       </c>
       <c r="P124" s="4" t="inlineStr">
         <is>
-          <t>2026-09-14</t>
+          <t>2026-09-21</t>
         </is>
       </c>
       <c r="Q124" s="4" t="n"/>
@@ -9853,7 +9853,7 @@
       </c>
       <c r="P125" s="4" t="inlineStr">
         <is>
-          <t>2026-09-14</t>
+          <t>2026-09-21</t>
         </is>
       </c>
       <c r="Q125" s="4" t="n"/>
@@ -9930,7 +9930,7 @@
       </c>
       <c r="P126" s="4" t="inlineStr">
         <is>
-          <t>2026-09-14</t>
+          <t>2026-09-21</t>
         </is>
       </c>
       <c r="Q126" s="4" t="n"/>
@@ -10007,7 +10007,7 @@
       </c>
       <c r="P127" s="4" t="inlineStr">
         <is>
-          <t>2026-09-14</t>
+          <t>2026-09-21</t>
         </is>
       </c>
       <c r="Q127" s="4" t="n"/>
@@ -10084,7 +10084,7 @@
       </c>
       <c r="P128" s="4" t="inlineStr">
         <is>
-          <t>2026-09-14</t>
+          <t>2026-09-21</t>
         </is>
       </c>
       <c r="Q128" s="4" t="n"/>
@@ -10161,7 +10161,7 @@
       </c>
       <c r="P129" s="4" t="inlineStr">
         <is>
-          <t>2026-09-14</t>
+          <t>2026-09-21</t>
         </is>
       </c>
       <c r="Q129" s="4" t="n"/>
@@ -10238,7 +10238,7 @@
       </c>
       <c r="P130" s="4" t="inlineStr">
         <is>
-          <t>2026-09-14</t>
+          <t>2026-09-21</t>
         </is>
       </c>
       <c r="Q130" s="4" t="n"/>
@@ -10315,7 +10315,7 @@
       </c>
       <c r="P131" s="4" t="inlineStr">
         <is>
-          <t>2026-09-14</t>
+          <t>2026-09-21</t>
         </is>
       </c>
       <c r="Q131" s="4" t="n"/>
@@ -10392,7 +10392,7 @@
       </c>
       <c r="P132" s="4" t="inlineStr">
         <is>
-          <t>2026-09-14</t>
+          <t>2026-09-21</t>
         </is>
       </c>
       <c r="Q132" s="4" t="n"/>
@@ -10469,7 +10469,7 @@
       </c>
       <c r="P133" s="4" t="inlineStr">
         <is>
-          <t>2026-09-14</t>
+          <t>2026-09-21</t>
         </is>
       </c>
       <c r="Q133" s="4" t="n"/>
@@ -10546,7 +10546,7 @@
       </c>
       <c r="P134" s="4" t="inlineStr">
         <is>
-          <t>2026-09-14</t>
+          <t>2026-09-21</t>
         </is>
       </c>
       <c r="Q134" s="4" t="n"/>
@@ -10623,7 +10623,7 @@
       </c>
       <c r="P135" s="4" t="inlineStr">
         <is>
-          <t>2026-09-14</t>
+          <t>2026-09-21</t>
         </is>
       </c>
       <c r="Q135" s="4" t="n"/>
@@ -10700,7 +10700,7 @@
       </c>
       <c r="P136" s="4" t="inlineStr">
         <is>
-          <t>2026-09-14</t>
+          <t>2026-09-21</t>
         </is>
       </c>
       <c r="Q136" s="4" t="n"/>
@@ -10777,7 +10777,7 @@
       </c>
       <c r="P137" s="4" t="inlineStr">
         <is>
-          <t>2026-09-14</t>
+          <t>2026-09-21</t>
         </is>
       </c>
       <c r="Q137" s="4" t="n"/>
@@ -10854,7 +10854,7 @@
       </c>
       <c r="P138" s="4" t="inlineStr">
         <is>
-          <t>2026-09-14</t>
+          <t>2026-09-21</t>
         </is>
       </c>
       <c r="Q138" s="4" t="n"/>
@@ -10931,7 +10931,7 @@
       </c>
       <c r="P139" s="4" t="inlineStr">
         <is>
-          <t>2026-09-14</t>
+          <t>2026-09-21</t>
         </is>
       </c>
       <c r="Q139" s="4" t="n"/>
@@ -11008,7 +11008,7 @@
       </c>
       <c r="P140" s="4" t="inlineStr">
         <is>
-          <t>2026-09-14</t>
+          <t>2026-09-21</t>
         </is>
       </c>
       <c r="Q140" s="4" t="n"/>
@@ -11085,7 +11085,7 @@
       </c>
       <c r="P141" s="4" t="inlineStr">
         <is>
-          <t>2026-09-14</t>
+          <t>2026-09-21</t>
         </is>
       </c>
       <c r="Q141" s="4" t="n"/>
@@ -11162,7 +11162,7 @@
       </c>
       <c r="P142" s="4" t="inlineStr">
         <is>
-          <t>2026-09-14</t>
+          <t>2026-09-21</t>
         </is>
       </c>
       <c r="Q142" s="4" t="n"/>
@@ -11239,7 +11239,7 @@
       </c>
       <c r="P143" s="4" t="inlineStr">
         <is>
-          <t>2026-09-14</t>
+          <t>2026-09-21</t>
         </is>
       </c>
       <c r="Q143" s="4" t="n"/>
@@ -11316,7 +11316,7 @@
       </c>
       <c r="P144" s="4" t="inlineStr">
         <is>
-          <t>2026-09-14</t>
+          <t>2026-09-21</t>
         </is>
       </c>
       <c r="Q144" s="4" t="n"/>
@@ -11393,7 +11393,7 @@
       </c>
       <c r="P145" s="4" t="inlineStr">
         <is>
-          <t>2026-09-14</t>
+          <t>2026-09-21</t>
         </is>
       </c>
       <c r="Q145" s="4" t="n"/>
@@ -11470,7 +11470,7 @@
       </c>
       <c r="P146" s="4" t="inlineStr">
         <is>
-          <t>2026-09-14</t>
+          <t>2026-09-21</t>
         </is>
       </c>
       <c r="Q146" s="4" t="n"/>
@@ -11547,7 +11547,7 @@
       </c>
       <c r="P147" s="4" t="inlineStr">
         <is>
-          <t>2026-09-14</t>
+          <t>2026-09-21</t>
         </is>
       </c>
       <c r="Q147" s="4" t="n"/>
@@ -11624,7 +11624,7 @@
       </c>
       <c r="P148" s="4" t="inlineStr">
         <is>
-          <t>2026-09-14</t>
+          <t>2026-09-21</t>
         </is>
       </c>
       <c r="Q148" s="4" t="n"/>
@@ -11701,7 +11701,7 @@
       </c>
       <c r="P149" s="4" t="inlineStr">
         <is>
-          <t>2026-09-14</t>
+          <t>2026-09-21</t>
         </is>
       </c>
       <c r="Q149" s="4" t="n"/>
@@ -11778,7 +11778,7 @@
       </c>
       <c r="P150" s="4" t="inlineStr">
         <is>
-          <t>2026-09-14</t>
+          <t>2026-09-21</t>
         </is>
       </c>
       <c r="Q150" s="4" t="n"/>
@@ -11855,7 +11855,7 @@
       </c>
       <c r="P151" s="4" t="inlineStr">
         <is>
-          <t>2026-09-14</t>
+          <t>2026-09-21</t>
         </is>
       </c>
       <c r="Q151" s="4" t="n"/>
@@ -11932,7 +11932,7 @@
       </c>
       <c r="P152" s="4" t="inlineStr">
         <is>
-          <t>2026-09-14</t>
+          <t>2026-09-21</t>
         </is>
       </c>
       <c r="Q152" s="4" t="n"/>
@@ -12009,7 +12009,7 @@
       </c>
       <c r="P153" s="4" t="inlineStr">
         <is>
-          <t>2026-09-14</t>
+          <t>2026-09-21</t>
         </is>
       </c>
       <c r="Q153" s="4" t="n"/>
@@ -12086,7 +12086,7 @@
       </c>
       <c r="P154" s="4" t="inlineStr">
         <is>
-          <t>2026-09-14</t>
+          <t>2026-09-21</t>
         </is>
       </c>
       <c r="Q154" s="4" t="n"/>
@@ -12163,7 +12163,7 @@
       </c>
       <c r="P155" s="4" t="inlineStr">
         <is>
-          <t>2026-09-14</t>
+          <t>2026-09-21</t>
         </is>
       </c>
       <c r="Q155" s="4" t="n"/>
@@ -12240,7 +12240,7 @@
       </c>
       <c r="P156" s="4" t="inlineStr">
         <is>
-          <t>2026-09-14</t>
+          <t>2026-09-21</t>
         </is>
       </c>
       <c r="Q156" s="4" t="n"/>
@@ -12317,7 +12317,7 @@
       </c>
       <c r="P157" s="4" t="inlineStr">
         <is>
-          <t>2026-09-14</t>
+          <t>2026-09-21</t>
         </is>
       </c>
       <c r="Q157" s="4" t="n"/>
@@ -12394,7 +12394,7 @@
       </c>
       <c r="P158" s="4" t="inlineStr">
         <is>
-          <t>2026-09-14</t>
+          <t>2026-09-21</t>
         </is>
       </c>
       <c r="Q158" s="4" t="n"/>
@@ -12471,7 +12471,7 @@
       </c>
       <c r="P159" s="4" t="inlineStr">
         <is>
-          <t>2026-09-14</t>
+          <t>2026-09-21</t>
         </is>
       </c>
       <c r="Q159" s="4" t="n"/>
@@ -12550,7 +12550,7 @@
       </c>
       <c r="P160" s="4" t="inlineStr">
         <is>
-          <t>2026-09-14</t>
+          <t>2026-09-21</t>
         </is>
       </c>
       <c r="Q160" s="4" t="n"/>
@@ -12627,7 +12627,7 @@
       </c>
       <c r="P161" s="4" t="inlineStr">
         <is>
-          <t>2026-09-14</t>
+          <t>2026-09-21</t>
         </is>
       </c>
       <c r="Q161" s="4" t="n"/>
@@ -12704,7 +12704,7 @@
       </c>
       <c r="P162" s="4" t="inlineStr">
         <is>
-          <t>2026-09-14</t>
+          <t>2026-09-21</t>
         </is>
       </c>
       <c r="Q162" s="4" t="n"/>
@@ -12781,7 +12781,7 @@
       </c>
       <c r="P163" s="4" t="inlineStr">
         <is>
-          <t>2026-09-14</t>
+          <t>2026-09-21</t>
         </is>
       </c>
       <c r="Q163" s="4" t="n"/>
@@ -12858,7 +12858,7 @@
       </c>
       <c r="P164" s="4" t="inlineStr">
         <is>
-          <t>2026-09-14</t>
+          <t>2026-09-21</t>
         </is>
       </c>
       <c r="Q164" s="4" t="n"/>
@@ -12935,7 +12935,7 @@
       </c>
       <c r="P165" s="4" t="inlineStr">
         <is>
-          <t>2026-09-14</t>
+          <t>2026-09-21</t>
         </is>
       </c>
       <c r="Q165" s="4" t="n"/>
@@ -13014,7 +13014,7 @@
       </c>
       <c r="P166" s="4" t="inlineStr">
         <is>
-          <t>2026-09-14</t>
+          <t>2026-09-21</t>
         </is>
       </c>
       <c r="Q166" s="4" t="n"/>
@@ -13091,7 +13091,7 @@
       </c>
       <c r="P167" s="4" t="inlineStr">
         <is>
-          <t>2026-09-14</t>
+          <t>2026-09-21</t>
         </is>
       </c>
       <c r="Q167" s="4" t="n"/>
@@ -13170,7 +13170,7 @@
       </c>
       <c r="P168" s="4" t="inlineStr">
         <is>
-          <t>2026-09-14</t>
+          <t>2026-09-21</t>
         </is>
       </c>
       <c r="Q168" s="4" t="n"/>
@@ -13247,7 +13247,7 @@
       </c>
       <c r="P169" s="4" t="inlineStr">
         <is>
-          <t>2026-09-14</t>
+          <t>2026-09-21</t>
         </is>
       </c>
       <c r="Q169" s="4" t="n"/>
@@ -13324,7 +13324,7 @@
       </c>
       <c r="P170" s="4" t="inlineStr">
         <is>
-          <t>2026-09-14</t>
+          <t>2026-09-21</t>
         </is>
       </c>
       <c r="Q170" s="4" t="n"/>
@@ -13403,7 +13403,7 @@
       </c>
       <c r="P171" s="4" t="inlineStr">
         <is>
-          <t>2026-09-14</t>
+          <t>2026-09-21</t>
         </is>
       </c>
       <c r="Q171" s="4" t="n"/>
@@ -13480,7 +13480,7 @@
       </c>
       <c r="P172" s="4" t="inlineStr">
         <is>
-          <t>2026-09-14</t>
+          <t>2026-09-21</t>
         </is>
       </c>
       <c r="Q172" s="4" t="n"/>
@@ -13557,7 +13557,7 @@
       </c>
       <c r="P173" s="4" t="inlineStr">
         <is>
-          <t>2026-09-14</t>
+          <t>2026-09-21</t>
         </is>
       </c>
       <c r="Q173" s="4" t="n"/>
@@ -13636,7 +13636,7 @@
       </c>
       <c r="P174" s="4" t="inlineStr">
         <is>
-          <t>2026-09-14</t>
+          <t>2026-09-21</t>
         </is>
       </c>
       <c r="Q174" s="4" t="n"/>
@@ -13713,7 +13713,7 @@
       </c>
       <c r="P175" s="4" t="inlineStr">
         <is>
-          <t>2026-09-14</t>
+          <t>2026-09-21</t>
         </is>
       </c>
       <c r="Q175" s="4" t="n"/>
@@ -13790,7 +13790,7 @@
       </c>
       <c r="P176" s="4" t="inlineStr">
         <is>
-          <t>2026-09-14</t>
+          <t>2026-09-21</t>
         </is>
       </c>
       <c r="Q176" s="4" t="n"/>
@@ -13869,7 +13869,7 @@
       </c>
       <c r="P177" s="4" t="inlineStr">
         <is>
-          <t>2026-09-14</t>
+          <t>2026-09-21</t>
         </is>
       </c>
       <c r="Q177" s="4" t="n"/>
@@ -13948,7 +13948,7 @@
       </c>
       <c r="P178" s="4" t="inlineStr">
         <is>
-          <t>2026-09-14</t>
+          <t>2026-09-21</t>
         </is>
       </c>
       <c r="Q178" s="4" t="n"/>
@@ -14025,7 +14025,7 @@
       </c>
       <c r="P179" s="4" t="inlineStr">
         <is>
-          <t>2026-09-14</t>
+          <t>2026-09-21</t>
         </is>
       </c>
       <c r="Q179" s="4" t="n"/>
@@ -14104,7 +14104,7 @@
       </c>
       <c r="P180" s="4" t="inlineStr">
         <is>
-          <t>2026-09-14</t>
+          <t>2026-09-21</t>
         </is>
       </c>
       <c r="Q180" s="4" t="n"/>
@@ -14183,7 +14183,7 @@
       </c>
       <c r="P181" s="4" t="inlineStr">
         <is>
-          <t>2026-09-14</t>
+          <t>2026-09-21</t>
         </is>
       </c>
       <c r="Q181" s="4" t="n"/>
@@ -14262,7 +14262,7 @@
       </c>
       <c r="P182" s="4" t="inlineStr">
         <is>
-          <t>2026-09-14</t>
+          <t>2026-09-21</t>
         </is>
       </c>
       <c r="Q182" s="4" t="n"/>
@@ -14341,7 +14341,7 @@
       </c>
       <c r="P183" s="4" t="inlineStr">
         <is>
-          <t>2026-09-14</t>
+          <t>2026-09-21</t>
         </is>
       </c>
       <c r="Q183" s="4" t="n"/>
@@ -14420,7 +14420,7 @@
       </c>
       <c r="P184" s="4" t="inlineStr">
         <is>
-          <t>2026-09-14</t>
+          <t>2026-09-21</t>
         </is>
       </c>
       <c r="Q184" s="4" t="n"/>
@@ -14499,7 +14499,7 @@
       </c>
       <c r="P185" s="4" t="inlineStr">
         <is>
-          <t>2026-09-14</t>
+          <t>2026-09-21</t>
         </is>
       </c>
       <c r="Q185" s="4" t="n"/>
@@ -14576,7 +14576,7 @@
       </c>
       <c r="P186" s="4" t="inlineStr">
         <is>
-          <t>2026-09-14</t>
+          <t>2026-09-21</t>
         </is>
       </c>
       <c r="Q186" s="4" t="n"/>
@@ -14653,7 +14653,7 @@
       </c>
       <c r="P187" s="4" t="inlineStr">
         <is>
-          <t>2026-09-14</t>
+          <t>2026-09-21</t>
         </is>
       </c>
       <c r="Q187" s="4" t="n"/>
@@ -14730,7 +14730,7 @@
       </c>
       <c r="P188" s="4" t="inlineStr">
         <is>
-          <t>2026-09-14</t>
+          <t>2026-09-21</t>
         </is>
       </c>
       <c r="Q188" s="4" t="n"/>
@@ -14807,7 +14807,7 @@
       </c>
       <c r="P189" s="4" t="inlineStr">
         <is>
-          <t>2026-09-14</t>
+          <t>2026-09-21</t>
         </is>
       </c>
       <c r="Q189" s="4" t="n"/>
@@ -14884,7 +14884,7 @@
       </c>
       <c r="P190" s="4" t="inlineStr">
         <is>
-          <t>2026-09-14</t>
+          <t>2026-09-21</t>
         </is>
       </c>
       <c r="Q190" s="4" t="n"/>
@@ -14961,7 +14961,7 @@
       </c>
       <c r="P191" s="4" t="inlineStr">
         <is>
-          <t>2026-09-14</t>
+          <t>2026-09-21</t>
         </is>
       </c>
       <c r="Q191" s="4" t="n"/>
@@ -15038,7 +15038,7 @@
       </c>
       <c r="P192" s="4" t="inlineStr">
         <is>
-          <t>2026-09-14</t>
+          <t>2026-09-21</t>
         </is>
       </c>
       <c r="Q192" s="4" t="n"/>
@@ -15115,7 +15115,7 @@
       </c>
       <c r="P193" s="4" t="inlineStr">
         <is>
-          <t>2026-09-14</t>
+          <t>2026-09-21</t>
         </is>
       </c>
       <c r="Q193" s="4" t="n"/>
@@ -15192,7 +15192,7 @@
       </c>
       <c r="P194" s="4" t="inlineStr">
         <is>
-          <t>2026-09-14</t>
+          <t>2026-09-21</t>
         </is>
       </c>
       <c r="Q194" s="4" t="n"/>
@@ -15269,7 +15269,7 @@
       </c>
       <c r="P195" s="4" t="inlineStr">
         <is>
-          <t>2026-09-14</t>
+          <t>2026-09-21</t>
         </is>
       </c>
       <c r="Q195" s="4" t="n"/>
@@ -15346,7 +15346,7 @@
       </c>
       <c r="P196" s="4" t="inlineStr">
         <is>
-          <t>2026-09-14</t>
+          <t>2026-09-21</t>
         </is>
       </c>
       <c r="Q196" s="4" t="n"/>
@@ -15423,7 +15423,7 @@
       </c>
       <c r="P197" s="4" t="inlineStr">
         <is>
-          <t>2026-09-14</t>
+          <t>2026-09-21</t>
         </is>
       </c>
       <c r="Q197" s="4" t="n"/>
@@ -15500,7 +15500,7 @@
       </c>
       <c r="P198" s="4" t="inlineStr">
         <is>
-          <t>2026-09-14</t>
+          <t>2026-09-21</t>
         </is>
       </c>
       <c r="Q198" s="4" t="n"/>
@@ -15577,7 +15577,7 @@
       </c>
       <c r="P199" s="4" t="inlineStr">
         <is>
-          <t>2026-09-14</t>
+          <t>2026-09-21</t>
         </is>
       </c>
       <c r="Q199" s="4" t="n"/>
@@ -15654,7 +15654,7 @@
       </c>
       <c r="P200" s="4" t="inlineStr">
         <is>
-          <t>2026-09-14</t>
+          <t>2026-09-21</t>
         </is>
       </c>
       <c r="Q200" s="4" t="n"/>
@@ -15731,7 +15731,7 @@
       </c>
       <c r="P201" s="4" t="inlineStr">
         <is>
-          <t>2026-09-14</t>
+          <t>2026-09-21</t>
         </is>
       </c>
       <c r="Q201" s="4" t="n"/>
@@ -15808,7 +15808,7 @@
       </c>
       <c r="P202" s="4" t="inlineStr">
         <is>
-          <t>2026-09-14</t>
+          <t>2026-09-21</t>
         </is>
       </c>
       <c r="Q202" s="4" t="n"/>
@@ -15885,7 +15885,7 @@
       </c>
       <c r="P203" s="4" t="inlineStr">
         <is>
-          <t>2026-09-14</t>
+          <t>2026-09-21</t>
         </is>
       </c>
       <c r="Q203" s="4" t="n"/>
@@ -15962,7 +15962,7 @@
       </c>
       <c r="P204" s="4" t="inlineStr">
         <is>
-          <t>2026-09-14</t>
+          <t>2026-09-21</t>
         </is>
       </c>
       <c r="Q204" s="4" t="n"/>
@@ -16039,7 +16039,7 @@
       </c>
       <c r="P205" s="4" t="inlineStr">
         <is>
-          <t>2026-09-14</t>
+          <t>2026-09-21</t>
         </is>
       </c>
       <c r="Q205" s="4" t="n"/>
@@ -16116,7 +16116,7 @@
       </c>
       <c r="P206" s="4" t="inlineStr">
         <is>
-          <t>2026-09-14</t>
+          <t>2026-09-21</t>
         </is>
       </c>
       <c r="Q206" s="4" t="n"/>
@@ -16193,7 +16193,7 @@
       </c>
       <c r="P207" s="4" t="inlineStr">
         <is>
-          <t>2026-09-14</t>
+          <t>2026-09-21</t>
         </is>
       </c>
       <c r="Q207" s="4" t="n"/>
@@ -16270,7 +16270,7 @@
       </c>
       <c r="P208" s="4" t="inlineStr">
         <is>
-          <t>2026-09-14</t>
+          <t>2026-09-21</t>
         </is>
       </c>
       <c r="Q208" s="4" t="n"/>
@@ -16347,7 +16347,7 @@
       </c>
       <c r="P209" s="4" t="inlineStr">
         <is>
-          <t>2026-09-14</t>
+          <t>2026-09-21</t>
         </is>
       </c>
       <c r="Q209" s="4" t="n"/>
@@ -16424,7 +16424,7 @@
       </c>
       <c r="P210" s="4" t="inlineStr">
         <is>
-          <t>2026-09-14</t>
+          <t>2026-09-21</t>
         </is>
       </c>
       <c r="Q210" s="4" t="n"/>
@@ -16501,7 +16501,7 @@
       </c>
       <c r="P211" s="4" t="inlineStr">
         <is>
-          <t>2026-09-14</t>
+          <t>2026-09-21</t>
         </is>
       </c>
       <c r="Q211" s="4" t="n"/>
@@ -16578,7 +16578,7 @@
       </c>
       <c r="P212" s="4" t="inlineStr">
         <is>
-          <t>2026-09-14</t>
+          <t>2026-09-21</t>
         </is>
       </c>
       <c r="Q212" s="4" t="n"/>
@@ -16655,7 +16655,7 @@
       </c>
       <c r="P213" s="4" t="inlineStr">
         <is>
-          <t>2026-09-14</t>
+          <t>2026-09-21</t>
         </is>
       </c>
       <c r="Q213" s="4" t="n"/>
@@ -16732,7 +16732,7 @@
       </c>
       <c r="P214" s="4" t="inlineStr">
         <is>
-          <t>2026-09-14</t>
+          <t>2026-09-21</t>
         </is>
       </c>
       <c r="Q214" s="4" t="n"/>
@@ -16809,7 +16809,7 @@
       </c>
       <c r="P215" s="4" t="inlineStr">
         <is>
-          <t>2026-09-14</t>
+          <t>2026-09-21</t>
         </is>
       </c>
       <c r="Q215" s="4" t="n"/>
@@ -16886,7 +16886,7 @@
       </c>
       <c r="P216" s="4" t="inlineStr">
         <is>
-          <t>2026-09-14</t>
+          <t>2026-09-21</t>
         </is>
       </c>
       <c r="Q216" s="4" t="n"/>
@@ -16963,7 +16963,7 @@
       </c>
       <c r="P217" s="4" t="inlineStr">
         <is>
-          <t>2026-09-14</t>
+          <t>2026-09-21</t>
         </is>
       </c>
       <c r="Q217" s="4" t="n"/>
@@ -17040,7 +17040,7 @@
       </c>
       <c r="P218" s="4" t="inlineStr">
         <is>
-          <t>2026-09-14</t>
+          <t>2026-09-21</t>
         </is>
       </c>
       <c r="Q218" s="4" t="n"/>
@@ -17117,7 +17117,7 @@
       </c>
       <c r="P219" s="4" t="inlineStr">
         <is>
-          <t>2026-09-14</t>
+          <t>2026-09-21</t>
         </is>
       </c>
       <c r="Q219" s="4" t="n"/>
@@ -17194,7 +17194,7 @@
       </c>
       <c r="P220" s="4" t="inlineStr">
         <is>
-          <t>2026-09-14</t>
+          <t>2026-09-21</t>
         </is>
       </c>
       <c r="Q220" s="4" t="n"/>
@@ -17271,7 +17271,7 @@
       </c>
       <c r="P221" s="4" t="inlineStr">
         <is>
-          <t>2026-09-14</t>
+          <t>2026-09-21</t>
         </is>
       </c>
       <c r="Q221" s="4" t="n"/>
@@ -17348,7 +17348,7 @@
       </c>
       <c r="P222" s="4" t="inlineStr">
         <is>
-          <t>2026-09-14</t>
+          <t>2026-09-21</t>
         </is>
       </c>
       <c r="Q222" s="4" t="n"/>
@@ -17425,7 +17425,7 @@
       </c>
       <c r="P223" s="4" t="inlineStr">
         <is>
-          <t>2026-09-14</t>
+          <t>2026-09-21</t>
         </is>
       </c>
       <c r="Q223" s="4" t="n"/>
@@ -17502,7 +17502,7 @@
       </c>
       <c r="P224" s="4" t="inlineStr">
         <is>
-          <t>2026-09-14</t>
+          <t>2026-09-21</t>
         </is>
       </c>
       <c r="Q224" s="4" t="n"/>
@@ -17579,7 +17579,7 @@
       </c>
       <c r="P225" s="4" t="inlineStr">
         <is>
-          <t>2026-09-14</t>
+          <t>2026-09-21</t>
         </is>
       </c>
       <c r="Q225" s="4" t="n"/>
@@ -17658,7 +17658,7 @@
       </c>
       <c r="P226" s="4" t="inlineStr">
         <is>
-          <t>2026-09-14</t>
+          <t>2026-09-21</t>
         </is>
       </c>
       <c r="Q226" s="4" t="n"/>
@@ -17735,7 +17735,7 @@
       </c>
       <c r="P227" s="4" t="inlineStr">
         <is>
-          <t>2026-09-14</t>
+          <t>2026-09-21</t>
         </is>
       </c>
       <c r="Q227" s="4" t="n"/>
@@ -17812,7 +17812,7 @@
       </c>
       <c r="P228" s="4" t="inlineStr">
         <is>
-          <t>2026-09-14</t>
+          <t>2026-09-21</t>
         </is>
       </c>
       <c r="Q228" s="4" t="n"/>
@@ -17889,7 +17889,7 @@
       </c>
       <c r="P229" s="4" t="inlineStr">
         <is>
-          <t>2026-09-14</t>
+          <t>2026-09-21</t>
         </is>
       </c>
       <c r="Q229" s="4" t="n"/>
@@ -17966,7 +17966,7 @@
       </c>
       <c r="P230" s="4" t="inlineStr">
         <is>
-          <t>2026-09-14</t>
+          <t>2026-09-21</t>
         </is>
       </c>
       <c r="Q230" s="4" t="n"/>
@@ -18043,7 +18043,7 @@
       </c>
       <c r="P231" s="4" t="inlineStr">
         <is>
-          <t>2026-09-14</t>
+          <t>2026-09-21</t>
         </is>
       </c>
       <c r="Q231" s="4" t="n"/>
@@ -18122,7 +18122,7 @@
       </c>
       <c r="P232" s="4" t="inlineStr">
         <is>
-          <t>2026-09-14</t>
+          <t>2026-09-21</t>
         </is>
       </c>
       <c r="Q232" s="4" t="n"/>
@@ -18199,7 +18199,7 @@
       </c>
       <c r="P233" s="4" t="inlineStr">
         <is>
-          <t>2026-09-14</t>
+          <t>2026-09-21</t>
         </is>
       </c>
       <c r="Q233" s="4" t="n"/>
@@ -18278,7 +18278,7 @@
       </c>
       <c r="P234" s="4" t="inlineStr">
         <is>
-          <t>2026-09-14</t>
+          <t>2026-09-21</t>
         </is>
       </c>
       <c r="Q234" s="4" t="n"/>
@@ -18355,7 +18355,7 @@
       </c>
       <c r="P235" s="4" t="inlineStr">
         <is>
-          <t>2026-09-14</t>
+          <t>2026-09-21</t>
         </is>
       </c>
       <c r="Q235" s="4" t="n"/>
@@ -18432,7 +18432,7 @@
       </c>
       <c r="P236" s="4" t="inlineStr">
         <is>
-          <t>2026-09-14</t>
+          <t>2026-09-21</t>
         </is>
       </c>
       <c r="Q236" s="4" t="n"/>
@@ -18511,7 +18511,7 @@
       </c>
       <c r="P237" s="4" t="inlineStr">
         <is>
-          <t>2026-09-14</t>
+          <t>2026-09-21</t>
         </is>
       </c>
       <c r="Q237" s="4" t="n"/>
@@ -18588,7 +18588,7 @@
       </c>
       <c r="P238" s="4" t="inlineStr">
         <is>
-          <t>2026-09-14</t>
+          <t>2026-09-21</t>
         </is>
       </c>
       <c r="Q238" s="4" t="n"/>
@@ -18665,7 +18665,7 @@
       </c>
       <c r="P239" s="4" t="inlineStr">
         <is>
-          <t>2026-09-14</t>
+          <t>2026-09-21</t>
         </is>
       </c>
       <c r="Q239" s="4" t="n"/>
@@ -18744,7 +18744,7 @@
       </c>
       <c r="P240" s="4" t="inlineStr">
         <is>
-          <t>2026-09-14</t>
+          <t>2026-09-21</t>
         </is>
       </c>
       <c r="Q240" s="4" t="n"/>
@@ -18821,7 +18821,7 @@
       </c>
       <c r="P241" s="4" t="inlineStr">
         <is>
-          <t>2026-09-14</t>
+          <t>2026-09-21</t>
         </is>
       </c>
       <c r="Q241" s="4" t="n"/>
@@ -18898,7 +18898,7 @@
       </c>
       <c r="P242" s="4" t="inlineStr">
         <is>
-          <t>2026-09-14</t>
+          <t>2026-09-21</t>
         </is>
       </c>
       <c r="Q242" s="4" t="n"/>
@@ -18977,7 +18977,7 @@
       </c>
       <c r="P243" s="4" t="inlineStr">
         <is>
-          <t>2026-09-14</t>
+          <t>2026-09-21</t>
         </is>
       </c>
       <c r="Q243" s="4" t="n"/>
@@ -19056,7 +19056,7 @@
       </c>
       <c r="P244" s="4" t="inlineStr">
         <is>
-          <t>2026-09-14</t>
+          <t>2026-09-21</t>
         </is>
       </c>
       <c r="Q244" s="4" t="n"/>
@@ -19133,7 +19133,7 @@
       </c>
       <c r="P245" s="4" t="inlineStr">
         <is>
-          <t>2026-09-14</t>
+          <t>2026-09-21</t>
         </is>
       </c>
       <c r="Q245" s="4" t="n"/>
@@ -19212,7 +19212,7 @@
       </c>
       <c r="P246" s="4" t="inlineStr">
         <is>
-          <t>2026-09-14</t>
+          <t>2026-09-21</t>
         </is>
       </c>
       <c r="Q246" s="4" t="n"/>
@@ -19291,7 +19291,7 @@
       </c>
       <c r="P247" s="4" t="inlineStr">
         <is>
-          <t>2026-09-14</t>
+          <t>2026-09-21</t>
         </is>
       </c>
       <c r="Q247" s="4" t="n"/>
@@ -19370,7 +19370,7 @@
       </c>
       <c r="P248" s="4" t="inlineStr">
         <is>
-          <t>2026-09-14</t>
+          <t>2026-09-21</t>
         </is>
       </c>
       <c r="Q248" s="4" t="n"/>
@@ -19449,7 +19449,7 @@
       </c>
       <c r="P249" s="4" t="inlineStr">
         <is>
-          <t>2026-09-14</t>
+          <t>2026-09-21</t>
         </is>
       </c>
       <c r="Q249" s="4" t="n"/>
@@ -19528,7 +19528,7 @@
       </c>
       <c r="P250" s="4" t="inlineStr">
         <is>
-          <t>2026-09-14</t>
+          <t>2026-09-21</t>
         </is>
       </c>
       <c r="Q250" s="4" t="n"/>
@@ -19607,7 +19607,7 @@
       </c>
       <c r="P251" s="4" t="inlineStr">
         <is>
-          <t>2026-09-14</t>
+          <t>2026-09-21</t>
         </is>
       </c>
       <c r="Q251" s="4" t="n"/>
@@ -19684,7 +19684,7 @@
       </c>
       <c r="P252" s="4" t="inlineStr">
         <is>
-          <t>2026-09-14</t>
+          <t>2026-09-21</t>
         </is>
       </c>
       <c r="Q252" s="4" t="n"/>
@@ -19761,7 +19761,7 @@
       </c>
       <c r="P253" s="4" t="inlineStr">
         <is>
-          <t>2026-09-14</t>
+          <t>2026-09-21</t>
         </is>
       </c>
       <c r="Q253" s="4" t="n"/>
@@ -19838,7 +19838,7 @@
       </c>
       <c r="P254" s="4" t="inlineStr">
         <is>
-          <t>2026-09-14</t>
+          <t>2026-09-21</t>
         </is>
       </c>
       <c r="Q254" s="4" t="n"/>
@@ -19915,7 +19915,7 @@
       </c>
       <c r="P255" s="4" t="inlineStr">
         <is>
-          <t>2026-09-14</t>
+          <t>2026-09-21</t>
         </is>
       </c>
       <c r="Q255" s="4" t="n"/>
@@ -19992,7 +19992,7 @@
       </c>
       <c r="P256" s="4" t="inlineStr">
         <is>
-          <t>2026-09-14</t>
+          <t>2026-09-21</t>
         </is>
       </c>
       <c r="Q256" s="4" t="n"/>
@@ -20069,7 +20069,7 @@
       </c>
       <c r="P257" s="4" t="inlineStr">
         <is>
-          <t>2026-09-14</t>
+          <t>2026-09-21</t>
         </is>
       </c>
       <c r="Q257" s="4" t="n"/>
@@ -20146,7 +20146,7 @@
       </c>
       <c r="P258" s="4" t="inlineStr">
         <is>
-          <t>2026-09-14</t>
+          <t>2026-09-21</t>
         </is>
       </c>
       <c r="Q258" s="4" t="n"/>
@@ -20223,7 +20223,7 @@
       </c>
       <c r="P259" s="4" t="inlineStr">
         <is>
-          <t>2026-09-14</t>
+          <t>2026-09-21</t>
         </is>
       </c>
       <c r="Q259" s="4" t="n"/>
@@ -20300,7 +20300,7 @@
       </c>
       <c r="P260" s="4" t="inlineStr">
         <is>
-          <t>2026-09-14</t>
+          <t>2026-09-21</t>
         </is>
       </c>
       <c r="Q260" s="4" t="n"/>
@@ -20377,7 +20377,7 @@
       </c>
       <c r="P261" s="4" t="inlineStr">
         <is>
-          <t>2026-09-14</t>
+          <t>2026-09-21</t>
         </is>
       </c>
       <c r="Q261" s="4" t="n"/>
@@ -20454,7 +20454,7 @@
       </c>
       <c r="P262" s="4" t="inlineStr">
         <is>
-          <t>2026-09-14</t>
+          <t>2026-09-21</t>
         </is>
       </c>
       <c r="Q262" s="4" t="n"/>
@@ -20531,7 +20531,7 @@
       </c>
       <c r="P263" s="4" t="inlineStr">
         <is>
-          <t>2026-09-14</t>
+          <t>2026-09-21</t>
         </is>
       </c>
       <c r="Q263" s="4" t="n"/>
@@ -20608,7 +20608,7 @@
       </c>
       <c r="P264" s="4" t="inlineStr">
         <is>
-          <t>2026-09-14</t>
+          <t>2026-09-21</t>
         </is>
       </c>
       <c r="Q264" s="4" t="n"/>
@@ -20685,7 +20685,7 @@
       </c>
       <c r="P265" s="4" t="inlineStr">
         <is>
-          <t>2026-09-14</t>
+          <t>2026-09-21</t>
         </is>
       </c>
       <c r="Q265" s="4" t="n"/>
@@ -20762,7 +20762,7 @@
       </c>
       <c r="P266" s="4" t="inlineStr">
         <is>
-          <t>2026-09-14</t>
+          <t>2026-09-21</t>
         </is>
       </c>
       <c r="Q266" s="4" t="n"/>
@@ -20839,7 +20839,7 @@
       </c>
       <c r="P267" s="4" t="inlineStr">
         <is>
-          <t>2026-09-14</t>
+          <t>2026-09-21</t>
         </is>
       </c>
       <c r="Q267" s="4" t="n"/>
@@ -20916,7 +20916,7 @@
       </c>
       <c r="P268" s="4" t="inlineStr">
         <is>
-          <t>2026-09-14</t>
+          <t>2026-09-21</t>
         </is>
       </c>
       <c r="Q268" s="4" t="n"/>
@@ -20993,7 +20993,7 @@
       </c>
       <c r="P269" s="4" t="inlineStr">
         <is>
-          <t>2026-09-14</t>
+          <t>2026-09-21</t>
         </is>
       </c>
       <c r="Q269" s="4" t="n"/>
@@ -21070,7 +21070,7 @@
       </c>
       <c r="P270" s="4" t="inlineStr">
         <is>
-          <t>2026-09-14</t>
+          <t>2026-09-21</t>
         </is>
       </c>
       <c r="Q270" s="4" t="n"/>
@@ -21147,7 +21147,7 @@
       </c>
       <c r="P271" s="4" t="inlineStr">
         <is>
-          <t>2026-09-14</t>
+          <t>2026-09-21</t>
         </is>
       </c>
       <c r="Q271" s="4" t="n"/>
@@ -21224,7 +21224,7 @@
       </c>
       <c r="P272" s="4" t="inlineStr">
         <is>
-          <t>2026-09-14</t>
+          <t>2026-09-21</t>
         </is>
       </c>
       <c r="Q272" s="4" t="n"/>
@@ -21301,7 +21301,7 @@
       </c>
       <c r="P273" s="4" t="inlineStr">
         <is>
-          <t>2026-09-14</t>
+          <t>2026-09-21</t>
         </is>
       </c>
       <c r="Q273" s="4" t="n"/>
@@ -21378,7 +21378,7 @@
       </c>
       <c r="P274" s="4" t="inlineStr">
         <is>
-          <t>2026-09-14</t>
+          <t>2026-09-21</t>
         </is>
       </c>
       <c r="Q274" s="4" t="n"/>
@@ -21455,7 +21455,7 @@
       </c>
       <c r="P275" s="4" t="inlineStr">
         <is>
-          <t>2026-09-14</t>
+          <t>2026-09-21</t>
         </is>
       </c>
       <c r="Q275" s="4" t="n"/>
@@ -21532,7 +21532,7 @@
       </c>
       <c r="P276" s="4" t="inlineStr">
         <is>
-          <t>2026-09-14</t>
+          <t>2026-09-21</t>
         </is>
       </c>
       <c r="Q276" s="4" t="n"/>
@@ -21609,7 +21609,7 @@
       </c>
       <c r="P277" s="4" t="inlineStr">
         <is>
-          <t>2026-09-14</t>
+          <t>2026-09-21</t>
         </is>
       </c>
       <c r="Q277" s="4" t="n"/>
@@ -21686,7 +21686,7 @@
       </c>
       <c r="P278" s="4" t="inlineStr">
         <is>
-          <t>2026-09-14</t>
+          <t>2026-09-21</t>
         </is>
       </c>
       <c r="Q278" s="4" t="n"/>
@@ -21763,7 +21763,7 @@
       </c>
       <c r="P279" s="4" t="inlineStr">
         <is>
-          <t>2026-09-14</t>
+          <t>2026-09-21</t>
         </is>
       </c>
       <c r="Q279" s="4" t="n"/>
@@ -21840,7 +21840,7 @@
       </c>
       <c r="P280" s="4" t="inlineStr">
         <is>
-          <t>2026-09-14</t>
+          <t>2026-09-21</t>
         </is>
       </c>
       <c r="Q280" s="4" t="n"/>
@@ -21917,7 +21917,7 @@
       </c>
       <c r="P281" s="4" t="inlineStr">
         <is>
-          <t>2026-09-14</t>
+          <t>2026-09-21</t>
         </is>
       </c>
       <c r="Q281" s="4" t="n"/>
@@ -21994,7 +21994,7 @@
       </c>
       <c r="P282" s="4" t="inlineStr">
         <is>
-          <t>2026-09-14</t>
+          <t>2026-09-21</t>
         </is>
       </c>
       <c r="Q282" s="4" t="n"/>
@@ -22071,7 +22071,7 @@
       </c>
       <c r="P283" s="4" t="inlineStr">
         <is>
-          <t>2026-09-14</t>
+          <t>2026-09-21</t>
         </is>
       </c>
       <c r="Q283" s="4" t="n"/>
@@ -22148,7 +22148,7 @@
       </c>
       <c r="P284" s="4" t="inlineStr">
         <is>
-          <t>2026-09-14</t>
+          <t>2026-09-21</t>
         </is>
       </c>
       <c r="Q284" s="4" t="n"/>
@@ -22225,7 +22225,7 @@
       </c>
       <c r="P285" s="4" t="inlineStr">
         <is>
-          <t>2026-09-14</t>
+          <t>2026-09-21</t>
         </is>
       </c>
       <c r="Q285" s="4" t="n"/>
@@ -22302,7 +22302,7 @@
       </c>
       <c r="P286" s="4" t="inlineStr">
         <is>
-          <t>2026-09-14</t>
+          <t>2026-09-21</t>
         </is>
       </c>
       <c r="Q286" s="4" t="n"/>
@@ -22379,7 +22379,7 @@
       </c>
       <c r="P287" s="4" t="inlineStr">
         <is>
-          <t>2026-09-14</t>
+          <t>2026-09-21</t>
         </is>
       </c>
       <c r="Q287" s="4" t="n"/>
@@ -22456,7 +22456,7 @@
       </c>
       <c r="P288" s="4" t="inlineStr">
         <is>
-          <t>2026-09-14</t>
+          <t>2026-09-21</t>
         </is>
       </c>
       <c r="Q288" s="4" t="n"/>
@@ -22533,7 +22533,7 @@
       </c>
       <c r="P289" s="4" t="inlineStr">
         <is>
-          <t>2026-09-14</t>
+          <t>2026-09-21</t>
         </is>
       </c>
       <c r="Q289" s="4" t="n"/>
@@ -22610,7 +22610,7 @@
       </c>
       <c r="P290" s="4" t="inlineStr">
         <is>
-          <t>2026-09-14</t>
+          <t>2026-09-21</t>
         </is>
       </c>
       <c r="Q290" s="4" t="n"/>
@@ -22687,7 +22687,7 @@
       </c>
       <c r="P291" s="4" t="inlineStr">
         <is>
-          <t>2026-09-14</t>
+          <t>2026-09-21</t>
         </is>
       </c>
       <c r="Q291" s="4" t="n"/>
@@ -22764,7 +22764,7 @@
       </c>
       <c r="P292" s="4" t="inlineStr">
         <is>
-          <t>2026-09-14</t>
+          <t>2026-09-21</t>
         </is>
       </c>
       <c r="Q292" s="4" t="n"/>
@@ -22841,7 +22841,7 @@
       </c>
       <c r="P293" s="4" t="inlineStr">
         <is>
-          <t>2026-09-14</t>
+          <t>2026-09-21</t>
         </is>
       </c>
       <c r="Q293" s="4" t="n"/>
@@ -22918,7 +22918,7 @@
       </c>
       <c r="P294" s="4" t="inlineStr">
         <is>
-          <t>2026-09-14</t>
+          <t>2026-09-21</t>
         </is>
       </c>
       <c r="Q294" s="4" t="n"/>
@@ -22995,7 +22995,7 @@
       </c>
       <c r="P295" s="4" t="inlineStr">
         <is>
-          <t>2026-09-14</t>
+          <t>2026-09-21</t>
         </is>
       </c>
       <c r="Q295" s="4" t="n"/>
@@ -23072,7 +23072,7 @@
       </c>
       <c r="P296" s="4" t="inlineStr">
         <is>
-          <t>2026-09-14</t>
+          <t>2026-09-21</t>
         </is>
       </c>
       <c r="Q296" s="4" t="n"/>
@@ -23149,7 +23149,7 @@
       </c>
       <c r="P297" s="4" t="inlineStr">
         <is>
-          <t>2026-09-14</t>
+          <t>2026-09-21</t>
         </is>
       </c>
       <c r="Q297" s="4" t="n"/>
@@ -23226,7 +23226,7 @@
       </c>
       <c r="P298" s="4" t="inlineStr">
         <is>
-          <t>2026-09-14</t>
+          <t>2026-09-21</t>
         </is>
       </c>
       <c r="Q298" s="4" t="n"/>
@@ -23303,7 +23303,7 @@
       </c>
       <c r="P299" s="4" t="inlineStr">
         <is>
-          <t>2026-09-14</t>
+          <t>2026-09-21</t>
         </is>
       </c>
       <c r="Q299" s="4" t="n"/>
@@ -23380,7 +23380,7 @@
       </c>
       <c r="P300" s="4" t="inlineStr">
         <is>
-          <t>2026-09-14</t>
+          <t>2026-09-21</t>
         </is>
       </c>
       <c r="Q300" s="4" t="n"/>
@@ -23457,7 +23457,7 @@
       </c>
       <c r="P301" s="4" t="inlineStr">
         <is>
-          <t>2026-09-14</t>
+          <t>2026-09-21</t>
         </is>
       </c>
       <c r="Q301" s="4" t="n"/>
@@ -23534,7 +23534,7 @@
       </c>
       <c r="P302" s="4" t="inlineStr">
         <is>
-          <t>2026-09-14</t>
+          <t>2026-09-21</t>
         </is>
       </c>
       <c r="Q302" s="4" t="n"/>
@@ -23611,7 +23611,7 @@
       </c>
       <c r="P303" s="4" t="inlineStr">
         <is>
-          <t>2026-09-14</t>
+          <t>2026-09-21</t>
         </is>
       </c>
       <c r="Q303" s="4" t="n"/>
@@ -23688,7 +23688,7 @@
       </c>
       <c r="P304" s="4" t="inlineStr">
         <is>
-          <t>2026-09-14</t>
+          <t>2026-09-21</t>
         </is>
       </c>
       <c r="Q304" s="4" t="n"/>
@@ -23765,7 +23765,7 @@
       </c>
       <c r="P305" s="4" t="inlineStr">
         <is>
-          <t>2026-09-14</t>
+          <t>2026-09-21</t>
         </is>
       </c>
       <c r="Q305" s="4" t="n"/>
@@ -23842,7 +23842,7 @@
       </c>
       <c r="P306" s="4" t="inlineStr">
         <is>
-          <t>2026-09-14</t>
+          <t>2026-09-21</t>
         </is>
       </c>
       <c r="Q306" s="4" t="n"/>
@@ -23919,7 +23919,7 @@
       </c>
       <c r="P307" s="4" t="inlineStr">
         <is>
-          <t>2026-09-14</t>
+          <t>2026-09-21</t>
         </is>
       </c>
       <c r="Q307" s="4" t="n"/>
@@ -23998,7 +23998,7 @@
       </c>
       <c r="P308" s="4" t="inlineStr">
         <is>
-          <t>2026-09-14</t>
+          <t>2026-09-21</t>
         </is>
       </c>
       <c r="Q308" s="4" t="n"/>
@@ -24077,7 +24077,7 @@
       </c>
       <c r="P309" s="4" t="inlineStr">
         <is>
-          <t>2026-09-14</t>
+          <t>2026-09-21</t>
         </is>
       </c>
       <c r="Q309" s="4" t="n"/>
@@ -24156,7 +24156,7 @@
       </c>
       <c r="P310" s="4" t="inlineStr">
         <is>
-          <t>2026-09-14</t>
+          <t>2026-09-21</t>
         </is>
       </c>
       <c r="Q310" s="4" t="n"/>
@@ -24235,7 +24235,7 @@
       </c>
       <c r="P311" s="4" t="inlineStr">
         <is>
-          <t>2026-09-14</t>
+          <t>2026-09-21</t>
         </is>
       </c>
       <c r="Q311" s="4" t="n"/>
@@ -24314,7 +24314,7 @@
       </c>
       <c r="P312" s="4" t="inlineStr">
         <is>
-          <t>2026-09-14</t>
+          <t>2026-09-21</t>
         </is>
       </c>
       <c r="Q312" s="4" t="n"/>
@@ -24393,7 +24393,7 @@
       </c>
       <c r="P313" s="4" t="inlineStr">
         <is>
-          <t>2026-09-14</t>
+          <t>2026-09-21</t>
         </is>
       </c>
       <c r="Q313" s="4" t="n"/>
@@ -24472,7 +24472,7 @@
       </c>
       <c r="P314" s="4" t="inlineStr">
         <is>
-          <t>2026-09-14</t>
+          <t>2026-09-21</t>
         </is>
       </c>
       <c r="Q314" s="4" t="n"/>
@@ -24551,7 +24551,7 @@
       </c>
       <c r="P315" s="4" t="inlineStr">
         <is>
-          <t>2026-09-14</t>
+          <t>2026-09-21</t>
         </is>
       </c>
       <c r="Q315" s="4" t="n"/>
@@ -24630,7 +24630,7 @@
       </c>
       <c r="P316" s="4" t="inlineStr">
         <is>
-          <t>2026-09-14</t>
+          <t>2026-09-21</t>
         </is>
       </c>
       <c r="Q316" s="4" t="n"/>
@@ -24709,7 +24709,7 @@
       </c>
       <c r="P317" s="4" t="inlineStr">
         <is>
-          <t>2026-09-14</t>
+          <t>2026-09-21</t>
         </is>
       </c>
       <c r="Q317" s="4" t="n"/>
@@ -24788,7 +24788,7 @@
       </c>
       <c r="P318" s="4" t="inlineStr">
         <is>
-          <t>2026-09-14</t>
+          <t>2026-09-21</t>
         </is>
       </c>
       <c r="Q318" s="4" t="n"/>
@@ -24867,7 +24867,7 @@
       </c>
       <c r="P319" s="4" t="inlineStr">
         <is>
-          <t>2026-09-14</t>
+          <t>2026-09-21</t>
         </is>
       </c>
       <c r="Q319" s="4" t="n"/>
@@ -24946,7 +24946,7 @@
       </c>
       <c r="P320" s="4" t="inlineStr">
         <is>
-          <t>2026-09-14</t>
+          <t>2026-09-21</t>
         </is>
       </c>
       <c r="Q320" s="4" t="n"/>
@@ -25025,7 +25025,7 @@
       </c>
       <c r="P321" s="4" t="inlineStr">
         <is>
-          <t>2026-09-14</t>
+          <t>2026-09-21</t>
         </is>
       </c>
       <c r="Q321" s="4" t="n"/>
@@ -25104,7 +25104,7 @@
       </c>
       <c r="P322" s="4" t="inlineStr">
         <is>
-          <t>2026-09-14</t>
+          <t>2026-09-21</t>
         </is>
       </c>
       <c r="Q322" s="4" t="n"/>
@@ -25183,7 +25183,7 @@
       </c>
       <c r="P323" s="4" t="inlineStr">
         <is>
-          <t>2026-09-14</t>
+          <t>2026-09-21</t>
         </is>
       </c>
       <c r="Q323" s="4" t="n"/>
@@ -25262,7 +25262,7 @@
       </c>
       <c r="P324" s="4" t="inlineStr">
         <is>
-          <t>2026-09-14</t>
+          <t>2026-09-21</t>
         </is>
       </c>
       <c r="Q324" s="4" t="n"/>
@@ -25341,7 +25341,7 @@
       </c>
       <c r="P325" s="4" t="inlineStr">
         <is>
-          <t>2026-09-14</t>
+          <t>2026-09-21</t>
         </is>
       </c>
       <c r="Q325" s="4" t="n"/>
@@ -25420,7 +25420,7 @@
       </c>
       <c r="P326" s="4" t="inlineStr">
         <is>
-          <t>2026-09-14</t>
+          <t>2026-09-21</t>
         </is>
       </c>
       <c r="Q326" s="4" t="n"/>
@@ -25497,7 +25497,7 @@
       </c>
       <c r="P327" s="4" t="inlineStr">
         <is>
-          <t>2026-09-14</t>
+          <t>2026-09-21</t>
         </is>
       </c>
       <c r="Q327" s="4" t="n"/>
@@ -25574,7 +25574,7 @@
       </c>
       <c r="P328" s="4" t="inlineStr">
         <is>
-          <t>2026-09-14</t>
+          <t>2026-09-21</t>
         </is>
       </c>
       <c r="Q328" s="4" t="n"/>
@@ -25651,7 +25651,7 @@
       </c>
       <c r="P329" s="4" t="inlineStr">
         <is>
-          <t>2026-09-14</t>
+          <t>2026-09-21</t>
         </is>
       </c>
       <c r="Q329" s="4" t="n"/>
@@ -25728,7 +25728,7 @@
       </c>
       <c r="P330" s="4" t="inlineStr">
         <is>
-          <t>2026-09-14</t>
+          <t>2026-09-21</t>
         </is>
       </c>
       <c r="Q330" s="4" t="n"/>
@@ -25805,7 +25805,7 @@
       </c>
       <c r="P331" s="4" t="inlineStr">
         <is>
-          <t>2026-09-14</t>
+          <t>2026-09-21</t>
         </is>
       </c>
       <c r="Q331" s="4" t="n"/>
@@ -25882,7 +25882,7 @@
       </c>
       <c r="P332" s="4" t="inlineStr">
         <is>
-          <t>2026-09-14</t>
+          <t>2026-09-21</t>
         </is>
       </c>
       <c r="Q332" s="4" t="n"/>
@@ -25959,7 +25959,7 @@
       </c>
       <c r="P333" s="4" t="inlineStr">
         <is>
-          <t>2026-09-14</t>
+          <t>2026-09-21</t>
         </is>
       </c>
       <c r="Q333" s="4" t="n"/>
@@ -26036,7 +26036,7 @@
       </c>
       <c r="P334" s="4" t="inlineStr">
         <is>
-          <t>2026-09-14</t>
+          <t>2026-09-21</t>
         </is>
       </c>
       <c r="Q334" s="4" t="n"/>
@@ -26113,7 +26113,7 @@
       </c>
       <c r="P335" s="4" t="inlineStr">
         <is>
-          <t>2026-09-14</t>
+          <t>2026-09-21</t>
         </is>
       </c>
       <c r="Q335" s="4" t="n"/>
@@ -26190,7 +26190,7 @@
       </c>
       <c r="P336" s="4" t="inlineStr">
         <is>
-          <t>2026-09-14</t>
+          <t>2026-09-21</t>
         </is>
       </c>
       <c r="Q336" s="4" t="n"/>
@@ -26275,7 +26275,7 @@
       </c>
       <c r="B9" s="4" t="inlineStr">
         <is>
-          <t>2026-09-14</t>
+          <t>2026-09-21</t>
         </is>
       </c>
     </row>

--- a/assets/data/world-bank/excel/ove_banco_mundial_venezuela_pobreza_y_desigualdad.xlsx
+++ b/assets/data/world-bank/excel/ove_banco_mundial_venezuela_pobreza_y_desigualdad.xlsx
@@ -715,7 +715,7 @@
       </c>
       <c r="P7" s="4" t="inlineStr">
         <is>
-          <t>2026-09-21</t>
+          <t>2026-09-28</t>
         </is>
       </c>
       <c r="Q7" s="4" t="n"/>
@@ -792,7 +792,7 @@
       </c>
       <c r="P8" s="4" t="inlineStr">
         <is>
-          <t>2026-09-21</t>
+          <t>2026-09-28</t>
         </is>
       </c>
       <c r="Q8" s="4" t="n"/>
@@ -869,7 +869,7 @@
       </c>
       <c r="P9" s="4" t="inlineStr">
         <is>
-          <t>2026-09-21</t>
+          <t>2026-09-28</t>
         </is>
       </c>
       <c r="Q9" s="4" t="n"/>
@@ -946,7 +946,7 @@
       </c>
       <c r="P10" s="4" t="inlineStr">
         <is>
-          <t>2026-09-21</t>
+          <t>2026-09-28</t>
         </is>
       </c>
       <c r="Q10" s="4" t="n"/>
@@ -1023,7 +1023,7 @@
       </c>
       <c r="P11" s="4" t="inlineStr">
         <is>
-          <t>2026-09-21</t>
+          <t>2026-09-28</t>
         </is>
       </c>
       <c r="Q11" s="4" t="n"/>
@@ -1100,7 +1100,7 @@
       </c>
       <c r="P12" s="4" t="inlineStr">
         <is>
-          <t>2026-09-21</t>
+          <t>2026-09-28</t>
         </is>
       </c>
       <c r="Q12" s="4" t="n"/>
@@ -1177,7 +1177,7 @@
       </c>
       <c r="P13" s="4" t="inlineStr">
         <is>
-          <t>2026-09-21</t>
+          <t>2026-09-28</t>
         </is>
       </c>
       <c r="Q13" s="4" t="n"/>
@@ -1254,7 +1254,7 @@
       </c>
       <c r="P14" s="4" t="inlineStr">
         <is>
-          <t>2026-09-21</t>
+          <t>2026-09-28</t>
         </is>
       </c>
       <c r="Q14" s="4" t="n"/>
@@ -1331,7 +1331,7 @@
       </c>
       <c r="P15" s="4" t="inlineStr">
         <is>
-          <t>2026-09-21</t>
+          <t>2026-09-28</t>
         </is>
       </c>
       <c r="Q15" s="4" t="n"/>
@@ -1408,7 +1408,7 @@
       </c>
       <c r="P16" s="4" t="inlineStr">
         <is>
-          <t>2026-09-21</t>
+          <t>2026-09-28</t>
         </is>
       </c>
       <c r="Q16" s="4" t="n"/>
@@ -1485,7 +1485,7 @@
       </c>
       <c r="P17" s="4" t="inlineStr">
         <is>
-          <t>2026-09-21</t>
+          <t>2026-09-28</t>
         </is>
       </c>
       <c r="Q17" s="4" t="n"/>
@@ -1562,7 +1562,7 @@
       </c>
       <c r="P18" s="4" t="inlineStr">
         <is>
-          <t>2026-09-21</t>
+          <t>2026-09-28</t>
         </is>
       </c>
       <c r="Q18" s="4" t="n"/>
@@ -1639,7 +1639,7 @@
       </c>
       <c r="P19" s="4" t="inlineStr">
         <is>
-          <t>2026-09-21</t>
+          <t>2026-09-28</t>
         </is>
       </c>
       <c r="Q19" s="4" t="n"/>
@@ -1716,7 +1716,7 @@
       </c>
       <c r="P20" s="4" t="inlineStr">
         <is>
-          <t>2026-09-21</t>
+          <t>2026-09-28</t>
         </is>
       </c>
       <c r="Q20" s="4" t="n"/>
@@ -1793,7 +1793,7 @@
       </c>
       <c r="P21" s="4" t="inlineStr">
         <is>
-          <t>2026-09-21</t>
+          <t>2026-09-28</t>
         </is>
       </c>
       <c r="Q21" s="4" t="n"/>
@@ -1870,7 +1870,7 @@
       </c>
       <c r="P22" s="4" t="inlineStr">
         <is>
-          <t>2026-09-21</t>
+          <t>2026-09-28</t>
         </is>
       </c>
       <c r="Q22" s="4" t="n"/>
@@ -1947,7 +1947,7 @@
       </c>
       <c r="P23" s="4" t="inlineStr">
         <is>
-          <t>2026-09-21</t>
+          <t>2026-09-28</t>
         </is>
       </c>
       <c r="Q23" s="4" t="n"/>
@@ -2024,7 +2024,7 @@
       </c>
       <c r="P24" s="4" t="inlineStr">
         <is>
-          <t>2026-09-21</t>
+          <t>2026-09-28</t>
         </is>
       </c>
       <c r="Q24" s="4" t="n"/>
@@ -2101,7 +2101,7 @@
       </c>
       <c r="P25" s="4" t="inlineStr">
         <is>
-          <t>2026-09-21</t>
+          <t>2026-09-28</t>
         </is>
       </c>
       <c r="Q25" s="4" t="n"/>
@@ -2178,7 +2178,7 @@
       </c>
       <c r="P26" s="4" t="inlineStr">
         <is>
-          <t>2026-09-21</t>
+          <t>2026-09-28</t>
         </is>
       </c>
       <c r="Q26" s="4" t="n"/>
@@ -2255,7 +2255,7 @@
       </c>
       <c r="P27" s="4" t="inlineStr">
         <is>
-          <t>2026-09-21</t>
+          <t>2026-09-28</t>
         </is>
       </c>
       <c r="Q27" s="4" t="n"/>
@@ -2334,7 +2334,7 @@
       </c>
       <c r="P28" s="4" t="inlineStr">
         <is>
-          <t>2026-09-21</t>
+          <t>2026-09-28</t>
         </is>
       </c>
       <c r="Q28" s="4" t="n"/>
@@ -2411,7 +2411,7 @@
       </c>
       <c r="P29" s="4" t="inlineStr">
         <is>
-          <t>2026-09-21</t>
+          <t>2026-09-28</t>
         </is>
       </c>
       <c r="Q29" s="4" t="n"/>
@@ -2488,7 +2488,7 @@
       </c>
       <c r="P30" s="4" t="inlineStr">
         <is>
-          <t>2026-09-21</t>
+          <t>2026-09-28</t>
         </is>
       </c>
       <c r="Q30" s="4" t="n"/>
@@ -2565,7 +2565,7 @@
       </c>
       <c r="P31" s="4" t="inlineStr">
         <is>
-          <t>2026-09-21</t>
+          <t>2026-09-28</t>
         </is>
       </c>
       <c r="Q31" s="4" t="n"/>
@@ -2642,7 +2642,7 @@
       </c>
       <c r="P32" s="4" t="inlineStr">
         <is>
-          <t>2026-09-21</t>
+          <t>2026-09-28</t>
         </is>
       </c>
       <c r="Q32" s="4" t="n"/>
@@ -2719,7 +2719,7 @@
       </c>
       <c r="P33" s="4" t="inlineStr">
         <is>
-          <t>2026-09-21</t>
+          <t>2026-09-28</t>
         </is>
       </c>
       <c r="Q33" s="4" t="n"/>
@@ -2798,7 +2798,7 @@
       </c>
       <c r="P34" s="4" t="inlineStr">
         <is>
-          <t>2026-09-21</t>
+          <t>2026-09-28</t>
         </is>
       </c>
       <c r="Q34" s="4" t="n"/>
@@ -2875,7 +2875,7 @@
       </c>
       <c r="P35" s="4" t="inlineStr">
         <is>
-          <t>2026-09-21</t>
+          <t>2026-09-28</t>
         </is>
       </c>
       <c r="Q35" s="4" t="n"/>
@@ -2954,7 +2954,7 @@
       </c>
       <c r="P36" s="4" t="inlineStr">
         <is>
-          <t>2026-09-21</t>
+          <t>2026-09-28</t>
         </is>
       </c>
       <c r="Q36" s="4" t="n"/>
@@ -3031,7 +3031,7 @@
       </c>
       <c r="P37" s="4" t="inlineStr">
         <is>
-          <t>2026-09-21</t>
+          <t>2026-09-28</t>
         </is>
       </c>
       <c r="Q37" s="4" t="n"/>
@@ -3108,7 +3108,7 @@
       </c>
       <c r="P38" s="4" t="inlineStr">
         <is>
-          <t>2026-09-21</t>
+          <t>2026-09-28</t>
         </is>
       </c>
       <c r="Q38" s="4" t="n"/>
@@ -3187,7 +3187,7 @@
       </c>
       <c r="P39" s="4" t="inlineStr">
         <is>
-          <t>2026-09-21</t>
+          <t>2026-09-28</t>
         </is>
       </c>
       <c r="Q39" s="4" t="n"/>
@@ -3264,7 +3264,7 @@
       </c>
       <c r="P40" s="4" t="inlineStr">
         <is>
-          <t>2026-09-21</t>
+          <t>2026-09-28</t>
         </is>
       </c>
       <c r="Q40" s="4" t="n"/>
@@ -3341,7 +3341,7 @@
       </c>
       <c r="P41" s="4" t="inlineStr">
         <is>
-          <t>2026-09-21</t>
+          <t>2026-09-28</t>
         </is>
       </c>
       <c r="Q41" s="4" t="n"/>
@@ -3420,7 +3420,7 @@
       </c>
       <c r="P42" s="4" t="inlineStr">
         <is>
-          <t>2026-09-21</t>
+          <t>2026-09-28</t>
         </is>
       </c>
       <c r="Q42" s="4" t="n"/>
@@ -3497,7 +3497,7 @@
       </c>
       <c r="P43" s="4" t="inlineStr">
         <is>
-          <t>2026-09-21</t>
+          <t>2026-09-28</t>
         </is>
       </c>
       <c r="Q43" s="4" t="n"/>
@@ -3574,7 +3574,7 @@
       </c>
       <c r="P44" s="4" t="inlineStr">
         <is>
-          <t>2026-09-21</t>
+          <t>2026-09-28</t>
         </is>
       </c>
       <c r="Q44" s="4" t="n"/>
@@ -3653,7 +3653,7 @@
       </c>
       <c r="P45" s="4" t="inlineStr">
         <is>
-          <t>2026-09-21</t>
+          <t>2026-09-28</t>
         </is>
       </c>
       <c r="Q45" s="4" t="n"/>
@@ -3732,7 +3732,7 @@
       </c>
       <c r="P46" s="4" t="inlineStr">
         <is>
-          <t>2026-09-21</t>
+          <t>2026-09-28</t>
         </is>
       </c>
       <c r="Q46" s="4" t="n"/>
@@ -3809,7 +3809,7 @@
       </c>
       <c r="P47" s="4" t="inlineStr">
         <is>
-          <t>2026-09-21</t>
+          <t>2026-09-28</t>
         </is>
       </c>
       <c r="Q47" s="4" t="n"/>
@@ -3888,7 +3888,7 @@
       </c>
       <c r="P48" s="4" t="inlineStr">
         <is>
-          <t>2026-09-21</t>
+          <t>2026-09-28</t>
         </is>
       </c>
       <c r="Q48" s="4" t="n"/>
@@ -3967,7 +3967,7 @@
       </c>
       <c r="P49" s="4" t="inlineStr">
         <is>
-          <t>2026-09-21</t>
+          <t>2026-09-28</t>
         </is>
       </c>
       <c r="Q49" s="4" t="n"/>
@@ -4046,7 +4046,7 @@
       </c>
       <c r="P50" s="4" t="inlineStr">
         <is>
-          <t>2026-09-21</t>
+          <t>2026-09-28</t>
         </is>
       </c>
       <c r="Q50" s="4" t="n"/>
@@ -4125,7 +4125,7 @@
       </c>
       <c r="P51" s="4" t="inlineStr">
         <is>
-          <t>2026-09-21</t>
+          <t>2026-09-28</t>
         </is>
       </c>
       <c r="Q51" s="4" t="n"/>
@@ -4204,7 +4204,7 @@
       </c>
       <c r="P52" s="4" t="inlineStr">
         <is>
-          <t>2026-09-21</t>
+          <t>2026-09-28</t>
         </is>
       </c>
       <c r="Q52" s="4" t="n"/>
@@ -4283,7 +4283,7 @@
       </c>
       <c r="P53" s="4" t="inlineStr">
         <is>
-          <t>2026-09-21</t>
+          <t>2026-09-28</t>
         </is>
       </c>
       <c r="Q53" s="4" t="n"/>
@@ -4360,7 +4360,7 @@
       </c>
       <c r="P54" s="4" t="inlineStr">
         <is>
-          <t>2026-09-21</t>
+          <t>2026-09-28</t>
         </is>
       </c>
       <c r="Q54" s="4" t="n"/>
@@ -4437,7 +4437,7 @@
       </c>
       <c r="P55" s="4" t="inlineStr">
         <is>
-          <t>2026-09-21</t>
+          <t>2026-09-28</t>
         </is>
       </c>
       <c r="Q55" s="4" t="n"/>
@@ -4514,7 +4514,7 @@
       </c>
       <c r="P56" s="4" t="inlineStr">
         <is>
-          <t>2026-09-21</t>
+          <t>2026-09-28</t>
         </is>
       </c>
       <c r="Q56" s="4" t="n"/>
@@ -4591,7 +4591,7 @@
       </c>
       <c r="P57" s="4" t="inlineStr">
         <is>
-          <t>2026-09-21</t>
+          <t>2026-09-28</t>
         </is>
       </c>
       <c r="Q57" s="4" t="n"/>
@@ -4668,7 +4668,7 @@
       </c>
       <c r="P58" s="4" t="inlineStr">
         <is>
-          <t>2026-09-21</t>
+          <t>2026-09-28</t>
         </is>
       </c>
       <c r="Q58" s="4" t="n"/>
@@ -4745,7 +4745,7 @@
       </c>
       <c r="P59" s="4" t="inlineStr">
         <is>
-          <t>2026-09-21</t>
+          <t>2026-09-28</t>
         </is>
       </c>
       <c r="Q59" s="4" t="n"/>
@@ -4822,7 +4822,7 @@
       </c>
       <c r="P60" s="4" t="inlineStr">
         <is>
-          <t>2026-09-21</t>
+          <t>2026-09-28</t>
         </is>
       </c>
       <c r="Q60" s="4" t="n"/>
@@ -4899,7 +4899,7 @@
       </c>
       <c r="P61" s="4" t="inlineStr">
         <is>
-          <t>2026-09-21</t>
+          <t>2026-09-28</t>
         </is>
       </c>
       <c r="Q61" s="4" t="n"/>
@@ -4976,7 +4976,7 @@
       </c>
       <c r="P62" s="4" t="inlineStr">
         <is>
-          <t>2026-09-21</t>
+          <t>2026-09-28</t>
         </is>
       </c>
       <c r="Q62" s="4" t="n"/>
@@ -5053,7 +5053,7 @@
       </c>
       <c r="P63" s="4" t="inlineStr">
         <is>
-          <t>2026-09-21</t>
+          <t>2026-09-28</t>
         </is>
       </c>
       <c r="Q63" s="4" t="n"/>
@@ -5130,7 +5130,7 @@
       </c>
       <c r="P64" s="4" t="inlineStr">
         <is>
-          <t>2026-09-21</t>
+          <t>2026-09-28</t>
         </is>
       </c>
       <c r="Q64" s="4" t="n"/>
@@ -5207,7 +5207,7 @@
       </c>
       <c r="P65" s="4" t="inlineStr">
         <is>
-          <t>2026-09-21</t>
+          <t>2026-09-28</t>
         </is>
       </c>
       <c r="Q65" s="4" t="n"/>
@@ -5284,7 +5284,7 @@
       </c>
       <c r="P66" s="4" t="inlineStr">
         <is>
-          <t>2026-09-21</t>
+          <t>2026-09-28</t>
         </is>
       </c>
       <c r="Q66" s="4" t="n"/>
@@ -5361,7 +5361,7 @@
       </c>
       <c r="P67" s="4" t="inlineStr">
         <is>
-          <t>2026-09-21</t>
+          <t>2026-09-28</t>
         </is>
       </c>
       <c r="Q67" s="4" t="n"/>
@@ -5438,7 +5438,7 @@
       </c>
       <c r="P68" s="4" t="inlineStr">
         <is>
-          <t>2026-09-21</t>
+          <t>2026-09-28</t>
         </is>
       </c>
       <c r="Q68" s="4" t="n"/>
@@ -5515,7 +5515,7 @@
       </c>
       <c r="P69" s="4" t="inlineStr">
         <is>
-          <t>2026-09-21</t>
+          <t>2026-09-28</t>
         </is>
       </c>
       <c r="Q69" s="4" t="n"/>
@@ -5592,7 +5592,7 @@
       </c>
       <c r="P70" s="4" t="inlineStr">
         <is>
-          <t>2026-09-21</t>
+          <t>2026-09-28</t>
         </is>
       </c>
       <c r="Q70" s="4" t="n"/>
@@ -5669,7 +5669,7 @@
       </c>
       <c r="P71" s="4" t="inlineStr">
         <is>
-          <t>2026-09-21</t>
+          <t>2026-09-28</t>
         </is>
       </c>
       <c r="Q71" s="4" t="n"/>
@@ -5746,7 +5746,7 @@
       </c>
       <c r="P72" s="4" t="inlineStr">
         <is>
-          <t>2026-09-21</t>
+          <t>2026-09-28</t>
         </is>
       </c>
       <c r="Q72" s="4" t="n"/>
@@ -5823,7 +5823,7 @@
       </c>
       <c r="P73" s="4" t="inlineStr">
         <is>
-          <t>2026-09-21</t>
+          <t>2026-09-28</t>
         </is>
       </c>
       <c r="Q73" s="4" t="n"/>
@@ -5900,7 +5900,7 @@
       </c>
       <c r="P74" s="4" t="inlineStr">
         <is>
-          <t>2026-09-21</t>
+          <t>2026-09-28</t>
         </is>
       </c>
       <c r="Q74" s="4" t="n"/>
@@ -5977,7 +5977,7 @@
       </c>
       <c r="P75" s="4" t="inlineStr">
         <is>
-          <t>2026-09-21</t>
+          <t>2026-09-28</t>
         </is>
       </c>
       <c r="Q75" s="4" t="n"/>
@@ -6054,7 +6054,7 @@
       </c>
       <c r="P76" s="4" t="inlineStr">
         <is>
-          <t>2026-09-21</t>
+          <t>2026-09-28</t>
         </is>
       </c>
       <c r="Q76" s="4" t="n"/>
@@ -6131,7 +6131,7 @@
       </c>
       <c r="P77" s="4" t="inlineStr">
         <is>
-          <t>2026-09-21</t>
+          <t>2026-09-28</t>
         </is>
       </c>
       <c r="Q77" s="4" t="n"/>
@@ -6208,7 +6208,7 @@
       </c>
       <c r="P78" s="4" t="inlineStr">
         <is>
-          <t>2026-09-21</t>
+          <t>2026-09-28</t>
         </is>
       </c>
       <c r="Q78" s="4" t="n"/>
@@ -6285,7 +6285,7 @@
       </c>
       <c r="P79" s="4" t="inlineStr">
         <is>
-          <t>2026-09-21</t>
+          <t>2026-09-28</t>
         </is>
       </c>
       <c r="Q79" s="4" t="n"/>
@@ -6362,7 +6362,7 @@
       </c>
       <c r="P80" s="4" t="inlineStr">
         <is>
-          <t>2026-09-21</t>
+          <t>2026-09-28</t>
         </is>
       </c>
       <c r="Q80" s="4" t="n"/>
@@ -6439,7 +6439,7 @@
       </c>
       <c r="P81" s="4" t="inlineStr">
         <is>
-          <t>2026-09-21</t>
+          <t>2026-09-28</t>
         </is>
       </c>
       <c r="Q81" s="4" t="n"/>
@@ -6516,7 +6516,7 @@
       </c>
       <c r="P82" s="4" t="inlineStr">
         <is>
-          <t>2026-09-21</t>
+          <t>2026-09-28</t>
         </is>
       </c>
       <c r="Q82" s="4" t="n"/>
@@ -6593,7 +6593,7 @@
       </c>
       <c r="P83" s="4" t="inlineStr">
         <is>
-          <t>2026-09-21</t>
+          <t>2026-09-28</t>
         </is>
       </c>
       <c r="Q83" s="4" t="n"/>
@@ -6670,7 +6670,7 @@
       </c>
       <c r="P84" s="4" t="inlineStr">
         <is>
-          <t>2026-09-21</t>
+          <t>2026-09-28</t>
         </is>
       </c>
       <c r="Q84" s="4" t="n"/>
@@ -6747,7 +6747,7 @@
       </c>
       <c r="P85" s="4" t="inlineStr">
         <is>
-          <t>2026-09-21</t>
+          <t>2026-09-28</t>
         </is>
       </c>
       <c r="Q85" s="4" t="n"/>
@@ -6824,7 +6824,7 @@
       </c>
       <c r="P86" s="4" t="inlineStr">
         <is>
-          <t>2026-09-21</t>
+          <t>2026-09-28</t>
         </is>
       </c>
       <c r="Q86" s="4" t="n"/>
@@ -6901,7 +6901,7 @@
       </c>
       <c r="P87" s="4" t="inlineStr">
         <is>
-          <t>2026-09-21</t>
+          <t>2026-09-28</t>
         </is>
       </c>
       <c r="Q87" s="4" t="n"/>
@@ -6978,7 +6978,7 @@
       </c>
       <c r="P88" s="4" t="inlineStr">
         <is>
-          <t>2026-09-21</t>
+          <t>2026-09-28</t>
         </is>
       </c>
       <c r="Q88" s="4" t="n"/>
@@ -7055,7 +7055,7 @@
       </c>
       <c r="P89" s="4" t="inlineStr">
         <is>
-          <t>2026-09-21</t>
+          <t>2026-09-28</t>
         </is>
       </c>
       <c r="Q89" s="4" t="n"/>
@@ -7132,7 +7132,7 @@
       </c>
       <c r="P90" s="4" t="inlineStr">
         <is>
-          <t>2026-09-21</t>
+          <t>2026-09-28</t>
         </is>
       </c>
       <c r="Q90" s="4" t="n"/>
@@ -7209,7 +7209,7 @@
       </c>
       <c r="P91" s="4" t="inlineStr">
         <is>
-          <t>2026-09-21</t>
+          <t>2026-09-28</t>
         </is>
       </c>
       <c r="Q91" s="4" t="n"/>
@@ -7286,7 +7286,7 @@
       </c>
       <c r="P92" s="4" t="inlineStr">
         <is>
-          <t>2026-09-21</t>
+          <t>2026-09-28</t>
         </is>
       </c>
       <c r="Q92" s="4" t="n"/>
@@ -7363,7 +7363,7 @@
       </c>
       <c r="P93" s="4" t="inlineStr">
         <is>
-          <t>2026-09-21</t>
+          <t>2026-09-28</t>
         </is>
       </c>
       <c r="Q93" s="4" t="n"/>
@@ -7442,7 +7442,7 @@
       </c>
       <c r="P94" s="4" t="inlineStr">
         <is>
-          <t>2026-09-21</t>
+          <t>2026-09-28</t>
         </is>
       </c>
       <c r="Q94" s="4" t="n"/>
@@ -7519,7 +7519,7 @@
       </c>
       <c r="P95" s="4" t="inlineStr">
         <is>
-          <t>2026-09-21</t>
+          <t>2026-09-28</t>
         </is>
       </c>
       <c r="Q95" s="4" t="n"/>
@@ -7596,7 +7596,7 @@
       </c>
       <c r="P96" s="4" t="inlineStr">
         <is>
-          <t>2026-09-21</t>
+          <t>2026-09-28</t>
         </is>
       </c>
       <c r="Q96" s="4" t="n"/>
@@ -7673,7 +7673,7 @@
       </c>
       <c r="P97" s="4" t="inlineStr">
         <is>
-          <t>2026-09-21</t>
+          <t>2026-09-28</t>
         </is>
       </c>
       <c r="Q97" s="4" t="n"/>
@@ -7750,7 +7750,7 @@
       </c>
       <c r="P98" s="4" t="inlineStr">
         <is>
-          <t>2026-09-21</t>
+          <t>2026-09-28</t>
         </is>
       </c>
       <c r="Q98" s="4" t="n"/>
@@ -7827,7 +7827,7 @@
       </c>
       <c r="P99" s="4" t="inlineStr">
         <is>
-          <t>2026-09-21</t>
+          <t>2026-09-28</t>
         </is>
       </c>
       <c r="Q99" s="4" t="n"/>
@@ -7906,7 +7906,7 @@
       </c>
       <c r="P100" s="4" t="inlineStr">
         <is>
-          <t>2026-09-21</t>
+          <t>2026-09-28</t>
         </is>
       </c>
       <c r="Q100" s="4" t="n"/>
@@ -7983,7 +7983,7 @@
       </c>
       <c r="P101" s="4" t="inlineStr">
         <is>
-          <t>2026-09-21</t>
+          <t>2026-09-28</t>
         </is>
       </c>
       <c r="Q101" s="4" t="n"/>
@@ -8062,7 +8062,7 @@
       </c>
       <c r="P102" s="4" t="inlineStr">
         <is>
-          <t>2026-09-21</t>
+          <t>2026-09-28</t>
         </is>
       </c>
       <c r="Q102" s="4" t="n"/>
@@ -8139,7 +8139,7 @@
       </c>
       <c r="P103" s="4" t="inlineStr">
         <is>
-          <t>2026-09-21</t>
+          <t>2026-09-28</t>
         </is>
       </c>
       <c r="Q103" s="4" t="n"/>
@@ -8216,7 +8216,7 @@
       </c>
       <c r="P104" s="4" t="inlineStr">
         <is>
-          <t>2026-09-21</t>
+          <t>2026-09-28</t>
         </is>
       </c>
       <c r="Q104" s="4" t="n"/>
@@ -8295,7 +8295,7 @@
       </c>
       <c r="P105" s="4" t="inlineStr">
         <is>
-          <t>2026-09-21</t>
+          <t>2026-09-28</t>
         </is>
       </c>
       <c r="Q105" s="4" t="n"/>
@@ -8372,7 +8372,7 @@
       </c>
       <c r="P106" s="4" t="inlineStr">
         <is>
-          <t>2026-09-21</t>
+          <t>2026-09-28</t>
         </is>
       </c>
       <c r="Q106" s="4" t="n"/>
@@ -8449,7 +8449,7 @@
       </c>
       <c r="P107" s="4" t="inlineStr">
         <is>
-          <t>2026-09-21</t>
+          <t>2026-09-28</t>
         </is>
       </c>
       <c r="Q107" s="4" t="n"/>
@@ -8528,7 +8528,7 @@
       </c>
       <c r="P108" s="4" t="inlineStr">
         <is>
-          <t>2026-09-21</t>
+          <t>2026-09-28</t>
         </is>
       </c>
       <c r="Q108" s="4" t="n"/>
@@ -8605,7 +8605,7 @@
       </c>
       <c r="P109" s="4" t="inlineStr">
         <is>
-          <t>2026-09-21</t>
+          <t>2026-09-28</t>
         </is>
       </c>
       <c r="Q109" s="4" t="n"/>
@@ -8682,7 +8682,7 @@
       </c>
       <c r="P110" s="4" t="inlineStr">
         <is>
-          <t>2026-09-21</t>
+          <t>2026-09-28</t>
         </is>
       </c>
       <c r="Q110" s="4" t="n"/>
@@ -8761,7 +8761,7 @@
       </c>
       <c r="P111" s="4" t="inlineStr">
         <is>
-          <t>2026-09-21</t>
+          <t>2026-09-28</t>
         </is>
       </c>
       <c r="Q111" s="4" t="n"/>
@@ -8840,7 +8840,7 @@
       </c>
       <c r="P112" s="4" t="inlineStr">
         <is>
-          <t>2026-09-21</t>
+          <t>2026-09-28</t>
         </is>
       </c>
       <c r="Q112" s="4" t="n"/>
@@ -8917,7 +8917,7 @@
       </c>
       <c r="P113" s="4" t="inlineStr">
         <is>
-          <t>2026-09-21</t>
+          <t>2026-09-28</t>
         </is>
       </c>
       <c r="Q113" s="4" t="n"/>
@@ -8996,7 +8996,7 @@
       </c>
       <c r="P114" s="4" t="inlineStr">
         <is>
-          <t>2026-09-21</t>
+          <t>2026-09-28</t>
         </is>
       </c>
       <c r="Q114" s="4" t="n"/>
@@ -9075,7 +9075,7 @@
       </c>
       <c r="P115" s="4" t="inlineStr">
         <is>
-          <t>2026-09-21</t>
+          <t>2026-09-28</t>
         </is>
       </c>
       <c r="Q115" s="4" t="n"/>
@@ -9154,7 +9154,7 @@
       </c>
       <c r="P116" s="4" t="inlineStr">
         <is>
-          <t>2026-09-21</t>
+          <t>2026-09-28</t>
         </is>
       </c>
       <c r="Q116" s="4" t="n"/>
@@ -9233,7 +9233,7 @@
       </c>
       <c r="P117" s="4" t="inlineStr">
         <is>
-          <t>2026-09-21</t>
+          <t>2026-09-28</t>
         </is>
       </c>
       <c r="Q117" s="4" t="n"/>
@@ -9312,7 +9312,7 @@
       </c>
       <c r="P118" s="4" t="inlineStr">
         <is>
-          <t>2026-09-21</t>
+          <t>2026-09-28</t>
         </is>
       </c>
       <c r="Q118" s="4" t="n"/>
@@ -9391,7 +9391,7 @@
       </c>
       <c r="P119" s="4" t="inlineStr">
         <is>
-          <t>2026-09-21</t>
+          <t>2026-09-28</t>
         </is>
       </c>
       <c r="Q119" s="4" t="n"/>
@@ -9468,7 +9468,7 @@
       </c>
       <c r="P120" s="4" t="inlineStr">
         <is>
-          <t>2026-09-21</t>
+          <t>2026-09-28</t>
         </is>
       </c>
       <c r="Q120" s="4" t="n"/>
@@ -9545,7 +9545,7 @@
       </c>
       <c r="P121" s="4" t="inlineStr">
         <is>
-          <t>2026-09-21</t>
+          <t>2026-09-28</t>
         </is>
       </c>
       <c r="Q121" s="4" t="n"/>
@@ -9622,7 +9622,7 @@
       </c>
       <c r="P122" s="4" t="inlineStr">
         <is>
-          <t>2026-09-21</t>
+          <t>2026-09-28</t>
         </is>
       </c>
       <c r="Q122" s="4" t="n"/>
@@ -9699,7 +9699,7 @@
       </c>
       <c r="P123" s="4" t="inlineStr">
         <is>
-          <t>2026-09-21</t>
+          <t>2026-09-28</t>
         </is>
       </c>
       <c r="Q123" s="4" t="n"/>
@@ -9776,7 +9776,7 @@
       </c>
       <c r="P124" s="4" t="inlineStr">
         <is>
-          <t>2026-09-21</t>
+          <t>2026-09-28</t>
         </is>
       </c>
       <c r="Q124" s="4" t="n"/>
@@ -9853,7 +9853,7 @@
       </c>
       <c r="P125" s="4" t="inlineStr">
         <is>
-          <t>2026-09-21</t>
+          <t>2026-09-28</t>
         </is>
       </c>
       <c r="Q125" s="4" t="n"/>
@@ -9930,7 +9930,7 @@
       </c>
       <c r="P126" s="4" t="inlineStr">
         <is>
-          <t>2026-09-21</t>
+          <t>2026-09-28</t>
         </is>
       </c>
       <c r="Q126" s="4" t="n"/>
@@ -10007,7 +10007,7 @@
       </c>
       <c r="P127" s="4" t="inlineStr">
         <is>
-          <t>2026-09-21</t>
+          <t>2026-09-28</t>
         </is>
       </c>
       <c r="Q127" s="4" t="n"/>
@@ -10084,7 +10084,7 @@
       </c>
       <c r="P128" s="4" t="inlineStr">
         <is>
-          <t>2026-09-21</t>
+          <t>2026-09-28</t>
         </is>
       </c>
       <c r="Q128" s="4" t="n"/>
@@ -10161,7 +10161,7 @@
       </c>
       <c r="P129" s="4" t="inlineStr">
         <is>
-          <t>2026-09-21</t>
+          <t>2026-09-28</t>
         </is>
       </c>
       <c r="Q129" s="4" t="n"/>
@@ -10238,7 +10238,7 @@
       </c>
       <c r="P130" s="4" t="inlineStr">
         <is>
-          <t>2026-09-21</t>
+          <t>2026-09-28</t>
         </is>
       </c>
       <c r="Q130" s="4" t="n"/>
@@ -10315,7 +10315,7 @@
       </c>
       <c r="P131" s="4" t="inlineStr">
         <is>
-          <t>2026-09-21</t>
+          <t>2026-09-28</t>
         </is>
       </c>
       <c r="Q131" s="4" t="n"/>
@@ -10392,7 +10392,7 @@
       </c>
       <c r="P132" s="4" t="inlineStr">
         <is>
-          <t>2026-09-21</t>
+          <t>2026-09-28</t>
         </is>
       </c>
       <c r="Q132" s="4" t="n"/>
@@ -10469,7 +10469,7 @@
       </c>
       <c r="P133" s="4" t="inlineStr">
         <is>
-          <t>2026-09-21</t>
+          <t>2026-09-28</t>
         </is>
       </c>
       <c r="Q133" s="4" t="n"/>
@@ -10546,7 +10546,7 @@
       </c>
       <c r="P134" s="4" t="inlineStr">
         <is>
-          <t>2026-09-21</t>
+          <t>2026-09-28</t>
         </is>
       </c>
       <c r="Q134" s="4" t="n"/>
@@ -10623,7 +10623,7 @@
       </c>
       <c r="P135" s="4" t="inlineStr">
         <is>
-          <t>2026-09-21</t>
+          <t>2026-09-28</t>
         </is>
       </c>
       <c r="Q135" s="4" t="n"/>
@@ -10700,7 +10700,7 @@
       </c>
       <c r="P136" s="4" t="inlineStr">
         <is>
-          <t>2026-09-21</t>
+          <t>2026-09-28</t>
         </is>
       </c>
       <c r="Q136" s="4" t="n"/>
@@ -10777,7 +10777,7 @@
       </c>
       <c r="P137" s="4" t="inlineStr">
         <is>
-          <t>2026-09-21</t>
+          <t>2026-09-28</t>
         </is>
       </c>
       <c r="Q137" s="4" t="n"/>
@@ -10854,7 +10854,7 @@
       </c>
       <c r="P138" s="4" t="inlineStr">
         <is>
-          <t>2026-09-21</t>
+          <t>2026-09-28</t>
         </is>
       </c>
       <c r="Q138" s="4" t="n"/>
@@ -10931,7 +10931,7 @@
       </c>
       <c r="P139" s="4" t="inlineStr">
         <is>
-          <t>2026-09-21</t>
+          <t>2026-09-28</t>
         </is>
       </c>
       <c r="Q139" s="4" t="n"/>
@@ -11008,7 +11008,7 @@
       </c>
       <c r="P140" s="4" t="inlineStr">
         <is>
-          <t>2026-09-21</t>
+          <t>2026-09-28</t>
         </is>
       </c>
       <c r="Q140" s="4" t="n"/>
@@ -11085,7 +11085,7 @@
       </c>
       <c r="P141" s="4" t="inlineStr">
         <is>
-          <t>2026-09-21</t>
+          <t>2026-09-28</t>
         </is>
       </c>
       <c r="Q141" s="4" t="n"/>
@@ -11162,7 +11162,7 @@
       </c>
       <c r="P142" s="4" t="inlineStr">
         <is>
-          <t>2026-09-21</t>
+          <t>2026-09-28</t>
         </is>
       </c>
       <c r="Q142" s="4" t="n"/>
@@ -11239,7 +11239,7 @@
       </c>
       <c r="P143" s="4" t="inlineStr">
         <is>
-          <t>2026-09-21</t>
+          <t>2026-09-28</t>
         </is>
       </c>
       <c r="Q143" s="4" t="n"/>
@@ -11316,7 +11316,7 @@
       </c>
       <c r="P144" s="4" t="inlineStr">
         <is>
-          <t>2026-09-21</t>
+          <t>2026-09-28</t>
         </is>
       </c>
       <c r="Q144" s="4" t="n"/>
@@ -11393,7 +11393,7 @@
       </c>
       <c r="P145" s="4" t="inlineStr">
         <is>
-          <t>2026-09-21</t>
+          <t>2026-09-28</t>
         </is>
       </c>
       <c r="Q145" s="4" t="n"/>
@@ -11470,7 +11470,7 @@
       </c>
       <c r="P146" s="4" t="inlineStr">
         <is>
-          <t>2026-09-21</t>
+          <t>2026-09-28</t>
         </is>
       </c>
       <c r="Q146" s="4" t="n"/>
@@ -11547,7 +11547,7 @@
       </c>
       <c r="P147" s="4" t="inlineStr">
         <is>
-          <t>2026-09-21</t>
+          <t>2026-09-28</t>
         </is>
       </c>
       <c r="Q147" s="4" t="n"/>
@@ -11624,7 +11624,7 @@
       </c>
       <c r="P148" s="4" t="inlineStr">
         <is>
-          <t>2026-09-21</t>
+          <t>2026-09-28</t>
         </is>
       </c>
       <c r="Q148" s="4" t="n"/>
@@ -11701,7 +11701,7 @@
       </c>
       <c r="P149" s="4" t="inlineStr">
         <is>
-          <t>2026-09-21</t>
+          <t>2026-09-28</t>
         </is>
       </c>
       <c r="Q149" s="4" t="n"/>
@@ -11778,7 +11778,7 @@
       </c>
       <c r="P150" s="4" t="inlineStr">
         <is>
-          <t>2026-09-21</t>
+          <t>2026-09-28</t>
         </is>
       </c>
       <c r="Q150" s="4" t="n"/>
@@ -11855,7 +11855,7 @@
       </c>
       <c r="P151" s="4" t="inlineStr">
         <is>
-          <t>2026-09-21</t>
+          <t>2026-09-28</t>
         </is>
       </c>
       <c r="Q151" s="4" t="n"/>
@@ -11932,7 +11932,7 @@
       </c>
       <c r="P152" s="4" t="inlineStr">
         <is>
-          <t>2026-09-21</t>
+          <t>2026-09-28</t>
         </is>
       </c>
       <c r="Q152" s="4" t="n"/>
@@ -12009,7 +12009,7 @@
       </c>
       <c r="P153" s="4" t="inlineStr">
         <is>
-          <t>2026-09-21</t>
+          <t>2026-09-28</t>
         </is>
       </c>
       <c r="Q153" s="4" t="n"/>
@@ -12086,7 +12086,7 @@
       </c>
       <c r="P154" s="4" t="inlineStr">
         <is>
-          <t>2026-09-21</t>
+          <t>2026-09-28</t>
         </is>
       </c>
       <c r="Q154" s="4" t="n"/>
@@ -12163,7 +12163,7 @@
       </c>
       <c r="P155" s="4" t="inlineStr">
         <is>
-          <t>2026-09-21</t>
+          <t>2026-09-28</t>
         </is>
       </c>
       <c r="Q155" s="4" t="n"/>
@@ -12240,7 +12240,7 @@
       </c>
       <c r="P156" s="4" t="inlineStr">
         <is>
-          <t>2026-09-21</t>
+          <t>2026-09-28</t>
         </is>
       </c>
       <c r="Q156" s="4" t="n"/>
@@ -12317,7 +12317,7 @@
       </c>
       <c r="P157" s="4" t="inlineStr">
         <is>
-          <t>2026-09-21</t>
+          <t>2026-09-28</t>
         </is>
       </c>
       <c r="Q157" s="4" t="n"/>
@@ -12394,7 +12394,7 @@
       </c>
       <c r="P158" s="4" t="inlineStr">
         <is>
-          <t>2026-09-21</t>
+          <t>2026-09-28</t>
         </is>
       </c>
       <c r="Q158" s="4" t="n"/>
@@ -12471,7 +12471,7 @@
       </c>
       <c r="P159" s="4" t="inlineStr">
         <is>
-          <t>2026-09-21</t>
+          <t>2026-09-28</t>
         </is>
       </c>
       <c r="Q159" s="4" t="n"/>
@@ -12550,7 +12550,7 @@
       </c>
       <c r="P160" s="4" t="inlineStr">
         <is>
-          <t>2026-09-21</t>
+          <t>2026-09-28</t>
         </is>
       </c>
       <c r="Q160" s="4" t="n"/>
@@ -12627,7 +12627,7 @@
       </c>
       <c r="P161" s="4" t="inlineStr">
         <is>
-          <t>2026-09-21</t>
+          <t>2026-09-28</t>
         </is>
       </c>
       <c r="Q161" s="4" t="n"/>
@@ -12704,7 +12704,7 @@
       </c>
       <c r="P162" s="4" t="inlineStr">
         <is>
-          <t>2026-09-21</t>
+          <t>2026-09-28</t>
         </is>
       </c>
       <c r="Q162" s="4" t="n"/>
@@ -12781,7 +12781,7 @@
       </c>
       <c r="P163" s="4" t="inlineStr">
         <is>
-          <t>2026-09-21</t>
+          <t>2026-09-28</t>
         </is>
       </c>
       <c r="Q163" s="4" t="n"/>
@@ -12858,7 +12858,7 @@
       </c>
       <c r="P164" s="4" t="inlineStr">
         <is>
-          <t>2026-09-21</t>
+          <t>2026-09-28</t>
         </is>
       </c>
       <c r="Q164" s="4" t="n"/>
@@ -12935,7 +12935,7 @@
       </c>
       <c r="P165" s="4" t="inlineStr">
         <is>
-          <t>2026-09-21</t>
+          <t>2026-09-28</t>
         </is>
       </c>
       <c r="Q165" s="4" t="n"/>
@@ -13014,7 +13014,7 @@
       </c>
       <c r="P166" s="4" t="inlineStr">
         <is>
-          <t>2026-09-21</t>
+          <t>2026-09-28</t>
         </is>
       </c>
       <c r="Q166" s="4" t="n"/>
@@ -13091,7 +13091,7 @@
       </c>
       <c r="P167" s="4" t="inlineStr">
         <is>
-          <t>2026-09-21</t>
+          <t>2026-09-28</t>
         </is>
       </c>
       <c r="Q167" s="4" t="n"/>
@@ -13170,7 +13170,7 @@
       </c>
       <c r="P168" s="4" t="inlineStr">
         <is>
-          <t>2026-09-21</t>
+          <t>2026-09-28</t>
         </is>
       </c>
       <c r="Q168" s="4" t="n"/>
@@ -13247,7 +13247,7 @@
       </c>
       <c r="P169" s="4" t="inlineStr">
         <is>
-          <t>2026-09-21</t>
+          <t>2026-09-28</t>
         </is>
       </c>
       <c r="Q169" s="4" t="n"/>
@@ -13324,7 +13324,7 @@
       </c>
       <c r="P170" s="4" t="inlineStr">
         <is>
-          <t>2026-09-21</t>
+          <t>2026-09-28</t>
         </is>
       </c>
       <c r="Q170" s="4" t="n"/>
@@ -13403,7 +13403,7 @@
       </c>
       <c r="P171" s="4" t="inlineStr">
         <is>
-          <t>2026-09-21</t>
+          <t>2026-09-28</t>
         </is>
       </c>
       <c r="Q171" s="4" t="n"/>
@@ -13480,7 +13480,7 @@
       </c>
       <c r="P172" s="4" t="inlineStr">
         <is>
-          <t>2026-09-21</t>
+          <t>2026-09-28</t>
         </is>
       </c>
       <c r="Q172" s="4" t="n"/>
@@ -13557,7 +13557,7 @@
       </c>
       <c r="P173" s="4" t="inlineStr">
         <is>
-          <t>2026-09-21</t>
+          <t>2026-09-28</t>
         </is>
       </c>
       <c r="Q173" s="4" t="n"/>
@@ -13636,7 +13636,7 @@
       </c>
       <c r="P174" s="4" t="inlineStr">
         <is>
-          <t>2026-09-21</t>
+          <t>2026-09-28</t>
         </is>
       </c>
       <c r="Q174" s="4" t="n"/>
@@ -13713,7 +13713,7 @@
       </c>
       <c r="P175" s="4" t="inlineStr">
         <is>
-          <t>2026-09-21</t>
+          <t>2026-09-28</t>
         </is>
       </c>
       <c r="Q175" s="4" t="n"/>
@@ -13790,7 +13790,7 @@
       </c>
       <c r="P176" s="4" t="inlineStr">
         <is>
-          <t>2026-09-21</t>
+          <t>2026-09-28</t>
         </is>
       </c>
       <c r="Q176" s="4" t="n"/>
@@ -13869,7 +13869,7 @@
       </c>
       <c r="P177" s="4" t="inlineStr">
         <is>
-          <t>2026-09-21</t>
+          <t>2026-09-28</t>
         </is>
       </c>
       <c r="Q177" s="4" t="n"/>
@@ -13948,7 +13948,7 @@
       </c>
       <c r="P178" s="4" t="inlineStr">
         <is>
-          <t>2026-09-21</t>
+          <t>2026-09-28</t>
         </is>
       </c>
       <c r="Q178" s="4" t="n"/>
@@ -14025,7 +14025,7 @@
       </c>
       <c r="P179" s="4" t="inlineStr">
         <is>
-          <t>2026-09-21</t>
+          <t>2026-09-28</t>
         </is>
       </c>
       <c r="Q179" s="4" t="n"/>
@@ -14104,7 +14104,7 @@
       </c>
       <c r="P180" s="4" t="inlineStr">
         <is>
-          <t>2026-09-21</t>
+          <t>2026-09-28</t>
         </is>
       </c>
       <c r="Q180" s="4" t="n"/>
@@ -14183,7 +14183,7 @@
       </c>
       <c r="P181" s="4" t="inlineStr">
         <is>
-          <t>2026-09-21</t>
+          <t>2026-09-28</t>
         </is>
       </c>
       <c r="Q181" s="4" t="n"/>
@@ -14262,7 +14262,7 @@
       </c>
       <c r="P182" s="4" t="inlineStr">
         <is>
-          <t>2026-09-21</t>
+          <t>2026-09-28</t>
         </is>
       </c>
       <c r="Q182" s="4" t="n"/>
@@ -14341,7 +14341,7 @@
       </c>
       <c r="P183" s="4" t="inlineStr">
         <is>
-          <t>2026-09-21</t>
+          <t>2026-09-28</t>
         </is>
       </c>
       <c r="Q183" s="4" t="n"/>
@@ -14420,7 +14420,7 @@
       </c>
       <c r="P184" s="4" t="inlineStr">
         <is>
-          <t>2026-09-21</t>
+          <t>2026-09-28</t>
         </is>
       </c>
       <c r="Q184" s="4" t="n"/>
@@ -14499,7 +14499,7 @@
       </c>
       <c r="P185" s="4" t="inlineStr">
         <is>
-          <t>2026-09-21</t>
+          <t>2026-09-28</t>
         </is>
       </c>
       <c r="Q185" s="4" t="n"/>
@@ -14576,7 +14576,7 @@
       </c>
       <c r="P186" s="4" t="inlineStr">
         <is>
-          <t>2026-09-21</t>
+          <t>2026-09-28</t>
         </is>
       </c>
       <c r="Q186" s="4" t="n"/>
@@ -14653,7 +14653,7 @@
       </c>
       <c r="P187" s="4" t="inlineStr">
         <is>
-          <t>2026-09-21</t>
+          <t>2026-09-28</t>
         </is>
       </c>
       <c r="Q187" s="4" t="n"/>
@@ -14730,7 +14730,7 @@
       </c>
       <c r="P188" s="4" t="inlineStr">
         <is>
-          <t>2026-09-21</t>
+          <t>2026-09-28</t>
         </is>
       </c>
       <c r="Q188" s="4" t="n"/>
@@ -14807,7 +14807,7 @@
       </c>
       <c r="P189" s="4" t="inlineStr">
         <is>
-          <t>2026-09-21</t>
+          <t>2026-09-28</t>
         </is>
       </c>
       <c r="Q189" s="4" t="n"/>
@@ -14884,7 +14884,7 @@
       </c>
       <c r="P190" s="4" t="inlineStr">
         <is>
-          <t>2026-09-21</t>
+          <t>2026-09-28</t>
         </is>
       </c>
       <c r="Q190" s="4" t="n"/>
@@ -14961,7 +14961,7 @@
       </c>
       <c r="P191" s="4" t="inlineStr">
         <is>
-          <t>2026-09-21</t>
+          <t>2026-09-28</t>
         </is>
       </c>
       <c r="Q191" s="4" t="n"/>
@@ -15038,7 +15038,7 @@
       </c>
       <c r="P192" s="4" t="inlineStr">
         <is>
-          <t>2026-09-21</t>
+          <t>2026-09-28</t>
         </is>
       </c>
       <c r="Q192" s="4" t="n"/>
@@ -15115,7 +15115,7 @@
       </c>
       <c r="P193" s="4" t="inlineStr">
         <is>
-          <t>2026-09-21</t>
+          <t>2026-09-28</t>
         </is>
       </c>
       <c r="Q193" s="4" t="n"/>
@@ -15192,7 +15192,7 @@
       </c>
       <c r="P194" s="4" t="inlineStr">
         <is>
-          <t>2026-09-21</t>
+          <t>2026-09-28</t>
         </is>
       </c>
       <c r="Q194" s="4" t="n"/>
@@ -15269,7 +15269,7 @@
       </c>
       <c r="P195" s="4" t="inlineStr">
         <is>
-          <t>2026-09-21</t>
+          <t>2026-09-28</t>
         </is>
       </c>
       <c r="Q195" s="4" t="n"/>
@@ -15346,7 +15346,7 @@
       </c>
       <c r="P196" s="4" t="inlineStr">
         <is>
-          <t>2026-09-21</t>
+          <t>2026-09-28</t>
         </is>
       </c>
       <c r="Q196" s="4" t="n"/>
@@ -15423,7 +15423,7 @@
       </c>
       <c r="P197" s="4" t="inlineStr">
         <is>
-          <t>2026-09-21</t>
+          <t>2026-09-28</t>
         </is>
       </c>
       <c r="Q197" s="4" t="n"/>
@@ -15500,7 +15500,7 @@
       </c>
       <c r="P198" s="4" t="inlineStr">
         <is>
-          <t>2026-09-21</t>
+          <t>2026-09-28</t>
         </is>
       </c>
       <c r="Q198" s="4" t="n"/>
@@ -15577,7 +15577,7 @@
       </c>
       <c r="P199" s="4" t="inlineStr">
         <is>
-          <t>2026-09-21</t>
+          <t>2026-09-28</t>
         </is>
       </c>
       <c r="Q199" s="4" t="n"/>
@@ -15654,7 +15654,7 @@
       </c>
       <c r="P200" s="4" t="inlineStr">
         <is>
-          <t>2026-09-21</t>
+          <t>2026-09-28</t>
         </is>
       </c>
       <c r="Q200" s="4" t="n"/>
@@ -15731,7 +15731,7 @@
       </c>
       <c r="P201" s="4" t="inlineStr">
         <is>
-          <t>2026-09-21</t>
+          <t>2026-09-28</t>
         </is>
       </c>
       <c r="Q201" s="4" t="n"/>
@@ -15808,7 +15808,7 @@
       </c>
       <c r="P202" s="4" t="inlineStr">
         <is>
-          <t>2026-09-21</t>
+          <t>2026-09-28</t>
         </is>
       </c>
       <c r="Q202" s="4" t="n"/>
@@ -15885,7 +15885,7 @@
       </c>
       <c r="P203" s="4" t="inlineStr">
         <is>
-          <t>2026-09-21</t>
+          <t>2026-09-28</t>
         </is>
       </c>
       <c r="Q203" s="4" t="n"/>
@@ -15962,7 +15962,7 @@
       </c>
       <c r="P204" s="4" t="inlineStr">
         <is>
-          <t>2026-09-21</t>
+          <t>2026-09-28</t>
         </is>
       </c>
       <c r="Q204" s="4" t="n"/>
@@ -16039,7 +16039,7 @@
       </c>
       <c r="P205" s="4" t="inlineStr">
         <is>
-          <t>2026-09-21</t>
+          <t>2026-09-28</t>
         </is>
       </c>
       <c r="Q205" s="4" t="n"/>
@@ -16116,7 +16116,7 @@
       </c>
       <c r="P206" s="4" t="inlineStr">
         <is>
-          <t>2026-09-21</t>
+          <t>2026-09-28</t>
         </is>
       </c>
       <c r="Q206" s="4" t="n"/>
@@ -16193,7 +16193,7 @@
       </c>
       <c r="P207" s="4" t="inlineStr">
         <is>
-          <t>2026-09-21</t>
+          <t>2026-09-28</t>
         </is>
       </c>
       <c r="Q207" s="4" t="n"/>
@@ -16270,7 +16270,7 @@
       </c>
       <c r="P208" s="4" t="inlineStr">
         <is>
-          <t>2026-09-21</t>
+          <t>2026-09-28</t>
         </is>
       </c>
       <c r="Q208" s="4" t="n"/>
@@ -16347,7 +16347,7 @@
       </c>
       <c r="P209" s="4" t="inlineStr">
         <is>
-          <t>2026-09-21</t>
+          <t>2026-09-28</t>
         </is>
       </c>
       <c r="Q209" s="4" t="n"/>
@@ -16424,7 +16424,7 @@
       </c>
       <c r="P210" s="4" t="inlineStr">
         <is>
-          <t>2026-09-21</t>
+          <t>2026-09-28</t>
         </is>
       </c>
       <c r="Q210" s="4" t="n"/>
@@ -16501,7 +16501,7 @@
       </c>
       <c r="P211" s="4" t="inlineStr">
         <is>
-          <t>2026-09-21</t>
+          <t>2026-09-28</t>
         </is>
       </c>
       <c r="Q211" s="4" t="n"/>
@@ -16578,7 +16578,7 @@
       </c>
       <c r="P212" s="4" t="inlineStr">
         <is>
-          <t>2026-09-21</t>
+          <t>2026-09-28</t>
         </is>
       </c>
       <c r="Q212" s="4" t="n"/>
@@ -16655,7 +16655,7 @@
       </c>
       <c r="P213" s="4" t="inlineStr">
         <is>
-          <t>2026-09-21</t>
+          <t>2026-09-28</t>
         </is>
       </c>
       <c r="Q213" s="4" t="n"/>
@@ -16732,7 +16732,7 @@
       </c>
       <c r="P214" s="4" t="inlineStr">
         <is>
-          <t>2026-09-21</t>
+          <t>2026-09-28</t>
         </is>
       </c>
       <c r="Q214" s="4" t="n"/>
@@ -16809,7 +16809,7 @@
       </c>
       <c r="P215" s="4" t="inlineStr">
         <is>
-          <t>2026-09-21</t>
+          <t>2026-09-28</t>
         </is>
       </c>
       <c r="Q215" s="4" t="n"/>
@@ -16886,7 +16886,7 @@
       </c>
       <c r="P216" s="4" t="inlineStr">
         <is>
-          <t>2026-09-21</t>
+          <t>2026-09-28</t>
         </is>
       </c>
       <c r="Q216" s="4" t="n"/>
@@ -16963,7 +16963,7 @@
       </c>
       <c r="P217" s="4" t="inlineStr">
         <is>
-          <t>2026-09-21</t>
+          <t>2026-09-28</t>
         </is>
       </c>
       <c r="Q217" s="4" t="n"/>
@@ -17040,7 +17040,7 @@
       </c>
       <c r="P218" s="4" t="inlineStr">
         <is>
-          <t>2026-09-21</t>
+          <t>2026-09-28</t>
         </is>
       </c>
       <c r="Q218" s="4" t="n"/>
@@ -17117,7 +17117,7 @@
       </c>
       <c r="P219" s="4" t="inlineStr">
         <is>
-          <t>2026-09-21</t>
+          <t>2026-09-28</t>
         </is>
       </c>
       <c r="Q219" s="4" t="n"/>
@@ -17194,7 +17194,7 @@
       </c>
       <c r="P220" s="4" t="inlineStr">
         <is>
-          <t>2026-09-21</t>
+          <t>2026-09-28</t>
         </is>
       </c>
       <c r="Q220" s="4" t="n"/>
@@ -17271,7 +17271,7 @@
       </c>
       <c r="P221" s="4" t="inlineStr">
         <is>
-          <t>2026-09-21</t>
+          <t>2026-09-28</t>
         </is>
       </c>
       <c r="Q221" s="4" t="n"/>
@@ -17348,7 +17348,7 @@
       </c>
       <c r="P222" s="4" t="inlineStr">
         <is>
-          <t>2026-09-21</t>
+          <t>2026-09-28</t>
         </is>
       </c>
       <c r="Q222" s="4" t="n"/>
@@ -17425,7 +17425,7 @@
       </c>
       <c r="P223" s="4" t="inlineStr">
         <is>
-          <t>2026-09-21</t>
+          <t>2026-09-28</t>
         </is>
       </c>
       <c r="Q223" s="4" t="n"/>
@@ -17502,7 +17502,7 @@
       </c>
       <c r="P224" s="4" t="inlineStr">
         <is>
-          <t>2026-09-21</t>
+          <t>2026-09-28</t>
         </is>
       </c>
       <c r="Q224" s="4" t="n"/>
@@ -17579,7 +17579,7 @@
       </c>
       <c r="P225" s="4" t="inlineStr">
         <is>
-          <t>2026-09-21</t>
+          <t>2026-09-28</t>
         </is>
       </c>
       <c r="Q225" s="4" t="n"/>
@@ -17658,7 +17658,7 @@
       </c>
       <c r="P226" s="4" t="inlineStr">
         <is>
-          <t>2026-09-21</t>
+          <t>2026-09-28</t>
         </is>
       </c>
       <c r="Q226" s="4" t="n"/>
@@ -17735,7 +17735,7 @@
       </c>
       <c r="P227" s="4" t="inlineStr">
         <is>
-          <t>2026-09-21</t>
+          <t>2026-09-28</t>
         </is>
       </c>
       <c r="Q227" s="4" t="n"/>
@@ -17812,7 +17812,7 @@
       </c>
       <c r="P228" s="4" t="inlineStr">
         <is>
-          <t>2026-09-21</t>
+          <t>2026-09-28</t>
         </is>
       </c>
       <c r="Q228" s="4" t="n"/>
@@ -17889,7 +17889,7 @@
       </c>
       <c r="P229" s="4" t="inlineStr">
         <is>
-          <t>2026-09-21</t>
+          <t>2026-09-28</t>
         </is>
       </c>
       <c r="Q229" s="4" t="n"/>
@@ -17966,7 +17966,7 @@
       </c>
       <c r="P230" s="4" t="inlineStr">
         <is>
-          <t>2026-09-21</t>
+          <t>2026-09-28</t>
         </is>
       </c>
       <c r="Q230" s="4" t="n"/>
@@ -18043,7 +18043,7 @@
       </c>
       <c r="P231" s="4" t="inlineStr">
         <is>
-          <t>2026-09-21</t>
+          <t>2026-09-28</t>
         </is>
       </c>
       <c r="Q231" s="4" t="n"/>
@@ -18122,7 +18122,7 @@
       </c>
       <c r="P232" s="4" t="inlineStr">
         <is>
-          <t>2026-09-21</t>
+          <t>2026-09-28</t>
         </is>
       </c>
       <c r="Q232" s="4" t="n"/>
@@ -18199,7 +18199,7 @@
       </c>
       <c r="P233" s="4" t="inlineStr">
         <is>
-          <t>2026-09-21</t>
+          <t>2026-09-28</t>
         </is>
       </c>
       <c r="Q233" s="4" t="n"/>
@@ -18278,7 +18278,7 @@
       </c>
       <c r="P234" s="4" t="inlineStr">
         <is>
-          <t>2026-09-21</t>
+          <t>2026-09-28</t>
         </is>
       </c>
       <c r="Q234" s="4" t="n"/>
@@ -18355,7 +18355,7 @@
       </c>
       <c r="P235" s="4" t="inlineStr">
         <is>
-          <t>2026-09-21</t>
+          <t>2026-09-28</t>
         </is>
       </c>
       <c r="Q235" s="4" t="n"/>
@@ -18432,7 +18432,7 @@
       </c>
       <c r="P236" s="4" t="inlineStr">
         <is>
-          <t>2026-09-21</t>
+          <t>2026-09-28</t>
         </is>
       </c>
       <c r="Q236" s="4" t="n"/>
@@ -18511,7 +18511,7 @@
       </c>
       <c r="P237" s="4" t="inlineStr">
         <is>
-          <t>2026-09-21</t>
+          <t>2026-09-28</t>
         </is>
       </c>
       <c r="Q237" s="4" t="n"/>
@@ -18588,7 +18588,7 @@
       </c>
       <c r="P238" s="4" t="inlineStr">
         <is>
-          <t>2026-09-21</t>
+          <t>2026-09-28</t>
         </is>
       </c>
       <c r="Q238" s="4" t="n"/>
@@ -18665,7 +18665,7 @@
       </c>
       <c r="P239" s="4" t="inlineStr">
         <is>
-          <t>2026-09-21</t>
+          <t>2026-09-28</t>
         </is>
       </c>
       <c r="Q239" s="4" t="n"/>
@@ -18744,7 +18744,7 @@
       </c>
       <c r="P240" s="4" t="inlineStr">
         <is>
-          <t>2026-09-21</t>
+          <t>2026-09-28</t>
         </is>
       </c>
       <c r="Q240" s="4" t="n"/>
@@ -18821,7 +18821,7 @@
       </c>
       <c r="P241" s="4" t="inlineStr">
         <is>
-          <t>2026-09-21</t>
+          <t>2026-09-28</t>
         </is>
       </c>
       <c r="Q241" s="4" t="n"/>
@@ -18898,7 +18898,7 @@
       </c>
       <c r="P242" s="4" t="inlineStr">
         <is>
-          <t>2026-09-21</t>
+          <t>2026-09-28</t>
         </is>
       </c>
       <c r="Q242" s="4" t="n"/>
@@ -18977,7 +18977,7 @@
       </c>
       <c r="P243" s="4" t="inlineStr">
         <is>
-          <t>2026-09-21</t>
+          <t>2026-09-28</t>
         </is>
       </c>
       <c r="Q243" s="4" t="n"/>
@@ -19056,7 +19056,7 @@
       </c>
       <c r="P244" s="4" t="inlineStr">
         <is>
-          <t>2026-09-21</t>
+          <t>2026-09-28</t>
         </is>
       </c>
       <c r="Q244" s="4" t="n"/>
@@ -19133,7 +19133,7 @@
       </c>
       <c r="P245" s="4" t="inlineStr">
         <is>
-          <t>2026-09-21</t>
+          <t>2026-09-28</t>
         </is>
       </c>
       <c r="Q245" s="4" t="n"/>
@@ -19212,7 +19212,7 @@
       </c>
       <c r="P246" s="4" t="inlineStr">
         <is>
-          <t>2026-09-21</t>
+          <t>2026-09-28</t>
         </is>
       </c>
       <c r="Q246" s="4" t="n"/>
@@ -19291,7 +19291,7 @@
       </c>
       <c r="P247" s="4" t="inlineStr">
         <is>
-          <t>2026-09-21</t>
+          <t>2026-09-28</t>
         </is>
       </c>
       <c r="Q247" s="4" t="n"/>
@@ -19370,7 +19370,7 @@
       </c>
       <c r="P248" s="4" t="inlineStr">
         <is>
-          <t>2026-09-21</t>
+          <t>2026-09-28</t>
         </is>
       </c>
       <c r="Q248" s="4" t="n"/>
@@ -19449,7 +19449,7 @@
       </c>
       <c r="P249" s="4" t="inlineStr">
         <is>
-          <t>2026-09-21</t>
+          <t>2026-09-28</t>
         </is>
       </c>
       <c r="Q249" s="4" t="n"/>
@@ -19528,7 +19528,7 @@
       </c>
       <c r="P250" s="4" t="inlineStr">
         <is>
-          <t>2026-09-21</t>
+          <t>2026-09-28</t>
         </is>
       </c>
       <c r="Q250" s="4" t="n"/>
@@ -19607,7 +19607,7 @@
       </c>
       <c r="P251" s="4" t="inlineStr">
         <is>
-          <t>2026-09-21</t>
+          <t>2026-09-28</t>
         </is>
       </c>
       <c r="Q251" s="4" t="n"/>
@@ -19684,7 +19684,7 @@
       </c>
       <c r="P252" s="4" t="inlineStr">
         <is>
-          <t>2026-09-21</t>
+          <t>2026-09-28</t>
         </is>
       </c>
       <c r="Q252" s="4" t="n"/>
@@ -19761,7 +19761,7 @@
       </c>
       <c r="P253" s="4" t="inlineStr">
         <is>
-          <t>2026-09-21</t>
+          <t>2026-09-28</t>
         </is>
       </c>
       <c r="Q253" s="4" t="n"/>
@@ -19838,7 +19838,7 @@
       </c>
       <c r="P254" s="4" t="inlineStr">
         <is>
-          <t>2026-09-21</t>
+          <t>2026-09-28</t>
         </is>
       </c>
       <c r="Q254" s="4" t="n"/>
@@ -19915,7 +19915,7 @@
       </c>
       <c r="P255" s="4" t="inlineStr">
         <is>
-          <t>2026-09-21</t>
+          <t>2026-09-28</t>
         </is>
       </c>
       <c r="Q255" s="4" t="n"/>
@@ -19992,7 +19992,7 @@
       </c>
       <c r="P256" s="4" t="inlineStr">
         <is>
-          <t>2026-09-21</t>
+          <t>2026-09-28</t>
         </is>
       </c>
       <c r="Q256" s="4" t="n"/>
@@ -20069,7 +20069,7 @@
       </c>
       <c r="P257" s="4" t="inlineStr">
         <is>
-          <t>2026-09-21</t>
+          <t>2026-09-28</t>
         </is>
       </c>
       <c r="Q257" s="4" t="n"/>
@@ -20146,7 +20146,7 @@
       </c>
       <c r="P258" s="4" t="inlineStr">
         <is>
-          <t>2026-09-21</t>
+          <t>2026-09-28</t>
         </is>
       </c>
       <c r="Q258" s="4" t="n"/>
@@ -20223,7 +20223,7 @@
       </c>
       <c r="P259" s="4" t="inlineStr">
         <is>
-          <t>2026-09-21</t>
+          <t>2026-09-28</t>
         </is>
       </c>
       <c r="Q259" s="4" t="n"/>
@@ -20300,7 +20300,7 @@
       </c>
       <c r="P260" s="4" t="inlineStr">
         <is>
-          <t>2026-09-21</t>
+          <t>2026-09-28</t>
         </is>
       </c>
       <c r="Q260" s="4" t="n"/>
@@ -20377,7 +20377,7 @@
       </c>
       <c r="P261" s="4" t="inlineStr">
         <is>
-          <t>2026-09-21</t>
+          <t>2026-09-28</t>
         </is>
       </c>
       <c r="Q261" s="4" t="n"/>
@@ -20454,7 +20454,7 @@
       </c>
       <c r="P262" s="4" t="inlineStr">
         <is>
-          <t>2026-09-21</t>
+          <t>2026-09-28</t>
         </is>
       </c>
       <c r="Q262" s="4" t="n"/>
@@ -20531,7 +20531,7 @@
       </c>
       <c r="P263" s="4" t="inlineStr">
         <is>
-          <t>2026-09-21</t>
+          <t>2026-09-28</t>
         </is>
       </c>
       <c r="Q263" s="4" t="n"/>
@@ -20608,7 +20608,7 @@
       </c>
       <c r="P264" s="4" t="inlineStr">
         <is>
-          <t>2026-09-21</t>
+          <t>2026-09-28</t>
         </is>
       </c>
       <c r="Q264" s="4" t="n"/>
@@ -20685,7 +20685,7 @@
       </c>
       <c r="P265" s="4" t="inlineStr">
         <is>
-          <t>2026-09-21</t>
+          <t>2026-09-28</t>
         </is>
       </c>
       <c r="Q265" s="4" t="n"/>
@@ -20762,7 +20762,7 @@
       </c>
       <c r="P266" s="4" t="inlineStr">
         <is>
-          <t>2026-09-21</t>
+          <t>2026-09-28</t>
         </is>
       </c>
       <c r="Q266" s="4" t="n"/>
@@ -20839,7 +20839,7 @@
       </c>
       <c r="P267" s="4" t="inlineStr">
         <is>
-          <t>2026-09-21</t>
+          <t>2026-09-28</t>
         </is>
       </c>
       <c r="Q267" s="4" t="n"/>
@@ -20916,7 +20916,7 @@
       </c>
       <c r="P268" s="4" t="inlineStr">
         <is>
-          <t>2026-09-21</t>
+          <t>2026-09-28</t>
         </is>
       </c>
       <c r="Q268" s="4" t="n"/>
@@ -20993,7 +20993,7 @@
       </c>
       <c r="P269" s="4" t="inlineStr">
         <is>
-          <t>2026-09-21</t>
+          <t>2026-09-28</t>
         </is>
       </c>
       <c r="Q269" s="4" t="n"/>
@@ -21070,7 +21070,7 @@
       </c>
       <c r="P270" s="4" t="inlineStr">
         <is>
-          <t>2026-09-21</t>
+          <t>2026-09-28</t>
         </is>
       </c>
       <c r="Q270" s="4" t="n"/>
@@ -21147,7 +21147,7 @@
       </c>
       <c r="P271" s="4" t="inlineStr">
         <is>
-          <t>2026-09-21</t>
+          <t>2026-09-28</t>
         </is>
       </c>
       <c r="Q271" s="4" t="n"/>
@@ -21224,7 +21224,7 @@
       </c>
       <c r="P272" s="4" t="inlineStr">
         <is>
-          <t>2026-09-21</t>
+          <t>2026-09-28</t>
         </is>
       </c>
       <c r="Q272" s="4" t="n"/>
@@ -21301,7 +21301,7 @@
       </c>
       <c r="P273" s="4" t="inlineStr">
         <is>
-          <t>2026-09-21</t>
+          <t>2026-09-28</t>
         </is>
       </c>
       <c r="Q273" s="4" t="n"/>
@@ -21378,7 +21378,7 @@
       </c>
       <c r="P274" s="4" t="inlineStr">
         <is>
-          <t>2026-09-21</t>
+          <t>2026-09-28</t>
         </is>
       </c>
       <c r="Q274" s="4" t="n"/>
@@ -21455,7 +21455,7 @@
       </c>
       <c r="P275" s="4" t="inlineStr">
         <is>
-          <t>2026-09-21</t>
+          <t>2026-09-28</t>
         </is>
       </c>
       <c r="Q275" s="4" t="n"/>
@@ -21532,7 +21532,7 @@
       </c>
       <c r="P276" s="4" t="inlineStr">
         <is>
-          <t>2026-09-21</t>
+          <t>2026-09-28</t>
         </is>
       </c>
       <c r="Q276" s="4" t="n"/>
@@ -21609,7 +21609,7 @@
       </c>
       <c r="P277" s="4" t="inlineStr">
         <is>
-          <t>2026-09-21</t>
+          <t>2026-09-28</t>
         </is>
       </c>
       <c r="Q277" s="4" t="n"/>
@@ -21686,7 +21686,7 @@
       </c>
       <c r="P278" s="4" t="inlineStr">
         <is>
-          <t>2026-09-21</t>
+          <t>2026-09-28</t>
         </is>
       </c>
       <c r="Q278" s="4" t="n"/>
@@ -21763,7 +21763,7 @@
       </c>
       <c r="P279" s="4" t="inlineStr">
         <is>
-          <t>2026-09-21</t>
+          <t>2026-09-28</t>
         </is>
       </c>
       <c r="Q279" s="4" t="n"/>
@@ -21840,7 +21840,7 @@
       </c>
       <c r="P280" s="4" t="inlineStr">
         <is>
-          <t>2026-09-21</t>
+          <t>2026-09-28</t>
         </is>
       </c>
       <c r="Q280" s="4" t="n"/>
@@ -21917,7 +21917,7 @@
       </c>
       <c r="P281" s="4" t="inlineStr">
         <is>
-          <t>2026-09-21</t>
+          <t>2026-09-28</t>
         </is>
       </c>
       <c r="Q281" s="4" t="n"/>
@@ -21994,7 +21994,7 @@
       </c>
       <c r="P282" s="4" t="inlineStr">
         <is>
-          <t>2026-09-21</t>
+          <t>2026-09-28</t>
         </is>
       </c>
       <c r="Q282" s="4" t="n"/>
@@ -22071,7 +22071,7 @@
       </c>
       <c r="P283" s="4" t="inlineStr">
         <is>
-          <t>2026-09-21</t>
+          <t>2026-09-28</t>
         </is>
       </c>
       <c r="Q283" s="4" t="n"/>
@@ -22148,7 +22148,7 @@
       </c>
       <c r="P284" s="4" t="inlineStr">
         <is>
-          <t>2026-09-21</t>
+          <t>2026-09-28</t>
         </is>
       </c>
       <c r="Q284" s="4" t="n"/>
@@ -22225,7 +22225,7 @@
       </c>
       <c r="P285" s="4" t="inlineStr">
         <is>
-          <t>2026-09-21</t>
+          <t>2026-09-28</t>
         </is>
       </c>
       <c r="Q285" s="4" t="n"/>
@@ -22302,7 +22302,7 @@
       </c>
       <c r="P286" s="4" t="inlineStr">
         <is>
-          <t>2026-09-21</t>
+          <t>2026-09-28</t>
         </is>
       </c>
       <c r="Q286" s="4" t="n"/>
@@ -22379,7 +22379,7 @@
       </c>
       <c r="P287" s="4" t="inlineStr">
         <is>
-          <t>2026-09-21</t>
+          <t>2026-09-28</t>
         </is>
       </c>
       <c r="Q287" s="4" t="n"/>
@@ -22456,7 +22456,7 @@
       </c>
       <c r="P288" s="4" t="inlineStr">
         <is>
-          <t>2026-09-21</t>
+          <t>2026-09-28</t>
         </is>
       </c>
       <c r="Q288" s="4" t="n"/>
@@ -22533,7 +22533,7 @@
       </c>
       <c r="P289" s="4" t="inlineStr">
         <is>
-          <t>2026-09-21</t>
+          <t>2026-09-28</t>
         </is>
       </c>
       <c r="Q289" s="4" t="n"/>
@@ -22610,7 +22610,7 @@
       </c>
       <c r="P290" s="4" t="inlineStr">
         <is>
-          <t>2026-09-21</t>
+          <t>2026-09-28</t>
         </is>
       </c>
       <c r="Q290" s="4" t="n"/>
@@ -22687,7 +22687,7 @@
       </c>
       <c r="P291" s="4" t="inlineStr">
         <is>
-          <t>2026-09-21</t>
+          <t>2026-09-28</t>
         </is>
       </c>
       <c r="Q291" s="4" t="n"/>
@@ -22764,7 +22764,7 @@
       </c>
       <c r="P292" s="4" t="inlineStr">
         <is>
-          <t>2026-09-21</t>
+          <t>2026-09-28</t>
         </is>
       </c>
       <c r="Q292" s="4" t="n"/>
@@ -22841,7 +22841,7 @@
       </c>
       <c r="P293" s="4" t="inlineStr">
         <is>
-          <t>2026-09-21</t>
+          <t>2026-09-28</t>
         </is>
       </c>
       <c r="Q293" s="4" t="n"/>
@@ -22918,7 +22918,7 @@
       </c>
       <c r="P294" s="4" t="inlineStr">
         <is>
-          <t>2026-09-21</t>
+          <t>2026-09-28</t>
         </is>
       </c>
       <c r="Q294" s="4" t="n"/>
@@ -22995,7 +22995,7 @@
       </c>
       <c r="P295" s="4" t="inlineStr">
         <is>
-          <t>2026-09-21</t>
+          <t>2026-09-28</t>
         </is>
       </c>
       <c r="Q295" s="4" t="n"/>
@@ -23072,7 +23072,7 @@
       </c>
       <c r="P296" s="4" t="inlineStr">
         <is>
-          <t>2026-09-21</t>
+          <t>2026-09-28</t>
         </is>
       </c>
       <c r="Q296" s="4" t="n"/>
@@ -23149,7 +23149,7 @@
       </c>
       <c r="P297" s="4" t="inlineStr">
         <is>
-          <t>2026-09-21</t>
+          <t>2026-09-28</t>
         </is>
       </c>
       <c r="Q297" s="4" t="n"/>
@@ -23226,7 +23226,7 @@
       </c>
       <c r="P298" s="4" t="inlineStr">
         <is>
-          <t>2026-09-21</t>
+          <t>2026-09-28</t>
         </is>
       </c>
       <c r="Q298" s="4" t="n"/>
@@ -23303,7 +23303,7 @@
       </c>
       <c r="P299" s="4" t="inlineStr">
         <is>
-          <t>2026-09-21</t>
+          <t>2026-09-28</t>
         </is>
       </c>
       <c r="Q299" s="4" t="n"/>
@@ -23380,7 +23380,7 @@
       </c>
       <c r="P300" s="4" t="inlineStr">
         <is>
-          <t>2026-09-21</t>
+          <t>2026-09-28</t>
         </is>
       </c>
       <c r="Q300" s="4" t="n"/>
@@ -23457,7 +23457,7 @@
       </c>
       <c r="P301" s="4" t="inlineStr">
         <is>
-          <t>2026-09-21</t>
+          <t>2026-09-28</t>
         </is>
       </c>
       <c r="Q301" s="4" t="n"/>
@@ -23534,7 +23534,7 @@
       </c>
       <c r="P302" s="4" t="inlineStr">
         <is>
-          <t>2026-09-21</t>
+          <t>2026-09-28</t>
         </is>
       </c>
       <c r="Q302" s="4" t="n"/>
@@ -23611,7 +23611,7 @@
       </c>
       <c r="P303" s="4" t="inlineStr">
         <is>
-          <t>2026-09-21</t>
+          <t>2026-09-28</t>
         </is>
       </c>
       <c r="Q303" s="4" t="n"/>
@@ -23688,7 +23688,7 @@
       </c>
       <c r="P304" s="4" t="inlineStr">
         <is>
-          <t>2026-09-21</t>
+          <t>2026-09-28</t>
         </is>
       </c>
       <c r="Q304" s="4" t="n"/>
@@ -23765,7 +23765,7 @@
       </c>
       <c r="P305" s="4" t="inlineStr">
         <is>
-          <t>2026-09-21</t>
+          <t>2026-09-28</t>
         </is>
       </c>
       <c r="Q305" s="4" t="n"/>
@@ -23842,7 +23842,7 @@
       </c>
       <c r="P306" s="4" t="inlineStr">
         <is>
-          <t>2026-09-21</t>
+          <t>2026-09-28</t>
         </is>
       </c>
       <c r="Q306" s="4" t="n"/>
@@ -23919,7 +23919,7 @@
       </c>
       <c r="P307" s="4" t="inlineStr">
         <is>
-          <t>2026-09-21</t>
+          <t>2026-09-28</t>
         </is>
       </c>
       <c r="Q307" s="4" t="n"/>
@@ -23998,7 +23998,7 @@
       </c>
       <c r="P308" s="4" t="inlineStr">
         <is>
-          <t>2026-09-21</t>
+          <t>2026-09-28</t>
         </is>
       </c>
       <c r="Q308" s="4" t="n"/>
@@ -24077,7 +24077,7 @@
       </c>
       <c r="P309" s="4" t="inlineStr">
         <is>
-          <t>2026-09-21</t>
+          <t>2026-09-28</t>
         </is>
       </c>
       <c r="Q309" s="4" t="n"/>
@@ -24156,7 +24156,7 @@
       </c>
       <c r="P310" s="4" t="inlineStr">
         <is>
-          <t>2026-09-21</t>
+          <t>2026-09-28</t>
         </is>
       </c>
       <c r="Q310" s="4" t="n"/>
@@ -24235,7 +24235,7 @@
       </c>
       <c r="P311" s="4" t="inlineStr">
         <is>
-          <t>2026-09-21</t>
+          <t>2026-09-28</t>
         </is>
       </c>
       <c r="Q311" s="4" t="n"/>
@@ -24314,7 +24314,7 @@
       </c>
       <c r="P312" s="4" t="inlineStr">
         <is>
-          <t>2026-09-21</t>
+          <t>2026-09-28</t>
         </is>
       </c>
       <c r="Q312" s="4" t="n"/>
@@ -24393,7 +24393,7 @@
       </c>
       <c r="P313" s="4" t="inlineStr">
         <is>
-          <t>2026-09-21</t>
+          <t>2026-09-28</t>
         </is>
       </c>
       <c r="Q313" s="4" t="n"/>
@@ -24472,7 +24472,7 @@
       </c>
       <c r="P314" s="4" t="inlineStr">
         <is>
-          <t>2026-09-21</t>
+          <t>2026-09-28</t>
         </is>
       </c>
       <c r="Q314" s="4" t="n"/>
@@ -24551,7 +24551,7 @@
       </c>
       <c r="P315" s="4" t="inlineStr">
         <is>
-          <t>2026-09-21</t>
+          <t>2026-09-28</t>
         </is>
       </c>
       <c r="Q315" s="4" t="n"/>
@@ -24630,7 +24630,7 @@
       </c>
       <c r="P316" s="4" t="inlineStr">
         <is>
-          <t>2026-09-21</t>
+          <t>2026-09-28</t>
         </is>
       </c>
       <c r="Q316" s="4" t="n"/>
@@ -24709,7 +24709,7 @@
       </c>
       <c r="P317" s="4" t="inlineStr">
         <is>
-          <t>2026-09-21</t>
+          <t>2026-09-28</t>
         </is>
       </c>
       <c r="Q317" s="4" t="n"/>
@@ -24788,7 +24788,7 @@
       </c>
       <c r="P318" s="4" t="inlineStr">
         <is>
-          <t>2026-09-21</t>
+          <t>2026-09-28</t>
         </is>
       </c>
       <c r="Q318" s="4" t="n"/>
@@ -24867,7 +24867,7 @@
       </c>
       <c r="P319" s="4" t="inlineStr">
         <is>
-          <t>2026-09-21</t>
+          <t>2026-09-28</t>
         </is>
       </c>
       <c r="Q319" s="4" t="n"/>
@@ -24946,7 +24946,7 @@
       </c>
       <c r="P320" s="4" t="inlineStr">
         <is>
-          <t>2026-09-21</t>
+          <t>2026-09-28</t>
         </is>
       </c>
       <c r="Q320" s="4" t="n"/>
@@ -25025,7 +25025,7 @@
       </c>
       <c r="P321" s="4" t="inlineStr">
         <is>
-          <t>2026-09-21</t>
+          <t>2026-09-28</t>
         </is>
       </c>
       <c r="Q321" s="4" t="n"/>
@@ -25104,7 +25104,7 @@
       </c>
       <c r="P322" s="4" t="inlineStr">
         <is>
-          <t>2026-09-21</t>
+          <t>2026-09-28</t>
         </is>
       </c>
       <c r="Q322" s="4" t="n"/>
@@ -25183,7 +25183,7 @@
       </c>
       <c r="P323" s="4" t="inlineStr">
         <is>
-          <t>2026-09-21</t>
+          <t>2026-09-28</t>
         </is>
       </c>
       <c r="Q323" s="4" t="n"/>
@@ -25262,7 +25262,7 @@
       </c>
       <c r="P324" s="4" t="inlineStr">
         <is>
-          <t>2026-09-21</t>
+          <t>2026-09-28</t>
         </is>
       </c>
       <c r="Q324" s="4" t="n"/>
@@ -25341,7 +25341,7 @@
       </c>
       <c r="P325" s="4" t="inlineStr">
         <is>
-          <t>2026-09-21</t>
+          <t>2026-09-28</t>
         </is>
       </c>
       <c r="Q325" s="4" t="n"/>
@@ -25420,7 +25420,7 @@
       </c>
       <c r="P326" s="4" t="inlineStr">
         <is>
-          <t>2026-09-21</t>
+          <t>2026-09-28</t>
         </is>
       </c>
       <c r="Q326" s="4" t="n"/>
@@ -25497,7 +25497,7 @@
       </c>
       <c r="P327" s="4" t="inlineStr">
         <is>
-          <t>2026-09-21</t>
+          <t>2026-09-28</t>
         </is>
       </c>
       <c r="Q327" s="4" t="n"/>
@@ -25574,7 +25574,7 @@
       </c>
       <c r="P328" s="4" t="inlineStr">
         <is>
-          <t>2026-09-21</t>
+          <t>2026-09-28</t>
         </is>
       </c>
       <c r="Q328" s="4" t="n"/>
@@ -25651,7 +25651,7 @@
       </c>
       <c r="P329" s="4" t="inlineStr">
         <is>
-          <t>2026-09-21</t>
+          <t>2026-09-28</t>
         </is>
       </c>
       <c r="Q329" s="4" t="n"/>
@@ -25728,7 +25728,7 @@
       </c>
       <c r="P330" s="4" t="inlineStr">
         <is>
-          <t>2026-09-21</t>
+          <t>2026-09-28</t>
         </is>
       </c>
       <c r="Q330" s="4" t="n"/>
@@ -25805,7 +25805,7 @@
       </c>
       <c r="P331" s="4" t="inlineStr">
         <is>
-          <t>2026-09-21</t>
+          <t>2026-09-28</t>
         </is>
       </c>
       <c r="Q331" s="4" t="n"/>
@@ -25882,7 +25882,7 @@
       </c>
       <c r="P332" s="4" t="inlineStr">
         <is>
-          <t>2026-09-21</t>
+          <t>2026-09-28</t>
         </is>
       </c>
       <c r="Q332" s="4" t="n"/>
@@ -25959,7 +25959,7 @@
       </c>
       <c r="P333" s="4" t="inlineStr">
         <is>
-          <t>2026-09-21</t>
+          <t>2026-09-28</t>
         </is>
       </c>
       <c r="Q333" s="4" t="n"/>
@@ -26036,7 +26036,7 @@
       </c>
       <c r="P334" s="4" t="inlineStr">
         <is>
-          <t>2026-09-21</t>
+          <t>2026-09-28</t>
         </is>
       </c>
       <c r="Q334" s="4" t="n"/>
@@ -26113,7 +26113,7 @@
       </c>
       <c r="P335" s="4" t="inlineStr">
         <is>
-          <t>2026-09-21</t>
+          <t>2026-09-28</t>
         </is>
       </c>
       <c r="Q335" s="4" t="n"/>
@@ -26190,7 +26190,7 @@
       </c>
       <c r="P336" s="4" t="inlineStr">
         <is>
-          <t>2026-09-21</t>
+          <t>2026-09-28</t>
         </is>
       </c>
       <c r="Q336" s="4" t="n"/>
@@ -26275,7 +26275,7 @@
       </c>
       <c r="B9" s="4" t="inlineStr">
         <is>
-          <t>2026-09-21</t>
+          <t>2026-09-28</t>
         </is>
       </c>
     </row>

--- a/assets/data/world-bank/excel/ove_banco_mundial_venezuela_pobreza_y_desigualdad.xlsx
+++ b/assets/data/world-bank/excel/ove_banco_mundial_venezuela_pobreza_y_desigualdad.xlsx
@@ -715,7 +715,7 @@
       </c>
       <c r="P7" s="4" t="inlineStr">
         <is>
-          <t>2026-09-28</t>
+          <t>2026-10-12</t>
         </is>
       </c>
       <c r="Q7" s="4" t="n"/>
@@ -792,7 +792,7 @@
       </c>
       <c r="P8" s="4" t="inlineStr">
         <is>
-          <t>2026-09-28</t>
+          <t>2026-10-12</t>
         </is>
       </c>
       <c r="Q8" s="4" t="n"/>
@@ -869,7 +869,7 @@
       </c>
       <c r="P9" s="4" t="inlineStr">
         <is>
-          <t>2026-09-28</t>
+          <t>2026-10-12</t>
         </is>
       </c>
       <c r="Q9" s="4" t="n"/>
@@ -946,7 +946,7 @@
       </c>
       <c r="P10" s="4" t="inlineStr">
         <is>
-          <t>2026-09-28</t>
+          <t>2026-10-12</t>
         </is>
       </c>
       <c r="Q10" s="4" t="n"/>
@@ -1023,7 +1023,7 @@
       </c>
       <c r="P11" s="4" t="inlineStr">
         <is>
-          <t>2026-09-28</t>
+          <t>2026-10-12</t>
         </is>
       </c>
       <c r="Q11" s="4" t="n"/>
@@ -1100,7 +1100,7 @@
       </c>
       <c r="P12" s="4" t="inlineStr">
         <is>
-          <t>2026-09-28</t>
+          <t>2026-10-12</t>
         </is>
       </c>
       <c r="Q12" s="4" t="n"/>
@@ -1177,7 +1177,7 @@
       </c>
       <c r="P13" s="4" t="inlineStr">
         <is>
-          <t>2026-09-28</t>
+          <t>2026-10-12</t>
         </is>
       </c>
       <c r="Q13" s="4" t="n"/>
@@ -1254,7 +1254,7 @@
       </c>
       <c r="P14" s="4" t="inlineStr">
         <is>
-          <t>2026-09-28</t>
+          <t>2026-10-12</t>
         </is>
       </c>
       <c r="Q14" s="4" t="n"/>
@@ -1331,7 +1331,7 @@
       </c>
       <c r="P15" s="4" t="inlineStr">
         <is>
-          <t>2026-09-28</t>
+          <t>2026-10-12</t>
         </is>
       </c>
       <c r="Q15" s="4" t="n"/>
@@ -1408,7 +1408,7 @@
       </c>
       <c r="P16" s="4" t="inlineStr">
         <is>
-          <t>2026-09-28</t>
+          <t>2026-10-12</t>
         </is>
       </c>
       <c r="Q16" s="4" t="n"/>
@@ -1485,7 +1485,7 @@
       </c>
       <c r="P17" s="4" t="inlineStr">
         <is>
-          <t>2026-09-28</t>
+          <t>2026-10-12</t>
         </is>
       </c>
       <c r="Q17" s="4" t="n"/>
@@ -1562,7 +1562,7 @@
       </c>
       <c r="P18" s="4" t="inlineStr">
         <is>
-          <t>2026-09-28</t>
+          <t>2026-10-12</t>
         </is>
       </c>
       <c r="Q18" s="4" t="n"/>
@@ -1639,7 +1639,7 @@
       </c>
       <c r="P19" s="4" t="inlineStr">
         <is>
-          <t>2026-09-28</t>
+          <t>2026-10-12</t>
         </is>
       </c>
       <c r="Q19" s="4" t="n"/>
@@ -1716,7 +1716,7 @@
       </c>
       <c r="P20" s="4" t="inlineStr">
         <is>
-          <t>2026-09-28</t>
+          <t>2026-10-12</t>
         </is>
       </c>
       <c r="Q20" s="4" t="n"/>
@@ -1793,7 +1793,7 @@
       </c>
       <c r="P21" s="4" t="inlineStr">
         <is>
-          <t>2026-09-28</t>
+          <t>2026-10-12</t>
         </is>
       </c>
       <c r="Q21" s="4" t="n"/>
@@ -1870,7 +1870,7 @@
       </c>
       <c r="P22" s="4" t="inlineStr">
         <is>
-          <t>2026-09-28</t>
+          <t>2026-10-12</t>
         </is>
       </c>
       <c r="Q22" s="4" t="n"/>
@@ -1947,7 +1947,7 @@
       </c>
       <c r="P23" s="4" t="inlineStr">
         <is>
-          <t>2026-09-28</t>
+          <t>2026-10-12</t>
         </is>
       </c>
       <c r="Q23" s="4" t="n"/>
@@ -2024,7 +2024,7 @@
       </c>
       <c r="P24" s="4" t="inlineStr">
         <is>
-          <t>2026-09-28</t>
+          <t>2026-10-12</t>
         </is>
       </c>
       <c r="Q24" s="4" t="n"/>
@@ -2101,7 +2101,7 @@
       </c>
       <c r="P25" s="4" t="inlineStr">
         <is>
-          <t>2026-09-28</t>
+          <t>2026-10-12</t>
         </is>
       </c>
       <c r="Q25" s="4" t="n"/>
@@ -2178,7 +2178,7 @@
       </c>
       <c r="P26" s="4" t="inlineStr">
         <is>
-          <t>2026-09-28</t>
+          <t>2026-10-12</t>
         </is>
       </c>
       <c r="Q26" s="4" t="n"/>
@@ -2255,7 +2255,7 @@
       </c>
       <c r="P27" s="4" t="inlineStr">
         <is>
-          <t>2026-09-28</t>
+          <t>2026-10-12</t>
         </is>
       </c>
       <c r="Q27" s="4" t="n"/>
@@ -2334,7 +2334,7 @@
       </c>
       <c r="P28" s="4" t="inlineStr">
         <is>
-          <t>2026-09-28</t>
+          <t>2026-10-12</t>
         </is>
       </c>
       <c r="Q28" s="4" t="n"/>
@@ -2411,7 +2411,7 @@
       </c>
       <c r="P29" s="4" t="inlineStr">
         <is>
-          <t>2026-09-28</t>
+          <t>2026-10-12</t>
         </is>
       </c>
       <c r="Q29" s="4" t="n"/>
@@ -2488,7 +2488,7 @@
       </c>
       <c r="P30" s="4" t="inlineStr">
         <is>
-          <t>2026-09-28</t>
+          <t>2026-10-12</t>
         </is>
       </c>
       <c r="Q30" s="4" t="n"/>
@@ -2565,7 +2565,7 @@
       </c>
       <c r="P31" s="4" t="inlineStr">
         <is>
-          <t>2026-09-28</t>
+          <t>2026-10-12</t>
         </is>
       </c>
       <c r="Q31" s="4" t="n"/>
@@ -2642,7 +2642,7 @@
       </c>
       <c r="P32" s="4" t="inlineStr">
         <is>
-          <t>2026-09-28</t>
+          <t>2026-10-12</t>
         </is>
       </c>
       <c r="Q32" s="4" t="n"/>
@@ -2719,7 +2719,7 @@
       </c>
       <c r="P33" s="4" t="inlineStr">
         <is>
-          <t>2026-09-28</t>
+          <t>2026-10-12</t>
         </is>
       </c>
       <c r="Q33" s="4" t="n"/>
@@ -2798,7 +2798,7 @@
       </c>
       <c r="P34" s="4" t="inlineStr">
         <is>
-          <t>2026-09-28</t>
+          <t>2026-10-12</t>
         </is>
       </c>
       <c r="Q34" s="4" t="n"/>
@@ -2875,7 +2875,7 @@
       </c>
       <c r="P35" s="4" t="inlineStr">
         <is>
-          <t>2026-09-28</t>
+          <t>2026-10-12</t>
         </is>
       </c>
       <c r="Q35" s="4" t="n"/>
@@ -2954,7 +2954,7 @@
       </c>
       <c r="P36" s="4" t="inlineStr">
         <is>
-          <t>2026-09-28</t>
+          <t>2026-10-12</t>
         </is>
       </c>
       <c r="Q36" s="4" t="n"/>
@@ -3031,7 +3031,7 @@
       </c>
       <c r="P37" s="4" t="inlineStr">
         <is>
-          <t>2026-09-28</t>
+          <t>2026-10-12</t>
         </is>
       </c>
       <c r="Q37" s="4" t="n"/>
@@ -3108,7 +3108,7 @@
       </c>
       <c r="P38" s="4" t="inlineStr">
         <is>
-          <t>2026-09-28</t>
+          <t>2026-10-12</t>
         </is>
       </c>
       <c r="Q38" s="4" t="n"/>
@@ -3187,7 +3187,7 @@
       </c>
       <c r="P39" s="4" t="inlineStr">
         <is>
-          <t>2026-09-28</t>
+          <t>2026-10-12</t>
         </is>
       </c>
       <c r="Q39" s="4" t="n"/>
@@ -3264,7 +3264,7 @@
       </c>
       <c r="P40" s="4" t="inlineStr">
         <is>
-          <t>2026-09-28</t>
+          <t>2026-10-12</t>
         </is>
       </c>
       <c r="Q40" s="4" t="n"/>
@@ -3341,7 +3341,7 @@
       </c>
       <c r="P41" s="4" t="inlineStr">
         <is>
-          <t>2026-09-28</t>
+          <t>2026-10-12</t>
         </is>
       </c>
       <c r="Q41" s="4" t="n"/>
@@ -3420,7 +3420,7 @@
       </c>
       <c r="P42" s="4" t="inlineStr">
         <is>
-          <t>2026-09-28</t>
+          <t>2026-10-12</t>
         </is>
       </c>
       <c r="Q42" s="4" t="n"/>
@@ -3497,7 +3497,7 @@
       </c>
       <c r="P43" s="4" t="inlineStr">
         <is>
-          <t>2026-09-28</t>
+          <t>2026-10-12</t>
         </is>
       </c>
       <c r="Q43" s="4" t="n"/>
@@ -3574,7 +3574,7 @@
       </c>
       <c r="P44" s="4" t="inlineStr">
         <is>
-          <t>2026-09-28</t>
+          <t>2026-10-12</t>
         </is>
       </c>
       <c r="Q44" s="4" t="n"/>
@@ -3653,7 +3653,7 @@
       </c>
       <c r="P45" s="4" t="inlineStr">
         <is>
-          <t>2026-09-28</t>
+          <t>2026-10-12</t>
         </is>
       </c>
       <c r="Q45" s="4" t="n"/>
@@ -3732,7 +3732,7 @@
       </c>
       <c r="P46" s="4" t="inlineStr">
         <is>
-          <t>2026-09-28</t>
+          <t>2026-10-12</t>
         </is>
       </c>
       <c r="Q46" s="4" t="n"/>
@@ -3809,7 +3809,7 @@
       </c>
       <c r="P47" s="4" t="inlineStr">
         <is>
-          <t>2026-09-28</t>
+          <t>2026-10-12</t>
         </is>
       </c>
       <c r="Q47" s="4" t="n"/>
@@ -3888,7 +3888,7 @@
       </c>
       <c r="P48" s="4" t="inlineStr">
         <is>
-          <t>2026-09-28</t>
+          <t>2026-10-12</t>
         </is>
       </c>
       <c r="Q48" s="4" t="n"/>
@@ -3967,7 +3967,7 @@
       </c>
       <c r="P49" s="4" t="inlineStr">
         <is>
-          <t>2026-09-28</t>
+          <t>2026-10-12</t>
         </is>
       </c>
       <c r="Q49" s="4" t="n"/>
@@ -4046,7 +4046,7 @@
       </c>
       <c r="P50" s="4" t="inlineStr">
         <is>
-          <t>2026-09-28</t>
+          <t>2026-10-12</t>
         </is>
       </c>
       <c r="Q50" s="4" t="n"/>
@@ -4125,7 +4125,7 @@
       </c>
       <c r="P51" s="4" t="inlineStr">
         <is>
-          <t>2026-09-28</t>
+          <t>2026-10-12</t>
         </is>
       </c>
       <c r="Q51" s="4" t="n"/>
@@ -4204,7 +4204,7 @@
       </c>
       <c r="P52" s="4" t="inlineStr">
         <is>
-          <t>2026-09-28</t>
+          <t>2026-10-12</t>
         </is>
       </c>
       <c r="Q52" s="4" t="n"/>
@@ -4283,7 +4283,7 @@
       </c>
       <c r="P53" s="4" t="inlineStr">
         <is>
-          <t>2026-09-28</t>
+          <t>2026-10-12</t>
         </is>
       </c>
       <c r="Q53" s="4" t="n"/>
@@ -4360,7 +4360,7 @@
       </c>
       <c r="P54" s="4" t="inlineStr">
         <is>
-          <t>2026-09-28</t>
+          <t>2026-10-12</t>
         </is>
       </c>
       <c r="Q54" s="4" t="n"/>
@@ -4437,7 +4437,7 @@
       </c>
       <c r="P55" s="4" t="inlineStr">
         <is>
-          <t>2026-09-28</t>
+          <t>2026-10-12</t>
         </is>
       </c>
       <c r="Q55" s="4" t="n"/>
@@ -4514,7 +4514,7 @@
       </c>
       <c r="P56" s="4" t="inlineStr">
         <is>
-          <t>2026-09-28</t>
+          <t>2026-10-12</t>
         </is>
       </c>
       <c r="Q56" s="4" t="n"/>
@@ -4591,7 +4591,7 @@
       </c>
       <c r="P57" s="4" t="inlineStr">
         <is>
-          <t>2026-09-28</t>
+          <t>2026-10-12</t>
         </is>
       </c>
       <c r="Q57" s="4" t="n"/>
@@ -4668,7 +4668,7 @@
       </c>
       <c r="P58" s="4" t="inlineStr">
         <is>
-          <t>2026-09-28</t>
+          <t>2026-10-12</t>
         </is>
       </c>
       <c r="Q58" s="4" t="n"/>
@@ -4745,7 +4745,7 @@
       </c>
       <c r="P59" s="4" t="inlineStr">
         <is>
-          <t>2026-09-28</t>
+          <t>2026-10-12</t>
         </is>
       </c>
       <c r="Q59" s="4" t="n"/>
@@ -4822,7 +4822,7 @@
       </c>
       <c r="P60" s="4" t="inlineStr">
         <is>
-          <t>2026-09-28</t>
+          <t>2026-10-12</t>
         </is>
       </c>
       <c r="Q60" s="4" t="n"/>
@@ -4899,7 +4899,7 @@
       </c>
       <c r="P61" s="4" t="inlineStr">
         <is>
-          <t>2026-09-28</t>
+          <t>2026-10-12</t>
         </is>
       </c>
       <c r="Q61" s="4" t="n"/>
@@ -4976,7 +4976,7 @@
       </c>
       <c r="P62" s="4" t="inlineStr">
         <is>
-          <t>2026-09-28</t>
+          <t>2026-10-12</t>
         </is>
       </c>
       <c r="Q62" s="4" t="n"/>
@@ -5053,7 +5053,7 @@
       </c>
       <c r="P63" s="4" t="inlineStr">
         <is>
-          <t>2026-09-28</t>
+          <t>2026-10-12</t>
         </is>
       </c>
       <c r="Q63" s="4" t="n"/>
@@ -5130,7 +5130,7 @@
       </c>
       <c r="P64" s="4" t="inlineStr">
         <is>
-          <t>2026-09-28</t>
+          <t>2026-10-12</t>
         </is>
       </c>
       <c r="Q64" s="4" t="n"/>
@@ -5207,7 +5207,7 @@
       </c>
       <c r="P65" s="4" t="inlineStr">
         <is>
-          <t>2026-09-28</t>
+          <t>2026-10-12</t>
         </is>
       </c>
       <c r="Q65" s="4" t="n"/>
@@ -5284,7 +5284,7 @@
       </c>
       <c r="P66" s="4" t="inlineStr">
         <is>
-          <t>2026-09-28</t>
+          <t>2026-10-12</t>
         </is>
       </c>
       <c r="Q66" s="4" t="n"/>
@@ -5361,7 +5361,7 @@
       </c>
       <c r="P67" s="4" t="inlineStr">
         <is>
-          <t>2026-09-28</t>
+          <t>2026-10-12</t>
         </is>
       </c>
       <c r="Q67" s="4" t="n"/>
@@ -5438,7 +5438,7 @@
       </c>
       <c r="P68" s="4" t="inlineStr">
         <is>
-          <t>2026-09-28</t>
+          <t>2026-10-12</t>
         </is>
       </c>
       <c r="Q68" s="4" t="n"/>
@@ -5515,7 +5515,7 @@
       </c>
       <c r="P69" s="4" t="inlineStr">
         <is>
-          <t>2026-09-28</t>
+          <t>2026-10-12</t>
         </is>
       </c>
       <c r="Q69" s="4" t="n"/>
@@ -5592,7 +5592,7 @@
       </c>
       <c r="P70" s="4" t="inlineStr">
         <is>
-          <t>2026-09-28</t>
+          <t>2026-10-12</t>
         </is>
       </c>
       <c r="Q70" s="4" t="n"/>
@@ -5669,7 +5669,7 @@
       </c>
       <c r="P71" s="4" t="inlineStr">
         <is>
-          <t>2026-09-28</t>
+          <t>2026-10-12</t>
         </is>
       </c>
       <c r="Q71" s="4" t="n"/>
@@ -5746,7 +5746,7 @@
       </c>
       <c r="P72" s="4" t="inlineStr">
         <is>
-          <t>2026-09-28</t>
+          <t>2026-10-12</t>
         </is>
       </c>
       <c r="Q72" s="4" t="n"/>
@@ -5823,7 +5823,7 @@
       </c>
       <c r="P73" s="4" t="inlineStr">
         <is>
-          <t>2026-09-28</t>
+          <t>2026-10-12</t>
         </is>
       </c>
       <c r="Q73" s="4" t="n"/>
@@ -5900,7 +5900,7 @@
       </c>
       <c r="P74" s="4" t="inlineStr">
         <is>
-          <t>2026-09-28</t>
+          <t>2026-10-12</t>
         </is>
       </c>
       <c r="Q74" s="4" t="n"/>
@@ -5977,7 +5977,7 @@
       </c>
       <c r="P75" s="4" t="inlineStr">
         <is>
-          <t>2026-09-28</t>
+          <t>2026-10-12</t>
         </is>
       </c>
       <c r="Q75" s="4" t="n"/>
@@ -6054,7 +6054,7 @@
       </c>
       <c r="P76" s="4" t="inlineStr">
         <is>
-          <t>2026-09-28</t>
+          <t>2026-10-12</t>
         </is>
       </c>
       <c r="Q76" s="4" t="n"/>
@@ -6131,7 +6131,7 @@
       </c>
       <c r="P77" s="4" t="inlineStr">
         <is>
-          <t>2026-09-28</t>
+          <t>2026-10-12</t>
         </is>
       </c>
       <c r="Q77" s="4" t="n"/>
@@ -6208,7 +6208,7 @@
       </c>
       <c r="P78" s="4" t="inlineStr">
         <is>
-          <t>2026-09-28</t>
+          <t>2026-10-12</t>
         </is>
       </c>
       <c r="Q78" s="4" t="n"/>
@@ -6285,7 +6285,7 @@
       </c>
       <c r="P79" s="4" t="inlineStr">
         <is>
-          <t>2026-09-28</t>
+          <t>2026-10-12</t>
         </is>
       </c>
       <c r="Q79" s="4" t="n"/>
@@ -6362,7 +6362,7 @@
       </c>
       <c r="P80" s="4" t="inlineStr">
         <is>
-          <t>2026-09-28</t>
+          <t>2026-10-12</t>
         </is>
       </c>
       <c r="Q80" s="4" t="n"/>
@@ -6439,7 +6439,7 @@
       </c>
       <c r="P81" s="4" t="inlineStr">
         <is>
-          <t>2026-09-28</t>
+          <t>2026-10-12</t>
         </is>
       </c>
       <c r="Q81" s="4" t="n"/>
@@ -6516,7 +6516,7 @@
       </c>
       <c r="P82" s="4" t="inlineStr">
         <is>
-          <t>2026-09-28</t>
+          <t>2026-10-12</t>
         </is>
       </c>
       <c r="Q82" s="4" t="n"/>
@@ -6593,7 +6593,7 @@
       </c>
       <c r="P83" s="4" t="inlineStr">
         <is>
-          <t>2026-09-28</t>
+          <t>2026-10-12</t>
         </is>
       </c>
       <c r="Q83" s="4" t="n"/>
@@ -6670,7 +6670,7 @@
       </c>
       <c r="P84" s="4" t="inlineStr">
         <is>
-          <t>2026-09-28</t>
+          <t>2026-10-12</t>
         </is>
       </c>
       <c r="Q84" s="4" t="n"/>
@@ -6747,7 +6747,7 @@
       </c>
       <c r="P85" s="4" t="inlineStr">
         <is>
-          <t>2026-09-28</t>
+          <t>2026-10-12</t>
         </is>
       </c>
       <c r="Q85" s="4" t="n"/>
@@ -6824,7 +6824,7 @@
       </c>
       <c r="P86" s="4" t="inlineStr">
         <is>
-          <t>2026-09-28</t>
+          <t>2026-10-12</t>
         </is>
       </c>
       <c r="Q86" s="4" t="n"/>
@@ -6901,7 +6901,7 @@
       </c>
       <c r="P87" s="4" t="inlineStr">
         <is>
-          <t>2026-09-28</t>
+          <t>2026-10-12</t>
         </is>
       </c>
       <c r="Q87" s="4" t="n"/>
@@ -6978,7 +6978,7 @@
       </c>
       <c r="P88" s="4" t="inlineStr">
         <is>
-          <t>2026-09-28</t>
+          <t>2026-10-12</t>
         </is>
       </c>
       <c r="Q88" s="4" t="n"/>
@@ -7055,7 +7055,7 @@
       </c>
       <c r="P89" s="4" t="inlineStr">
         <is>
-          <t>2026-09-28</t>
+          <t>2026-10-12</t>
         </is>
       </c>
       <c r="Q89" s="4" t="n"/>
@@ -7132,7 +7132,7 @@
       </c>
       <c r="P90" s="4" t="inlineStr">
         <is>
-          <t>2026-09-28</t>
+          <t>2026-10-12</t>
         </is>
       </c>
       <c r="Q90" s="4" t="n"/>
@@ -7209,7 +7209,7 @@
       </c>
       <c r="P91" s="4" t="inlineStr">
         <is>
-          <t>2026-09-28</t>
+          <t>2026-10-12</t>
         </is>
       </c>
       <c r="Q91" s="4" t="n"/>
@@ -7286,7 +7286,7 @@
       </c>
       <c r="P92" s="4" t="inlineStr">
         <is>
-          <t>2026-09-28</t>
+          <t>2026-10-12</t>
         </is>
       </c>
       <c r="Q92" s="4" t="n"/>
@@ -7363,7 +7363,7 @@
       </c>
       <c r="P93" s="4" t="inlineStr">
         <is>
-          <t>2026-09-28</t>
+          <t>2026-10-12</t>
         </is>
       </c>
       <c r="Q93" s="4" t="n"/>
@@ -7442,7 +7442,7 @@
       </c>
       <c r="P94" s="4" t="inlineStr">
         <is>
-          <t>2026-09-28</t>
+          <t>2026-10-12</t>
         </is>
       </c>
       <c r="Q94" s="4" t="n"/>
@@ -7519,7 +7519,7 @@
       </c>
       <c r="P95" s="4" t="inlineStr">
         <is>
-          <t>2026-09-28</t>
+          <t>2026-10-12</t>
         </is>
       </c>
       <c r="Q95" s="4" t="n"/>
@@ -7596,7 +7596,7 @@
       </c>
       <c r="P96" s="4" t="inlineStr">
         <is>
-          <t>2026-09-28</t>
+          <t>2026-10-12</t>
         </is>
       </c>
       <c r="Q96" s="4" t="n"/>
@@ -7673,7 +7673,7 @@
       </c>
       <c r="P97" s="4" t="inlineStr">
         <is>
-          <t>2026-09-28</t>
+          <t>2026-10-12</t>
         </is>
       </c>
       <c r="Q97" s="4" t="n"/>
@@ -7750,7 +7750,7 @@
       </c>
       <c r="P98" s="4" t="inlineStr">
         <is>
-          <t>2026-09-28</t>
+          <t>2026-10-12</t>
         </is>
       </c>
       <c r="Q98" s="4" t="n"/>
@@ -7827,7 +7827,7 @@
       </c>
       <c r="P99" s="4" t="inlineStr">
         <is>
-          <t>2026-09-28</t>
+          <t>2026-10-12</t>
         </is>
       </c>
       <c r="Q99" s="4" t="n"/>
@@ -7906,7 +7906,7 @@
       </c>
       <c r="P100" s="4" t="inlineStr">
         <is>
-          <t>2026-09-28</t>
+          <t>2026-10-12</t>
         </is>
       </c>
       <c r="Q100" s="4" t="n"/>
@@ -7983,7 +7983,7 @@
       </c>
       <c r="P101" s="4" t="inlineStr">
         <is>
-          <t>2026-09-28</t>
+          <t>2026-10-12</t>
         </is>
       </c>
       <c r="Q101" s="4" t="n"/>
@@ -8062,7 +8062,7 @@
       </c>
       <c r="P102" s="4" t="inlineStr">
         <is>
-          <t>2026-09-28</t>
+          <t>2026-10-12</t>
         </is>
       </c>
       <c r="Q102" s="4" t="n"/>
@@ -8139,7 +8139,7 @@
       </c>
       <c r="P103" s="4" t="inlineStr">
         <is>
-          <t>2026-09-28</t>
+          <t>2026-10-12</t>
         </is>
       </c>
       <c r="Q103" s="4" t="n"/>
@@ -8216,7 +8216,7 @@
       </c>
       <c r="P104" s="4" t="inlineStr">
         <is>
-          <t>2026-09-28</t>
+          <t>2026-10-12</t>
         </is>
       </c>
       <c r="Q104" s="4" t="n"/>
@@ -8295,7 +8295,7 @@
       </c>
       <c r="P105" s="4" t="inlineStr">
         <is>
-          <t>2026-09-28</t>
+          <t>2026-10-12</t>
         </is>
       </c>
       <c r="Q105" s="4" t="n"/>
@@ -8372,7 +8372,7 @@
       </c>
       <c r="P106" s="4" t="inlineStr">
         <is>
-          <t>2026-09-28</t>
+          <t>2026-10-12</t>
         </is>
       </c>
       <c r="Q106" s="4" t="n"/>
@@ -8449,7 +8449,7 @@
       </c>
       <c r="P107" s="4" t="inlineStr">
         <is>
-          <t>2026-09-28</t>
+          <t>2026-10-12</t>
         </is>
       </c>
       <c r="Q107" s="4" t="n"/>
@@ -8528,7 +8528,7 @@
       </c>
       <c r="P108" s="4" t="inlineStr">
         <is>
-          <t>2026-09-28</t>
+          <t>2026-10-12</t>
         </is>
       </c>
       <c r="Q108" s="4" t="n"/>
@@ -8605,7 +8605,7 @@
       </c>
       <c r="P109" s="4" t="inlineStr">
         <is>
-          <t>2026-09-28</t>
+          <t>2026-10-12</t>
         </is>
       </c>
       <c r="Q109" s="4" t="n"/>
@@ -8682,7 +8682,7 @@
       </c>
       <c r="P110" s="4" t="inlineStr">
         <is>
-          <t>2026-09-28</t>
+          <t>2026-10-12</t>
         </is>
       </c>
       <c r="Q110" s="4" t="n"/>
@@ -8761,7 +8761,7 @@
       </c>
       <c r="P111" s="4" t="inlineStr">
         <is>
-          <t>2026-09-28</t>
+          <t>2026-10-12</t>
         </is>
       </c>
       <c r="Q111" s="4" t="n"/>
@@ -8840,7 +8840,7 @@
       </c>
       <c r="P112" s="4" t="inlineStr">
         <is>
-          <t>2026-09-28</t>
+          <t>2026-10-12</t>
         </is>
       </c>
       <c r="Q112" s="4" t="n"/>
@@ -8917,7 +8917,7 @@
       </c>
       <c r="P113" s="4" t="inlineStr">
         <is>
-          <t>2026-09-28</t>
+          <t>2026-10-12</t>
         </is>
       </c>
       <c r="Q113" s="4" t="n"/>
@@ -8996,7 +8996,7 @@
       </c>
       <c r="P114" s="4" t="inlineStr">
         <is>
-          <t>2026-09-28</t>
+          <t>2026-10-12</t>
         </is>
       </c>
       <c r="Q114" s="4" t="n"/>
@@ -9075,7 +9075,7 @@
       </c>
       <c r="P115" s="4" t="inlineStr">
         <is>
-          <t>2026-09-28</t>
+          <t>2026-10-12</t>
         </is>
       </c>
       <c r="Q115" s="4" t="n"/>
@@ -9154,7 +9154,7 @@
       </c>
       <c r="P116" s="4" t="inlineStr">
         <is>
-          <t>2026-09-28</t>
+          <t>2026-10-12</t>
         </is>
       </c>
       <c r="Q116" s="4" t="n"/>
@@ -9233,7 +9233,7 @@
       </c>
       <c r="P117" s="4" t="inlineStr">
         <is>
-          <t>2026-09-28</t>
+          <t>2026-10-12</t>
         </is>
       </c>
       <c r="Q117" s="4" t="n"/>
@@ -9312,7 +9312,7 @@
       </c>
       <c r="P118" s="4" t="inlineStr">
         <is>
-          <t>2026-09-28</t>
+          <t>2026-10-12</t>
         </is>
       </c>
       <c r="Q118" s="4" t="n"/>
@@ -9391,7 +9391,7 @@
       </c>
       <c r="P119" s="4" t="inlineStr">
         <is>
-          <t>2026-09-28</t>
+          <t>2026-10-12</t>
         </is>
       </c>
       <c r="Q119" s="4" t="n"/>
@@ -9468,7 +9468,7 @@
       </c>
       <c r="P120" s="4" t="inlineStr">
         <is>
-          <t>2026-09-28</t>
+          <t>2026-10-12</t>
         </is>
       </c>
       <c r="Q120" s="4" t="n"/>
@@ -9545,7 +9545,7 @@
       </c>
       <c r="P121" s="4" t="inlineStr">
         <is>
-          <t>2026-09-28</t>
+          <t>2026-10-12</t>
         </is>
       </c>
       <c r="Q121" s="4" t="n"/>
@@ -9622,7 +9622,7 @@
       </c>
       <c r="P122" s="4" t="inlineStr">
         <is>
-          <t>2026-09-28</t>
+          <t>2026-10-12</t>
         </is>
       </c>
       <c r="Q122" s="4" t="n"/>
@@ -9699,7 +9699,7 @@
       </c>
       <c r="P123" s="4" t="inlineStr">
         <is>
-          <t>2026-09-28</t>
+          <t>2026-10-12</t>
         </is>
       </c>
       <c r="Q123" s="4" t="n"/>
@@ -9776,7 +9776,7 @@
       </c>
       <c r="P124" s="4" t="inlineStr">
         <is>
-          <t>2026-09-28</t>
+          <t>2026-10-12</t>
         </is>
       </c>
       <c r="Q124" s="4" t="n"/>
@@ -9853,7 +9853,7 @@
       </c>
       <c r="P125" s="4" t="inlineStr">
         <is>
-          <t>2026-09-28</t>
+          <t>2026-10-12</t>
         </is>
       </c>
       <c r="Q125" s="4" t="n"/>
@@ -9930,7 +9930,7 @@
       </c>
       <c r="P126" s="4" t="inlineStr">
         <is>
-          <t>2026-09-28</t>
+          <t>2026-10-12</t>
         </is>
       </c>
       <c r="Q126" s="4" t="n"/>
@@ -10007,7 +10007,7 @@
       </c>
       <c r="P127" s="4" t="inlineStr">
         <is>
-          <t>2026-09-28</t>
+          <t>2026-10-12</t>
         </is>
       </c>
       <c r="Q127" s="4" t="n"/>
@@ -10084,7 +10084,7 @@
       </c>
       <c r="P128" s="4" t="inlineStr">
         <is>
-          <t>2026-09-28</t>
+          <t>2026-10-12</t>
         </is>
       </c>
       <c r="Q128" s="4" t="n"/>
@@ -10161,7 +10161,7 @@
       </c>
       <c r="P129" s="4" t="inlineStr">
         <is>
-          <t>2026-09-28</t>
+          <t>2026-10-12</t>
         </is>
       </c>
       <c r="Q129" s="4" t="n"/>
@@ -10238,7 +10238,7 @@
       </c>
       <c r="P130" s="4" t="inlineStr">
         <is>
-          <t>2026-09-28</t>
+          <t>2026-10-12</t>
         </is>
       </c>
       <c r="Q130" s="4" t="n"/>
@@ -10315,7 +10315,7 @@
       </c>
       <c r="P131" s="4" t="inlineStr">
         <is>
-          <t>2026-09-28</t>
+          <t>2026-10-12</t>
         </is>
       </c>
       <c r="Q131" s="4" t="n"/>
@@ -10392,7 +10392,7 @@
       </c>
       <c r="P132" s="4" t="inlineStr">
         <is>
-          <t>2026-09-28</t>
+          <t>2026-10-12</t>
         </is>
       </c>
       <c r="Q132" s="4" t="n"/>
@@ -10469,7 +10469,7 @@
       </c>
       <c r="P133" s="4" t="inlineStr">
         <is>
-          <t>2026-09-28</t>
+          <t>2026-10-12</t>
         </is>
       </c>
       <c r="Q133" s="4" t="n"/>
@@ -10546,7 +10546,7 @@
       </c>
       <c r="P134" s="4" t="inlineStr">
         <is>
-          <t>2026-09-28</t>
+          <t>2026-10-12</t>
         </is>
       </c>
       <c r="Q134" s="4" t="n"/>
@@ -10623,7 +10623,7 @@
       </c>
       <c r="P135" s="4" t="inlineStr">
         <is>
-          <t>2026-09-28</t>
+          <t>2026-10-12</t>
         </is>
       </c>
       <c r="Q135" s="4" t="n"/>
@@ -10700,7 +10700,7 @@
       </c>
       <c r="P136" s="4" t="inlineStr">
         <is>
-          <t>2026-09-28</t>
+          <t>2026-10-12</t>
         </is>
       </c>
       <c r="Q136" s="4" t="n"/>
@@ -10777,7 +10777,7 @@
       </c>
       <c r="P137" s="4" t="inlineStr">
         <is>
-          <t>2026-09-28</t>
+          <t>2026-10-12</t>
         </is>
       </c>
       <c r="Q137" s="4" t="n"/>
@@ -10854,7 +10854,7 @@
       </c>
       <c r="P138" s="4" t="inlineStr">
         <is>
-          <t>2026-09-28</t>
+          <t>2026-10-12</t>
         </is>
       </c>
       <c r="Q138" s="4" t="n"/>
@@ -10931,7 +10931,7 @@
       </c>
       <c r="P139" s="4" t="inlineStr">
         <is>
-          <t>2026-09-28</t>
+          <t>2026-10-12</t>
         </is>
       </c>
       <c r="Q139" s="4" t="n"/>
@@ -11008,7 +11008,7 @@
       </c>
       <c r="P140" s="4" t="inlineStr">
         <is>
-          <t>2026-09-28</t>
+          <t>2026-10-12</t>
         </is>
       </c>
       <c r="Q140" s="4" t="n"/>
@@ -11085,7 +11085,7 @@
       </c>
       <c r="P141" s="4" t="inlineStr">
         <is>
-          <t>2026-09-28</t>
+          <t>2026-10-12</t>
         </is>
       </c>
       <c r="Q141" s="4" t="n"/>
@@ -11162,7 +11162,7 @@
       </c>
       <c r="P142" s="4" t="inlineStr">
         <is>
-          <t>2026-09-28</t>
+          <t>2026-10-12</t>
         </is>
       </c>
       <c r="Q142" s="4" t="n"/>
@@ -11239,7 +11239,7 @@
       </c>
       <c r="P143" s="4" t="inlineStr">
         <is>
-          <t>2026-09-28</t>
+          <t>2026-10-12</t>
         </is>
       </c>
       <c r="Q143" s="4" t="n"/>
@@ -11316,7 +11316,7 @@
       </c>
       <c r="P144" s="4" t="inlineStr">
         <is>
-          <t>2026-09-28</t>
+          <t>2026-10-12</t>
         </is>
       </c>
       <c r="Q144" s="4" t="n"/>
@@ -11393,7 +11393,7 @@
       </c>
       <c r="P145" s="4" t="inlineStr">
         <is>
-          <t>2026-09-28</t>
+          <t>2026-10-12</t>
         </is>
       </c>
       <c r="Q145" s="4" t="n"/>
@@ -11470,7 +11470,7 @@
       </c>
       <c r="P146" s="4" t="inlineStr">
         <is>
-          <t>2026-09-28</t>
+          <t>2026-10-12</t>
         </is>
       </c>
       <c r="Q146" s="4" t="n"/>
@@ -11547,7 +11547,7 @@
       </c>
       <c r="P147" s="4" t="inlineStr">
         <is>
-          <t>2026-09-28</t>
+          <t>2026-10-12</t>
         </is>
       </c>
       <c r="Q147" s="4" t="n"/>
@@ -11624,7 +11624,7 @@
       </c>
       <c r="P148" s="4" t="inlineStr">
         <is>
-          <t>2026-09-28</t>
+          <t>2026-10-12</t>
         </is>
       </c>
       <c r="Q148" s="4" t="n"/>
@@ -11701,7 +11701,7 @@
       </c>
       <c r="P149" s="4" t="inlineStr">
         <is>
-          <t>2026-09-28</t>
+          <t>2026-10-12</t>
         </is>
       </c>
       <c r="Q149" s="4" t="n"/>
@@ -11778,7 +11778,7 @@
       </c>
       <c r="P150" s="4" t="inlineStr">
         <is>
-          <t>2026-09-28</t>
+          <t>2026-10-12</t>
         </is>
       </c>
       <c r="Q150" s="4" t="n"/>
@@ -11855,7 +11855,7 @@
       </c>
       <c r="P151" s="4" t="inlineStr">
         <is>
-          <t>2026-09-28</t>
+          <t>2026-10-12</t>
         </is>
       </c>
       <c r="Q151" s="4" t="n"/>
@@ -11932,7 +11932,7 @@
       </c>
       <c r="P152" s="4" t="inlineStr">
         <is>
-          <t>2026-09-28</t>
+          <t>2026-10-12</t>
         </is>
       </c>
       <c r="Q152" s="4" t="n"/>
@@ -12009,7 +12009,7 @@
       </c>
       <c r="P153" s="4" t="inlineStr">
         <is>
-          <t>2026-09-28</t>
+          <t>2026-10-12</t>
         </is>
       </c>
       <c r="Q153" s="4" t="n"/>
@@ -12086,7 +12086,7 @@
       </c>
       <c r="P154" s="4" t="inlineStr">
         <is>
-          <t>2026-09-28</t>
+          <t>2026-10-12</t>
         </is>
       </c>
       <c r="Q154" s="4" t="n"/>
@@ -12163,7 +12163,7 @@
       </c>
       <c r="P155" s="4" t="inlineStr">
         <is>
-          <t>2026-09-28</t>
+          <t>2026-10-12</t>
         </is>
       </c>
       <c r="Q155" s="4" t="n"/>
@@ -12240,7 +12240,7 @@
       </c>
       <c r="P156" s="4" t="inlineStr">
         <is>
-          <t>2026-09-28</t>
+          <t>2026-10-12</t>
         </is>
       </c>
       <c r="Q156" s="4" t="n"/>
@@ -12317,7 +12317,7 @@
       </c>
       <c r="P157" s="4" t="inlineStr">
         <is>
-          <t>2026-09-28</t>
+          <t>2026-10-12</t>
         </is>
       </c>
       <c r="Q157" s="4" t="n"/>
@@ -12394,7 +12394,7 @@
       </c>
       <c r="P158" s="4" t="inlineStr">
         <is>
-          <t>2026-09-28</t>
+          <t>2026-10-12</t>
         </is>
       </c>
       <c r="Q158" s="4" t="n"/>
@@ -12471,7 +12471,7 @@
       </c>
       <c r="P159" s="4" t="inlineStr">
         <is>
-          <t>2026-09-28</t>
+          <t>2026-10-12</t>
         </is>
       </c>
       <c r="Q159" s="4" t="n"/>
@@ -12550,7 +12550,7 @@
       </c>
       <c r="P160" s="4" t="inlineStr">
         <is>
-          <t>2026-09-28</t>
+          <t>2026-10-12</t>
         </is>
       </c>
       <c r="Q160" s="4" t="n"/>
@@ -12627,7 +12627,7 @@
       </c>
       <c r="P161" s="4" t="inlineStr">
         <is>
-          <t>2026-09-28</t>
+          <t>2026-10-12</t>
         </is>
       </c>
       <c r="Q161" s="4" t="n"/>
@@ -12704,7 +12704,7 @@
       </c>
       <c r="P162" s="4" t="inlineStr">
         <is>
-          <t>2026-09-28</t>
+          <t>2026-10-12</t>
         </is>
       </c>
       <c r="Q162" s="4" t="n"/>
@@ -12781,7 +12781,7 @@
       </c>
       <c r="P163" s="4" t="inlineStr">
         <is>
-          <t>2026-09-28</t>
+          <t>2026-10-12</t>
         </is>
       </c>
       <c r="Q163" s="4" t="n"/>
@@ -12858,7 +12858,7 @@
       </c>
       <c r="P164" s="4" t="inlineStr">
         <is>
-          <t>2026-09-28</t>
+          <t>2026-10-12</t>
         </is>
       </c>
       <c r="Q164" s="4" t="n"/>
@@ -12935,7 +12935,7 @@
       </c>
       <c r="P165" s="4" t="inlineStr">
         <is>
-          <t>2026-09-28</t>
+          <t>2026-10-12</t>
         </is>
       </c>
       <c r="Q165" s="4" t="n"/>
@@ -13014,7 +13014,7 @@
       </c>
       <c r="P166" s="4" t="inlineStr">
         <is>
-          <t>2026-09-28</t>
+          <t>2026-10-12</t>
         </is>
       </c>
       <c r="Q166" s="4" t="n"/>
@@ -13091,7 +13091,7 @@
       </c>
       <c r="P167" s="4" t="inlineStr">
         <is>
-          <t>2026-09-28</t>
+          <t>2026-10-12</t>
         </is>
       </c>
       <c r="Q167" s="4" t="n"/>
@@ -13170,7 +13170,7 @@
       </c>
       <c r="P168" s="4" t="inlineStr">
         <is>
-          <t>2026-09-28</t>
+          <t>2026-10-12</t>
         </is>
       </c>
       <c r="Q168" s="4" t="n"/>
@@ -13247,7 +13247,7 @@
       </c>
       <c r="P169" s="4" t="inlineStr">
         <is>
-          <t>2026-09-28</t>
+          <t>2026-10-12</t>
         </is>
       </c>
       <c r="Q169" s="4" t="n"/>
@@ -13324,7 +13324,7 @@
       </c>
       <c r="P170" s="4" t="inlineStr">
         <is>
-          <t>2026-09-28</t>
+          <t>2026-10-12</t>
         </is>
       </c>
       <c r="Q170" s="4" t="n"/>
@@ -13403,7 +13403,7 @@
       </c>
       <c r="P171" s="4" t="inlineStr">
         <is>
-          <t>2026-09-28</t>
+          <t>2026-10-12</t>
         </is>
       </c>
       <c r="Q171" s="4" t="n"/>
@@ -13480,7 +13480,7 @@
       </c>
       <c r="P172" s="4" t="inlineStr">
         <is>
-          <t>2026-09-28</t>
+          <t>2026-10-12</t>
         </is>
       </c>
       <c r="Q172" s="4" t="n"/>
@@ -13557,7 +13557,7 @@
       </c>
       <c r="P173" s="4" t="inlineStr">
         <is>
-          <t>2026-09-28</t>
+          <t>2026-10-12</t>
         </is>
       </c>
       <c r="Q173" s="4" t="n"/>
@@ -13636,7 +13636,7 @@
       </c>
       <c r="P174" s="4" t="inlineStr">
         <is>
-          <t>2026-09-28</t>
+          <t>2026-10-12</t>
         </is>
       </c>
       <c r="Q174" s="4" t="n"/>
@@ -13713,7 +13713,7 @@
       </c>
       <c r="P175" s="4" t="inlineStr">
         <is>
-          <t>2026-09-28</t>
+          <t>2026-10-12</t>
         </is>
       </c>
       <c r="Q175" s="4" t="n"/>
@@ -13790,7 +13790,7 @@
       </c>
       <c r="P176" s="4" t="inlineStr">
         <is>
-          <t>2026-09-28</t>
+          <t>2026-10-12</t>
         </is>
       </c>
       <c r="Q176" s="4" t="n"/>
@@ -13869,7 +13869,7 @@
       </c>
       <c r="P177" s="4" t="inlineStr">
         <is>
-          <t>2026-09-28</t>
+          <t>2026-10-12</t>
         </is>
       </c>
       <c r="Q177" s="4" t="n"/>
@@ -13948,7 +13948,7 @@
       </c>
       <c r="P178" s="4" t="inlineStr">
         <is>
-          <t>2026-09-28</t>
+          <t>2026-10-12</t>
         </is>
       </c>
       <c r="Q178" s="4" t="n"/>
@@ -14025,7 +14025,7 @@
       </c>
       <c r="P179" s="4" t="inlineStr">
         <is>
-          <t>2026-09-28</t>
+          <t>2026-10-12</t>
         </is>
       </c>
       <c r="Q179" s="4" t="n"/>
@@ -14104,7 +14104,7 @@
       </c>
       <c r="P180" s="4" t="inlineStr">
         <is>
-          <t>2026-09-28</t>
+          <t>2026-10-12</t>
         </is>
       </c>
       <c r="Q180" s="4" t="n"/>
@@ -14183,7 +14183,7 @@
       </c>
       <c r="P181" s="4" t="inlineStr">
         <is>
-          <t>2026-09-28</t>
+          <t>2026-10-12</t>
         </is>
       </c>
       <c r="Q181" s="4" t="n"/>
@@ -14262,7 +14262,7 @@
       </c>
       <c r="P182" s="4" t="inlineStr">
         <is>
-          <t>2026-09-28</t>
+          <t>2026-10-12</t>
         </is>
       </c>
       <c r="Q182" s="4" t="n"/>
@@ -14341,7 +14341,7 @@
       </c>
       <c r="P183" s="4" t="inlineStr">
         <is>
-          <t>2026-09-28</t>
+          <t>2026-10-12</t>
         </is>
       </c>
       <c r="Q183" s="4" t="n"/>
@@ -14420,7 +14420,7 @@
       </c>
       <c r="P184" s="4" t="inlineStr">
         <is>
-          <t>2026-09-28</t>
+          <t>2026-10-12</t>
         </is>
       </c>
       <c r="Q184" s="4" t="n"/>
@@ -14499,7 +14499,7 @@
       </c>
       <c r="P185" s="4" t="inlineStr">
         <is>
-          <t>2026-09-28</t>
+          <t>2026-10-12</t>
         </is>
       </c>
       <c r="Q185" s="4" t="n"/>
@@ -14576,7 +14576,7 @@
       </c>
       <c r="P186" s="4" t="inlineStr">
         <is>
-          <t>2026-09-28</t>
+          <t>2026-10-12</t>
         </is>
       </c>
       <c r="Q186" s="4" t="n"/>
@@ -14653,7 +14653,7 @@
       </c>
       <c r="P187" s="4" t="inlineStr">
         <is>
-          <t>2026-09-28</t>
+          <t>2026-10-12</t>
         </is>
       </c>
       <c r="Q187" s="4" t="n"/>
@@ -14730,7 +14730,7 @@
       </c>
       <c r="P188" s="4" t="inlineStr">
         <is>
-          <t>2026-09-28</t>
+          <t>2026-10-12</t>
         </is>
       </c>
       <c r="Q188" s="4" t="n"/>
@@ -14807,7 +14807,7 @@
       </c>
       <c r="P189" s="4" t="inlineStr">
         <is>
-          <t>2026-09-28</t>
+          <t>2026-10-12</t>
         </is>
       </c>
       <c r="Q189" s="4" t="n"/>
@@ -14884,7 +14884,7 @@
       </c>
       <c r="P190" s="4" t="inlineStr">
         <is>
-          <t>2026-09-28</t>
+          <t>2026-10-12</t>
         </is>
       </c>
       <c r="Q190" s="4" t="n"/>
@@ -14961,7 +14961,7 @@
       </c>
       <c r="P191" s="4" t="inlineStr">
         <is>
-          <t>2026-09-28</t>
+          <t>2026-10-12</t>
         </is>
       </c>
       <c r="Q191" s="4" t="n"/>
@@ -15038,7 +15038,7 @@
       </c>
       <c r="P192" s="4" t="inlineStr">
         <is>
-          <t>2026-09-28</t>
+          <t>2026-10-12</t>
         </is>
       </c>
       <c r="Q192" s="4" t="n"/>
@@ -15115,7 +15115,7 @@
       </c>
       <c r="P193" s="4" t="inlineStr">
         <is>
-          <t>2026-09-28</t>
+          <t>2026-10-12</t>
         </is>
       </c>
       <c r="Q193" s="4" t="n"/>
@@ -15192,7 +15192,7 @@
       </c>
       <c r="P194" s="4" t="inlineStr">
         <is>
-          <t>2026-09-28</t>
+          <t>2026-10-12</t>
         </is>
       </c>
       <c r="Q194" s="4" t="n"/>
@@ -15269,7 +15269,7 @@
       </c>
       <c r="P195" s="4" t="inlineStr">
         <is>
-          <t>2026-09-28</t>
+          <t>2026-10-12</t>
         </is>
       </c>
       <c r="Q195" s="4" t="n"/>
@@ -15346,7 +15346,7 @@
       </c>
       <c r="P196" s="4" t="inlineStr">
         <is>
-          <t>2026-09-28</t>
+          <t>2026-10-12</t>
         </is>
       </c>
       <c r="Q196" s="4" t="n"/>
@@ -15423,7 +15423,7 @@
       </c>
       <c r="P197" s="4" t="inlineStr">
         <is>
-          <t>2026-09-28</t>
+          <t>2026-10-12</t>
         </is>
       </c>
       <c r="Q197" s="4" t="n"/>
@@ -15500,7 +15500,7 @@
       </c>
       <c r="P198" s="4" t="inlineStr">
         <is>
-          <t>2026-09-28</t>
+          <t>2026-10-12</t>
         </is>
       </c>
       <c r="Q198" s="4" t="n"/>
@@ -15577,7 +15577,7 @@
       </c>
       <c r="P199" s="4" t="inlineStr">
         <is>
-          <t>2026-09-28</t>
+          <t>2026-10-12</t>
         </is>
       </c>
       <c r="Q199" s="4" t="n"/>
@@ -15654,7 +15654,7 @@
       </c>
       <c r="P200" s="4" t="inlineStr">
         <is>
-          <t>2026-09-28</t>
+          <t>2026-10-12</t>
         </is>
       </c>
       <c r="Q200" s="4" t="n"/>
@@ -15731,7 +15731,7 @@
       </c>
       <c r="P201" s="4" t="inlineStr">
         <is>
-          <t>2026-09-28</t>
+          <t>2026-10-12</t>
         </is>
       </c>
       <c r="Q201" s="4" t="n"/>
@@ -15808,7 +15808,7 @@
       </c>
       <c r="P202" s="4" t="inlineStr">
         <is>
-          <t>2026-09-28</t>
+          <t>2026-10-12</t>
         </is>
       </c>
       <c r="Q202" s="4" t="n"/>
@@ -15885,7 +15885,7 @@
       </c>
       <c r="P203" s="4" t="inlineStr">
         <is>
-          <t>2026-09-28</t>
+          <t>2026-10-12</t>
         </is>
       </c>
       <c r="Q203" s="4" t="n"/>
@@ -15962,7 +15962,7 @@
       </c>
       <c r="P204" s="4" t="inlineStr">
         <is>
-          <t>2026-09-28</t>
+          <t>2026-10-12</t>
         </is>
       </c>
       <c r="Q204" s="4" t="n"/>
@@ -16039,7 +16039,7 @@
       </c>
       <c r="P205" s="4" t="inlineStr">
         <is>
-          <t>2026-09-28</t>
+          <t>2026-10-12</t>
         </is>
       </c>
       <c r="Q205" s="4" t="n"/>
@@ -16116,7 +16116,7 @@
       </c>
       <c r="P206" s="4" t="inlineStr">
         <is>
-          <t>2026-09-28</t>
+          <t>2026-10-12</t>
         </is>
       </c>
       <c r="Q206" s="4" t="n"/>
@@ -16193,7 +16193,7 @@
       </c>
       <c r="P207" s="4" t="inlineStr">
         <is>
-          <t>2026-09-28</t>
+          <t>2026-10-12</t>
         </is>
       </c>
       <c r="Q207" s="4" t="n"/>
@@ -16270,7 +16270,7 @@
       </c>
       <c r="P208" s="4" t="inlineStr">
         <is>
-          <t>2026-09-28</t>
+          <t>2026-10-12</t>
         </is>
       </c>
       <c r="Q208" s="4" t="n"/>
@@ -16347,7 +16347,7 @@
       </c>
       <c r="P209" s="4" t="inlineStr">
         <is>
-          <t>2026-09-28</t>
+          <t>2026-10-12</t>
         </is>
       </c>
       <c r="Q209" s="4" t="n"/>
@@ -16424,7 +16424,7 @@
       </c>
       <c r="P210" s="4" t="inlineStr">
         <is>
-          <t>2026-09-28</t>
+          <t>2026-10-12</t>
         </is>
       </c>
       <c r="Q210" s="4" t="n"/>
@@ -16501,7 +16501,7 @@
       </c>
       <c r="P211" s="4" t="inlineStr">
         <is>
-          <t>2026-09-28</t>
+          <t>2026-10-12</t>
         </is>
       </c>
       <c r="Q211" s="4" t="n"/>
@@ -16578,7 +16578,7 @@
       </c>
       <c r="P212" s="4" t="inlineStr">
         <is>
-          <t>2026-09-28</t>
+          <t>2026-10-12</t>
         </is>
       </c>
       <c r="Q212" s="4" t="n"/>
@@ -16655,7 +16655,7 @@
       </c>
       <c r="P213" s="4" t="inlineStr">
         <is>
-          <t>2026-09-28</t>
+          <t>2026-10-12</t>
         </is>
       </c>
       <c r="Q213" s="4" t="n"/>
@@ -16732,7 +16732,7 @@
       </c>
       <c r="P214" s="4" t="inlineStr">
         <is>
-          <t>2026-09-28</t>
+          <t>2026-10-12</t>
         </is>
       </c>
       <c r="Q214" s="4" t="n"/>
@@ -16809,7 +16809,7 @@
       </c>
       <c r="P215" s="4" t="inlineStr">
         <is>
-          <t>2026-09-28</t>
+          <t>2026-10-12</t>
         </is>
       </c>
       <c r="Q215" s="4" t="n"/>
@@ -16886,7 +16886,7 @@
       </c>
       <c r="P216" s="4" t="inlineStr">
         <is>
-          <t>2026-09-28</t>
+          <t>2026-10-12</t>
         </is>
       </c>
       <c r="Q216" s="4" t="n"/>
@@ -16963,7 +16963,7 @@
       </c>
       <c r="P217" s="4" t="inlineStr">
         <is>
-          <t>2026-09-28</t>
+          <t>2026-10-12</t>
         </is>
       </c>
       <c r="Q217" s="4" t="n"/>
@@ -17040,7 +17040,7 @@
       </c>
       <c r="P218" s="4" t="inlineStr">
         <is>
-          <t>2026-09-28</t>
+          <t>2026-10-12</t>
         </is>
       </c>
       <c r="Q218" s="4" t="n"/>
@@ -17117,7 +17117,7 @@
       </c>
       <c r="P219" s="4" t="inlineStr">
         <is>
-          <t>2026-09-28</t>
+          <t>2026-10-12</t>
         </is>
       </c>
       <c r="Q219" s="4" t="n"/>
@@ -17194,7 +17194,7 @@
       </c>
       <c r="P220" s="4" t="inlineStr">
         <is>
-          <t>2026-09-28</t>
+          <t>2026-10-12</t>
         </is>
       </c>
       <c r="Q220" s="4" t="n"/>
@@ -17271,7 +17271,7 @@
       </c>
       <c r="P221" s="4" t="inlineStr">
         <is>
-          <t>2026-09-28</t>
+          <t>2026-10-12</t>
         </is>
       </c>
       <c r="Q221" s="4" t="n"/>
@@ -17348,7 +17348,7 @@
       </c>
       <c r="P222" s="4" t="inlineStr">
         <is>
-          <t>2026-09-28</t>
+          <t>2026-10-12</t>
         </is>
       </c>
       <c r="Q222" s="4" t="n"/>
@@ -17425,7 +17425,7 @@
       </c>
       <c r="P223" s="4" t="inlineStr">
         <is>
-          <t>2026-09-28</t>
+          <t>2026-10-12</t>
         </is>
       </c>
       <c r="Q223" s="4" t="n"/>
@@ -17502,7 +17502,7 @@
       </c>
       <c r="P224" s="4" t="inlineStr">
         <is>
-          <t>2026-09-28</t>
+          <t>2026-10-12</t>
         </is>
       </c>
       <c r="Q224" s="4" t="n"/>
@@ -17579,7 +17579,7 @@
       </c>
       <c r="P225" s="4" t="inlineStr">
         <is>
-          <t>2026-09-28</t>
+          <t>2026-10-12</t>
         </is>
       </c>
       <c r="Q225" s="4" t="n"/>
@@ -17658,7 +17658,7 @@
       </c>
       <c r="P226" s="4" t="inlineStr">
         <is>
-          <t>2026-09-28</t>
+          <t>2026-10-12</t>
         </is>
       </c>
       <c r="Q226" s="4" t="n"/>
@@ -17735,7 +17735,7 @@
       </c>
       <c r="P227" s="4" t="inlineStr">
         <is>
-          <t>2026-09-28</t>
+          <t>2026-10-12</t>
         </is>
       </c>
       <c r="Q227" s="4" t="n"/>
@@ -17812,7 +17812,7 @@
       </c>
       <c r="P228" s="4" t="inlineStr">
         <is>
-          <t>2026-09-28</t>
+          <t>2026-10-12</t>
         </is>
       </c>
       <c r="Q228" s="4" t="n"/>
@@ -17889,7 +17889,7 @@
       </c>
       <c r="P229" s="4" t="inlineStr">
         <is>
-          <t>2026-09-28</t>
+          <t>2026-10-12</t>
         </is>
       </c>
       <c r="Q229" s="4" t="n"/>
@@ -17966,7 +17966,7 @@
       </c>
       <c r="P230" s="4" t="inlineStr">
         <is>
-          <t>2026-09-28</t>
+          <t>2026-10-12</t>
         </is>
       </c>
       <c r="Q230" s="4" t="n"/>
@@ -18043,7 +18043,7 @@
       </c>
       <c r="P231" s="4" t="inlineStr">
         <is>
-          <t>2026-09-28</t>
+          <t>2026-10-12</t>
         </is>
       </c>
       <c r="Q231" s="4" t="n"/>
@@ -18122,7 +18122,7 @@
       </c>
       <c r="P232" s="4" t="inlineStr">
         <is>
-          <t>2026-09-28</t>
+          <t>2026-10-12</t>
         </is>
       </c>
       <c r="Q232" s="4" t="n"/>
@@ -18199,7 +18199,7 @@
       </c>
       <c r="P233" s="4" t="inlineStr">
         <is>
-          <t>2026-09-28</t>
+          <t>2026-10-12</t>
         </is>
       </c>
       <c r="Q233" s="4" t="n"/>
@@ -18278,7 +18278,7 @@
       </c>
       <c r="P234" s="4" t="inlineStr">
         <is>
-          <t>2026-09-28</t>
+          <t>2026-10-12</t>
         </is>
       </c>
       <c r="Q234" s="4" t="n"/>
@@ -18355,7 +18355,7 @@
       </c>
       <c r="P235" s="4" t="inlineStr">
         <is>
-          <t>2026-09-28</t>
+          <t>2026-10-12</t>
         </is>
       </c>
       <c r="Q235" s="4" t="n"/>
@@ -18432,7 +18432,7 @@
       </c>
       <c r="P236" s="4" t="inlineStr">
         <is>
-          <t>2026-09-28</t>
+          <t>2026-10-12</t>
         </is>
       </c>
       <c r="Q236" s="4" t="n"/>
@@ -18511,7 +18511,7 @@
       </c>
       <c r="P237" s="4" t="inlineStr">
         <is>
-          <t>2026-09-28</t>
+          <t>2026-10-12</t>
         </is>
       </c>
       <c r="Q237" s="4" t="n"/>
@@ -18588,7 +18588,7 @@
       </c>
       <c r="P238" s="4" t="inlineStr">
         <is>
-          <t>2026-09-28</t>
+          <t>2026-10-12</t>
         </is>
       </c>
       <c r="Q238" s="4" t="n"/>
@@ -18665,7 +18665,7 @@
       </c>
       <c r="P239" s="4" t="inlineStr">
         <is>
-          <t>2026-09-28</t>
+          <t>2026-10-12</t>
         </is>
       </c>
       <c r="Q239" s="4" t="n"/>
@@ -18744,7 +18744,7 @@
       </c>
       <c r="P240" s="4" t="inlineStr">
         <is>
-          <t>2026-09-28</t>
+          <t>2026-10-12</t>
         </is>
       </c>
       <c r="Q240" s="4" t="n"/>
@@ -18821,7 +18821,7 @@
       </c>
       <c r="P241" s="4" t="inlineStr">
         <is>
-          <t>2026-09-28</t>
+          <t>2026-10-12</t>
         </is>
       </c>
       <c r="Q241" s="4" t="n"/>
@@ -18898,7 +18898,7 @@
       </c>
       <c r="P242" s="4" t="inlineStr">
         <is>
-          <t>2026-09-28</t>
+          <t>2026-10-12</t>
         </is>
       </c>
       <c r="Q242" s="4" t="n"/>
@@ -18977,7 +18977,7 @@
       </c>
       <c r="P243" s="4" t="inlineStr">
         <is>
-          <t>2026-09-28</t>
+          <t>2026-10-12</t>
         </is>
       </c>
       <c r="Q243" s="4" t="n"/>
@@ -19056,7 +19056,7 @@
       </c>
       <c r="P244" s="4" t="inlineStr">
         <is>
-          <t>2026-09-28</t>
+          <t>2026-10-12</t>
         </is>
       </c>
       <c r="Q244" s="4" t="n"/>
@@ -19133,7 +19133,7 @@
       </c>
       <c r="P245" s="4" t="inlineStr">
         <is>
-          <t>2026-09-28</t>
+          <t>2026-10-12</t>
         </is>
       </c>
       <c r="Q245" s="4" t="n"/>
@@ -19212,7 +19212,7 @@
       </c>
       <c r="P246" s="4" t="inlineStr">
         <is>
-          <t>2026-09-28</t>
+          <t>2026-10-12</t>
         </is>
       </c>
       <c r="Q246" s="4" t="n"/>
@@ -19291,7 +19291,7 @@
       </c>
       <c r="P247" s="4" t="inlineStr">
         <is>
-          <t>2026-09-28</t>
+          <t>2026-10-12</t>
         </is>
       </c>
       <c r="Q247" s="4" t="n"/>
@@ -19370,7 +19370,7 @@
       </c>
       <c r="P248" s="4" t="inlineStr">
         <is>
-          <t>2026-09-28</t>
+          <t>2026-10-12</t>
         </is>
       </c>
       <c r="Q248" s="4" t="n"/>
@@ -19449,7 +19449,7 @@
       </c>
       <c r="P249" s="4" t="inlineStr">
         <is>
-          <t>2026-09-28</t>
+          <t>2026-10-12</t>
         </is>
       </c>
       <c r="Q249" s="4" t="n"/>
@@ -19528,7 +19528,7 @@
       </c>
       <c r="P250" s="4" t="inlineStr">
         <is>
-          <t>2026-09-28</t>
+          <t>2026-10-12</t>
         </is>
       </c>
       <c r="Q250" s="4" t="n"/>
@@ -19607,7 +19607,7 @@
       </c>
       <c r="P251" s="4" t="inlineStr">
         <is>
-          <t>2026-09-28</t>
+          <t>2026-10-12</t>
         </is>
       </c>
       <c r="Q251" s="4" t="n"/>
@@ -19684,7 +19684,7 @@
       </c>
       <c r="P252" s="4" t="inlineStr">
         <is>
-          <t>2026-09-28</t>
+          <t>2026-10-12</t>
         </is>
       </c>
       <c r="Q252" s="4" t="n"/>
@@ -19761,7 +19761,7 @@
       </c>
       <c r="P253" s="4" t="inlineStr">
         <is>
-          <t>2026-09-28</t>
+          <t>2026-10-12</t>
         </is>
       </c>
       <c r="Q253" s="4" t="n"/>
@@ -19838,7 +19838,7 @@
       </c>
       <c r="P254" s="4" t="inlineStr">
         <is>
-          <t>2026-09-28</t>
+          <t>2026-10-12</t>
         </is>
       </c>
       <c r="Q254" s="4" t="n"/>
@@ -19915,7 +19915,7 @@
       </c>
       <c r="P255" s="4" t="inlineStr">
         <is>
-          <t>2026-09-28</t>
+          <t>2026-10-12</t>
         </is>
       </c>
       <c r="Q255" s="4" t="n"/>
@@ -19992,7 +19992,7 @@
       </c>
       <c r="P256" s="4" t="inlineStr">
         <is>
-          <t>2026-09-28</t>
+          <t>2026-10-12</t>
         </is>
       </c>
       <c r="Q256" s="4" t="n"/>
@@ -20069,7 +20069,7 @@
       </c>
       <c r="P257" s="4" t="inlineStr">
         <is>
-          <t>2026-09-28</t>
+          <t>2026-10-12</t>
         </is>
       </c>
       <c r="Q257" s="4" t="n"/>
@@ -20146,7 +20146,7 @@
       </c>
       <c r="P258" s="4" t="inlineStr">
         <is>
-          <t>2026-09-28</t>
+          <t>2026-10-12</t>
         </is>
       </c>
       <c r="Q258" s="4" t="n"/>
@@ -20223,7 +20223,7 @@
       </c>
       <c r="P259" s="4" t="inlineStr">
         <is>
-          <t>2026-09-28</t>
+          <t>2026-10-12</t>
         </is>
       </c>
       <c r="Q259" s="4" t="n"/>
@@ -20300,7 +20300,7 @@
       </c>
       <c r="P260" s="4" t="inlineStr">
         <is>
-          <t>2026-09-28</t>
+          <t>2026-10-12</t>
         </is>
       </c>
       <c r="Q260" s="4" t="n"/>
@@ -20377,7 +20377,7 @@
       </c>
       <c r="P261" s="4" t="inlineStr">
         <is>
-          <t>2026-09-28</t>
+          <t>2026-10-12</t>
         </is>
       </c>
       <c r="Q261" s="4" t="n"/>
@@ -20454,7 +20454,7 @@
       </c>
       <c r="P262" s="4" t="inlineStr">
         <is>
-          <t>2026-09-28</t>
+          <t>2026-10-12</t>
         </is>
       </c>
       <c r="Q262" s="4" t="n"/>
@@ -20531,7 +20531,7 @@
       </c>
       <c r="P263" s="4" t="inlineStr">
         <is>
-          <t>2026-09-28</t>
+          <t>2026-10-12</t>
         </is>
       </c>
       <c r="Q263" s="4" t="n"/>
@@ -20608,7 +20608,7 @@
       </c>
       <c r="P264" s="4" t="inlineStr">
         <is>
-          <t>2026-09-28</t>
+          <t>2026-10-12</t>
         </is>
       </c>
       <c r="Q264" s="4" t="n"/>
@@ -20685,7 +20685,7 @@
       </c>
       <c r="P265" s="4" t="inlineStr">
         <is>
-          <t>2026-09-28</t>
+          <t>2026-10-12</t>
         </is>
       </c>
       <c r="Q265" s="4" t="n"/>
@@ -20762,7 +20762,7 @@
       </c>
       <c r="P266" s="4" t="inlineStr">
         <is>
-          <t>2026-09-28</t>
+          <t>2026-10-12</t>
         </is>
       </c>
       <c r="Q266" s="4" t="n"/>
@@ -20839,7 +20839,7 @@
       </c>
       <c r="P267" s="4" t="inlineStr">
         <is>
-          <t>2026-09-28</t>
+          <t>2026-10-12</t>
         </is>
       </c>
       <c r="Q267" s="4" t="n"/>
@@ -20916,7 +20916,7 @@
       </c>
       <c r="P268" s="4" t="inlineStr">
         <is>
-          <t>2026-09-28</t>
+          <t>2026-10-12</t>
         </is>
       </c>
       <c r="Q268" s="4" t="n"/>
@@ -20993,7 +20993,7 @@
       </c>
       <c r="P269" s="4" t="inlineStr">
         <is>
-          <t>2026-09-28</t>
+          <t>2026-10-12</t>
         </is>
       </c>
       <c r="Q269" s="4" t="n"/>
@@ -21070,7 +21070,7 @@
       </c>
       <c r="P270" s="4" t="inlineStr">
         <is>
-          <t>2026-09-28</t>
+          <t>2026-10-12</t>
         </is>
       </c>
       <c r="Q270" s="4" t="n"/>
@@ -21147,7 +21147,7 @@
       </c>
       <c r="P271" s="4" t="inlineStr">
         <is>
-          <t>2026-09-28</t>
+          <t>2026-10-12</t>
         </is>
       </c>
       <c r="Q271" s="4" t="n"/>
@@ -21224,7 +21224,7 @@
       </c>
       <c r="P272" s="4" t="inlineStr">
         <is>
-          <t>2026-09-28</t>
+          <t>2026-10-12</t>
         </is>
       </c>
       <c r="Q272" s="4" t="n"/>
@@ -21301,7 +21301,7 @@
       </c>
       <c r="P273" s="4" t="inlineStr">
         <is>
-          <t>2026-09-28</t>
+          <t>2026-10-12</t>
         </is>
       </c>
       <c r="Q273" s="4" t="n"/>
@@ -21378,7 +21378,7 @@
       </c>
       <c r="P274" s="4" t="inlineStr">
         <is>
-          <t>2026-09-28</t>
+          <t>2026-10-12</t>
         </is>
       </c>
       <c r="Q274" s="4" t="n"/>
@@ -21455,7 +21455,7 @@
       </c>
       <c r="P275" s="4" t="inlineStr">
         <is>
-          <t>2026-09-28</t>
+          <t>2026-10-12</t>
         </is>
       </c>
       <c r="Q275" s="4" t="n"/>
@@ -21532,7 +21532,7 @@
       </c>
       <c r="P276" s="4" t="inlineStr">
         <is>
-          <t>2026-09-28</t>
+          <t>2026-10-12</t>
         </is>
       </c>
       <c r="Q276" s="4" t="n"/>
@@ -21609,7 +21609,7 @@
       </c>
       <c r="P277" s="4" t="inlineStr">
         <is>
-          <t>2026-09-28</t>
+          <t>2026-10-12</t>
         </is>
       </c>
       <c r="Q277" s="4" t="n"/>
@@ -21686,7 +21686,7 @@
       </c>
       <c r="P278" s="4" t="inlineStr">
         <is>
-          <t>2026-09-28</t>
+          <t>2026-10-12</t>
         </is>
       </c>
       <c r="Q278" s="4" t="n"/>
@@ -21763,7 +21763,7 @@
       </c>
       <c r="P279" s="4" t="inlineStr">
         <is>
-          <t>2026-09-28</t>
+          <t>2026-10-12</t>
         </is>
       </c>
       <c r="Q279" s="4" t="n"/>
@@ -21840,7 +21840,7 @@
       </c>
       <c r="P280" s="4" t="inlineStr">
         <is>
-          <t>2026-09-28</t>
+          <t>2026-10-12</t>
         </is>
       </c>
       <c r="Q280" s="4" t="n"/>
@@ -21917,7 +21917,7 @@
       </c>
       <c r="P281" s="4" t="inlineStr">
         <is>
-          <t>2026-09-28</t>
+          <t>2026-10-12</t>
         </is>
       </c>
       <c r="Q281" s="4" t="n"/>
@@ -21994,7 +21994,7 @@
       </c>
       <c r="P282" s="4" t="inlineStr">
         <is>
-          <t>2026-09-28</t>
+          <t>2026-10-12</t>
         </is>
       </c>
       <c r="Q282" s="4" t="n"/>
@@ -22071,7 +22071,7 @@
       </c>
       <c r="P283" s="4" t="inlineStr">
         <is>
-          <t>2026-09-28</t>
+          <t>2026-10-12</t>
         </is>
       </c>
       <c r="Q283" s="4" t="n"/>
@@ -22148,7 +22148,7 @@
       </c>
       <c r="P284" s="4" t="inlineStr">
         <is>
-          <t>2026-09-28</t>
+          <t>2026-10-12</t>
         </is>
       </c>
       <c r="Q284" s="4" t="n"/>
@@ -22225,7 +22225,7 @@
       </c>
       <c r="P285" s="4" t="inlineStr">
         <is>
-          <t>2026-09-28</t>
+          <t>2026-10-12</t>
         </is>
       </c>
       <c r="Q285" s="4" t="n"/>
@@ -22302,7 +22302,7 @@
       </c>
       <c r="P286" s="4" t="inlineStr">
         <is>
-          <t>2026-09-28</t>
+          <t>2026-10-12</t>
         </is>
       </c>
       <c r="Q286" s="4" t="n"/>
@@ -22379,7 +22379,7 @@
       </c>
       <c r="P287" s="4" t="inlineStr">
         <is>
-          <t>2026-09-28</t>
+          <t>2026-10-12</t>
         </is>
       </c>
       <c r="Q287" s="4" t="n"/>
@@ -22456,7 +22456,7 @@
       </c>
       <c r="P288" s="4" t="inlineStr">
         <is>
-          <t>2026-09-28</t>
+          <t>2026-10-12</t>
         </is>
       </c>
       <c r="Q288" s="4" t="n"/>
@@ -22533,7 +22533,7 @@
       </c>
       <c r="P289" s="4" t="inlineStr">
         <is>
-          <t>2026-09-28</t>
+          <t>2026-10-12</t>
         </is>
       </c>
       <c r="Q289" s="4" t="n"/>
@@ -22610,7 +22610,7 @@
       </c>
       <c r="P290" s="4" t="inlineStr">
         <is>
-          <t>2026-09-28</t>
+          <t>2026-10-12</t>
         </is>
       </c>
       <c r="Q290" s="4" t="n"/>
@@ -22687,7 +22687,7 @@
       </c>
       <c r="P291" s="4" t="inlineStr">
         <is>
-          <t>2026-09-28</t>
+          <t>2026-10-12</t>
         </is>
       </c>
       <c r="Q291" s="4" t="n"/>
@@ -22764,7 +22764,7 @@
       </c>
       <c r="P292" s="4" t="inlineStr">
         <is>
-          <t>2026-09-28</t>
+          <t>2026-10-12</t>
         </is>
       </c>
       <c r="Q292" s="4" t="n"/>
@@ -22841,7 +22841,7 @@
       </c>
       <c r="P293" s="4" t="inlineStr">
         <is>
-          <t>2026-09-28</t>
+          <t>2026-10-12</t>
         </is>
       </c>
       <c r="Q293" s="4" t="n"/>
@@ -22918,7 +22918,7 @@
       </c>
       <c r="P294" s="4" t="inlineStr">
         <is>
-          <t>2026-09-28</t>
+          <t>2026-10-12</t>
         </is>
       </c>
       <c r="Q294" s="4" t="n"/>
@@ -22995,7 +22995,7 @@
       </c>
       <c r="P295" s="4" t="inlineStr">
         <is>
-          <t>2026-09-28</t>
+          <t>2026-10-12</t>
         </is>
       </c>
       <c r="Q295" s="4" t="n"/>
@@ -23072,7 +23072,7 @@
       </c>
       <c r="P296" s="4" t="inlineStr">
         <is>
-          <t>2026-09-28</t>
+          <t>2026-10-12</t>
         </is>
       </c>
       <c r="Q296" s="4" t="n"/>
@@ -23149,7 +23149,7 @@
       </c>
       <c r="P297" s="4" t="inlineStr">
         <is>
-          <t>2026-09-28</t>
+          <t>2026-10-12</t>
         </is>
       </c>
       <c r="Q297" s="4" t="n"/>
@@ -23226,7 +23226,7 @@
       </c>
       <c r="P298" s="4" t="inlineStr">
         <is>
-          <t>2026-09-28</t>
+          <t>2026-10-12</t>
         </is>
       </c>
       <c r="Q298" s="4" t="n"/>
@@ -23303,7 +23303,7 @@
       </c>
       <c r="P299" s="4" t="inlineStr">
         <is>
-          <t>2026-09-28</t>
+          <t>2026-10-12</t>
         </is>
       </c>
       <c r="Q299" s="4" t="n"/>
@@ -23380,7 +23380,7 @@
       </c>
       <c r="P300" s="4" t="inlineStr">
         <is>
-          <t>2026-09-28</t>
+          <t>2026-10-12</t>
         </is>
       </c>
       <c r="Q300" s="4" t="n"/>
@@ -23457,7 +23457,7 @@
       </c>
       <c r="P301" s="4" t="inlineStr">
         <is>
-          <t>2026-09-28</t>
+          <t>2026-10-12</t>
         </is>
       </c>
       <c r="Q301" s="4" t="n"/>
@@ -23534,7 +23534,7 @@
       </c>
       <c r="P302" s="4" t="inlineStr">
         <is>
-          <t>2026-09-28</t>
+          <t>2026-10-12</t>
         </is>
       </c>
       <c r="Q302" s="4" t="n"/>
@@ -23611,7 +23611,7 @@
       </c>
       <c r="P303" s="4" t="inlineStr">
         <is>
-          <t>2026-09-28</t>
+          <t>2026-10-12</t>
         </is>
       </c>
       <c r="Q303" s="4" t="n"/>
@@ -23688,7 +23688,7 @@
       </c>
       <c r="P304" s="4" t="inlineStr">
         <is>
-          <t>2026-09-28</t>
+          <t>2026-10-12</t>
         </is>
       </c>
       <c r="Q304" s="4" t="n"/>
@@ -23765,7 +23765,7 @@
       </c>
       <c r="P305" s="4" t="inlineStr">
         <is>
-          <t>2026-09-28</t>
+          <t>2026-10-12</t>
         </is>
       </c>
       <c r="Q305" s="4" t="n"/>
@@ -23842,7 +23842,7 @@
       </c>
       <c r="P306" s="4" t="inlineStr">
         <is>
-          <t>2026-09-28</t>
+          <t>2026-10-12</t>
         </is>
       </c>
       <c r="Q306" s="4" t="n"/>
@@ -23919,7 +23919,7 @@
       </c>
       <c r="P307" s="4" t="inlineStr">
         <is>
-          <t>2026-09-28</t>
+          <t>2026-10-12</t>
         </is>
       </c>
       <c r="Q307" s="4" t="n"/>
@@ -23998,7 +23998,7 @@
       </c>
       <c r="P308" s="4" t="inlineStr">
         <is>
-          <t>2026-09-28</t>
+          <t>2026-10-12</t>
         </is>
       </c>
       <c r="Q308" s="4" t="n"/>
@@ -24077,7 +24077,7 @@
       </c>
       <c r="P309" s="4" t="inlineStr">
         <is>
-          <t>2026-09-28</t>
+          <t>2026-10-12</t>
         </is>
       </c>
       <c r="Q309" s="4" t="n"/>
@@ -24156,7 +24156,7 @@
       </c>
       <c r="P310" s="4" t="inlineStr">
         <is>
-          <t>2026-09-28</t>
+          <t>2026-10-12</t>
         </is>
       </c>
       <c r="Q310" s="4" t="n"/>
@@ -24235,7 +24235,7 @@
       </c>
       <c r="P311" s="4" t="inlineStr">
         <is>
-          <t>2026-09-28</t>
+          <t>2026-10-12</t>
         </is>
       </c>
       <c r="Q311" s="4" t="n"/>
@@ -24314,7 +24314,7 @@
       </c>
       <c r="P312" s="4" t="inlineStr">
         <is>
-          <t>2026-09-28</t>
+          <t>2026-10-12</t>
         </is>
       </c>
       <c r="Q312" s="4" t="n"/>
@@ -24393,7 +24393,7 @@
       </c>
       <c r="P313" s="4" t="inlineStr">
         <is>
-          <t>2026-09-28</t>
+          <t>2026-10-12</t>
         </is>
       </c>
       <c r="Q313" s="4" t="n"/>
@@ -24472,7 +24472,7 @@
       </c>
       <c r="P314" s="4" t="inlineStr">
         <is>
-          <t>2026-09-28</t>
+          <t>2026-10-12</t>
         </is>
       </c>
       <c r="Q314" s="4" t="n"/>
@@ -24551,7 +24551,7 @@
       </c>
       <c r="P315" s="4" t="inlineStr">
         <is>
-          <t>2026-09-28</t>
+          <t>2026-10-12</t>
         </is>
       </c>
       <c r="Q315" s="4" t="n"/>
@@ -24630,7 +24630,7 @@
       </c>
       <c r="P316" s="4" t="inlineStr">
         <is>
-          <t>2026-09-28</t>
+          <t>2026-10-12</t>
         </is>
       </c>
       <c r="Q316" s="4" t="n"/>
@@ -24709,7 +24709,7 @@
       </c>
       <c r="P317" s="4" t="inlineStr">
         <is>
-          <t>2026-09-28</t>
+          <t>2026-10-12</t>
         </is>
       </c>
       <c r="Q317" s="4" t="n"/>
@@ -24788,7 +24788,7 @@
       </c>
       <c r="P318" s="4" t="inlineStr">
         <is>
-          <t>2026-09-28</t>
+          <t>2026-10-12</t>
         </is>
       </c>
       <c r="Q318" s="4" t="n"/>
@@ -24867,7 +24867,7 @@
       </c>
       <c r="P319" s="4" t="inlineStr">
         <is>
-          <t>2026-09-28</t>
+          <t>2026-10-12</t>
         </is>
       </c>
       <c r="Q319" s="4" t="n"/>
@@ -24946,7 +24946,7 @@
       </c>
       <c r="P320" s="4" t="inlineStr">
         <is>
-          <t>2026-09-28</t>
+          <t>2026-10-12</t>
         </is>
       </c>
       <c r="Q320" s="4" t="n"/>
@@ -25025,7 +25025,7 @@
       </c>
       <c r="P321" s="4" t="inlineStr">
         <is>
-          <t>2026-09-28</t>
+          <t>2026-10-12</t>
         </is>
       </c>
       <c r="Q321" s="4" t="n"/>
@@ -25104,7 +25104,7 @@
       </c>
       <c r="P322" s="4" t="inlineStr">
         <is>
-          <t>2026-09-28</t>
+          <t>2026-10-12</t>
         </is>
       </c>
       <c r="Q322" s="4" t="n"/>
@@ -25183,7 +25183,7 @@
       </c>
       <c r="P323" s="4" t="inlineStr">
         <is>
-          <t>2026-09-28</t>
+          <t>2026-10-12</t>
         </is>
       </c>
       <c r="Q323" s="4" t="n"/>
@@ -25262,7 +25262,7 @@
       </c>
       <c r="P324" s="4" t="inlineStr">
         <is>
-          <t>2026-09-28</t>
+          <t>2026-10-12</t>
         </is>
       </c>
       <c r="Q324" s="4" t="n"/>
@@ -25341,7 +25341,7 @@
       </c>
       <c r="P325" s="4" t="inlineStr">
         <is>
-          <t>2026-09-28</t>
+          <t>2026-10-12</t>
         </is>
       </c>
       <c r="Q325" s="4" t="n"/>
@@ -25420,7 +25420,7 @@
       </c>
       <c r="P326" s="4" t="inlineStr">
         <is>
-          <t>2026-09-28</t>
+          <t>2026-10-12</t>
         </is>
       </c>
       <c r="Q326" s="4" t="n"/>
@@ -25497,7 +25497,7 @@
       </c>
       <c r="P327" s="4" t="inlineStr">
         <is>
-          <t>2026-09-28</t>
+          <t>2026-10-12</t>
         </is>
       </c>
       <c r="Q327" s="4" t="n"/>
@@ -25574,7 +25574,7 @@
       </c>
       <c r="P328" s="4" t="inlineStr">
         <is>
-          <t>2026-09-28</t>
+          <t>2026-10-12</t>
         </is>
       </c>
       <c r="Q328" s="4" t="n"/>
@@ -25651,7 +25651,7 @@
       </c>
       <c r="P329" s="4" t="inlineStr">
         <is>
-          <t>2026-09-28</t>
+          <t>2026-10-12</t>
         </is>
       </c>
       <c r="Q329" s="4" t="n"/>
@@ -25728,7 +25728,7 @@
       </c>
       <c r="P330" s="4" t="inlineStr">
         <is>
-          <t>2026-09-28</t>
+          <t>2026-10-12</t>
         </is>
       </c>
       <c r="Q330" s="4" t="n"/>
@@ -25805,7 +25805,7 @@
       </c>
       <c r="P331" s="4" t="inlineStr">
         <is>
-          <t>2026-09-28</t>
+          <t>2026-10-12</t>
         </is>
       </c>
       <c r="Q331" s="4" t="n"/>
@@ -25882,7 +25882,7 @@
       </c>
       <c r="P332" s="4" t="inlineStr">
         <is>
-          <t>2026-09-28</t>
+          <t>2026-10-12</t>
         </is>
       </c>
       <c r="Q332" s="4" t="n"/>
@@ -25959,7 +25959,7 @@
       </c>
       <c r="P333" s="4" t="inlineStr">
         <is>
-          <t>2026-09-28</t>
+          <t>2026-10-12</t>
         </is>
       </c>
       <c r="Q333" s="4" t="n"/>
@@ -26036,7 +26036,7 @@
       </c>
       <c r="P334" s="4" t="inlineStr">
         <is>
-          <t>2026-09-28</t>
+          <t>2026-10-12</t>
         </is>
       </c>
       <c r="Q334" s="4" t="n"/>
@@ -26113,7 +26113,7 @@
       </c>
       <c r="P335" s="4" t="inlineStr">
         <is>
-          <t>2026-09-28</t>
+          <t>2026-10-12</t>
         </is>
       </c>
       <c r="Q335" s="4" t="n"/>
@@ -26190,7 +26190,7 @@
       </c>
       <c r="P336" s="4" t="inlineStr">
         <is>
-          <t>2026-09-28</t>
+          <t>2026-10-12</t>
         </is>
       </c>
       <c r="Q336" s="4" t="n"/>
@@ -26275,7 +26275,7 @@
       </c>
       <c r="B9" s="4" t="inlineStr">
         <is>
-          <t>2026-09-28</t>
+          <t>2026-10-12</t>
         </is>
       </c>
     </row>

--- a/assets/data/world-bank/excel/ove_banco_mundial_venezuela_pobreza_y_desigualdad.xlsx
+++ b/assets/data/world-bank/excel/ove_banco_mundial_venezuela_pobreza_y_desigualdad.xlsx
@@ -715,7 +715,7 @@
       </c>
       <c r="P7" s="4" t="inlineStr">
         <is>
-          <t>2026-10-12</t>
+          <t>2026-10-19</t>
         </is>
       </c>
       <c r="Q7" s="4" t="n"/>
@@ -792,7 +792,7 @@
       </c>
       <c r="P8" s="4" t="inlineStr">
         <is>
-          <t>2026-10-12</t>
+          <t>2026-10-19</t>
         </is>
       </c>
       <c r="Q8" s="4" t="n"/>
@@ -869,7 +869,7 @@
       </c>
       <c r="P9" s="4" t="inlineStr">
         <is>
-          <t>2026-10-12</t>
+          <t>2026-10-19</t>
         </is>
       </c>
       <c r="Q9" s="4" t="n"/>
@@ -946,7 +946,7 @@
       </c>
       <c r="P10" s="4" t="inlineStr">
         <is>
-          <t>2026-10-12</t>
+          <t>2026-10-19</t>
         </is>
       </c>
       <c r="Q10" s="4" t="n"/>
@@ -1023,7 +1023,7 @@
       </c>
       <c r="P11" s="4" t="inlineStr">
         <is>
-          <t>2026-10-12</t>
+          <t>2026-10-19</t>
         </is>
       </c>
       <c r="Q11" s="4" t="n"/>
@@ -1100,7 +1100,7 @@
       </c>
       <c r="P12" s="4" t="inlineStr">
         <is>
-          <t>2026-10-12</t>
+          <t>2026-10-19</t>
         </is>
       </c>
       <c r="Q12" s="4" t="n"/>
@@ -1177,7 +1177,7 @@
       </c>
       <c r="P13" s="4" t="inlineStr">
         <is>
-          <t>2026-10-12</t>
+          <t>2026-10-19</t>
         </is>
       </c>
       <c r="Q13" s="4" t="n"/>
@@ -1254,7 +1254,7 @@
       </c>
       <c r="P14" s="4" t="inlineStr">
         <is>
-          <t>2026-10-12</t>
+          <t>2026-10-19</t>
         </is>
       </c>
       <c r="Q14" s="4" t="n"/>
@@ -1331,7 +1331,7 @@
       </c>
       <c r="P15" s="4" t="inlineStr">
         <is>
-          <t>2026-10-12</t>
+          <t>2026-10-19</t>
         </is>
       </c>
       <c r="Q15" s="4" t="n"/>
@@ -1408,7 +1408,7 @@
       </c>
       <c r="P16" s="4" t="inlineStr">
         <is>
-          <t>2026-10-12</t>
+          <t>2026-10-19</t>
         </is>
       </c>
       <c r="Q16" s="4" t="n"/>
@@ -1485,7 +1485,7 @@
       </c>
       <c r="P17" s="4" t="inlineStr">
         <is>
-          <t>2026-10-12</t>
+          <t>2026-10-19</t>
         </is>
       </c>
       <c r="Q17" s="4" t="n"/>
@@ -1562,7 +1562,7 @@
       </c>
       <c r="P18" s="4" t="inlineStr">
         <is>
-          <t>2026-10-12</t>
+          <t>2026-10-19</t>
         </is>
       </c>
       <c r="Q18" s="4" t="n"/>
@@ -1639,7 +1639,7 @@
       </c>
       <c r="P19" s="4" t="inlineStr">
         <is>
-          <t>2026-10-12</t>
+          <t>2026-10-19</t>
         </is>
       </c>
       <c r="Q19" s="4" t="n"/>
@@ -1716,7 +1716,7 @@
       </c>
       <c r="P20" s="4" t="inlineStr">
         <is>
-          <t>2026-10-12</t>
+          <t>2026-10-19</t>
         </is>
       </c>
       <c r="Q20" s="4" t="n"/>
@@ -1793,7 +1793,7 @@
       </c>
       <c r="P21" s="4" t="inlineStr">
         <is>
-          <t>2026-10-12</t>
+          <t>2026-10-19</t>
         </is>
       </c>
       <c r="Q21" s="4" t="n"/>
@@ -1870,7 +1870,7 @@
       </c>
       <c r="P22" s="4" t="inlineStr">
         <is>
-          <t>2026-10-12</t>
+          <t>2026-10-19</t>
         </is>
       </c>
       <c r="Q22" s="4" t="n"/>
@@ -1947,7 +1947,7 @@
       </c>
       <c r="P23" s="4" t="inlineStr">
         <is>
-          <t>2026-10-12</t>
+          <t>2026-10-19</t>
         </is>
       </c>
       <c r="Q23" s="4" t="n"/>
@@ -2024,7 +2024,7 @@
       </c>
       <c r="P24" s="4" t="inlineStr">
         <is>
-          <t>2026-10-12</t>
+          <t>2026-10-19</t>
         </is>
       </c>
       <c r="Q24" s="4" t="n"/>
@@ -2101,7 +2101,7 @@
       </c>
       <c r="P25" s="4" t="inlineStr">
         <is>
-          <t>2026-10-12</t>
+          <t>2026-10-19</t>
         </is>
       </c>
       <c r="Q25" s="4" t="n"/>
@@ -2178,7 +2178,7 @@
       </c>
       <c r="P26" s="4" t="inlineStr">
         <is>
-          <t>2026-10-12</t>
+          <t>2026-10-19</t>
         </is>
       </c>
       <c r="Q26" s="4" t="n"/>
@@ -2255,7 +2255,7 @@
       </c>
       <c r="P27" s="4" t="inlineStr">
         <is>
-          <t>2026-10-12</t>
+          <t>2026-10-19</t>
         </is>
       </c>
       <c r="Q27" s="4" t="n"/>
@@ -2334,7 +2334,7 @@
       </c>
       <c r="P28" s="4" t="inlineStr">
         <is>
-          <t>2026-10-12</t>
+          <t>2026-10-19</t>
         </is>
       </c>
       <c r="Q28" s="4" t="n"/>
@@ -2411,7 +2411,7 @@
       </c>
       <c r="P29" s="4" t="inlineStr">
         <is>
-          <t>2026-10-12</t>
+          <t>2026-10-19</t>
         </is>
       </c>
       <c r="Q29" s="4" t="n"/>
@@ -2488,7 +2488,7 @@
       </c>
       <c r="P30" s="4" t="inlineStr">
         <is>
-          <t>2026-10-12</t>
+          <t>2026-10-19</t>
         </is>
       </c>
       <c r="Q30" s="4" t="n"/>
@@ -2565,7 +2565,7 @@
       </c>
       <c r="P31" s="4" t="inlineStr">
         <is>
-          <t>2026-10-12</t>
+          <t>2026-10-19</t>
         </is>
       </c>
       <c r="Q31" s="4" t="n"/>
@@ -2642,7 +2642,7 @@
       </c>
       <c r="P32" s="4" t="inlineStr">
         <is>
-          <t>2026-10-12</t>
+          <t>2026-10-19</t>
         </is>
       </c>
       <c r="Q32" s="4" t="n"/>
@@ -2719,7 +2719,7 @@
       </c>
       <c r="P33" s="4" t="inlineStr">
         <is>
-          <t>2026-10-12</t>
+          <t>2026-10-19</t>
         </is>
       </c>
       <c r="Q33" s="4" t="n"/>
@@ -2798,7 +2798,7 @@
       </c>
       <c r="P34" s="4" t="inlineStr">
         <is>
-          <t>2026-10-12</t>
+          <t>2026-10-19</t>
         </is>
       </c>
       <c r="Q34" s="4" t="n"/>
@@ -2875,7 +2875,7 @@
       </c>
       <c r="P35" s="4" t="inlineStr">
         <is>
-          <t>2026-10-12</t>
+          <t>2026-10-19</t>
         </is>
       </c>
       <c r="Q35" s="4" t="n"/>
@@ -2954,7 +2954,7 @@
       </c>
       <c r="P36" s="4" t="inlineStr">
         <is>
-          <t>2026-10-12</t>
+          <t>2026-10-19</t>
         </is>
       </c>
       <c r="Q36" s="4" t="n"/>
@@ -3031,7 +3031,7 @@
       </c>
       <c r="P37" s="4" t="inlineStr">
         <is>
-          <t>2026-10-12</t>
+          <t>2026-10-19</t>
         </is>
       </c>
       <c r="Q37" s="4" t="n"/>
@@ -3108,7 +3108,7 @@
       </c>
       <c r="P38" s="4" t="inlineStr">
         <is>
-          <t>2026-10-12</t>
+          <t>2026-10-19</t>
         </is>
       </c>
       <c r="Q38" s="4" t="n"/>
@@ -3187,7 +3187,7 @@
       </c>
       <c r="P39" s="4" t="inlineStr">
         <is>
-          <t>2026-10-12</t>
+          <t>2026-10-19</t>
         </is>
       </c>
       <c r="Q39" s="4" t="n"/>
@@ -3264,7 +3264,7 @@
       </c>
       <c r="P40" s="4" t="inlineStr">
         <is>
-          <t>2026-10-12</t>
+          <t>2026-10-19</t>
         </is>
       </c>
       <c r="Q40" s="4" t="n"/>
@@ -3341,7 +3341,7 @@
       </c>
       <c r="P41" s="4" t="inlineStr">
         <is>
-          <t>2026-10-12</t>
+          <t>2026-10-19</t>
         </is>
       </c>
       <c r="Q41" s="4" t="n"/>
@@ -3420,7 +3420,7 @@
       </c>
       <c r="P42" s="4" t="inlineStr">
         <is>
-          <t>2026-10-12</t>
+          <t>2026-10-19</t>
         </is>
       </c>
       <c r="Q42" s="4" t="n"/>
@@ -3497,7 +3497,7 @@
       </c>
       <c r="P43" s="4" t="inlineStr">
         <is>
-          <t>2026-10-12</t>
+          <t>2026-10-19</t>
         </is>
       </c>
       <c r="Q43" s="4" t="n"/>
@@ -3574,7 +3574,7 @@
       </c>
       <c r="P44" s="4" t="inlineStr">
         <is>
-          <t>2026-10-12</t>
+          <t>2026-10-19</t>
         </is>
       </c>
       <c r="Q44" s="4" t="n"/>
@@ -3653,7 +3653,7 @@
       </c>
       <c r="P45" s="4" t="inlineStr">
         <is>
-          <t>2026-10-12</t>
+          <t>2026-10-19</t>
         </is>
       </c>
       <c r="Q45" s="4" t="n"/>
@@ -3732,7 +3732,7 @@
       </c>
       <c r="P46" s="4" t="inlineStr">
         <is>
-          <t>2026-10-12</t>
+          <t>2026-10-19</t>
         </is>
       </c>
       <c r="Q46" s="4" t="n"/>
@@ -3809,7 +3809,7 @@
       </c>
       <c r="P47" s="4" t="inlineStr">
         <is>
-          <t>2026-10-12</t>
+          <t>2026-10-19</t>
         </is>
       </c>
       <c r="Q47" s="4" t="n"/>
@@ -3888,7 +3888,7 @@
       </c>
       <c r="P48" s="4" t="inlineStr">
         <is>
-          <t>2026-10-12</t>
+          <t>2026-10-19</t>
         </is>
       </c>
       <c r="Q48" s="4" t="n"/>
@@ -3967,7 +3967,7 @@
       </c>
       <c r="P49" s="4" t="inlineStr">
         <is>
-          <t>2026-10-12</t>
+          <t>2026-10-19</t>
         </is>
       </c>
       <c r="Q49" s="4" t="n"/>
@@ -4046,7 +4046,7 @@
       </c>
       <c r="P50" s="4" t="inlineStr">
         <is>
-          <t>2026-10-12</t>
+          <t>2026-10-19</t>
         </is>
       </c>
       <c r="Q50" s="4" t="n"/>
@@ -4125,7 +4125,7 @@
       </c>
       <c r="P51" s="4" t="inlineStr">
         <is>
-          <t>2026-10-12</t>
+          <t>2026-10-19</t>
         </is>
       </c>
       <c r="Q51" s="4" t="n"/>
@@ -4204,7 +4204,7 @@
       </c>
       <c r="P52" s="4" t="inlineStr">
         <is>
-          <t>2026-10-12</t>
+          <t>2026-10-19</t>
         </is>
       </c>
       <c r="Q52" s="4" t="n"/>
@@ -4283,7 +4283,7 @@
       </c>
       <c r="P53" s="4" t="inlineStr">
         <is>
-          <t>2026-10-12</t>
+          <t>2026-10-19</t>
         </is>
       </c>
       <c r="Q53" s="4" t="n"/>
@@ -4360,7 +4360,7 @@
       </c>
       <c r="P54" s="4" t="inlineStr">
         <is>
-          <t>2026-10-12</t>
+          <t>2026-10-19</t>
         </is>
       </c>
       <c r="Q54" s="4" t="n"/>
@@ -4437,7 +4437,7 @@
       </c>
       <c r="P55" s="4" t="inlineStr">
         <is>
-          <t>2026-10-12</t>
+          <t>2026-10-19</t>
         </is>
       </c>
       <c r="Q55" s="4" t="n"/>
@@ -4514,7 +4514,7 @@
       </c>
       <c r="P56" s="4" t="inlineStr">
         <is>
-          <t>2026-10-12</t>
+          <t>2026-10-19</t>
         </is>
       </c>
       <c r="Q56" s="4" t="n"/>
@@ -4591,7 +4591,7 @@
       </c>
       <c r="P57" s="4" t="inlineStr">
         <is>
-          <t>2026-10-12</t>
+          <t>2026-10-19</t>
         </is>
       </c>
       <c r="Q57" s="4" t="n"/>
@@ -4668,7 +4668,7 @@
       </c>
       <c r="P58" s="4" t="inlineStr">
         <is>
-          <t>2026-10-12</t>
+          <t>2026-10-19</t>
         </is>
       </c>
       <c r="Q58" s="4" t="n"/>
@@ -4745,7 +4745,7 @@
       </c>
       <c r="P59" s="4" t="inlineStr">
         <is>
-          <t>2026-10-12</t>
+          <t>2026-10-19</t>
         </is>
       </c>
       <c r="Q59" s="4" t="n"/>
@@ -4822,7 +4822,7 @@
       </c>
       <c r="P60" s="4" t="inlineStr">
         <is>
-          <t>2026-10-12</t>
+          <t>2026-10-19</t>
         </is>
       </c>
       <c r="Q60" s="4" t="n"/>
@@ -4899,7 +4899,7 @@
       </c>
       <c r="P61" s="4" t="inlineStr">
         <is>
-          <t>2026-10-12</t>
+          <t>2026-10-19</t>
         </is>
       </c>
       <c r="Q61" s="4" t="n"/>
@@ -4976,7 +4976,7 @@
       </c>
       <c r="P62" s="4" t="inlineStr">
         <is>
-          <t>2026-10-12</t>
+          <t>2026-10-19</t>
         </is>
       </c>
       <c r="Q62" s="4" t="n"/>
@@ -5053,7 +5053,7 @@
       </c>
       <c r="P63" s="4" t="inlineStr">
         <is>
-          <t>2026-10-12</t>
+          <t>2026-10-19</t>
         </is>
       </c>
       <c r="Q63" s="4" t="n"/>
@@ -5130,7 +5130,7 @@
       </c>
       <c r="P64" s="4" t="inlineStr">
         <is>
-          <t>2026-10-12</t>
+          <t>2026-10-19</t>
         </is>
       </c>
       <c r="Q64" s="4" t="n"/>
@@ -5207,7 +5207,7 @@
       </c>
       <c r="P65" s="4" t="inlineStr">
         <is>
-          <t>2026-10-12</t>
+          <t>2026-10-19</t>
         </is>
       </c>
       <c r="Q65" s="4" t="n"/>
@@ -5284,7 +5284,7 @@
       </c>
       <c r="P66" s="4" t="inlineStr">
         <is>
-          <t>2026-10-12</t>
+          <t>2026-10-19</t>
         </is>
       </c>
       <c r="Q66" s="4" t="n"/>
@@ -5361,7 +5361,7 @@
       </c>
       <c r="P67" s="4" t="inlineStr">
         <is>
-          <t>2026-10-12</t>
+          <t>2026-10-19</t>
         </is>
       </c>
       <c r="Q67" s="4" t="n"/>
@@ -5438,7 +5438,7 @@
       </c>
       <c r="P68" s="4" t="inlineStr">
         <is>
-          <t>2026-10-12</t>
+          <t>2026-10-19</t>
         </is>
       </c>
       <c r="Q68" s="4" t="n"/>
@@ -5515,7 +5515,7 @@
       </c>
       <c r="P69" s="4" t="inlineStr">
         <is>
-          <t>2026-10-12</t>
+          <t>2026-10-19</t>
         </is>
       </c>
       <c r="Q69" s="4" t="n"/>
@@ -5592,7 +5592,7 @@
       </c>
       <c r="P70" s="4" t="inlineStr">
         <is>
-          <t>2026-10-12</t>
+          <t>2026-10-19</t>
         </is>
       </c>
       <c r="Q70" s="4" t="n"/>
@@ -5669,7 +5669,7 @@
       </c>
       <c r="P71" s="4" t="inlineStr">
         <is>
-          <t>2026-10-12</t>
+          <t>2026-10-19</t>
         </is>
       </c>
       <c r="Q71" s="4" t="n"/>
@@ -5746,7 +5746,7 @@
       </c>
       <c r="P72" s="4" t="inlineStr">
         <is>
-          <t>2026-10-12</t>
+          <t>2026-10-19</t>
         </is>
       </c>
       <c r="Q72" s="4" t="n"/>
@@ -5823,7 +5823,7 @@
       </c>
       <c r="P73" s="4" t="inlineStr">
         <is>
-          <t>2026-10-12</t>
+          <t>2026-10-19</t>
         </is>
       </c>
       <c r="Q73" s="4" t="n"/>
@@ -5900,7 +5900,7 @@
       </c>
       <c r="P74" s="4" t="inlineStr">
         <is>
-          <t>2026-10-12</t>
+          <t>2026-10-19</t>
         </is>
       </c>
       <c r="Q74" s="4" t="n"/>
@@ -5977,7 +5977,7 @@
       </c>
       <c r="P75" s="4" t="inlineStr">
         <is>
-          <t>2026-10-12</t>
+          <t>2026-10-19</t>
         </is>
       </c>
       <c r="Q75" s="4" t="n"/>
@@ -6054,7 +6054,7 @@
       </c>
       <c r="P76" s="4" t="inlineStr">
         <is>
-          <t>2026-10-12</t>
+          <t>2026-10-19</t>
         </is>
       </c>
       <c r="Q76" s="4" t="n"/>
@@ -6131,7 +6131,7 @@
       </c>
       <c r="P77" s="4" t="inlineStr">
         <is>
-          <t>2026-10-12</t>
+          <t>2026-10-19</t>
         </is>
       </c>
       <c r="Q77" s="4" t="n"/>
@@ -6208,7 +6208,7 @@
       </c>
       <c r="P78" s="4" t="inlineStr">
         <is>
-          <t>2026-10-12</t>
+          <t>2026-10-19</t>
         </is>
       </c>
       <c r="Q78" s="4" t="n"/>
@@ -6285,7 +6285,7 @@
       </c>
       <c r="P79" s="4" t="inlineStr">
         <is>
-          <t>2026-10-12</t>
+          <t>2026-10-19</t>
         </is>
       </c>
       <c r="Q79" s="4" t="n"/>
@@ -6362,7 +6362,7 @@
       </c>
       <c r="P80" s="4" t="inlineStr">
         <is>
-          <t>2026-10-12</t>
+          <t>2026-10-19</t>
         </is>
       </c>
       <c r="Q80" s="4" t="n"/>
@@ -6439,7 +6439,7 @@
       </c>
       <c r="P81" s="4" t="inlineStr">
         <is>
-          <t>2026-10-12</t>
+          <t>2026-10-19</t>
         </is>
       </c>
       <c r="Q81" s="4" t="n"/>
@@ -6516,7 +6516,7 @@
       </c>
       <c r="P82" s="4" t="inlineStr">
         <is>
-          <t>2026-10-12</t>
+          <t>2026-10-19</t>
         </is>
       </c>
       <c r="Q82" s="4" t="n"/>
@@ -6593,7 +6593,7 @@
       </c>
       <c r="P83" s="4" t="inlineStr">
         <is>
-          <t>2026-10-12</t>
+          <t>2026-10-19</t>
         </is>
       </c>
       <c r="Q83" s="4" t="n"/>
@@ -6670,7 +6670,7 @@
       </c>
       <c r="P84" s="4" t="inlineStr">
         <is>
-          <t>2026-10-12</t>
+          <t>2026-10-19</t>
         </is>
       </c>
       <c r="Q84" s="4" t="n"/>
@@ -6747,7 +6747,7 @@
       </c>
       <c r="P85" s="4" t="inlineStr">
         <is>
-          <t>2026-10-12</t>
+          <t>2026-10-19</t>
         </is>
       </c>
       <c r="Q85" s="4" t="n"/>
@@ -6824,7 +6824,7 @@
       </c>
       <c r="P86" s="4" t="inlineStr">
         <is>
-          <t>2026-10-12</t>
+          <t>2026-10-19</t>
         </is>
       </c>
       <c r="Q86" s="4" t="n"/>
@@ -6901,7 +6901,7 @@
       </c>
       <c r="P87" s="4" t="inlineStr">
         <is>
-          <t>2026-10-12</t>
+          <t>2026-10-19</t>
         </is>
       </c>
       <c r="Q87" s="4" t="n"/>
@@ -6978,7 +6978,7 @@
       </c>
       <c r="P88" s="4" t="inlineStr">
         <is>
-          <t>2026-10-12</t>
+          <t>2026-10-19</t>
         </is>
       </c>
       <c r="Q88" s="4" t="n"/>
@@ -7055,7 +7055,7 @@
       </c>
       <c r="P89" s="4" t="inlineStr">
         <is>
-          <t>2026-10-12</t>
+          <t>2026-10-19</t>
         </is>
       </c>
       <c r="Q89" s="4" t="n"/>
@@ -7132,7 +7132,7 @@
       </c>
       <c r="P90" s="4" t="inlineStr">
         <is>
-          <t>2026-10-12</t>
+          <t>2026-10-19</t>
         </is>
       </c>
       <c r="Q90" s="4" t="n"/>
@@ -7209,7 +7209,7 @@
       </c>
       <c r="P91" s="4" t="inlineStr">
         <is>
-          <t>2026-10-12</t>
+          <t>2026-10-19</t>
         </is>
       </c>
       <c r="Q91" s="4" t="n"/>
@@ -7286,7 +7286,7 @@
       </c>
       <c r="P92" s="4" t="inlineStr">
         <is>
-          <t>2026-10-12</t>
+          <t>2026-10-19</t>
         </is>
       </c>
       <c r="Q92" s="4" t="n"/>
@@ -7363,7 +7363,7 @@
       </c>
       <c r="P93" s="4" t="inlineStr">
         <is>
-          <t>2026-10-12</t>
+          <t>2026-10-19</t>
         </is>
       </c>
       <c r="Q93" s="4" t="n"/>
@@ -7442,7 +7442,7 @@
       </c>
       <c r="P94" s="4" t="inlineStr">
         <is>
-          <t>2026-10-12</t>
+          <t>2026-10-19</t>
         </is>
       </c>
       <c r="Q94" s="4" t="n"/>
@@ -7519,7 +7519,7 @@
       </c>
       <c r="P95" s="4" t="inlineStr">
         <is>
-          <t>2026-10-12</t>
+          <t>2026-10-19</t>
         </is>
       </c>
       <c r="Q95" s="4" t="n"/>
@@ -7596,7 +7596,7 @@
       </c>
       <c r="P96" s="4" t="inlineStr">
         <is>
-          <t>2026-10-12</t>
+          <t>2026-10-19</t>
         </is>
       </c>
       <c r="Q96" s="4" t="n"/>
@@ -7673,7 +7673,7 @@
       </c>
       <c r="P97" s="4" t="inlineStr">
         <is>
-          <t>2026-10-12</t>
+          <t>2026-10-19</t>
         </is>
       </c>
       <c r="Q97" s="4" t="n"/>
@@ -7750,7 +7750,7 @@
       </c>
       <c r="P98" s="4" t="inlineStr">
         <is>
-          <t>2026-10-12</t>
+          <t>2026-10-19</t>
         </is>
       </c>
       <c r="Q98" s="4" t="n"/>
@@ -7827,7 +7827,7 @@
       </c>
       <c r="P99" s="4" t="inlineStr">
         <is>
-          <t>2026-10-12</t>
+          <t>2026-10-19</t>
         </is>
       </c>
       <c r="Q99" s="4" t="n"/>
@@ -7906,7 +7906,7 @@
       </c>
       <c r="P100" s="4" t="inlineStr">
         <is>
-          <t>2026-10-12</t>
+          <t>2026-10-19</t>
         </is>
       </c>
       <c r="Q100" s="4" t="n"/>
@@ -7983,7 +7983,7 @@
       </c>
       <c r="P101" s="4" t="inlineStr">
         <is>
-          <t>2026-10-12</t>
+          <t>2026-10-19</t>
         </is>
       </c>
       <c r="Q101" s="4" t="n"/>
@@ -8062,7 +8062,7 @@
       </c>
       <c r="P102" s="4" t="inlineStr">
         <is>
-          <t>2026-10-12</t>
+          <t>2026-10-19</t>
         </is>
       </c>
       <c r="Q102" s="4" t="n"/>
@@ -8139,7 +8139,7 @@
       </c>
       <c r="P103" s="4" t="inlineStr">
         <is>
-          <t>2026-10-12</t>
+          <t>2026-10-19</t>
         </is>
       </c>
       <c r="Q103" s="4" t="n"/>
@@ -8216,7 +8216,7 @@
       </c>
       <c r="P104" s="4" t="inlineStr">
         <is>
-          <t>2026-10-12</t>
+          <t>2026-10-19</t>
         </is>
       </c>
       <c r="Q104" s="4" t="n"/>
@@ -8295,7 +8295,7 @@
       </c>
       <c r="P105" s="4" t="inlineStr">
         <is>
-          <t>2026-10-12</t>
+          <t>2026-10-19</t>
         </is>
       </c>
       <c r="Q105" s="4" t="n"/>
@@ -8372,7 +8372,7 @@
       </c>
       <c r="P106" s="4" t="inlineStr">
         <is>
-          <t>2026-10-12</t>
+          <t>2026-10-19</t>
         </is>
       </c>
       <c r="Q106" s="4" t="n"/>
@@ -8449,7 +8449,7 @@
       </c>
       <c r="P107" s="4" t="inlineStr">
         <is>
-          <t>2026-10-12</t>
+          <t>2026-10-19</t>
         </is>
       </c>
       <c r="Q107" s="4" t="n"/>
@@ -8528,7 +8528,7 @@
       </c>
       <c r="P108" s="4" t="inlineStr">
         <is>
-          <t>2026-10-12</t>
+          <t>2026-10-19</t>
         </is>
       </c>
       <c r="Q108" s="4" t="n"/>
@@ -8605,7 +8605,7 @@
       </c>
       <c r="P109" s="4" t="inlineStr">
         <is>
-          <t>2026-10-12</t>
+          <t>2026-10-19</t>
         </is>
       </c>
       <c r="Q109" s="4" t="n"/>
@@ -8682,7 +8682,7 @@
       </c>
       <c r="P110" s="4" t="inlineStr">
         <is>
-          <t>2026-10-12</t>
+          <t>2026-10-19</t>
         </is>
       </c>
       <c r="Q110" s="4" t="n"/>
@@ -8761,7 +8761,7 @@
       </c>
       <c r="P111" s="4" t="inlineStr">
         <is>
-          <t>2026-10-12</t>
+          <t>2026-10-19</t>
         </is>
       </c>
       <c r="Q111" s="4" t="n"/>
@@ -8840,7 +8840,7 @@
       </c>
       <c r="P112" s="4" t="inlineStr">
         <is>
-          <t>2026-10-12</t>
+          <t>2026-10-19</t>
         </is>
       </c>
       <c r="Q112" s="4" t="n"/>
@@ -8917,7 +8917,7 @@
       </c>
       <c r="P113" s="4" t="inlineStr">
         <is>
-          <t>2026-10-12</t>
+          <t>2026-10-19</t>
         </is>
       </c>
       <c r="Q113" s="4" t="n"/>
@@ -8996,7 +8996,7 @@
       </c>
       <c r="P114" s="4" t="inlineStr">
         <is>
-          <t>2026-10-12</t>
+          <t>2026-10-19</t>
         </is>
       </c>
       <c r="Q114" s="4" t="n"/>
@@ -9075,7 +9075,7 @@
       </c>
       <c r="P115" s="4" t="inlineStr">
         <is>
-          <t>2026-10-12</t>
+          <t>2026-10-19</t>
         </is>
       </c>
       <c r="Q115" s="4" t="n"/>
@@ -9154,7 +9154,7 @@
       </c>
       <c r="P116" s="4" t="inlineStr">
         <is>
-          <t>2026-10-12</t>
+          <t>2026-10-19</t>
         </is>
       </c>
       <c r="Q116" s="4" t="n"/>
@@ -9233,7 +9233,7 @@
       </c>
       <c r="P117" s="4" t="inlineStr">
         <is>
-          <t>2026-10-12</t>
+          <t>2026-10-19</t>
         </is>
       </c>
       <c r="Q117" s="4" t="n"/>
@@ -9312,7 +9312,7 @@
       </c>
       <c r="P118" s="4" t="inlineStr">
         <is>
-          <t>2026-10-12</t>
+          <t>2026-10-19</t>
         </is>
       </c>
       <c r="Q118" s="4" t="n"/>
@@ -9391,7 +9391,7 @@
       </c>
       <c r="P119" s="4" t="inlineStr">
         <is>
-          <t>2026-10-12</t>
+          <t>2026-10-19</t>
         </is>
       </c>
       <c r="Q119" s="4" t="n"/>
@@ -9468,7 +9468,7 @@
       </c>
       <c r="P120" s="4" t="inlineStr">
         <is>
-          <t>2026-10-12</t>
+          <t>2026-10-19</t>
         </is>
       </c>
       <c r="Q120" s="4" t="n"/>
@@ -9545,7 +9545,7 @@
       </c>
       <c r="P121" s="4" t="inlineStr">
         <is>
-          <t>2026-10-12</t>
+          <t>2026-10-19</t>
         </is>
       </c>
       <c r="Q121" s="4" t="n"/>
@@ -9622,7 +9622,7 @@
       </c>
       <c r="P122" s="4" t="inlineStr">
         <is>
-          <t>2026-10-12</t>
+          <t>2026-10-19</t>
         </is>
       </c>
       <c r="Q122" s="4" t="n"/>
@@ -9699,7 +9699,7 @@
       </c>
       <c r="P123" s="4" t="inlineStr">
         <is>
-          <t>2026-10-12</t>
+          <t>2026-10-19</t>
         </is>
       </c>
       <c r="Q123" s="4" t="n"/>
@@ -9776,7 +9776,7 @@
       </c>
       <c r="P124" s="4" t="inlineStr">
         <is>
-          <t>2026-10-12</t>
+          <t>2026-10-19</t>
         </is>
       </c>
       <c r="Q124" s="4" t="n"/>
@@ -9853,7 +9853,7 @@
       </c>
       <c r="P125" s="4" t="inlineStr">
         <is>
-          <t>2026-10-12</t>
+          <t>2026-10-19</t>
         </is>
       </c>
       <c r="Q125" s="4" t="n"/>
@@ -9930,7 +9930,7 @@
       </c>
       <c r="P126" s="4" t="inlineStr">
         <is>
-          <t>2026-10-12</t>
+          <t>2026-10-19</t>
         </is>
       </c>
       <c r="Q126" s="4" t="n"/>
@@ -10007,7 +10007,7 @@
       </c>
       <c r="P127" s="4" t="inlineStr">
         <is>
-          <t>2026-10-12</t>
+          <t>2026-10-19</t>
         </is>
       </c>
       <c r="Q127" s="4" t="n"/>
@@ -10084,7 +10084,7 @@
       </c>
       <c r="P128" s="4" t="inlineStr">
         <is>
-          <t>2026-10-12</t>
+          <t>2026-10-19</t>
         </is>
       </c>
       <c r="Q128" s="4" t="n"/>
@@ -10161,7 +10161,7 @@
       </c>
       <c r="P129" s="4" t="inlineStr">
         <is>
-          <t>2026-10-12</t>
+          <t>2026-10-19</t>
         </is>
       </c>
       <c r="Q129" s="4" t="n"/>
@@ -10238,7 +10238,7 @@
       </c>
       <c r="P130" s="4" t="inlineStr">
         <is>
-          <t>2026-10-12</t>
+          <t>2026-10-19</t>
         </is>
       </c>
       <c r="Q130" s="4" t="n"/>
@@ -10315,7 +10315,7 @@
       </c>
       <c r="P131" s="4" t="inlineStr">
         <is>
-          <t>2026-10-12</t>
+          <t>2026-10-19</t>
         </is>
       </c>
       <c r="Q131" s="4" t="n"/>
@@ -10392,7 +10392,7 @@
       </c>
       <c r="P132" s="4" t="inlineStr">
         <is>
-          <t>2026-10-12</t>
+          <t>2026-10-19</t>
         </is>
       </c>
       <c r="Q132" s="4" t="n"/>
@@ -10469,7 +10469,7 @@
       </c>
       <c r="P133" s="4" t="inlineStr">
         <is>
-          <t>2026-10-12</t>
+          <t>2026-10-19</t>
         </is>
       </c>
       <c r="Q133" s="4" t="n"/>
@@ -10546,7 +10546,7 @@
       </c>
       <c r="P134" s="4" t="inlineStr">
         <is>
-          <t>2026-10-12</t>
+          <t>2026-10-19</t>
         </is>
       </c>
       <c r="Q134" s="4" t="n"/>
@@ -10623,7 +10623,7 @@
       </c>
       <c r="P135" s="4" t="inlineStr">
         <is>
-          <t>2026-10-12</t>
+          <t>2026-10-19</t>
         </is>
       </c>
       <c r="Q135" s="4" t="n"/>
@@ -10700,7 +10700,7 @@
       </c>
       <c r="P136" s="4" t="inlineStr">
         <is>
-          <t>2026-10-12</t>
+          <t>2026-10-19</t>
         </is>
       </c>
       <c r="Q136" s="4" t="n"/>
@@ -10777,7 +10777,7 @@
       </c>
       <c r="P137" s="4" t="inlineStr">
         <is>
-          <t>2026-10-12</t>
+          <t>2026-10-19</t>
         </is>
       </c>
       <c r="Q137" s="4" t="n"/>
@@ -10854,7 +10854,7 @@
       </c>
       <c r="P138" s="4" t="inlineStr">
         <is>
-          <t>2026-10-12</t>
+          <t>2026-10-19</t>
         </is>
       </c>
       <c r="Q138" s="4" t="n"/>
@@ -10931,7 +10931,7 @@
       </c>
       <c r="P139" s="4" t="inlineStr">
         <is>
-          <t>2026-10-12</t>
+          <t>2026-10-19</t>
         </is>
       </c>
       <c r="Q139" s="4" t="n"/>
@@ -11008,7 +11008,7 @@
       </c>
       <c r="P140" s="4" t="inlineStr">
         <is>
-          <t>2026-10-12</t>
+          <t>2026-10-19</t>
         </is>
       </c>
       <c r="Q140" s="4" t="n"/>
@@ -11085,7 +11085,7 @@
       </c>
       <c r="P141" s="4" t="inlineStr">
         <is>
-          <t>2026-10-12</t>
+          <t>2026-10-19</t>
         </is>
       </c>
       <c r="Q141" s="4" t="n"/>
@@ -11162,7 +11162,7 @@
       </c>
       <c r="P142" s="4" t="inlineStr">
         <is>
-          <t>2026-10-12</t>
+          <t>2026-10-19</t>
         </is>
       </c>
       <c r="Q142" s="4" t="n"/>
@@ -11239,7 +11239,7 @@
       </c>
       <c r="P143" s="4" t="inlineStr">
         <is>
-          <t>2026-10-12</t>
+          <t>2026-10-19</t>
         </is>
       </c>
       <c r="Q143" s="4" t="n"/>
@@ -11316,7 +11316,7 @@
       </c>
       <c r="P144" s="4" t="inlineStr">
         <is>
-          <t>2026-10-12</t>
+          <t>2026-10-19</t>
         </is>
       </c>
       <c r="Q144" s="4" t="n"/>
@@ -11393,7 +11393,7 @@
       </c>
       <c r="P145" s="4" t="inlineStr">
         <is>
-          <t>2026-10-12</t>
+          <t>2026-10-19</t>
         </is>
       </c>
       <c r="Q145" s="4" t="n"/>
@@ -11470,7 +11470,7 @@
       </c>
       <c r="P146" s="4" t="inlineStr">
         <is>
-          <t>2026-10-12</t>
+          <t>2026-10-19</t>
         </is>
       </c>
       <c r="Q146" s="4" t="n"/>
@@ -11547,7 +11547,7 @@
       </c>
       <c r="P147" s="4" t="inlineStr">
         <is>
-          <t>2026-10-12</t>
+          <t>2026-10-19</t>
         </is>
       </c>
       <c r="Q147" s="4" t="n"/>
@@ -11624,7 +11624,7 @@
       </c>
       <c r="P148" s="4" t="inlineStr">
         <is>
-          <t>2026-10-12</t>
+          <t>2026-10-19</t>
         </is>
       </c>
       <c r="Q148" s="4" t="n"/>
@@ -11701,7 +11701,7 @@
       </c>
       <c r="P149" s="4" t="inlineStr">
         <is>
-          <t>2026-10-12</t>
+          <t>2026-10-19</t>
         </is>
       </c>
       <c r="Q149" s="4" t="n"/>
@@ -11778,7 +11778,7 @@
       </c>
       <c r="P150" s="4" t="inlineStr">
         <is>
-          <t>2026-10-12</t>
+          <t>2026-10-19</t>
         </is>
       </c>
       <c r="Q150" s="4" t="n"/>
@@ -11855,7 +11855,7 @@
       </c>
       <c r="P151" s="4" t="inlineStr">
         <is>
-          <t>2026-10-12</t>
+          <t>2026-10-19</t>
         </is>
       </c>
       <c r="Q151" s="4" t="n"/>
@@ -11932,7 +11932,7 @@
       </c>
       <c r="P152" s="4" t="inlineStr">
         <is>
-          <t>2026-10-12</t>
+          <t>2026-10-19</t>
         </is>
       </c>
       <c r="Q152" s="4" t="n"/>
@@ -12009,7 +12009,7 @@
       </c>
       <c r="P153" s="4" t="inlineStr">
         <is>
-          <t>2026-10-12</t>
+          <t>2026-10-19</t>
         </is>
       </c>
       <c r="Q153" s="4" t="n"/>
@@ -12086,7 +12086,7 @@
       </c>
       <c r="P154" s="4" t="inlineStr">
         <is>
-          <t>2026-10-12</t>
+          <t>2026-10-19</t>
         </is>
       </c>
       <c r="Q154" s="4" t="n"/>
@@ -12163,7 +12163,7 @@
       </c>
       <c r="P155" s="4" t="inlineStr">
         <is>
-          <t>2026-10-12</t>
+          <t>2026-10-19</t>
         </is>
       </c>
       <c r="Q155" s="4" t="n"/>
@@ -12240,7 +12240,7 @@
       </c>
       <c r="P156" s="4" t="inlineStr">
         <is>
-          <t>2026-10-12</t>
+          <t>2026-10-19</t>
         </is>
       </c>
       <c r="Q156" s="4" t="n"/>
@@ -12317,7 +12317,7 @@
       </c>
       <c r="P157" s="4" t="inlineStr">
         <is>
-          <t>2026-10-12</t>
+          <t>2026-10-19</t>
         </is>
       </c>
       <c r="Q157" s="4" t="n"/>
@@ -12394,7 +12394,7 @@
       </c>
       <c r="P158" s="4" t="inlineStr">
         <is>
-          <t>2026-10-12</t>
+          <t>2026-10-19</t>
         </is>
       </c>
       <c r="Q158" s="4" t="n"/>
@@ -12471,7 +12471,7 @@
       </c>
       <c r="P159" s="4" t="inlineStr">
         <is>
-          <t>2026-10-12</t>
+          <t>2026-10-19</t>
         </is>
       </c>
       <c r="Q159" s="4" t="n"/>
@@ -12550,7 +12550,7 @@
       </c>
       <c r="P160" s="4" t="inlineStr">
         <is>
-          <t>2026-10-12</t>
+          <t>2026-10-19</t>
         </is>
       </c>
       <c r="Q160" s="4" t="n"/>
@@ -12627,7 +12627,7 @@
       </c>
       <c r="P161" s="4" t="inlineStr">
         <is>
-          <t>2026-10-12</t>
+          <t>2026-10-19</t>
         </is>
       </c>
       <c r="Q161" s="4" t="n"/>
@@ -12704,7 +12704,7 @@
       </c>
       <c r="P162" s="4" t="inlineStr">
         <is>
-          <t>2026-10-12</t>
+          <t>2026-10-19</t>
         </is>
       </c>
       <c r="Q162" s="4" t="n"/>
@@ -12781,7 +12781,7 @@
       </c>
       <c r="P163" s="4" t="inlineStr">
         <is>
-          <t>2026-10-12</t>
+          <t>2026-10-19</t>
         </is>
       </c>
       <c r="Q163" s="4" t="n"/>
@@ -12858,7 +12858,7 @@
       </c>
       <c r="P164" s="4" t="inlineStr">
         <is>
-          <t>2026-10-12</t>
+          <t>2026-10-19</t>
         </is>
       </c>
       <c r="Q164" s="4" t="n"/>
@@ -12935,7 +12935,7 @@
       </c>
       <c r="P165" s="4" t="inlineStr">
         <is>
-          <t>2026-10-12</t>
+          <t>2026-10-19</t>
         </is>
       </c>
       <c r="Q165" s="4" t="n"/>
@@ -13014,7 +13014,7 @@
       </c>
       <c r="P166" s="4" t="inlineStr">
         <is>
-          <t>2026-10-12</t>
+          <t>2026-10-19</t>
         </is>
       </c>
       <c r="Q166" s="4" t="n"/>
@@ -13091,7 +13091,7 @@
       </c>
       <c r="P167" s="4" t="inlineStr">
         <is>
-          <t>2026-10-12</t>
+          <t>2026-10-19</t>
         </is>
       </c>
       <c r="Q167" s="4" t="n"/>
@@ -13170,7 +13170,7 @@
       </c>
       <c r="P168" s="4" t="inlineStr">
         <is>
-          <t>2026-10-12</t>
+          <t>2026-10-19</t>
         </is>
       </c>
       <c r="Q168" s="4" t="n"/>
@@ -13247,7 +13247,7 @@
       </c>
       <c r="P169" s="4" t="inlineStr">
         <is>
-          <t>2026-10-12</t>
+          <t>2026-10-19</t>
         </is>
       </c>
       <c r="Q169" s="4" t="n"/>
@@ -13324,7 +13324,7 @@
       </c>
       <c r="P170" s="4" t="inlineStr">
         <is>
-          <t>2026-10-12</t>
+          <t>2026-10-19</t>
         </is>
       </c>
       <c r="Q170" s="4" t="n"/>
@@ -13403,7 +13403,7 @@
       </c>
       <c r="P171" s="4" t="inlineStr">
         <is>
-          <t>2026-10-12</t>
+          <t>2026-10-19</t>
         </is>
       </c>
       <c r="Q171" s="4" t="n"/>
@@ -13480,7 +13480,7 @@
       </c>
       <c r="P172" s="4" t="inlineStr">
         <is>
-          <t>2026-10-12</t>
+          <t>2026-10-19</t>
         </is>
       </c>
       <c r="Q172" s="4" t="n"/>
@@ -13557,7 +13557,7 @@
       </c>
       <c r="P173" s="4" t="inlineStr">
         <is>
-          <t>2026-10-12</t>
+          <t>2026-10-19</t>
         </is>
       </c>
       <c r="Q173" s="4" t="n"/>
@@ -13636,7 +13636,7 @@
       </c>
       <c r="P174" s="4" t="inlineStr">
         <is>
-          <t>2026-10-12</t>
+          <t>2026-10-19</t>
         </is>
       </c>
       <c r="Q174" s="4" t="n"/>
@@ -13713,7 +13713,7 @@
       </c>
       <c r="P175" s="4" t="inlineStr">
         <is>
-          <t>2026-10-12</t>
+          <t>2026-10-19</t>
         </is>
       </c>
       <c r="Q175" s="4" t="n"/>
@@ -13790,7 +13790,7 @@
       </c>
       <c r="P176" s="4" t="inlineStr">
         <is>
-          <t>2026-10-12</t>
+          <t>2026-10-19</t>
         </is>
       </c>
       <c r="Q176" s="4" t="n"/>
@@ -13869,7 +13869,7 @@
       </c>
       <c r="P177" s="4" t="inlineStr">
         <is>
-          <t>2026-10-12</t>
+          <t>2026-10-19</t>
         </is>
       </c>
       <c r="Q177" s="4" t="n"/>
@@ -13948,7 +13948,7 @@
       </c>
       <c r="P178" s="4" t="inlineStr">
         <is>
-          <t>2026-10-12</t>
+          <t>2026-10-19</t>
         </is>
       </c>
       <c r="Q178" s="4" t="n"/>
@@ -14025,7 +14025,7 @@
       </c>
       <c r="P179" s="4" t="inlineStr">
         <is>
-          <t>2026-10-12</t>
+          <t>2026-10-19</t>
         </is>
       </c>
       <c r="Q179" s="4" t="n"/>
@@ -14104,7 +14104,7 @@
       </c>
       <c r="P180" s="4" t="inlineStr">
         <is>
-          <t>2026-10-12</t>
+          <t>2026-10-19</t>
         </is>
       </c>
       <c r="Q180" s="4" t="n"/>
@@ -14183,7 +14183,7 @@
       </c>
       <c r="P181" s="4" t="inlineStr">
         <is>
-          <t>2026-10-12</t>
+          <t>2026-10-19</t>
         </is>
       </c>
       <c r="Q181" s="4" t="n"/>
@@ -14262,7 +14262,7 @@
       </c>
       <c r="P182" s="4" t="inlineStr">
         <is>
-          <t>2026-10-12</t>
+          <t>2026-10-19</t>
         </is>
       </c>
       <c r="Q182" s="4" t="n"/>
@@ -14341,7 +14341,7 @@
       </c>
       <c r="P183" s="4" t="inlineStr">
         <is>
-          <t>2026-10-12</t>
+          <t>2026-10-19</t>
         </is>
       </c>
       <c r="Q183" s="4" t="n"/>
@@ -14420,7 +14420,7 @@
       </c>
       <c r="P184" s="4" t="inlineStr">
         <is>
-          <t>2026-10-12</t>
+          <t>2026-10-19</t>
         </is>
       </c>
       <c r="Q184" s="4" t="n"/>
@@ -14499,7 +14499,7 @@
       </c>
       <c r="P185" s="4" t="inlineStr">
         <is>
-          <t>2026-10-12</t>
+          <t>2026-10-19</t>
         </is>
       </c>
       <c r="Q185" s="4" t="n"/>
@@ -14576,7 +14576,7 @@
       </c>
       <c r="P186" s="4" t="inlineStr">
         <is>
-          <t>2026-10-12</t>
+          <t>2026-10-19</t>
         </is>
       </c>
       <c r="Q186" s="4" t="n"/>
@@ -14653,7 +14653,7 @@
       </c>
       <c r="P187" s="4" t="inlineStr">
         <is>
-          <t>2026-10-12</t>
+          <t>2026-10-19</t>
         </is>
       </c>
       <c r="Q187" s="4" t="n"/>
@@ -14730,7 +14730,7 @@
       </c>
       <c r="P188" s="4" t="inlineStr">
         <is>
-          <t>2026-10-12</t>
+          <t>2026-10-19</t>
         </is>
       </c>
       <c r="Q188" s="4" t="n"/>
@@ -14807,7 +14807,7 @@
       </c>
       <c r="P189" s="4" t="inlineStr">
         <is>
-          <t>2026-10-12</t>
+          <t>2026-10-19</t>
         </is>
       </c>
       <c r="Q189" s="4" t="n"/>
@@ -14884,7 +14884,7 @@
       </c>
       <c r="P190" s="4" t="inlineStr">
         <is>
-          <t>2026-10-12</t>
+          <t>2026-10-19</t>
         </is>
       </c>
       <c r="Q190" s="4" t="n"/>
@@ -14961,7 +14961,7 @@
       </c>
       <c r="P191" s="4" t="inlineStr">
         <is>
-          <t>2026-10-12</t>
+          <t>2026-10-19</t>
         </is>
       </c>
       <c r="Q191" s="4" t="n"/>
@@ -15038,7 +15038,7 @@
       </c>
       <c r="P192" s="4" t="inlineStr">
         <is>
-          <t>2026-10-12</t>
+          <t>2026-10-19</t>
         </is>
       </c>
       <c r="Q192" s="4" t="n"/>
@@ -15115,7 +15115,7 @@
       </c>
       <c r="P193" s="4" t="inlineStr">
         <is>
-          <t>2026-10-12</t>
+          <t>2026-10-19</t>
         </is>
       </c>
       <c r="Q193" s="4" t="n"/>
@@ -15192,7 +15192,7 @@
       </c>
       <c r="P194" s="4" t="inlineStr">
         <is>
-          <t>2026-10-12</t>
+          <t>2026-10-19</t>
         </is>
       </c>
       <c r="Q194" s="4" t="n"/>
@@ -15269,7 +15269,7 @@
       </c>
       <c r="P195" s="4" t="inlineStr">
         <is>
-          <t>2026-10-12</t>
+          <t>2026-10-19</t>
         </is>
       </c>
       <c r="Q195" s="4" t="n"/>
@@ -15346,7 +15346,7 @@
       </c>
       <c r="P196" s="4" t="inlineStr">
         <is>
-          <t>2026-10-12</t>
+          <t>2026-10-19</t>
         </is>
       </c>
       <c r="Q196" s="4" t="n"/>
@@ -15423,7 +15423,7 @@
       </c>
       <c r="P197" s="4" t="inlineStr">
         <is>
-          <t>2026-10-12</t>
+          <t>2026-10-19</t>
         </is>
       </c>
       <c r="Q197" s="4" t="n"/>
@@ -15500,7 +15500,7 @@
       </c>
       <c r="P198" s="4" t="inlineStr">
         <is>
-          <t>2026-10-12</t>
+          <t>2026-10-19</t>
         </is>
       </c>
       <c r="Q198" s="4" t="n"/>
@@ -15577,7 +15577,7 @@
       </c>
       <c r="P199" s="4" t="inlineStr">
         <is>
-          <t>2026-10-12</t>
+          <t>2026-10-19</t>
         </is>
       </c>
       <c r="Q199" s="4" t="n"/>
@@ -15654,7 +15654,7 @@
       </c>
       <c r="P200" s="4" t="inlineStr">
         <is>
-          <t>2026-10-12</t>
+          <t>2026-10-19</t>
         </is>
       </c>
       <c r="Q200" s="4" t="n"/>
@@ -15731,7 +15731,7 @@
       </c>
       <c r="P201" s="4" t="inlineStr">
         <is>
-          <t>2026-10-12</t>
+          <t>2026-10-19</t>
         </is>
       </c>
       <c r="Q201" s="4" t="n"/>
@@ -15808,7 +15808,7 @@
       </c>
       <c r="P202" s="4" t="inlineStr">
         <is>
-          <t>2026-10-12</t>
+          <t>2026-10-19</t>
         </is>
       </c>
       <c r="Q202" s="4" t="n"/>
@@ -15885,7 +15885,7 @@
       </c>
       <c r="P203" s="4" t="inlineStr">
         <is>
-          <t>2026-10-12</t>
+          <t>2026-10-19</t>
         </is>
       </c>
       <c r="Q203" s="4" t="n"/>
@@ -15962,7 +15962,7 @@
       </c>
       <c r="P204" s="4" t="inlineStr">
         <is>
-          <t>2026-10-12</t>
+          <t>2026-10-19</t>
         </is>
       </c>
       <c r="Q204" s="4" t="n"/>
@@ -16039,7 +16039,7 @@
       </c>
       <c r="P205" s="4" t="inlineStr">
         <is>
-          <t>2026-10-12</t>
+          <t>2026-10-19</t>
         </is>
       </c>
       <c r="Q205" s="4" t="n"/>
@@ -16116,7 +16116,7 @@
       </c>
       <c r="P206" s="4" t="inlineStr">
         <is>
-          <t>2026-10-12</t>
+          <t>2026-10-19</t>
         </is>
       </c>
       <c r="Q206" s="4" t="n"/>
@@ -16193,7 +16193,7 @@
       </c>
       <c r="P207" s="4" t="inlineStr">
         <is>
-          <t>2026-10-12</t>
+          <t>2026-10-19</t>
         </is>
       </c>
       <c r="Q207" s="4" t="n"/>
@@ -16270,7 +16270,7 @@
       </c>
       <c r="P208" s="4" t="inlineStr">
         <is>
-          <t>2026-10-12</t>
+          <t>2026-10-19</t>
         </is>
       </c>
       <c r="Q208" s="4" t="n"/>
@@ -16347,7 +16347,7 @@
       </c>
       <c r="P209" s="4" t="inlineStr">
         <is>
-          <t>2026-10-12</t>
+          <t>2026-10-19</t>
         </is>
       </c>
       <c r="Q209" s="4" t="n"/>
@@ -16424,7 +16424,7 @@
       </c>
       <c r="P210" s="4" t="inlineStr">
         <is>
-          <t>2026-10-12</t>
+          <t>2026-10-19</t>
         </is>
       </c>
       <c r="Q210" s="4" t="n"/>
@@ -16501,7 +16501,7 @@
       </c>
       <c r="P211" s="4" t="inlineStr">
         <is>
-          <t>2026-10-12</t>
+          <t>2026-10-19</t>
         </is>
       </c>
       <c r="Q211" s="4" t="n"/>
@@ -16578,7 +16578,7 @@
       </c>
       <c r="P212" s="4" t="inlineStr">
         <is>
-          <t>2026-10-12</t>
+          <t>2026-10-19</t>
         </is>
       </c>
       <c r="Q212" s="4" t="n"/>
@@ -16655,7 +16655,7 @@
       </c>
       <c r="P213" s="4" t="inlineStr">
         <is>
-          <t>2026-10-12</t>
+          <t>2026-10-19</t>
         </is>
       </c>
       <c r="Q213" s="4" t="n"/>
@@ -16732,7 +16732,7 @@
       </c>
       <c r="P214" s="4" t="inlineStr">
         <is>
-          <t>2026-10-12</t>
+          <t>2026-10-19</t>
         </is>
       </c>
       <c r="Q214" s="4" t="n"/>
@@ -16809,7 +16809,7 @@
       </c>
       <c r="P215" s="4" t="inlineStr">
         <is>
-          <t>2026-10-12</t>
+          <t>2026-10-19</t>
         </is>
       </c>
       <c r="Q215" s="4" t="n"/>
@@ -16886,7 +16886,7 @@
       </c>
       <c r="P216" s="4" t="inlineStr">
         <is>
-          <t>2026-10-12</t>
+          <t>2026-10-19</t>
         </is>
       </c>
       <c r="Q216" s="4" t="n"/>
@@ -16963,7 +16963,7 @@
       </c>
       <c r="P217" s="4" t="inlineStr">
         <is>
-          <t>2026-10-12</t>
+          <t>2026-10-19</t>
         </is>
       </c>
       <c r="Q217" s="4" t="n"/>
@@ -17040,7 +17040,7 @@
       </c>
       <c r="P218" s="4" t="inlineStr">
         <is>
-          <t>2026-10-12</t>
+          <t>2026-10-19</t>
         </is>
       </c>
       <c r="Q218" s="4" t="n"/>
@@ -17117,7 +17117,7 @@
       </c>
       <c r="P219" s="4" t="inlineStr">
         <is>
-          <t>2026-10-12</t>
+          <t>2026-10-19</t>
         </is>
       </c>
       <c r="Q219" s="4" t="n"/>
@@ -17194,7 +17194,7 @@
       </c>
       <c r="P220" s="4" t="inlineStr">
         <is>
-          <t>2026-10-12</t>
+          <t>2026-10-19</t>
         </is>
       </c>
       <c r="Q220" s="4" t="n"/>
@@ -17271,7 +17271,7 @@
       </c>
       <c r="P221" s="4" t="inlineStr">
         <is>
-          <t>2026-10-12</t>
+          <t>2026-10-19</t>
         </is>
       </c>
       <c r="Q221" s="4" t="n"/>
@@ -17348,7 +17348,7 @@
       </c>
       <c r="P222" s="4" t="inlineStr">
         <is>
-          <t>2026-10-12</t>
+          <t>2026-10-19</t>
         </is>
       </c>
       <c r="Q222" s="4" t="n"/>
@@ -17425,7 +17425,7 @@
       </c>
       <c r="P223" s="4" t="inlineStr">
         <is>
-          <t>2026-10-12</t>
+          <t>2026-10-19</t>
         </is>
       </c>
       <c r="Q223" s="4" t="n"/>
@@ -17502,7 +17502,7 @@
       </c>
       <c r="P224" s="4" t="inlineStr">
         <is>
-          <t>2026-10-12</t>
+          <t>2026-10-19</t>
         </is>
       </c>
       <c r="Q224" s="4" t="n"/>
@@ -17579,7 +17579,7 @@
       </c>
       <c r="P225" s="4" t="inlineStr">
         <is>
-          <t>2026-10-12</t>
+          <t>2026-10-19</t>
         </is>
       </c>
       <c r="Q225" s="4" t="n"/>
@@ -17658,7 +17658,7 @@
       </c>
       <c r="P226" s="4" t="inlineStr">
         <is>
-          <t>2026-10-12</t>
+          <t>2026-10-19</t>
         </is>
       </c>
       <c r="Q226" s="4" t="n"/>
@@ -17735,7 +17735,7 @@
       </c>
       <c r="P227" s="4" t="inlineStr">
         <is>
-          <t>2026-10-12</t>
+          <t>2026-10-19</t>
         </is>
       </c>
       <c r="Q227" s="4" t="n"/>
@@ -17812,7 +17812,7 @@
       </c>
       <c r="P228" s="4" t="inlineStr">
         <is>
-          <t>2026-10-12</t>
+          <t>2026-10-19</t>
         </is>
       </c>
       <c r="Q228" s="4" t="n"/>
@@ -17889,7 +17889,7 @@
       </c>
       <c r="P229" s="4" t="inlineStr">
         <is>
-          <t>2026-10-12</t>
+          <t>2026-10-19</t>
         </is>
       </c>
       <c r="Q229" s="4" t="n"/>
@@ -17966,7 +17966,7 @@
       </c>
       <c r="P230" s="4" t="inlineStr">
         <is>
-          <t>2026-10-12</t>
+          <t>2026-10-19</t>
         </is>
       </c>
       <c r="Q230" s="4" t="n"/>
@@ -18043,7 +18043,7 @@
       </c>
       <c r="P231" s="4" t="inlineStr">
         <is>
-          <t>2026-10-12</t>
+          <t>2026-10-19</t>
         </is>
       </c>
       <c r="Q231" s="4" t="n"/>
@@ -18122,7 +18122,7 @@
       </c>
       <c r="P232" s="4" t="inlineStr">
         <is>
-          <t>2026-10-12</t>
+          <t>2026-10-19</t>
         </is>
       </c>
       <c r="Q232" s="4" t="n"/>
@@ -18199,7 +18199,7 @@
       </c>
       <c r="P233" s="4" t="inlineStr">
         <is>
-          <t>2026-10-12</t>
+          <t>2026-10-19</t>
         </is>
       </c>
       <c r="Q233" s="4" t="n"/>
@@ -18278,7 +18278,7 @@
       </c>
       <c r="P234" s="4" t="inlineStr">
         <is>
-          <t>2026-10-12</t>
+          <t>2026-10-19</t>
         </is>
       </c>
       <c r="Q234" s="4" t="n"/>
@@ -18355,7 +18355,7 @@
       </c>
       <c r="P235" s="4" t="inlineStr">
         <is>
-          <t>2026-10-12</t>
+          <t>2026-10-19</t>
         </is>
       </c>
       <c r="Q235" s="4" t="n"/>
@@ -18432,7 +18432,7 @@
       </c>
       <c r="P236" s="4" t="inlineStr">
         <is>
-          <t>2026-10-12</t>
+          <t>2026-10-19</t>
         </is>
       </c>
       <c r="Q236" s="4" t="n"/>
@@ -18511,7 +18511,7 @@
       </c>
       <c r="P237" s="4" t="inlineStr">
         <is>
-          <t>2026-10-12</t>
+          <t>2026-10-19</t>
         </is>
       </c>
       <c r="Q237" s="4" t="n"/>
@@ -18588,7 +18588,7 @@
       </c>
       <c r="P238" s="4" t="inlineStr">
         <is>
-          <t>2026-10-12</t>
+          <t>2026-10-19</t>
         </is>
       </c>
       <c r="Q238" s="4" t="n"/>
@@ -18665,7 +18665,7 @@
       </c>
       <c r="P239" s="4" t="inlineStr">
         <is>
-          <t>2026-10-12</t>
+          <t>2026-10-19</t>
         </is>
       </c>
       <c r="Q239" s="4" t="n"/>
@@ -18744,7 +18744,7 @@
       </c>
       <c r="P240" s="4" t="inlineStr">
         <is>
-          <t>2026-10-12</t>
+          <t>2026-10-19</t>
         </is>
       </c>
       <c r="Q240" s="4" t="n"/>
@@ -18821,7 +18821,7 @@
       </c>
       <c r="P241" s="4" t="inlineStr">
         <is>
-          <t>2026-10-12</t>
+          <t>2026-10-19</t>
         </is>
       </c>
       <c r="Q241" s="4" t="n"/>
@@ -18898,7 +18898,7 @@
       </c>
       <c r="P242" s="4" t="inlineStr">
         <is>
-          <t>2026-10-12</t>
+          <t>2026-10-19</t>
         </is>
       </c>
       <c r="Q242" s="4" t="n"/>
@@ -18977,7 +18977,7 @@
       </c>
       <c r="P243" s="4" t="inlineStr">
         <is>
-          <t>2026-10-12</t>
+          <t>2026-10-19</t>
         </is>
       </c>
       <c r="Q243" s="4" t="n"/>
@@ -19056,7 +19056,7 @@
       </c>
       <c r="P244" s="4" t="inlineStr">
         <is>
-          <t>2026-10-12</t>
+          <t>2026-10-19</t>
         </is>
       </c>
       <c r="Q244" s="4" t="n"/>
@@ -19133,7 +19133,7 @@
       </c>
       <c r="P245" s="4" t="inlineStr">
         <is>
-          <t>2026-10-12</t>
+          <t>2026-10-19</t>
         </is>
       </c>
       <c r="Q245" s="4" t="n"/>
@@ -19212,7 +19212,7 @@
       </c>
       <c r="P246" s="4" t="inlineStr">
         <is>
-          <t>2026-10-12</t>
+          <t>2026-10-19</t>
         </is>
       </c>
       <c r="Q246" s="4" t="n"/>
@@ -19291,7 +19291,7 @@
       </c>
       <c r="P247" s="4" t="inlineStr">
         <is>
-          <t>2026-10-12</t>
+          <t>2026-10-19</t>
         </is>
       </c>
       <c r="Q247" s="4" t="n"/>
@@ -19370,7 +19370,7 @@
       </c>
       <c r="P248" s="4" t="inlineStr">
         <is>
-          <t>2026-10-12</t>
+          <t>2026-10-19</t>
         </is>
       </c>
       <c r="Q248" s="4" t="n"/>
@@ -19449,7 +19449,7 @@
       </c>
       <c r="P249" s="4" t="inlineStr">
         <is>
-          <t>2026-10-12</t>
+          <t>2026-10-19</t>
         </is>
       </c>
       <c r="Q249" s="4" t="n"/>
@@ -19528,7 +19528,7 @@
       </c>
       <c r="P250" s="4" t="inlineStr">
         <is>
-          <t>2026-10-12</t>
+          <t>2026-10-19</t>
         </is>
       </c>
       <c r="Q250" s="4" t="n"/>
@@ -19607,7 +19607,7 @@
       </c>
       <c r="P251" s="4" t="inlineStr">
         <is>
-          <t>2026-10-12</t>
+          <t>2026-10-19</t>
         </is>
       </c>
       <c r="Q251" s="4" t="n"/>
@@ -19684,7 +19684,7 @@
       </c>
       <c r="P252" s="4" t="inlineStr">
         <is>
-          <t>2026-10-12</t>
+          <t>2026-10-19</t>
         </is>
       </c>
       <c r="Q252" s="4" t="n"/>
@@ -19761,7 +19761,7 @@
       </c>
       <c r="P253" s="4" t="inlineStr">
         <is>
-          <t>2026-10-12</t>
+          <t>2026-10-19</t>
         </is>
       </c>
       <c r="Q253" s="4" t="n"/>
@@ -19838,7 +19838,7 @@
       </c>
       <c r="P254" s="4" t="inlineStr">
         <is>
-          <t>2026-10-12</t>
+          <t>2026-10-19</t>
         </is>
       </c>
       <c r="Q254" s="4" t="n"/>
@@ -19915,7 +19915,7 @@
       </c>
       <c r="P255" s="4" t="inlineStr">
         <is>
-          <t>2026-10-12</t>
+          <t>2026-10-19</t>
         </is>
       </c>
       <c r="Q255" s="4" t="n"/>
@@ -19992,7 +19992,7 @@
       </c>
       <c r="P256" s="4" t="inlineStr">
         <is>
-          <t>2026-10-12</t>
+          <t>2026-10-19</t>
         </is>
       </c>
       <c r="Q256" s="4" t="n"/>
@@ -20069,7 +20069,7 @@
       </c>
       <c r="P257" s="4" t="inlineStr">
         <is>
-          <t>2026-10-12</t>
+          <t>2026-10-19</t>
         </is>
       </c>
       <c r="Q257" s="4" t="n"/>
@@ -20146,7 +20146,7 @@
       </c>
       <c r="P258" s="4" t="inlineStr">
         <is>
-          <t>2026-10-12</t>
+          <t>2026-10-19</t>
         </is>
       </c>
       <c r="Q258" s="4" t="n"/>
@@ -20223,7 +20223,7 @@
       </c>
       <c r="P259" s="4" t="inlineStr">
         <is>
-          <t>2026-10-12</t>
+          <t>2026-10-19</t>
         </is>
       </c>
       <c r="Q259" s="4" t="n"/>
@@ -20300,7 +20300,7 @@
       </c>
       <c r="P260" s="4" t="inlineStr">
         <is>
-          <t>2026-10-12</t>
+          <t>2026-10-19</t>
         </is>
       </c>
       <c r="Q260" s="4" t="n"/>
@@ -20377,7 +20377,7 @@
       </c>
       <c r="P261" s="4" t="inlineStr">
         <is>
-          <t>2026-10-12</t>
+          <t>2026-10-19</t>
         </is>
       </c>
       <c r="Q261" s="4" t="n"/>
@@ -20454,7 +20454,7 @@
       </c>
       <c r="P262" s="4" t="inlineStr">
         <is>
-          <t>2026-10-12</t>
+          <t>2026-10-19</t>
         </is>
       </c>
       <c r="Q262" s="4" t="n"/>
@@ -20531,7 +20531,7 @@
       </c>
       <c r="P263" s="4" t="inlineStr">
         <is>
-          <t>2026-10-12</t>
+          <t>2026-10-19</t>
         </is>
       </c>
       <c r="Q263" s="4" t="n"/>
@@ -20608,7 +20608,7 @@
       </c>
       <c r="P264" s="4" t="inlineStr">
         <is>
-          <t>2026-10-12</t>
+          <t>2026-10-19</t>
         </is>
       </c>
       <c r="Q264" s="4" t="n"/>
@@ -20685,7 +20685,7 @@
       </c>
       <c r="P265" s="4" t="inlineStr">
         <is>
-          <t>2026-10-12</t>
+          <t>2026-10-19</t>
         </is>
       </c>
       <c r="Q265" s="4" t="n"/>
@@ -20762,7 +20762,7 @@
       </c>
       <c r="P266" s="4" t="inlineStr">
         <is>
-          <t>2026-10-12</t>
+          <t>2026-10-19</t>
         </is>
       </c>
       <c r="Q266" s="4" t="n"/>
@@ -20839,7 +20839,7 @@
       </c>
       <c r="P267" s="4" t="inlineStr">
         <is>
-          <t>2026-10-12</t>
+          <t>2026-10-19</t>
         </is>
       </c>
       <c r="Q267" s="4" t="n"/>
@@ -20916,7 +20916,7 @@
       </c>
       <c r="P268" s="4" t="inlineStr">
         <is>
-          <t>2026-10-12</t>
+          <t>2026-10-19</t>
         </is>
       </c>
       <c r="Q268" s="4" t="n"/>
@@ -20993,7 +20993,7 @@
       </c>
       <c r="P269" s="4" t="inlineStr">
         <is>
-          <t>2026-10-12</t>
+          <t>2026-10-19</t>
         </is>
       </c>
       <c r="Q269" s="4" t="n"/>
@@ -21070,7 +21070,7 @@
       </c>
       <c r="P270" s="4" t="inlineStr">
         <is>
-          <t>2026-10-12</t>
+          <t>2026-10-19</t>
         </is>
       </c>
       <c r="Q270" s="4" t="n"/>
@@ -21147,7 +21147,7 @@
       </c>
       <c r="P271" s="4" t="inlineStr">
         <is>
-          <t>2026-10-12</t>
+          <t>2026-10-19</t>
         </is>
       </c>
       <c r="Q271" s="4" t="n"/>
@@ -21224,7 +21224,7 @@
       </c>
       <c r="P272" s="4" t="inlineStr">
         <is>
-          <t>2026-10-12</t>
+          <t>2026-10-19</t>
         </is>
       </c>
       <c r="Q272" s="4" t="n"/>
@@ -21301,7 +21301,7 @@
       </c>
       <c r="P273" s="4" t="inlineStr">
         <is>
-          <t>2026-10-12</t>
+          <t>2026-10-19</t>
         </is>
       </c>
       <c r="Q273" s="4" t="n"/>
@@ -21378,7 +21378,7 @@
       </c>
       <c r="P274" s="4" t="inlineStr">
         <is>
-          <t>2026-10-12</t>
+          <t>2026-10-19</t>
         </is>
       </c>
       <c r="Q274" s="4" t="n"/>
@@ -21455,7 +21455,7 @@
       </c>
       <c r="P275" s="4" t="inlineStr">
         <is>
-          <t>2026-10-12</t>
+          <t>2026-10-19</t>
         </is>
       </c>
       <c r="Q275" s="4" t="n"/>
@@ -21532,7 +21532,7 @@
       </c>
       <c r="P276" s="4" t="inlineStr">
         <is>
-          <t>2026-10-12</t>
+          <t>2026-10-19</t>
         </is>
       </c>
       <c r="Q276" s="4" t="n"/>
@@ -21609,7 +21609,7 @@
       </c>
       <c r="P277" s="4" t="inlineStr">
         <is>
-          <t>2026-10-12</t>
+          <t>2026-10-19</t>
         </is>
       </c>
       <c r="Q277" s="4" t="n"/>
@@ -21686,7 +21686,7 @@
       </c>
       <c r="P278" s="4" t="inlineStr">
         <is>
-          <t>2026-10-12</t>
+          <t>2026-10-19</t>
         </is>
       </c>
       <c r="Q278" s="4" t="n"/>
@@ -21763,7 +21763,7 @@
       </c>
       <c r="P279" s="4" t="inlineStr">
         <is>
-          <t>2026-10-12</t>
+          <t>2026-10-19</t>
         </is>
       </c>
       <c r="Q279" s="4" t="n"/>
@@ -21840,7 +21840,7 @@
       </c>
       <c r="P280" s="4" t="inlineStr">
         <is>
-          <t>2026-10-12</t>
+          <t>2026-10-19</t>
         </is>
       </c>
       <c r="Q280" s="4" t="n"/>
@@ -21917,7 +21917,7 @@
       </c>
       <c r="P281" s="4" t="inlineStr">
         <is>
-          <t>2026-10-12</t>
+          <t>2026-10-19</t>
         </is>
       </c>
       <c r="Q281" s="4" t="n"/>
@@ -21994,7 +21994,7 @@
       </c>
       <c r="P282" s="4" t="inlineStr">
         <is>
-          <t>2026-10-12</t>
+          <t>2026-10-19</t>
         </is>
       </c>
       <c r="Q282" s="4" t="n"/>
@@ -22071,7 +22071,7 @@
       </c>
       <c r="P283" s="4" t="inlineStr">
         <is>
-          <t>2026-10-12</t>
+          <t>2026-10-19</t>
         </is>
       </c>
       <c r="Q283" s="4" t="n"/>
@@ -22148,7 +22148,7 @@
       </c>
       <c r="P284" s="4" t="inlineStr">
         <is>
-          <t>2026-10-12</t>
+          <t>2026-10-19</t>
         </is>
       </c>
       <c r="Q284" s="4" t="n"/>
@@ -22225,7 +22225,7 @@
       </c>
       <c r="P285" s="4" t="inlineStr">
         <is>
-          <t>2026-10-12</t>
+          <t>2026-10-19</t>
         </is>
       </c>
       <c r="Q285" s="4" t="n"/>
@@ -22302,7 +22302,7 @@
       </c>
       <c r="P286" s="4" t="inlineStr">
         <is>
-          <t>2026-10-12</t>
+          <t>2026-10-19</t>
         </is>
       </c>
       <c r="Q286" s="4" t="n"/>
@@ -22379,7 +22379,7 @@
       </c>
       <c r="P287" s="4" t="inlineStr">
         <is>
-          <t>2026-10-12</t>
+          <t>2026-10-19</t>
         </is>
       </c>
       <c r="Q287" s="4" t="n"/>
@@ -22456,7 +22456,7 @@
       </c>
       <c r="P288" s="4" t="inlineStr">
         <is>
-          <t>2026-10-12</t>
+          <t>2026-10-19</t>
         </is>
       </c>
       <c r="Q288" s="4" t="n"/>
@@ -22533,7 +22533,7 @@
       </c>
       <c r="P289" s="4" t="inlineStr">
         <is>
-          <t>2026-10-12</t>
+          <t>2026-10-19</t>
         </is>
       </c>
       <c r="Q289" s="4" t="n"/>
@@ -22610,7 +22610,7 @@
       </c>
       <c r="P290" s="4" t="inlineStr">
         <is>
-          <t>2026-10-12</t>
+          <t>2026-10-19</t>
         </is>
       </c>
       <c r="Q290" s="4" t="n"/>
@@ -22687,7 +22687,7 @@
       </c>
       <c r="P291" s="4" t="inlineStr">
         <is>
-          <t>2026-10-12</t>
+          <t>2026-10-19</t>
         </is>
       </c>
       <c r="Q291" s="4" t="n"/>
@@ -22764,7 +22764,7 @@
       </c>
       <c r="P292" s="4" t="inlineStr">
         <is>
-          <t>2026-10-12</t>
+          <t>2026-10-19</t>
         </is>
       </c>
       <c r="Q292" s="4" t="n"/>
@@ -22841,7 +22841,7 @@
       </c>
       <c r="P293" s="4" t="inlineStr">
         <is>
-          <t>2026-10-12</t>
+          <t>2026-10-19</t>
         </is>
       </c>
       <c r="Q293" s="4" t="n"/>
@@ -22918,7 +22918,7 @@
       </c>
       <c r="P294" s="4" t="inlineStr">
         <is>
-          <t>2026-10-12</t>
+          <t>2026-10-19</t>
         </is>
       </c>
       <c r="Q294" s="4" t="n"/>
@@ -22995,7 +22995,7 @@
       </c>
       <c r="P295" s="4" t="inlineStr">
         <is>
-          <t>2026-10-12</t>
+          <t>2026-10-19</t>
         </is>
       </c>
       <c r="Q295" s="4" t="n"/>
@@ -23072,7 +23072,7 @@
       </c>
       <c r="P296" s="4" t="inlineStr">
         <is>
-          <t>2026-10-12</t>
+          <t>2026-10-19</t>
         </is>
       </c>
       <c r="Q296" s="4" t="n"/>
@@ -23149,7 +23149,7 @@
       </c>
       <c r="P297" s="4" t="inlineStr">
         <is>
-          <t>2026-10-12</t>
+          <t>2026-10-19</t>
         </is>
       </c>
       <c r="Q297" s="4" t="n"/>
@@ -23226,7 +23226,7 @@
       </c>
       <c r="P298" s="4" t="inlineStr">
         <is>
-          <t>2026-10-12</t>
+          <t>2026-10-19</t>
         </is>
       </c>
       <c r="Q298" s="4" t="n"/>
@@ -23303,7 +23303,7 @@
       </c>
       <c r="P299" s="4" t="inlineStr">
         <is>
-          <t>2026-10-12</t>
+          <t>2026-10-19</t>
         </is>
       </c>
       <c r="Q299" s="4" t="n"/>
@@ -23380,7 +23380,7 @@
       </c>
       <c r="P300" s="4" t="inlineStr">
         <is>
-          <t>2026-10-12</t>
+          <t>2026-10-19</t>
         </is>
       </c>
       <c r="Q300" s="4" t="n"/>
@@ -23457,7 +23457,7 @@
       </c>
       <c r="P301" s="4" t="inlineStr">
         <is>
-          <t>2026-10-12</t>
+          <t>2026-10-19</t>
         </is>
       </c>
       <c r="Q301" s="4" t="n"/>
@@ -23534,7 +23534,7 @@
       </c>
       <c r="P302" s="4" t="inlineStr">
         <is>
-          <t>2026-10-12</t>
+          <t>2026-10-19</t>
         </is>
       </c>
       <c r="Q302" s="4" t="n"/>
@@ -23611,7 +23611,7 @@
       </c>
       <c r="P303" s="4" t="inlineStr">
         <is>
-          <t>2026-10-12</t>
+          <t>2026-10-19</t>
         </is>
       </c>
       <c r="Q303" s="4" t="n"/>
@@ -23688,7 +23688,7 @@
       </c>
       <c r="P304" s="4" t="inlineStr">
         <is>
-          <t>2026-10-12</t>
+          <t>2026-10-19</t>
         </is>
       </c>
       <c r="Q304" s="4" t="n"/>
@@ -23765,7 +23765,7 @@
       </c>
       <c r="P305" s="4" t="inlineStr">
         <is>
-          <t>2026-10-12</t>
+          <t>2026-10-19</t>
         </is>
       </c>
       <c r="Q305" s="4" t="n"/>
@@ -23842,7 +23842,7 @@
       </c>
       <c r="P306" s="4" t="inlineStr">
         <is>
-          <t>2026-10-12</t>
+          <t>2026-10-19</t>
         </is>
       </c>
       <c r="Q306" s="4" t="n"/>
@@ -23919,7 +23919,7 @@
       </c>
       <c r="P307" s="4" t="inlineStr">
         <is>
-          <t>2026-10-12</t>
+          <t>2026-10-19</t>
         </is>
       </c>
       <c r="Q307" s="4" t="n"/>
@@ -23998,7 +23998,7 @@
       </c>
       <c r="P308" s="4" t="inlineStr">
         <is>
-          <t>2026-10-12</t>
+          <t>2026-10-19</t>
         </is>
       </c>
       <c r="Q308" s="4" t="n"/>
@@ -24077,7 +24077,7 @@
       </c>
       <c r="P309" s="4" t="inlineStr">
         <is>
-          <t>2026-10-12</t>
+          <t>2026-10-19</t>
         </is>
       </c>
       <c r="Q309" s="4" t="n"/>
@@ -24156,7 +24156,7 @@
       </c>
       <c r="P310" s="4" t="inlineStr">
         <is>
-          <t>2026-10-12</t>
+          <t>2026-10-19</t>
         </is>
       </c>
       <c r="Q310" s="4" t="n"/>
@@ -24235,7 +24235,7 @@
       </c>
       <c r="P311" s="4" t="inlineStr">
         <is>
-          <t>2026-10-12</t>
+          <t>2026-10-19</t>
         </is>
       </c>
       <c r="Q311" s="4" t="n"/>
@@ -24314,7 +24314,7 @@
       </c>
       <c r="P312" s="4" t="inlineStr">
         <is>
-          <t>2026-10-12</t>
+          <t>2026-10-19</t>
         </is>
       </c>
       <c r="Q312" s="4" t="n"/>
@@ -24393,7 +24393,7 @@
       </c>
       <c r="P313" s="4" t="inlineStr">
         <is>
-          <t>2026-10-12</t>
+          <t>2026-10-19</t>
         </is>
       </c>
       <c r="Q313" s="4" t="n"/>
@@ -24472,7 +24472,7 @@
       </c>
       <c r="P314" s="4" t="inlineStr">
         <is>
-          <t>2026-10-12</t>
+          <t>2026-10-19</t>
         </is>
       </c>
       <c r="Q314" s="4" t="n"/>
@@ -24551,7 +24551,7 @@
       </c>
       <c r="P315" s="4" t="inlineStr">
         <is>
-          <t>2026-10-12</t>
+          <t>2026-10-19</t>
         </is>
       </c>
       <c r="Q315" s="4" t="n"/>
@@ -24630,7 +24630,7 @@
       </c>
       <c r="P316" s="4" t="inlineStr">
         <is>
-          <t>2026-10-12</t>
+          <t>2026-10-19</t>
         </is>
       </c>
       <c r="Q316" s="4" t="n"/>
@@ -24709,7 +24709,7 @@
       </c>
       <c r="P317" s="4" t="inlineStr">
         <is>
-          <t>2026-10-12</t>
+          <t>2026-10-19</t>
         </is>
       </c>
       <c r="Q317" s="4" t="n"/>
@@ -24788,7 +24788,7 @@
       </c>
       <c r="P318" s="4" t="inlineStr">
         <is>
-          <t>2026-10-12</t>
+          <t>2026-10-19</t>
         </is>
       </c>
       <c r="Q318" s="4" t="n"/>
@@ -24867,7 +24867,7 @@
       </c>
       <c r="P319" s="4" t="inlineStr">
         <is>
-          <t>2026-10-12</t>
+          <t>2026-10-19</t>
         </is>
       </c>
       <c r="Q319" s="4" t="n"/>
@@ -24946,7 +24946,7 @@
       </c>
       <c r="P320" s="4" t="inlineStr">
         <is>
-          <t>2026-10-12</t>
+          <t>2026-10-19</t>
         </is>
       </c>
       <c r="Q320" s="4" t="n"/>
@@ -25025,7 +25025,7 @@
       </c>
       <c r="P321" s="4" t="inlineStr">
         <is>
-          <t>2026-10-12</t>
+          <t>2026-10-19</t>
         </is>
       </c>
       <c r="Q321" s="4" t="n"/>
@@ -25104,7 +25104,7 @@
       </c>
       <c r="P322" s="4" t="inlineStr">
         <is>
-          <t>2026-10-12</t>
+          <t>2026-10-19</t>
         </is>
       </c>
       <c r="Q322" s="4" t="n"/>
@@ -25183,7 +25183,7 @@
       </c>
       <c r="P323" s="4" t="inlineStr">
         <is>
-          <t>2026-10-12</t>
+          <t>2026-10-19</t>
         </is>
       </c>
       <c r="Q323" s="4" t="n"/>
@@ -25262,7 +25262,7 @@
       </c>
       <c r="P324" s="4" t="inlineStr">
         <is>
-          <t>2026-10-12</t>
+          <t>2026-10-19</t>
         </is>
       </c>
       <c r="Q324" s="4" t="n"/>
@@ -25341,7 +25341,7 @@
       </c>
       <c r="P325" s="4" t="inlineStr">
         <is>
-          <t>2026-10-12</t>
+          <t>2026-10-19</t>
         </is>
       </c>
       <c r="Q325" s="4" t="n"/>
@@ -25420,7 +25420,7 @@
       </c>
       <c r="P326" s="4" t="inlineStr">
         <is>
-          <t>2026-10-12</t>
+          <t>2026-10-19</t>
         </is>
       </c>
       <c r="Q326" s="4" t="n"/>
@@ -25497,7 +25497,7 @@
       </c>
       <c r="P327" s="4" t="inlineStr">
         <is>
-          <t>2026-10-12</t>
+          <t>2026-10-19</t>
         </is>
       </c>
       <c r="Q327" s="4" t="n"/>
@@ -25574,7 +25574,7 @@
       </c>
       <c r="P328" s="4" t="inlineStr">
         <is>
-          <t>2026-10-12</t>
+          <t>2026-10-19</t>
         </is>
       </c>
       <c r="Q328" s="4" t="n"/>
@@ -25651,7 +25651,7 @@
       </c>
       <c r="P329" s="4" t="inlineStr">
         <is>
-          <t>2026-10-12</t>
+          <t>2026-10-19</t>
         </is>
       </c>
       <c r="Q329" s="4" t="n"/>
@@ -25728,7 +25728,7 @@
       </c>
       <c r="P330" s="4" t="inlineStr">
         <is>
-          <t>2026-10-12</t>
+          <t>2026-10-19</t>
         </is>
       </c>
       <c r="Q330" s="4" t="n"/>
@@ -25805,7 +25805,7 @@
       </c>
       <c r="P331" s="4" t="inlineStr">
         <is>
-          <t>2026-10-12</t>
+          <t>2026-10-19</t>
         </is>
       </c>
       <c r="Q331" s="4" t="n"/>
@@ -25882,7 +25882,7 @@
       </c>
       <c r="P332" s="4" t="inlineStr">
         <is>
-          <t>2026-10-12</t>
+          <t>2026-10-19</t>
         </is>
       </c>
       <c r="Q332" s="4" t="n"/>
@@ -25959,7 +25959,7 @@
       </c>
       <c r="P333" s="4" t="inlineStr">
         <is>
-          <t>2026-10-12</t>
+          <t>2026-10-19</t>
         </is>
       </c>
       <c r="Q333" s="4" t="n"/>
@@ -26036,7 +26036,7 @@
       </c>
       <c r="P334" s="4" t="inlineStr">
         <is>
-          <t>2026-10-12</t>
+          <t>2026-10-19</t>
         </is>
       </c>
       <c r="Q334" s="4" t="n"/>
@@ -26113,7 +26113,7 @@
       </c>
       <c r="P335" s="4" t="inlineStr">
         <is>
-          <t>2026-10-12</t>
+          <t>2026-10-19</t>
         </is>
       </c>
       <c r="Q335" s="4" t="n"/>
@@ -26190,7 +26190,7 @@
       </c>
       <c r="P336" s="4" t="inlineStr">
         <is>
-          <t>2026-10-12</t>
+          <t>2026-10-19</t>
         </is>
       </c>
       <c r="Q336" s="4" t="n"/>
@@ -26275,7 +26275,7 @@
       </c>
       <c r="B9" s="4" t="inlineStr">
         <is>
-          <t>2026-10-12</t>
+          <t>2026-10-19</t>
         </is>
       </c>
     </row>

--- a/assets/data/world-bank/excel/ove_banco_mundial_venezuela_pobreza_y_desigualdad.xlsx
+++ b/assets/data/world-bank/excel/ove_banco_mundial_venezuela_pobreza_y_desigualdad.xlsx
@@ -715,7 +715,7 @@
       </c>
       <c r="P7" s="4" t="inlineStr">
         <is>
-          <t>2026-10-19</t>
+          <t>2026-10-26</t>
         </is>
       </c>
       <c r="Q7" s="4" t="n"/>
@@ -792,7 +792,7 @@
       </c>
       <c r="P8" s="4" t="inlineStr">
         <is>
-          <t>2026-10-19</t>
+          <t>2026-10-26</t>
         </is>
       </c>
       <c r="Q8" s="4" t="n"/>
@@ -869,7 +869,7 @@
       </c>
       <c r="P9" s="4" t="inlineStr">
         <is>
-          <t>2026-10-19</t>
+          <t>2026-10-26</t>
         </is>
       </c>
       <c r="Q9" s="4" t="n"/>
@@ -946,7 +946,7 @@
       </c>
       <c r="P10" s="4" t="inlineStr">
         <is>
-          <t>2026-10-19</t>
+          <t>2026-10-26</t>
         </is>
       </c>
       <c r="Q10" s="4" t="n"/>
@@ -1023,7 +1023,7 @@
       </c>
       <c r="P11" s="4" t="inlineStr">
         <is>
-          <t>2026-10-19</t>
+          <t>2026-10-26</t>
         </is>
       </c>
       <c r="Q11" s="4" t="n"/>
@@ -1100,7 +1100,7 @@
       </c>
       <c r="P12" s="4" t="inlineStr">
         <is>
-          <t>2026-10-19</t>
+          <t>2026-10-26</t>
         </is>
       </c>
       <c r="Q12" s="4" t="n"/>
@@ -1177,7 +1177,7 @@
       </c>
       <c r="P13" s="4" t="inlineStr">
         <is>
-          <t>2026-10-19</t>
+          <t>2026-10-26</t>
         </is>
       </c>
       <c r="Q13" s="4" t="n"/>
@@ -1254,7 +1254,7 @@
       </c>
       <c r="P14" s="4" t="inlineStr">
         <is>
-          <t>2026-10-19</t>
+          <t>2026-10-26</t>
         </is>
       </c>
       <c r="Q14" s="4" t="n"/>
@@ -1331,7 +1331,7 @@
       </c>
       <c r="P15" s="4" t="inlineStr">
         <is>
-          <t>2026-10-19</t>
+          <t>2026-10-26</t>
         </is>
       </c>
       <c r="Q15" s="4" t="n"/>
@@ -1408,7 +1408,7 @@
       </c>
       <c r="P16" s="4" t="inlineStr">
         <is>
-          <t>2026-10-19</t>
+          <t>2026-10-26</t>
         </is>
       </c>
       <c r="Q16" s="4" t="n"/>
@@ -1485,7 +1485,7 @@
       </c>
       <c r="P17" s="4" t="inlineStr">
         <is>
-          <t>2026-10-19</t>
+          <t>2026-10-26</t>
         </is>
       </c>
       <c r="Q17" s="4" t="n"/>
@@ -1562,7 +1562,7 @@
       </c>
       <c r="P18" s="4" t="inlineStr">
         <is>
-          <t>2026-10-19</t>
+          <t>2026-10-26</t>
         </is>
       </c>
       <c r="Q18" s="4" t="n"/>
@@ -1639,7 +1639,7 @@
       </c>
       <c r="P19" s="4" t="inlineStr">
         <is>
-          <t>2026-10-19</t>
+          <t>2026-10-26</t>
         </is>
       </c>
       <c r="Q19" s="4" t="n"/>
@@ -1716,7 +1716,7 @@
       </c>
       <c r="P20" s="4" t="inlineStr">
         <is>
-          <t>2026-10-19</t>
+          <t>2026-10-26</t>
         </is>
       </c>
       <c r="Q20" s="4" t="n"/>
@@ -1793,7 +1793,7 @@
       </c>
       <c r="P21" s="4" t="inlineStr">
         <is>
-          <t>2026-10-19</t>
+          <t>2026-10-26</t>
         </is>
       </c>
       <c r="Q21" s="4" t="n"/>
@@ -1870,7 +1870,7 @@
       </c>
       <c r="P22" s="4" t="inlineStr">
         <is>
-          <t>2026-10-19</t>
+          <t>2026-10-26</t>
         </is>
       </c>
       <c r="Q22" s="4" t="n"/>
@@ -1947,7 +1947,7 @@
       </c>
       <c r="P23" s="4" t="inlineStr">
         <is>
-          <t>2026-10-19</t>
+          <t>2026-10-26</t>
         </is>
       </c>
       <c r="Q23" s="4" t="n"/>
@@ -2024,7 +2024,7 @@
       </c>
       <c r="P24" s="4" t="inlineStr">
         <is>
-          <t>2026-10-19</t>
+          <t>2026-10-26</t>
         </is>
       </c>
       <c r="Q24" s="4" t="n"/>
@@ -2101,7 +2101,7 @@
       </c>
       <c r="P25" s="4" t="inlineStr">
         <is>
-          <t>2026-10-19</t>
+          <t>2026-10-26</t>
         </is>
       </c>
       <c r="Q25" s="4" t="n"/>
@@ -2178,7 +2178,7 @@
       </c>
       <c r="P26" s="4" t="inlineStr">
         <is>
-          <t>2026-10-19</t>
+          <t>2026-10-26</t>
         </is>
       </c>
       <c r="Q26" s="4" t="n"/>
@@ -2255,7 +2255,7 @@
       </c>
       <c r="P27" s="4" t="inlineStr">
         <is>
-          <t>2026-10-19</t>
+          <t>2026-10-26</t>
         </is>
       </c>
       <c r="Q27" s="4" t="n"/>
@@ -2334,7 +2334,7 @@
       </c>
       <c r="P28" s="4" t="inlineStr">
         <is>
-          <t>2026-10-19</t>
+          <t>2026-10-26</t>
         </is>
       </c>
       <c r="Q28" s="4" t="n"/>
@@ -2411,7 +2411,7 @@
       </c>
       <c r="P29" s="4" t="inlineStr">
         <is>
-          <t>2026-10-19</t>
+          <t>2026-10-26</t>
         </is>
       </c>
       <c r="Q29" s="4" t="n"/>
@@ -2488,7 +2488,7 @@
       </c>
       <c r="P30" s="4" t="inlineStr">
         <is>
-          <t>2026-10-19</t>
+          <t>2026-10-26</t>
         </is>
       </c>
       <c r="Q30" s="4" t="n"/>
@@ -2565,7 +2565,7 @@
       </c>
       <c r="P31" s="4" t="inlineStr">
         <is>
-          <t>2026-10-19</t>
+          <t>2026-10-26</t>
         </is>
       </c>
       <c r="Q31" s="4" t="n"/>
@@ -2642,7 +2642,7 @@
       </c>
       <c r="P32" s="4" t="inlineStr">
         <is>
-          <t>2026-10-19</t>
+          <t>2026-10-26</t>
         </is>
       </c>
       <c r="Q32" s="4" t="n"/>
@@ -2719,7 +2719,7 @@
       </c>
       <c r="P33" s="4" t="inlineStr">
         <is>
-          <t>2026-10-19</t>
+          <t>2026-10-26</t>
         </is>
       </c>
       <c r="Q33" s="4" t="n"/>
@@ -2798,7 +2798,7 @@
       </c>
       <c r="P34" s="4" t="inlineStr">
         <is>
-          <t>2026-10-19</t>
+          <t>2026-10-26</t>
         </is>
       </c>
       <c r="Q34" s="4" t="n"/>
@@ -2875,7 +2875,7 @@
       </c>
       <c r="P35" s="4" t="inlineStr">
         <is>
-          <t>2026-10-19</t>
+          <t>2026-10-26</t>
         </is>
       </c>
       <c r="Q35" s="4" t="n"/>
@@ -2954,7 +2954,7 @@
       </c>
       <c r="P36" s="4" t="inlineStr">
         <is>
-          <t>2026-10-19</t>
+          <t>2026-10-26</t>
         </is>
       </c>
       <c r="Q36" s="4" t="n"/>
@@ -3031,7 +3031,7 @@
       </c>
       <c r="P37" s="4" t="inlineStr">
         <is>
-          <t>2026-10-19</t>
+          <t>2026-10-26</t>
         </is>
       </c>
       <c r="Q37" s="4" t="n"/>
@@ -3108,7 +3108,7 @@
       </c>
       <c r="P38" s="4" t="inlineStr">
         <is>
-          <t>2026-10-19</t>
+          <t>2026-10-26</t>
         </is>
       </c>
       <c r="Q38" s="4" t="n"/>
@@ -3187,7 +3187,7 @@
       </c>
       <c r="P39" s="4" t="inlineStr">
         <is>
-          <t>2026-10-19</t>
+          <t>2026-10-26</t>
         </is>
       </c>
       <c r="Q39" s="4" t="n"/>
@@ -3264,7 +3264,7 @@
       </c>
       <c r="P40" s="4" t="inlineStr">
         <is>
-          <t>2026-10-19</t>
+          <t>2026-10-26</t>
         </is>
       </c>
       <c r="Q40" s="4" t="n"/>
@@ -3341,7 +3341,7 @@
       </c>
       <c r="P41" s="4" t="inlineStr">
         <is>
-          <t>2026-10-19</t>
+          <t>2026-10-26</t>
         </is>
       </c>
       <c r="Q41" s="4" t="n"/>
@@ -3420,7 +3420,7 @@
       </c>
       <c r="P42" s="4" t="inlineStr">
         <is>
-          <t>2026-10-19</t>
+          <t>2026-10-26</t>
         </is>
       </c>
       <c r="Q42" s="4" t="n"/>
@@ -3497,7 +3497,7 @@
       </c>
       <c r="P43" s="4" t="inlineStr">
         <is>
-          <t>2026-10-19</t>
+          <t>2026-10-26</t>
         </is>
       </c>
       <c r="Q43" s="4" t="n"/>
@@ -3574,7 +3574,7 @@
       </c>
       <c r="P44" s="4" t="inlineStr">
         <is>
-          <t>2026-10-19</t>
+          <t>2026-10-26</t>
         </is>
       </c>
       <c r="Q44" s="4" t="n"/>
@@ -3653,7 +3653,7 @@
       </c>
       <c r="P45" s="4" t="inlineStr">
         <is>
-          <t>2026-10-19</t>
+          <t>2026-10-26</t>
         </is>
       </c>
       <c r="Q45" s="4" t="n"/>
@@ -3732,7 +3732,7 @@
       </c>
       <c r="P46" s="4" t="inlineStr">
         <is>
-          <t>2026-10-19</t>
+          <t>2026-10-26</t>
         </is>
       </c>
       <c r="Q46" s="4" t="n"/>
@@ -3809,7 +3809,7 @@
       </c>
       <c r="P47" s="4" t="inlineStr">
         <is>
-          <t>2026-10-19</t>
+          <t>2026-10-26</t>
         </is>
       </c>
       <c r="Q47" s="4" t="n"/>
@@ -3888,7 +3888,7 @@
       </c>
       <c r="P48" s="4" t="inlineStr">
         <is>
-          <t>2026-10-19</t>
+          <t>2026-10-26</t>
         </is>
       </c>
       <c r="Q48" s="4" t="n"/>
@@ -3967,7 +3967,7 @@
       </c>
       <c r="P49" s="4" t="inlineStr">
         <is>
-          <t>2026-10-19</t>
+          <t>2026-10-26</t>
         </is>
       </c>
       <c r="Q49" s="4" t="n"/>
@@ -4046,7 +4046,7 @@
       </c>
       <c r="P50" s="4" t="inlineStr">
         <is>
-          <t>2026-10-19</t>
+          <t>2026-10-26</t>
         </is>
       </c>
       <c r="Q50" s="4" t="n"/>
@@ -4125,7 +4125,7 @@
       </c>
       <c r="P51" s="4" t="inlineStr">
         <is>
-          <t>2026-10-19</t>
+          <t>2026-10-26</t>
         </is>
       </c>
       <c r="Q51" s="4" t="n"/>
@@ -4204,7 +4204,7 @@
       </c>
       <c r="P52" s="4" t="inlineStr">
         <is>
-          <t>2026-10-19</t>
+          <t>2026-10-26</t>
         </is>
       </c>
       <c r="Q52" s="4" t="n"/>
@@ -4283,7 +4283,7 @@
       </c>
       <c r="P53" s="4" t="inlineStr">
         <is>
-          <t>2026-10-19</t>
+          <t>2026-10-26</t>
         </is>
       </c>
       <c r="Q53" s="4" t="n"/>
@@ -4360,7 +4360,7 @@
       </c>
       <c r="P54" s="4" t="inlineStr">
         <is>
-          <t>2026-10-19</t>
+          <t>2026-10-26</t>
         </is>
       </c>
       <c r="Q54" s="4" t="n"/>
@@ -4437,7 +4437,7 @@
       </c>
       <c r="P55" s="4" t="inlineStr">
         <is>
-          <t>2026-10-19</t>
+          <t>2026-10-26</t>
         </is>
       </c>
       <c r="Q55" s="4" t="n"/>
@@ -4514,7 +4514,7 @@
       </c>
       <c r="P56" s="4" t="inlineStr">
         <is>
-          <t>2026-10-19</t>
+          <t>2026-10-26</t>
         </is>
       </c>
       <c r="Q56" s="4" t="n"/>
@@ -4591,7 +4591,7 @@
       </c>
       <c r="P57" s="4" t="inlineStr">
         <is>
-          <t>2026-10-19</t>
+          <t>2026-10-26</t>
         </is>
       </c>
       <c r="Q57" s="4" t="n"/>
@@ -4668,7 +4668,7 @@
       </c>
       <c r="P58" s="4" t="inlineStr">
         <is>
-          <t>2026-10-19</t>
+          <t>2026-10-26</t>
         </is>
       </c>
       <c r="Q58" s="4" t="n"/>
@@ -4745,7 +4745,7 @@
       </c>
       <c r="P59" s="4" t="inlineStr">
         <is>
-          <t>2026-10-19</t>
+          <t>2026-10-26</t>
         </is>
       </c>
       <c r="Q59" s="4" t="n"/>
@@ -4822,7 +4822,7 @@
       </c>
       <c r="P60" s="4" t="inlineStr">
         <is>
-          <t>2026-10-19</t>
+          <t>2026-10-26</t>
         </is>
       </c>
       <c r="Q60" s="4" t="n"/>
@@ -4899,7 +4899,7 @@
       </c>
       <c r="P61" s="4" t="inlineStr">
         <is>
-          <t>2026-10-19</t>
+          <t>2026-10-26</t>
         </is>
       </c>
       <c r="Q61" s="4" t="n"/>
@@ -4976,7 +4976,7 @@
       </c>
       <c r="P62" s="4" t="inlineStr">
         <is>
-          <t>2026-10-19</t>
+          <t>2026-10-26</t>
         </is>
       </c>
       <c r="Q62" s="4" t="n"/>
@@ -5053,7 +5053,7 @@
       </c>
       <c r="P63" s="4" t="inlineStr">
         <is>
-          <t>2026-10-19</t>
+          <t>2026-10-26</t>
         </is>
       </c>
       <c r="Q63" s="4" t="n"/>
@@ -5130,7 +5130,7 @@
       </c>
       <c r="P64" s="4" t="inlineStr">
         <is>
-          <t>2026-10-19</t>
+          <t>2026-10-26</t>
         </is>
       </c>
       <c r="Q64" s="4" t="n"/>
@@ -5207,7 +5207,7 @@
       </c>
       <c r="P65" s="4" t="inlineStr">
         <is>
-          <t>2026-10-19</t>
+          <t>2026-10-26</t>
         </is>
       </c>
       <c r="Q65" s="4" t="n"/>
@@ -5284,7 +5284,7 @@
       </c>
       <c r="P66" s="4" t="inlineStr">
         <is>
-          <t>2026-10-19</t>
+          <t>2026-10-26</t>
         </is>
       </c>
       <c r="Q66" s="4" t="n"/>
@@ -5361,7 +5361,7 @@
       </c>
       <c r="P67" s="4" t="inlineStr">
         <is>
-          <t>2026-10-19</t>
+          <t>2026-10-26</t>
         </is>
       </c>
       <c r="Q67" s="4" t="n"/>
@@ -5438,7 +5438,7 @@
       </c>
       <c r="P68" s="4" t="inlineStr">
         <is>
-          <t>2026-10-19</t>
+          <t>2026-10-26</t>
         </is>
       </c>
       <c r="Q68" s="4" t="n"/>
@@ -5515,7 +5515,7 @@
       </c>
       <c r="P69" s="4" t="inlineStr">
         <is>
-          <t>2026-10-19</t>
+          <t>2026-10-26</t>
         </is>
       </c>
       <c r="Q69" s="4" t="n"/>
@@ -5592,7 +5592,7 @@
       </c>
       <c r="P70" s="4" t="inlineStr">
         <is>
-          <t>2026-10-19</t>
+          <t>2026-10-26</t>
         </is>
       </c>
       <c r="Q70" s="4" t="n"/>
@@ -5669,7 +5669,7 @@
       </c>
       <c r="P71" s="4" t="inlineStr">
         <is>
-          <t>2026-10-19</t>
+          <t>2026-10-26</t>
         </is>
       </c>
       <c r="Q71" s="4" t="n"/>
@@ -5746,7 +5746,7 @@
       </c>
       <c r="P72" s="4" t="inlineStr">
         <is>
-          <t>2026-10-19</t>
+          <t>2026-10-26</t>
         </is>
       </c>
       <c r="Q72" s="4" t="n"/>
@@ -5823,7 +5823,7 @@
       </c>
       <c r="P73" s="4" t="inlineStr">
         <is>
-          <t>2026-10-19</t>
+          <t>2026-10-26</t>
         </is>
       </c>
       <c r="Q73" s="4" t="n"/>
@@ -5900,7 +5900,7 @@
       </c>
       <c r="P74" s="4" t="inlineStr">
         <is>
-          <t>2026-10-19</t>
+          <t>2026-10-26</t>
         </is>
       </c>
       <c r="Q74" s="4" t="n"/>
@@ -5977,7 +5977,7 @@
       </c>
       <c r="P75" s="4" t="inlineStr">
         <is>
-          <t>2026-10-19</t>
+          <t>2026-10-26</t>
         </is>
       </c>
       <c r="Q75" s="4" t="n"/>
@@ -6054,7 +6054,7 @@
       </c>
       <c r="P76" s="4" t="inlineStr">
         <is>
-          <t>2026-10-19</t>
+          <t>2026-10-26</t>
         </is>
       </c>
       <c r="Q76" s="4" t="n"/>
@@ -6131,7 +6131,7 @@
       </c>
       <c r="P77" s="4" t="inlineStr">
         <is>
-          <t>2026-10-19</t>
+          <t>2026-10-26</t>
         </is>
       </c>
       <c r="Q77" s="4" t="n"/>
@@ -6208,7 +6208,7 @@
       </c>
       <c r="P78" s="4" t="inlineStr">
         <is>
-          <t>2026-10-19</t>
+          <t>2026-10-26</t>
         </is>
       </c>
       <c r="Q78" s="4" t="n"/>
@@ -6285,7 +6285,7 @@
       </c>
       <c r="P79" s="4" t="inlineStr">
         <is>
-          <t>2026-10-19</t>
+          <t>2026-10-26</t>
         </is>
       </c>
       <c r="Q79" s="4" t="n"/>
@@ -6362,7 +6362,7 @@
       </c>
       <c r="P80" s="4" t="inlineStr">
         <is>
-          <t>2026-10-19</t>
+          <t>2026-10-26</t>
         </is>
       </c>
       <c r="Q80" s="4" t="n"/>
@@ -6439,7 +6439,7 @@
       </c>
       <c r="P81" s="4" t="inlineStr">
         <is>
-          <t>2026-10-19</t>
+          <t>2026-10-26</t>
         </is>
       </c>
       <c r="Q81" s="4" t="n"/>
@@ -6516,7 +6516,7 @@
       </c>
       <c r="P82" s="4" t="inlineStr">
         <is>
-          <t>2026-10-19</t>
+          <t>2026-10-26</t>
         </is>
       </c>
       <c r="Q82" s="4" t="n"/>
@@ -6593,7 +6593,7 @@
       </c>
       <c r="P83" s="4" t="inlineStr">
         <is>
-          <t>2026-10-19</t>
+          <t>2026-10-26</t>
         </is>
       </c>
       <c r="Q83" s="4" t="n"/>
@@ -6670,7 +6670,7 @@
       </c>
       <c r="P84" s="4" t="inlineStr">
         <is>
-          <t>2026-10-19</t>
+          <t>2026-10-26</t>
         </is>
       </c>
       <c r="Q84" s="4" t="n"/>
@@ -6747,7 +6747,7 @@
       </c>
       <c r="P85" s="4" t="inlineStr">
         <is>
-          <t>2026-10-19</t>
+          <t>2026-10-26</t>
         </is>
       </c>
       <c r="Q85" s="4" t="n"/>
@@ -6824,7 +6824,7 @@
       </c>
       <c r="P86" s="4" t="inlineStr">
         <is>
-          <t>2026-10-19</t>
+          <t>2026-10-26</t>
         </is>
       </c>
       <c r="Q86" s="4" t="n"/>
@@ -6901,7 +6901,7 @@
       </c>
       <c r="P87" s="4" t="inlineStr">
         <is>
-          <t>2026-10-19</t>
+          <t>2026-10-26</t>
         </is>
       </c>
       <c r="Q87" s="4" t="n"/>
@@ -6978,7 +6978,7 @@
       </c>
       <c r="P88" s="4" t="inlineStr">
         <is>
-          <t>2026-10-19</t>
+          <t>2026-10-26</t>
         </is>
       </c>
       <c r="Q88" s="4" t="n"/>
@@ -7055,7 +7055,7 @@
       </c>
       <c r="P89" s="4" t="inlineStr">
         <is>
-          <t>2026-10-19</t>
+          <t>2026-10-26</t>
         </is>
       </c>
       <c r="Q89" s="4" t="n"/>
@@ -7132,7 +7132,7 @@
       </c>
       <c r="P90" s="4" t="inlineStr">
         <is>
-          <t>2026-10-19</t>
+          <t>2026-10-26</t>
         </is>
       </c>
       <c r="Q90" s="4" t="n"/>
@@ -7209,7 +7209,7 @@
       </c>
       <c r="P91" s="4" t="inlineStr">
         <is>
-          <t>2026-10-19</t>
+          <t>2026-10-26</t>
         </is>
       </c>
       <c r="Q91" s="4" t="n"/>
@@ -7286,7 +7286,7 @@
       </c>
       <c r="P92" s="4" t="inlineStr">
         <is>
-          <t>2026-10-19</t>
+          <t>2026-10-26</t>
         </is>
       </c>
       <c r="Q92" s="4" t="n"/>
@@ -7363,7 +7363,7 @@
       </c>
       <c r="P93" s="4" t="inlineStr">
         <is>
-          <t>2026-10-19</t>
+          <t>2026-10-26</t>
         </is>
       </c>
       <c r="Q93" s="4" t="n"/>
@@ -7442,7 +7442,7 @@
       </c>
       <c r="P94" s="4" t="inlineStr">
         <is>
-          <t>2026-10-19</t>
+          <t>2026-10-26</t>
         </is>
       </c>
       <c r="Q94" s="4" t="n"/>
@@ -7519,7 +7519,7 @@
       </c>
       <c r="P95" s="4" t="inlineStr">
         <is>
-          <t>2026-10-19</t>
+          <t>2026-10-26</t>
         </is>
       </c>
       <c r="Q95" s="4" t="n"/>
@@ -7596,7 +7596,7 @@
       </c>
       <c r="P96" s="4" t="inlineStr">
         <is>
-          <t>2026-10-19</t>
+          <t>2026-10-26</t>
         </is>
       </c>
       <c r="Q96" s="4" t="n"/>
@@ -7673,7 +7673,7 @@
       </c>
       <c r="P97" s="4" t="inlineStr">
         <is>
-          <t>2026-10-19</t>
+          <t>2026-10-26</t>
         </is>
       </c>
       <c r="Q97" s="4" t="n"/>
@@ -7750,7 +7750,7 @@
       </c>
       <c r="P98" s="4" t="inlineStr">
         <is>
-          <t>2026-10-19</t>
+          <t>2026-10-26</t>
         </is>
       </c>
       <c r="Q98" s="4" t="n"/>
@@ -7827,7 +7827,7 @@
       </c>
       <c r="P99" s="4" t="inlineStr">
         <is>
-          <t>2026-10-19</t>
+          <t>2026-10-26</t>
         </is>
       </c>
       <c r="Q99" s="4" t="n"/>
@@ -7906,7 +7906,7 @@
       </c>
       <c r="P100" s="4" t="inlineStr">
         <is>
-          <t>2026-10-19</t>
+          <t>2026-10-26</t>
         </is>
       </c>
       <c r="Q100" s="4" t="n"/>
@@ -7983,7 +7983,7 @@
       </c>
       <c r="P101" s="4" t="inlineStr">
         <is>
-          <t>2026-10-19</t>
+          <t>2026-10-26</t>
         </is>
       </c>
       <c r="Q101" s="4" t="n"/>
@@ -8062,7 +8062,7 @@
       </c>
       <c r="P102" s="4" t="inlineStr">
         <is>
-          <t>2026-10-19</t>
+          <t>2026-10-26</t>
         </is>
       </c>
       <c r="Q102" s="4" t="n"/>
@@ -8139,7 +8139,7 @@
       </c>
       <c r="P103" s="4" t="inlineStr">
         <is>
-          <t>2026-10-19</t>
+          <t>2026-10-26</t>
         </is>
       </c>
       <c r="Q103" s="4" t="n"/>
@@ -8216,7 +8216,7 @@
       </c>
       <c r="P104" s="4" t="inlineStr">
         <is>
-          <t>2026-10-19</t>
+          <t>2026-10-26</t>
         </is>
       </c>
       <c r="Q104" s="4" t="n"/>
@@ -8295,7 +8295,7 @@
       </c>
       <c r="P105" s="4" t="inlineStr">
         <is>
-          <t>2026-10-19</t>
+          <t>2026-10-26</t>
         </is>
       </c>
       <c r="Q105" s="4" t="n"/>
@@ -8372,7 +8372,7 @@
       </c>
       <c r="P106" s="4" t="inlineStr">
         <is>
-          <t>2026-10-19</t>
+          <t>2026-10-26</t>
         </is>
       </c>
       <c r="Q106" s="4" t="n"/>
@@ -8449,7 +8449,7 @@
       </c>
       <c r="P107" s="4" t="inlineStr">
         <is>
-          <t>2026-10-19</t>
+          <t>2026-10-26</t>
         </is>
       </c>
       <c r="Q107" s="4" t="n"/>
@@ -8528,7 +8528,7 @@
       </c>
       <c r="P108" s="4" t="inlineStr">
         <is>
-          <t>2026-10-19</t>
+          <t>2026-10-26</t>
         </is>
       </c>
       <c r="Q108" s="4" t="n"/>
@@ -8605,7 +8605,7 @@
       </c>
       <c r="P109" s="4" t="inlineStr">
         <is>
-          <t>2026-10-19</t>
+          <t>2026-10-26</t>
         </is>
       </c>
       <c r="Q109" s="4" t="n"/>
@@ -8682,7 +8682,7 @@
       </c>
       <c r="P110" s="4" t="inlineStr">
         <is>
-          <t>2026-10-19</t>
+          <t>2026-10-26</t>
         </is>
       </c>
       <c r="Q110" s="4" t="n"/>
@@ -8761,7 +8761,7 @@
       </c>
       <c r="P111" s="4" t="inlineStr">
         <is>
-          <t>2026-10-19</t>
+          <t>2026-10-26</t>
         </is>
       </c>
       <c r="Q111" s="4" t="n"/>
@@ -8840,7 +8840,7 @@
       </c>
       <c r="P112" s="4" t="inlineStr">
         <is>
-          <t>2026-10-19</t>
+          <t>2026-10-26</t>
         </is>
       </c>
       <c r="Q112" s="4" t="n"/>
@@ -8917,7 +8917,7 @@
       </c>
       <c r="P113" s="4" t="inlineStr">
         <is>
-          <t>2026-10-19</t>
+          <t>2026-10-26</t>
         </is>
       </c>
       <c r="Q113" s="4" t="n"/>
@@ -8996,7 +8996,7 @@
       </c>
       <c r="P114" s="4" t="inlineStr">
         <is>
-          <t>2026-10-19</t>
+          <t>2026-10-26</t>
         </is>
       </c>
       <c r="Q114" s="4" t="n"/>
@@ -9075,7 +9075,7 @@
       </c>
       <c r="P115" s="4" t="inlineStr">
         <is>
-          <t>2026-10-19</t>
+          <t>2026-10-26</t>
         </is>
       </c>
       <c r="Q115" s="4" t="n"/>
@@ -9154,7 +9154,7 @@
       </c>
       <c r="P116" s="4" t="inlineStr">
         <is>
-          <t>2026-10-19</t>
+          <t>2026-10-26</t>
         </is>
       </c>
       <c r="Q116" s="4" t="n"/>
@@ -9233,7 +9233,7 @@
       </c>
       <c r="P117" s="4" t="inlineStr">
         <is>
-          <t>2026-10-19</t>
+          <t>2026-10-26</t>
         </is>
       </c>
       <c r="Q117" s="4" t="n"/>
@@ -9312,7 +9312,7 @@
       </c>
       <c r="P118" s="4" t="inlineStr">
         <is>
-          <t>2026-10-19</t>
+          <t>2026-10-26</t>
         </is>
       </c>
       <c r="Q118" s="4" t="n"/>
@@ -9391,7 +9391,7 @@
       </c>
       <c r="P119" s="4" t="inlineStr">
         <is>
-          <t>2026-10-19</t>
+          <t>2026-10-26</t>
         </is>
       </c>
       <c r="Q119" s="4" t="n"/>
@@ -9468,7 +9468,7 @@
       </c>
       <c r="P120" s="4" t="inlineStr">
         <is>
-          <t>2026-10-19</t>
+          <t>2026-10-26</t>
         </is>
       </c>
       <c r="Q120" s="4" t="n"/>
@@ -9545,7 +9545,7 @@
       </c>
       <c r="P121" s="4" t="inlineStr">
         <is>
-          <t>2026-10-19</t>
+          <t>2026-10-26</t>
         </is>
       </c>
       <c r="Q121" s="4" t="n"/>
@@ -9622,7 +9622,7 @@
       </c>
       <c r="P122" s="4" t="inlineStr">
         <is>
-          <t>2026-10-19</t>
+          <t>2026-10-26</t>
         </is>
       </c>
       <c r="Q122" s="4" t="n"/>
@@ -9699,7 +9699,7 @@
       </c>
       <c r="P123" s="4" t="inlineStr">
         <is>
-          <t>2026-10-19</t>
+          <t>2026-10-26</t>
         </is>
       </c>
       <c r="Q123" s="4" t="n"/>
@@ -9776,7 +9776,7 @@
       </c>
       <c r="P124" s="4" t="inlineStr">
         <is>
-          <t>2026-10-19</t>
+          <t>2026-10-26</t>
         </is>
       </c>
       <c r="Q124" s="4" t="n"/>
@@ -9853,7 +9853,7 @@
       </c>
       <c r="P125" s="4" t="inlineStr">
         <is>
-          <t>2026-10-19</t>
+          <t>2026-10-26</t>
         </is>
       </c>
       <c r="Q125" s="4" t="n"/>
@@ -9930,7 +9930,7 @@
       </c>
       <c r="P126" s="4" t="inlineStr">
         <is>
-          <t>2026-10-19</t>
+          <t>2026-10-26</t>
         </is>
       </c>
       <c r="Q126" s="4" t="n"/>
@@ -10007,7 +10007,7 @@
       </c>
       <c r="P127" s="4" t="inlineStr">
         <is>
-          <t>2026-10-19</t>
+          <t>2026-10-26</t>
         </is>
       </c>
       <c r="Q127" s="4" t="n"/>
@@ -10084,7 +10084,7 @@
       </c>
       <c r="P128" s="4" t="inlineStr">
         <is>
-          <t>2026-10-19</t>
+          <t>2026-10-26</t>
         </is>
       </c>
       <c r="Q128" s="4" t="n"/>
@@ -10161,7 +10161,7 @@
       </c>
       <c r="P129" s="4" t="inlineStr">
         <is>
-          <t>2026-10-19</t>
+          <t>2026-10-26</t>
         </is>
       </c>
       <c r="Q129" s="4" t="n"/>
@@ -10238,7 +10238,7 @@
       </c>
       <c r="P130" s="4" t="inlineStr">
         <is>
-          <t>2026-10-19</t>
+          <t>2026-10-26</t>
         </is>
       </c>
       <c r="Q130" s="4" t="n"/>
@@ -10315,7 +10315,7 @@
       </c>
       <c r="P131" s="4" t="inlineStr">
         <is>
-          <t>2026-10-19</t>
+          <t>2026-10-26</t>
         </is>
       </c>
       <c r="Q131" s="4" t="n"/>
@@ -10392,7 +10392,7 @@
       </c>
       <c r="P132" s="4" t="inlineStr">
         <is>
-          <t>2026-10-19</t>
+          <t>2026-10-26</t>
         </is>
       </c>
       <c r="Q132" s="4" t="n"/>
@@ -10469,7 +10469,7 @@
       </c>
       <c r="P133" s="4" t="inlineStr">
         <is>
-          <t>2026-10-19</t>
+          <t>2026-10-26</t>
         </is>
       </c>
       <c r="Q133" s="4" t="n"/>
@@ -10546,7 +10546,7 @@
       </c>
       <c r="P134" s="4" t="inlineStr">
         <is>
-          <t>2026-10-19</t>
+          <t>2026-10-26</t>
         </is>
       </c>
       <c r="Q134" s="4" t="n"/>
@@ -10623,7 +10623,7 @@
       </c>
       <c r="P135" s="4" t="inlineStr">
         <is>
-          <t>2026-10-19</t>
+          <t>2026-10-26</t>
         </is>
       </c>
       <c r="Q135" s="4" t="n"/>
@@ -10700,7 +10700,7 @@
       </c>
       <c r="P136" s="4" t="inlineStr">
         <is>
-          <t>2026-10-19</t>
+          <t>2026-10-26</t>
         </is>
       </c>
       <c r="Q136" s="4" t="n"/>
@@ -10777,7 +10777,7 @@
       </c>
       <c r="P137" s="4" t="inlineStr">
         <is>
-          <t>2026-10-19</t>
+          <t>2026-10-26</t>
         </is>
       </c>
       <c r="Q137" s="4" t="n"/>
@@ -10854,7 +10854,7 @@
       </c>
       <c r="P138" s="4" t="inlineStr">
         <is>
-          <t>2026-10-19</t>
+          <t>2026-10-26</t>
         </is>
       </c>
       <c r="Q138" s="4" t="n"/>
@@ -10931,7 +10931,7 @@
       </c>
       <c r="P139" s="4" t="inlineStr">
         <is>
-          <t>2026-10-19</t>
+          <t>2026-10-26</t>
         </is>
       </c>
       <c r="Q139" s="4" t="n"/>
@@ -11008,7 +11008,7 @@
       </c>
       <c r="P140" s="4" t="inlineStr">
         <is>
-          <t>2026-10-19</t>
+          <t>2026-10-26</t>
         </is>
       </c>
       <c r="Q140" s="4" t="n"/>
@@ -11085,7 +11085,7 @@
       </c>
       <c r="P141" s="4" t="inlineStr">
         <is>
-          <t>2026-10-19</t>
+          <t>2026-10-26</t>
         </is>
       </c>
       <c r="Q141" s="4" t="n"/>
@@ -11162,7 +11162,7 @@
       </c>
       <c r="P142" s="4" t="inlineStr">
         <is>
-          <t>2026-10-19</t>
+          <t>2026-10-26</t>
         </is>
       </c>
       <c r="Q142" s="4" t="n"/>
@@ -11239,7 +11239,7 @@
       </c>
       <c r="P143" s="4" t="inlineStr">
         <is>
-          <t>2026-10-19</t>
+          <t>2026-10-26</t>
         </is>
       </c>
       <c r="Q143" s="4" t="n"/>
@@ -11316,7 +11316,7 @@
       </c>
       <c r="P144" s="4" t="inlineStr">
         <is>
-          <t>2026-10-19</t>
+          <t>2026-10-26</t>
         </is>
       </c>
       <c r="Q144" s="4" t="n"/>
@@ -11393,7 +11393,7 @@
       </c>
       <c r="P145" s="4" t="inlineStr">
         <is>
-          <t>2026-10-19</t>
+          <t>2026-10-26</t>
         </is>
       </c>
       <c r="Q145" s="4" t="n"/>
@@ -11470,7 +11470,7 @@
       </c>
       <c r="P146" s="4" t="inlineStr">
         <is>
-          <t>2026-10-19</t>
+          <t>2026-10-26</t>
         </is>
       </c>
       <c r="Q146" s="4" t="n"/>
@@ -11547,7 +11547,7 @@
       </c>
       <c r="P147" s="4" t="inlineStr">
         <is>
-          <t>2026-10-19</t>
+          <t>2026-10-26</t>
         </is>
       </c>
       <c r="Q147" s="4" t="n"/>
@@ -11624,7 +11624,7 @@
       </c>
       <c r="P148" s="4" t="inlineStr">
         <is>
-          <t>2026-10-19</t>
+          <t>2026-10-26</t>
         </is>
       </c>
       <c r="Q148" s="4" t="n"/>
@@ -11701,7 +11701,7 @@
       </c>
       <c r="P149" s="4" t="inlineStr">
         <is>
-          <t>2026-10-19</t>
+          <t>2026-10-26</t>
         </is>
       </c>
       <c r="Q149" s="4" t="n"/>
@@ -11778,7 +11778,7 @@
       </c>
       <c r="P150" s="4" t="inlineStr">
         <is>
-          <t>2026-10-19</t>
+          <t>2026-10-26</t>
         </is>
       </c>
       <c r="Q150" s="4" t="n"/>
@@ -11855,7 +11855,7 @@
       </c>
       <c r="P151" s="4" t="inlineStr">
         <is>
-          <t>2026-10-19</t>
+          <t>2026-10-26</t>
         </is>
       </c>
       <c r="Q151" s="4" t="n"/>
@@ -11932,7 +11932,7 @@
       </c>
       <c r="P152" s="4" t="inlineStr">
         <is>
-          <t>2026-10-19</t>
+          <t>2026-10-26</t>
         </is>
       </c>
       <c r="Q152" s="4" t="n"/>
@@ -12009,7 +12009,7 @@
       </c>
       <c r="P153" s="4" t="inlineStr">
         <is>
-          <t>2026-10-19</t>
+          <t>2026-10-26</t>
         </is>
       </c>
       <c r="Q153" s="4" t="n"/>
@@ -12086,7 +12086,7 @@
       </c>
       <c r="P154" s="4" t="inlineStr">
         <is>
-          <t>2026-10-19</t>
+          <t>2026-10-26</t>
         </is>
       </c>
       <c r="Q154" s="4" t="n"/>
@@ -12163,7 +12163,7 @@
       </c>
       <c r="P155" s="4" t="inlineStr">
         <is>
-          <t>2026-10-19</t>
+          <t>2026-10-26</t>
         </is>
       </c>
       <c r="Q155" s="4" t="n"/>
@@ -12240,7 +12240,7 @@
       </c>
       <c r="P156" s="4" t="inlineStr">
         <is>
-          <t>2026-10-19</t>
+          <t>2026-10-26</t>
         </is>
       </c>
       <c r="Q156" s="4" t="n"/>
@@ -12317,7 +12317,7 @@
       </c>
       <c r="P157" s="4" t="inlineStr">
         <is>
-          <t>2026-10-19</t>
+          <t>2026-10-26</t>
         </is>
       </c>
       <c r="Q157" s="4" t="n"/>
@@ -12394,7 +12394,7 @@
       </c>
       <c r="P158" s="4" t="inlineStr">
         <is>
-          <t>2026-10-19</t>
+          <t>2026-10-26</t>
         </is>
       </c>
       <c r="Q158" s="4" t="n"/>
@@ -12471,7 +12471,7 @@
       </c>
       <c r="P159" s="4" t="inlineStr">
         <is>
-          <t>2026-10-19</t>
+          <t>2026-10-26</t>
         </is>
       </c>
       <c r="Q159" s="4" t="n"/>
@@ -12550,7 +12550,7 @@
       </c>
       <c r="P160" s="4" t="inlineStr">
         <is>
-          <t>2026-10-19</t>
+          <t>2026-10-26</t>
         </is>
       </c>
       <c r="Q160" s="4" t="n"/>
@@ -12627,7 +12627,7 @@
       </c>
       <c r="P161" s="4" t="inlineStr">
         <is>
-          <t>2026-10-19</t>
+          <t>2026-10-26</t>
         </is>
       </c>
       <c r="Q161" s="4" t="n"/>
@@ -12704,7 +12704,7 @@
       </c>
       <c r="P162" s="4" t="inlineStr">
         <is>
-          <t>2026-10-19</t>
+          <t>2026-10-26</t>
         </is>
       </c>
       <c r="Q162" s="4" t="n"/>
@@ -12781,7 +12781,7 @@
       </c>
       <c r="P163" s="4" t="inlineStr">
         <is>
-          <t>2026-10-19</t>
+          <t>2026-10-26</t>
         </is>
       </c>
       <c r="Q163" s="4" t="n"/>
@@ -12858,7 +12858,7 @@
       </c>
       <c r="P164" s="4" t="inlineStr">
         <is>
-          <t>2026-10-19</t>
+          <t>2026-10-26</t>
         </is>
       </c>
       <c r="Q164" s="4" t="n"/>
@@ -12935,7 +12935,7 @@
       </c>
       <c r="P165" s="4" t="inlineStr">
         <is>
-          <t>2026-10-19</t>
+          <t>2026-10-26</t>
         </is>
       </c>
       <c r="Q165" s="4" t="n"/>
@@ -13014,7 +13014,7 @@
       </c>
       <c r="P166" s="4" t="inlineStr">
         <is>
-          <t>2026-10-19</t>
+          <t>2026-10-26</t>
         </is>
       </c>
       <c r="Q166" s="4" t="n"/>
@@ -13091,7 +13091,7 @@
       </c>
       <c r="P167" s="4" t="inlineStr">
         <is>
-          <t>2026-10-19</t>
+          <t>2026-10-26</t>
         </is>
       </c>
       <c r="Q167" s="4" t="n"/>
@@ -13170,7 +13170,7 @@
       </c>
       <c r="P168" s="4" t="inlineStr">
         <is>
-          <t>2026-10-19</t>
+          <t>2026-10-26</t>
         </is>
       </c>
       <c r="Q168" s="4" t="n"/>
@@ -13247,7 +13247,7 @@
       </c>
       <c r="P169" s="4" t="inlineStr">
         <is>
-          <t>2026-10-19</t>
+          <t>2026-10-26</t>
         </is>
       </c>
       <c r="Q169" s="4" t="n"/>
@@ -13324,7 +13324,7 @@
       </c>
       <c r="P170" s="4" t="inlineStr">
         <is>
-          <t>2026-10-19</t>
+          <t>2026-10-26</t>
         </is>
       </c>
       <c r="Q170" s="4" t="n"/>
@@ -13403,7 +13403,7 @@
       </c>
       <c r="P171" s="4" t="inlineStr">
         <is>
-          <t>2026-10-19</t>
+          <t>2026-10-26</t>
         </is>
       </c>
       <c r="Q171" s="4" t="n"/>
@@ -13480,7 +13480,7 @@
       </c>
       <c r="P172" s="4" t="inlineStr">
         <is>
-          <t>2026-10-19</t>
+          <t>2026-10-26</t>
         </is>
       </c>
       <c r="Q172" s="4" t="n"/>
@@ -13557,7 +13557,7 @@
       </c>
       <c r="P173" s="4" t="inlineStr">
         <is>
-          <t>2026-10-19</t>
+          <t>2026-10-26</t>
         </is>
       </c>
       <c r="Q173" s="4" t="n"/>
@@ -13636,7 +13636,7 @@
       </c>
       <c r="P174" s="4" t="inlineStr">
         <is>
-          <t>2026-10-19</t>
+          <t>2026-10-26</t>
         </is>
       </c>
       <c r="Q174" s="4" t="n"/>
@@ -13713,7 +13713,7 @@
       </c>
       <c r="P175" s="4" t="inlineStr">
         <is>
-          <t>2026-10-19</t>
+          <t>2026-10-26</t>
         </is>
       </c>
       <c r="Q175" s="4" t="n"/>
@@ -13790,7 +13790,7 @@
       </c>
       <c r="P176" s="4" t="inlineStr">
         <is>
-          <t>2026-10-19</t>
+          <t>2026-10-26</t>
         </is>
       </c>
       <c r="Q176" s="4" t="n"/>
@@ -13869,7 +13869,7 @@
       </c>
       <c r="P177" s="4" t="inlineStr">
         <is>
-          <t>2026-10-19</t>
+          <t>2026-10-26</t>
         </is>
       </c>
       <c r="Q177" s="4" t="n"/>
@@ -13948,7 +13948,7 @@
       </c>
       <c r="P178" s="4" t="inlineStr">
         <is>
-          <t>2026-10-19</t>
+          <t>2026-10-26</t>
         </is>
       </c>
       <c r="Q178" s="4" t="n"/>
@@ -14025,7 +14025,7 @@
       </c>
       <c r="P179" s="4" t="inlineStr">
         <is>
-          <t>2026-10-19</t>
+          <t>2026-10-26</t>
         </is>
       </c>
       <c r="Q179" s="4" t="n"/>
@@ -14104,7 +14104,7 @@
       </c>
       <c r="P180" s="4" t="inlineStr">
         <is>
-          <t>2026-10-19</t>
+          <t>2026-10-26</t>
         </is>
       </c>
       <c r="Q180" s="4" t="n"/>
@@ -14183,7 +14183,7 @@
       </c>
       <c r="P181" s="4" t="inlineStr">
         <is>
-          <t>2026-10-19</t>
+          <t>2026-10-26</t>
         </is>
       </c>
       <c r="Q181" s="4" t="n"/>
@@ -14262,7 +14262,7 @@
       </c>
       <c r="P182" s="4" t="inlineStr">
         <is>
-          <t>2026-10-19</t>
+          <t>2026-10-26</t>
         </is>
       </c>
       <c r="Q182" s="4" t="n"/>
@@ -14341,7 +14341,7 @@
       </c>
       <c r="P183" s="4" t="inlineStr">
         <is>
-          <t>2026-10-19</t>
+          <t>2026-10-26</t>
         </is>
       </c>
       <c r="Q183" s="4" t="n"/>
@@ -14420,7 +14420,7 @@
       </c>
       <c r="P184" s="4" t="inlineStr">
         <is>
-          <t>2026-10-19</t>
+          <t>2026-10-26</t>
         </is>
       </c>
       <c r="Q184" s="4" t="n"/>
@@ -14499,7 +14499,7 @@
       </c>
       <c r="P185" s="4" t="inlineStr">
         <is>
-          <t>2026-10-19</t>
+          <t>2026-10-26</t>
         </is>
       </c>
       <c r="Q185" s="4" t="n"/>
@@ -14576,7 +14576,7 @@
       </c>
       <c r="P186" s="4" t="inlineStr">
         <is>
-          <t>2026-10-19</t>
+          <t>2026-10-26</t>
         </is>
       </c>
       <c r="Q186" s="4" t="n"/>
@@ -14653,7 +14653,7 @@
       </c>
       <c r="P187" s="4" t="inlineStr">
         <is>
-          <t>2026-10-19</t>
+          <t>2026-10-26</t>
         </is>
       </c>
       <c r="Q187" s="4" t="n"/>
@@ -14730,7 +14730,7 @@
       </c>
       <c r="P188" s="4" t="inlineStr">
         <is>
-          <t>2026-10-19</t>
+          <t>2026-10-26</t>
         </is>
       </c>
       <c r="Q188" s="4" t="n"/>
@@ -14807,7 +14807,7 @@
       </c>
       <c r="P189" s="4" t="inlineStr">
         <is>
-          <t>2026-10-19</t>
+          <t>2026-10-26</t>
         </is>
       </c>
       <c r="Q189" s="4" t="n"/>
@@ -14884,7 +14884,7 @@
       </c>
       <c r="P190" s="4" t="inlineStr">
         <is>
-          <t>2026-10-19</t>
+          <t>2026-10-26</t>
         </is>
       </c>
       <c r="Q190" s="4" t="n"/>
@@ -14961,7 +14961,7 @@
       </c>
       <c r="P191" s="4" t="inlineStr">
         <is>
-          <t>2026-10-19</t>
+          <t>2026-10-26</t>
         </is>
       </c>
       <c r="Q191" s="4" t="n"/>
@@ -15038,7 +15038,7 @@
       </c>
       <c r="P192" s="4" t="inlineStr">
         <is>
-          <t>2026-10-19</t>
+          <t>2026-10-26</t>
         </is>
       </c>
       <c r="Q192" s="4" t="n"/>
@@ -15115,7 +15115,7 @@
       </c>
       <c r="P193" s="4" t="inlineStr">
         <is>
-          <t>2026-10-19</t>
+          <t>2026-10-26</t>
         </is>
       </c>
       <c r="Q193" s="4" t="n"/>
@@ -15192,7 +15192,7 @@
       </c>
       <c r="P194" s="4" t="inlineStr">
         <is>
-          <t>2026-10-19</t>
+          <t>2026-10-26</t>
         </is>
       </c>
       <c r="Q194" s="4" t="n"/>
@@ -15269,7 +15269,7 @@
       </c>
       <c r="P195" s="4" t="inlineStr">
         <is>
-          <t>2026-10-19</t>
+          <t>2026-10-26</t>
         </is>
       </c>
       <c r="Q195" s="4" t="n"/>
@@ -15346,7 +15346,7 @@
       </c>
       <c r="P196" s="4" t="inlineStr">
         <is>
-          <t>2026-10-19</t>
+          <t>2026-10-26</t>
         </is>
       </c>
       <c r="Q196" s="4" t="n"/>
@@ -15423,7 +15423,7 @@
       </c>
       <c r="P197" s="4" t="inlineStr">
         <is>
-          <t>2026-10-19</t>
+          <t>2026-10-26</t>
         </is>
       </c>
       <c r="Q197" s="4" t="n"/>
@@ -15500,7 +15500,7 @@
       </c>
       <c r="P198" s="4" t="inlineStr">
         <is>
-          <t>2026-10-19</t>
+          <t>2026-10-26</t>
         </is>
       </c>
       <c r="Q198" s="4" t="n"/>
@@ -15577,7 +15577,7 @@
       </c>
       <c r="P199" s="4" t="inlineStr">
         <is>
-          <t>2026-10-19</t>
+          <t>2026-10-26</t>
         </is>
       </c>
       <c r="Q199" s="4" t="n"/>
@@ -15654,7 +15654,7 @@
       </c>
       <c r="P200" s="4" t="inlineStr">
         <is>
-          <t>2026-10-19</t>
+          <t>2026-10-26</t>
         </is>
       </c>
       <c r="Q200" s="4" t="n"/>
@@ -15731,7 +15731,7 @@
       </c>
       <c r="P201" s="4" t="inlineStr">
         <is>
-          <t>2026-10-19</t>
+          <t>2026-10-26</t>
         </is>
       </c>
       <c r="Q201" s="4" t="n"/>
@@ -15808,7 +15808,7 @@
       </c>
       <c r="P202" s="4" t="inlineStr">
         <is>
-          <t>2026-10-19</t>
+          <t>2026-10-26</t>
         </is>
       </c>
       <c r="Q202" s="4" t="n"/>
@@ -15885,7 +15885,7 @@
       </c>
       <c r="P203" s="4" t="inlineStr">
         <is>
-          <t>2026-10-19</t>
+          <t>2026-10-26</t>
         </is>
       </c>
       <c r="Q203" s="4" t="n"/>
@@ -15962,7 +15962,7 @@
       </c>
       <c r="P204" s="4" t="inlineStr">
         <is>
-          <t>2026-10-19</t>
+          <t>2026-10-26</t>
         </is>
       </c>
       <c r="Q204" s="4" t="n"/>
@@ -16039,7 +16039,7 @@
       </c>
       <c r="P205" s="4" t="inlineStr">
         <is>
-          <t>2026-10-19</t>
+          <t>2026-10-26</t>
         </is>
       </c>
       <c r="Q205" s="4" t="n"/>
@@ -16116,7 +16116,7 @@
       </c>
       <c r="P206" s="4" t="inlineStr">
         <is>
-          <t>2026-10-19</t>
+          <t>2026-10-26</t>
         </is>
       </c>
       <c r="Q206" s="4" t="n"/>
@@ -16193,7 +16193,7 @@
       </c>
       <c r="P207" s="4" t="inlineStr">
         <is>
-          <t>2026-10-19</t>
+          <t>2026-10-26</t>
         </is>
       </c>
       <c r="Q207" s="4" t="n"/>
@@ -16270,7 +16270,7 @@
       </c>
       <c r="P208" s="4" t="inlineStr">
         <is>
-          <t>2026-10-19</t>
+          <t>2026-10-26</t>
         </is>
       </c>
       <c r="Q208" s="4" t="n"/>
@@ -16347,7 +16347,7 @@
       </c>
       <c r="P209" s="4" t="inlineStr">
         <is>
-          <t>2026-10-19</t>
+          <t>2026-10-26</t>
         </is>
       </c>
       <c r="Q209" s="4" t="n"/>
@@ -16424,7 +16424,7 @@
       </c>
       <c r="P210" s="4" t="inlineStr">
         <is>
-          <t>2026-10-19</t>
+          <t>2026-10-26</t>
         </is>
       </c>
       <c r="Q210" s="4" t="n"/>
@@ -16501,7 +16501,7 @@
       </c>
       <c r="P211" s="4" t="inlineStr">
         <is>
-          <t>2026-10-19</t>
+          <t>2026-10-26</t>
         </is>
       </c>
       <c r="Q211" s="4" t="n"/>
@@ -16578,7 +16578,7 @@
       </c>
       <c r="P212" s="4" t="inlineStr">
         <is>
-          <t>2026-10-19</t>
+          <t>2026-10-26</t>
         </is>
       </c>
       <c r="Q212" s="4" t="n"/>
@@ -16655,7 +16655,7 @@
       </c>
       <c r="P213" s="4" t="inlineStr">
         <is>
-          <t>2026-10-19</t>
+          <t>2026-10-26</t>
         </is>
       </c>
       <c r="Q213" s="4" t="n"/>
@@ -16732,7 +16732,7 @@
       </c>
       <c r="P214" s="4" t="inlineStr">
         <is>
-          <t>2026-10-19</t>
+          <t>2026-10-26</t>
         </is>
       </c>
       <c r="Q214" s="4" t="n"/>
@@ -16809,7 +16809,7 @@
       </c>
       <c r="P215" s="4" t="inlineStr">
         <is>
-          <t>2026-10-19</t>
+          <t>2026-10-26</t>
         </is>
       </c>
       <c r="Q215" s="4" t="n"/>
@@ -16886,7 +16886,7 @@
       </c>
       <c r="P216" s="4" t="inlineStr">
         <is>
-          <t>2026-10-19</t>
+          <t>2026-10-26</t>
         </is>
       </c>
       <c r="Q216" s="4" t="n"/>
@@ -16963,7 +16963,7 @@
       </c>
       <c r="P217" s="4" t="inlineStr">
         <is>
-          <t>2026-10-19</t>
+          <t>2026-10-26</t>
         </is>
       </c>
       <c r="Q217" s="4" t="n"/>
@@ -17040,7 +17040,7 @@
       </c>
       <c r="P218" s="4" t="inlineStr">
         <is>
-          <t>2026-10-19</t>
+          <t>2026-10-26</t>
         </is>
       </c>
       <c r="Q218" s="4" t="n"/>
@@ -17117,7 +17117,7 @@
       </c>
       <c r="P219" s="4" t="inlineStr">
         <is>
-          <t>2026-10-19</t>
+          <t>2026-10-26</t>
         </is>
       </c>
       <c r="Q219" s="4" t="n"/>
@@ -17194,7 +17194,7 @@
       </c>
       <c r="P220" s="4" t="inlineStr">
         <is>
-          <t>2026-10-19</t>
+          <t>2026-10-26</t>
         </is>
       </c>
       <c r="Q220" s="4" t="n"/>
@@ -17271,7 +17271,7 @@
       </c>
       <c r="P221" s="4" t="inlineStr">
         <is>
-          <t>2026-10-19</t>
+          <t>2026-10-26</t>
         </is>
       </c>
       <c r="Q221" s="4" t="n"/>
@@ -17348,7 +17348,7 @@
       </c>
       <c r="P222" s="4" t="inlineStr">
         <is>
-          <t>2026-10-19</t>
+          <t>2026-10-26</t>
         </is>
       </c>
       <c r="Q222" s="4" t="n"/>
@@ -17425,7 +17425,7 @@
       </c>
       <c r="P223" s="4" t="inlineStr">
         <is>
-          <t>2026-10-19</t>
+          <t>2026-10-26</t>
         </is>
       </c>
       <c r="Q223" s="4" t="n"/>
@@ -17502,7 +17502,7 @@
       </c>
       <c r="P224" s="4" t="inlineStr">
         <is>
-          <t>2026-10-19</t>
+          <t>2026-10-26</t>
         </is>
       </c>
       <c r="Q224" s="4" t="n"/>
@@ -17579,7 +17579,7 @@
       </c>
       <c r="P225" s="4" t="inlineStr">
         <is>
-          <t>2026-10-19</t>
+          <t>2026-10-26</t>
         </is>
       </c>
       <c r="Q225" s="4" t="n"/>
@@ -17658,7 +17658,7 @@
       </c>
       <c r="P226" s="4" t="inlineStr">
         <is>
-          <t>2026-10-19</t>
+          <t>2026-10-26</t>
         </is>
       </c>
       <c r="Q226" s="4" t="n"/>
@@ -17735,7 +17735,7 @@
       </c>
       <c r="P227" s="4" t="inlineStr">
         <is>
-          <t>2026-10-19</t>
+          <t>2026-10-26</t>
         </is>
       </c>
       <c r="Q227" s="4" t="n"/>
@@ -17812,7 +17812,7 @@
       </c>
       <c r="P228" s="4" t="inlineStr">
         <is>
-          <t>2026-10-19</t>
+          <t>2026-10-26</t>
         </is>
       </c>
       <c r="Q228" s="4" t="n"/>
@@ -17889,7 +17889,7 @@
       </c>
       <c r="P229" s="4" t="inlineStr">
         <is>
-          <t>2026-10-19</t>
+          <t>2026-10-26</t>
         </is>
       </c>
       <c r="Q229" s="4" t="n"/>
@@ -17966,7 +17966,7 @@
       </c>
       <c r="P230" s="4" t="inlineStr">
         <is>
-          <t>2026-10-19</t>
+          <t>2026-10-26</t>
         </is>
       </c>
       <c r="Q230" s="4" t="n"/>
@@ -18043,7 +18043,7 @@
       </c>
       <c r="P231" s="4" t="inlineStr">
         <is>
-          <t>2026-10-19</t>
+          <t>2026-10-26</t>
         </is>
       </c>
       <c r="Q231" s="4" t="n"/>
@@ -18122,7 +18122,7 @@
       </c>
       <c r="P232" s="4" t="inlineStr">
         <is>
-          <t>2026-10-19</t>
+          <t>2026-10-26</t>
         </is>
       </c>
       <c r="Q232" s="4" t="n"/>
@@ -18199,7 +18199,7 @@
       </c>
       <c r="P233" s="4" t="inlineStr">
         <is>
-          <t>2026-10-19</t>
+          <t>2026-10-26</t>
         </is>
       </c>
       <c r="Q233" s="4" t="n"/>
@@ -18278,7 +18278,7 @@
       </c>
       <c r="P234" s="4" t="inlineStr">
         <is>
-          <t>2026-10-19</t>
+          <t>2026-10-26</t>
         </is>
       </c>
       <c r="Q234" s="4" t="n"/>
@@ -18355,7 +18355,7 @@
       </c>
       <c r="P235" s="4" t="inlineStr">
         <is>
-          <t>2026-10-19</t>
+          <t>2026-10-26</t>
         </is>
       </c>
       <c r="Q235" s="4" t="n"/>
@@ -18432,7 +18432,7 @@
       </c>
       <c r="P236" s="4" t="inlineStr">
         <is>
-          <t>2026-10-19</t>
+          <t>2026-10-26</t>
         </is>
       </c>
       <c r="Q236" s="4" t="n"/>
@@ -18511,7 +18511,7 @@
       </c>
       <c r="P237" s="4" t="inlineStr">
         <is>
-          <t>2026-10-19</t>
+          <t>2026-10-26</t>
         </is>
       </c>
       <c r="Q237" s="4" t="n"/>
@@ -18588,7 +18588,7 @@
       </c>
       <c r="P238" s="4" t="inlineStr">
         <is>
-          <t>2026-10-19</t>
+          <t>2026-10-26</t>
         </is>
       </c>
       <c r="Q238" s="4" t="n"/>
@@ -18665,7 +18665,7 @@
       </c>
       <c r="P239" s="4" t="inlineStr">
         <is>
-          <t>2026-10-19</t>
+          <t>2026-10-26</t>
         </is>
       </c>
       <c r="Q239" s="4" t="n"/>
@@ -18744,7 +18744,7 @@
       </c>
       <c r="P240" s="4" t="inlineStr">
         <is>
-          <t>2026-10-19</t>
+          <t>2026-10-26</t>
         </is>
       </c>
       <c r="Q240" s="4" t="n"/>
@@ -18821,7 +18821,7 @@
       </c>
       <c r="P241" s="4" t="inlineStr">
         <is>
-          <t>2026-10-19</t>
+          <t>2026-10-26</t>
         </is>
       </c>
       <c r="Q241" s="4" t="n"/>
@@ -18898,7 +18898,7 @@
       </c>
       <c r="P242" s="4" t="inlineStr">
         <is>
-          <t>2026-10-19</t>
+          <t>2026-10-26</t>
         </is>
       </c>
       <c r="Q242" s="4" t="n"/>
@@ -18977,7 +18977,7 @@
       </c>
       <c r="P243" s="4" t="inlineStr">
         <is>
-          <t>2026-10-19</t>
+          <t>2026-10-26</t>
         </is>
       </c>
       <c r="Q243" s="4" t="n"/>
@@ -19056,7 +19056,7 @@
       </c>
       <c r="P244" s="4" t="inlineStr">
         <is>
-          <t>2026-10-19</t>
+          <t>2026-10-26</t>
         </is>
       </c>
       <c r="Q244" s="4" t="n"/>
@@ -19133,7 +19133,7 @@
       </c>
       <c r="P245" s="4" t="inlineStr">
         <is>
-          <t>2026-10-19</t>
+          <t>2026-10-26</t>
         </is>
       </c>
       <c r="Q245" s="4" t="n"/>
@@ -19212,7 +19212,7 @@
       </c>
       <c r="P246" s="4" t="inlineStr">
         <is>
-          <t>2026-10-19</t>
+          <t>2026-10-26</t>
         </is>
       </c>
       <c r="Q246" s="4" t="n"/>
@@ -19291,7 +19291,7 @@
       </c>
       <c r="P247" s="4" t="inlineStr">
         <is>
-          <t>2026-10-19</t>
+          <t>2026-10-26</t>
         </is>
       </c>
       <c r="Q247" s="4" t="n"/>
@@ -19370,7 +19370,7 @@
       </c>
       <c r="P248" s="4" t="inlineStr">
         <is>
-          <t>2026-10-19</t>
+          <t>2026-10-26</t>
         </is>
       </c>
       <c r="Q248" s="4" t="n"/>
@@ -19449,7 +19449,7 @@
       </c>
       <c r="P249" s="4" t="inlineStr">
         <is>
-          <t>2026-10-19</t>
+          <t>2026-10-26</t>
         </is>
       </c>
       <c r="Q249" s="4" t="n"/>
@@ -19528,7 +19528,7 @@
       </c>
       <c r="P250" s="4" t="inlineStr">
         <is>
-          <t>2026-10-19</t>
+          <t>2026-10-26</t>
         </is>
       </c>
       <c r="Q250" s="4" t="n"/>
@@ -19607,7 +19607,7 @@
       </c>
       <c r="P251" s="4" t="inlineStr">
         <is>
-          <t>2026-10-19</t>
+          <t>2026-10-26</t>
         </is>
       </c>
       <c r="Q251" s="4" t="n"/>
@@ -19684,7 +19684,7 @@
       </c>
       <c r="P252" s="4" t="inlineStr">
         <is>
-          <t>2026-10-19</t>
+          <t>2026-10-26</t>
         </is>
       </c>
       <c r="Q252" s="4" t="n"/>
@@ -19761,7 +19761,7 @@
       </c>
       <c r="P253" s="4" t="inlineStr">
         <is>
-          <t>2026-10-19</t>
+          <t>2026-10-26</t>
         </is>
       </c>
       <c r="Q253" s="4" t="n"/>
@@ -19838,7 +19838,7 @@
       </c>
       <c r="P254" s="4" t="inlineStr">
         <is>
-          <t>2026-10-19</t>
+          <t>2026-10-26</t>
         </is>
       </c>
       <c r="Q254" s="4" t="n"/>
@@ -19915,7 +19915,7 @@
       </c>
       <c r="P255" s="4" t="inlineStr">
         <is>
-          <t>2026-10-19</t>
+          <t>2026-10-26</t>
         </is>
       </c>
       <c r="Q255" s="4" t="n"/>
@@ -19992,7 +19992,7 @@
       </c>
       <c r="P256" s="4" t="inlineStr">
         <is>
-          <t>2026-10-19</t>
+          <t>2026-10-26</t>
         </is>
       </c>
       <c r="Q256" s="4" t="n"/>
@@ -20069,7 +20069,7 @@
       </c>
       <c r="P257" s="4" t="inlineStr">
         <is>
-          <t>2026-10-19</t>
+          <t>2026-10-26</t>
         </is>
       </c>
       <c r="Q257" s="4" t="n"/>
@@ -20146,7 +20146,7 @@
       </c>
       <c r="P258" s="4" t="inlineStr">
         <is>
-          <t>2026-10-19</t>
+          <t>2026-10-26</t>
         </is>
       </c>
       <c r="Q258" s="4" t="n"/>
@@ -20223,7 +20223,7 @@
       </c>
       <c r="P259" s="4" t="inlineStr">
         <is>
-          <t>2026-10-19</t>
+          <t>2026-10-26</t>
         </is>
       </c>
       <c r="Q259" s="4" t="n"/>
@@ -20300,7 +20300,7 @@
       </c>
       <c r="P260" s="4" t="inlineStr">
         <is>
-          <t>2026-10-19</t>
+          <t>2026-10-26</t>
         </is>
       </c>
       <c r="Q260" s="4" t="n"/>
@@ -20377,7 +20377,7 @@
       </c>
       <c r="P261" s="4" t="inlineStr">
         <is>
-          <t>2026-10-19</t>
+          <t>2026-10-26</t>
         </is>
       </c>
       <c r="Q261" s="4" t="n"/>
@@ -20454,7 +20454,7 @@
       </c>
       <c r="P262" s="4" t="inlineStr">
         <is>
-          <t>2026-10-19</t>
+          <t>2026-10-26</t>
         </is>
       </c>
       <c r="Q262" s="4" t="n"/>
@@ -20531,7 +20531,7 @@
       </c>
       <c r="P263" s="4" t="inlineStr">
         <is>
-          <t>2026-10-19</t>
+          <t>2026-10-26</t>
         </is>
       </c>
       <c r="Q263" s="4" t="n"/>
@@ -20608,7 +20608,7 @@
       </c>
       <c r="P264" s="4" t="inlineStr">
         <is>
-          <t>2026-10-19</t>
+          <t>2026-10-26</t>
         </is>
       </c>
       <c r="Q264" s="4" t="n"/>
@@ -20685,7 +20685,7 @@
       </c>
       <c r="P265" s="4" t="inlineStr">
         <is>
-          <t>2026-10-19</t>
+          <t>2026-10-26</t>
         </is>
       </c>
       <c r="Q265" s="4" t="n"/>
@@ -20762,7 +20762,7 @@
       </c>
       <c r="P266" s="4" t="inlineStr">
         <is>
-          <t>2026-10-19</t>
+          <t>2026-10-26</t>
         </is>
       </c>
       <c r="Q266" s="4" t="n"/>
@@ -20839,7 +20839,7 @@
       </c>
       <c r="P267" s="4" t="inlineStr">
         <is>
-          <t>2026-10-19</t>
+          <t>2026-10-26</t>
         </is>
       </c>
       <c r="Q267" s="4" t="n"/>
@@ -20916,7 +20916,7 @@
       </c>
       <c r="P268" s="4" t="inlineStr">
         <is>
-          <t>2026-10-19</t>
+          <t>2026-10-26</t>
         </is>
       </c>
       <c r="Q268" s="4" t="n"/>
@@ -20993,7 +20993,7 @@
       </c>
       <c r="P269" s="4" t="inlineStr">
         <is>
-          <t>2026-10-19</t>
+          <t>2026-10-26</t>
         </is>
       </c>
       <c r="Q269" s="4" t="n"/>
@@ -21070,7 +21070,7 @@
       </c>
       <c r="P270" s="4" t="inlineStr">
         <is>
-          <t>2026-10-19</t>
+          <t>2026-10-26</t>
         </is>
       </c>
       <c r="Q270" s="4" t="n"/>
@@ -21147,7 +21147,7 @@
       </c>
       <c r="P271" s="4" t="inlineStr">
         <is>
-          <t>2026-10-19</t>
+          <t>2026-10-26</t>
         </is>
       </c>
       <c r="Q271" s="4" t="n"/>
@@ -21224,7 +21224,7 @@
       </c>
       <c r="P272" s="4" t="inlineStr">
         <is>
-          <t>2026-10-19</t>
+          <t>2026-10-26</t>
         </is>
       </c>
       <c r="Q272" s="4" t="n"/>
@@ -21301,7 +21301,7 @@
       </c>
       <c r="P273" s="4" t="inlineStr">
         <is>
-          <t>2026-10-19</t>
+          <t>2026-10-26</t>
         </is>
       </c>
       <c r="Q273" s="4" t="n"/>
@@ -21378,7 +21378,7 @@
       </c>
       <c r="P274" s="4" t="inlineStr">
         <is>
-          <t>2026-10-19</t>
+          <t>2026-10-26</t>
         </is>
       </c>
       <c r="Q274" s="4" t="n"/>
@@ -21455,7 +21455,7 @@
       </c>
       <c r="P275" s="4" t="inlineStr">
         <is>
-          <t>2026-10-19</t>
+          <t>2026-10-26</t>
         </is>
       </c>
       <c r="Q275" s="4" t="n"/>
@@ -21532,7 +21532,7 @@
       </c>
       <c r="P276" s="4" t="inlineStr">
         <is>
-          <t>2026-10-19</t>
+          <t>2026-10-26</t>
         </is>
       </c>
       <c r="Q276" s="4" t="n"/>
@@ -21609,7 +21609,7 @@
       </c>
       <c r="P277" s="4" t="inlineStr">
         <is>
-          <t>2026-10-19</t>
+          <t>2026-10-26</t>
         </is>
       </c>
       <c r="Q277" s="4" t="n"/>
@@ -21686,7 +21686,7 @@
       </c>
       <c r="P278" s="4" t="inlineStr">
         <is>
-          <t>2026-10-19</t>
+          <t>2026-10-26</t>
         </is>
       </c>
       <c r="Q278" s="4" t="n"/>
@@ -21763,7 +21763,7 @@
       </c>
       <c r="P279" s="4" t="inlineStr">
         <is>
-          <t>2026-10-19</t>
+          <t>2026-10-26</t>
         </is>
       </c>
       <c r="Q279" s="4" t="n"/>
@@ -21840,7 +21840,7 @@
       </c>
       <c r="P280" s="4" t="inlineStr">
         <is>
-          <t>2026-10-19</t>
+          <t>2026-10-26</t>
         </is>
       </c>
       <c r="Q280" s="4" t="n"/>
@@ -21917,7 +21917,7 @@
       </c>
       <c r="P281" s="4" t="inlineStr">
         <is>
-          <t>2026-10-19</t>
+          <t>2026-10-26</t>
         </is>
       </c>
       <c r="Q281" s="4" t="n"/>
@@ -21994,7 +21994,7 @@
       </c>
       <c r="P282" s="4" t="inlineStr">
         <is>
-          <t>2026-10-19</t>
+          <t>2026-10-26</t>
         </is>
       </c>
       <c r="Q282" s="4" t="n"/>
@@ -22071,7 +22071,7 @@
       </c>
       <c r="P283" s="4" t="inlineStr">
         <is>
-          <t>2026-10-19</t>
+          <t>2026-10-26</t>
         </is>
       </c>
       <c r="Q283" s="4" t="n"/>
@@ -22148,7 +22148,7 @@
       </c>
       <c r="P284" s="4" t="inlineStr">
         <is>
-          <t>2026-10-19</t>
+          <t>2026-10-26</t>
         </is>
       </c>
       <c r="Q284" s="4" t="n"/>
@@ -22225,7 +22225,7 @@
       </c>
       <c r="P285" s="4" t="inlineStr">
         <is>
-          <t>2026-10-19</t>
+          <t>2026-10-26</t>
         </is>
       </c>
       <c r="Q285" s="4" t="n"/>
@@ -22302,7 +22302,7 @@
       </c>
       <c r="P286" s="4" t="inlineStr">
         <is>
-          <t>2026-10-19</t>
+          <t>2026-10-26</t>
         </is>
       </c>
       <c r="Q286" s="4" t="n"/>
@@ -22379,7 +22379,7 @@
       </c>
       <c r="P287" s="4" t="inlineStr">
         <is>
-          <t>2026-10-19</t>
+          <t>2026-10-26</t>
         </is>
       </c>
       <c r="Q287" s="4" t="n"/>
@@ -22456,7 +22456,7 @@
       </c>
       <c r="P288" s="4" t="inlineStr">
         <is>
-          <t>2026-10-19</t>
+          <t>2026-10-26</t>
         </is>
       </c>
       <c r="Q288" s="4" t="n"/>
@@ -22533,7 +22533,7 @@
       </c>
       <c r="P289" s="4" t="inlineStr">
         <is>
-          <t>2026-10-19</t>
+          <t>2026-10-26</t>
         </is>
       </c>
       <c r="Q289" s="4" t="n"/>
@@ -22610,7 +22610,7 @@
       </c>
       <c r="P290" s="4" t="inlineStr">
         <is>
-          <t>2026-10-19</t>
+          <t>2026-10-26</t>
         </is>
       </c>
       <c r="Q290" s="4" t="n"/>
@@ -22687,7 +22687,7 @@
       </c>
       <c r="P291" s="4" t="inlineStr">
         <is>
-          <t>2026-10-19</t>
+          <t>2026-10-26</t>
         </is>
       </c>
       <c r="Q291" s="4" t="n"/>
@@ -22764,7 +22764,7 @@
       </c>
       <c r="P292" s="4" t="inlineStr">
         <is>
-          <t>2026-10-19</t>
+          <t>2026-10-26</t>
         </is>
       </c>
       <c r="Q292" s="4" t="n"/>
@@ -22841,7 +22841,7 @@
       </c>
       <c r="P293" s="4" t="inlineStr">
         <is>
-          <t>2026-10-19</t>
+          <t>2026-10-26</t>
         </is>
       </c>
       <c r="Q293" s="4" t="n"/>
@@ -22918,7 +22918,7 @@
       </c>
       <c r="P294" s="4" t="inlineStr">
         <is>
-          <t>2026-10-19</t>
+          <t>2026-10-26</t>
         </is>
       </c>
       <c r="Q294" s="4" t="n"/>
@@ -22995,7 +22995,7 @@
       </c>
       <c r="P295" s="4" t="inlineStr">
         <is>
-          <t>2026-10-19</t>
+          <t>2026-10-26</t>
         </is>
       </c>
       <c r="Q295" s="4" t="n"/>
@@ -23072,7 +23072,7 @@
       </c>
       <c r="P296" s="4" t="inlineStr">
         <is>
-          <t>2026-10-19</t>
+          <t>2026-10-26</t>
         </is>
       </c>
       <c r="Q296" s="4" t="n"/>
@@ -23149,7 +23149,7 @@
       </c>
       <c r="P297" s="4" t="inlineStr">
         <is>
-          <t>2026-10-19</t>
+          <t>2026-10-26</t>
         </is>
       </c>
       <c r="Q297" s="4" t="n"/>
@@ -23226,7 +23226,7 @@
       </c>
       <c r="P298" s="4" t="inlineStr">
         <is>
-          <t>2026-10-19</t>
+          <t>2026-10-26</t>
         </is>
       </c>
       <c r="Q298" s="4" t="n"/>
@@ -23303,7 +23303,7 @@
       </c>
       <c r="P299" s="4" t="inlineStr">
         <is>
-          <t>2026-10-19</t>
+          <t>2026-10-26</t>
         </is>
       </c>
       <c r="Q299" s="4" t="n"/>
@@ -23380,7 +23380,7 @@
       </c>
       <c r="P300" s="4" t="inlineStr">
         <is>
-          <t>2026-10-19</t>
+          <t>2026-10-26</t>
         </is>
       </c>
       <c r="Q300" s="4" t="n"/>
@@ -23457,7 +23457,7 @@
       </c>
       <c r="P301" s="4" t="inlineStr">
         <is>
-          <t>2026-10-19</t>
+          <t>2026-10-26</t>
         </is>
       </c>
       <c r="Q301" s="4" t="n"/>
@@ -23534,7 +23534,7 @@
       </c>
       <c r="P302" s="4" t="inlineStr">
         <is>
-          <t>2026-10-19</t>
+          <t>2026-10-26</t>
         </is>
       </c>
       <c r="Q302" s="4" t="n"/>
@@ -23611,7 +23611,7 @@
       </c>
       <c r="P303" s="4" t="inlineStr">
         <is>
-          <t>2026-10-19</t>
+          <t>2026-10-26</t>
         </is>
       </c>
       <c r="Q303" s="4" t="n"/>
@@ -23688,7 +23688,7 @@
       </c>
       <c r="P304" s="4" t="inlineStr">
         <is>
-          <t>2026-10-19</t>
+          <t>2026-10-26</t>
         </is>
       </c>
       <c r="Q304" s="4" t="n"/>
@@ -23765,7 +23765,7 @@
       </c>
       <c r="P305" s="4" t="inlineStr">
         <is>
-          <t>2026-10-19</t>
+          <t>2026-10-26</t>
         </is>
       </c>
       <c r="Q305" s="4" t="n"/>
@@ -23842,7 +23842,7 @@
       </c>
       <c r="P306" s="4" t="inlineStr">
         <is>
-          <t>2026-10-19</t>
+          <t>2026-10-26</t>
         </is>
       </c>
       <c r="Q306" s="4" t="n"/>
@@ -23919,7 +23919,7 @@
       </c>
       <c r="P307" s="4" t="inlineStr">
         <is>
-          <t>2026-10-19</t>
+          <t>2026-10-26</t>
         </is>
       </c>
       <c r="Q307" s="4" t="n"/>
@@ -23998,7 +23998,7 @@
       </c>
       <c r="P308" s="4" t="inlineStr">
         <is>
-          <t>2026-10-19</t>
+          <t>2026-10-26</t>
         </is>
       </c>
       <c r="Q308" s="4" t="n"/>
@@ -24077,7 +24077,7 @@
       </c>
       <c r="P309" s="4" t="inlineStr">
         <is>
-          <t>2026-10-19</t>
+          <t>2026-10-26</t>
         </is>
       </c>
       <c r="Q309" s="4" t="n"/>
@@ -24156,7 +24156,7 @@
       </c>
       <c r="P310" s="4" t="inlineStr">
         <is>
-          <t>2026-10-19</t>
+          <t>2026-10-26</t>
         </is>
       </c>
       <c r="Q310" s="4" t="n"/>
@@ -24235,7 +24235,7 @@
       </c>
       <c r="P311" s="4" t="inlineStr">
         <is>
-          <t>2026-10-19</t>
+          <t>2026-10-26</t>
         </is>
       </c>
       <c r="Q311" s="4" t="n"/>
@@ -24314,7 +24314,7 @@
       </c>
       <c r="P312" s="4" t="inlineStr">
         <is>
-          <t>2026-10-19</t>
+          <t>2026-10-26</t>
         </is>
       </c>
       <c r="Q312" s="4" t="n"/>
@@ -24393,7 +24393,7 @@
       </c>
       <c r="P313" s="4" t="inlineStr">
         <is>
-          <t>2026-10-19</t>
+          <t>2026-10-26</t>
         </is>
       </c>
       <c r="Q313" s="4" t="n"/>
@@ -24472,7 +24472,7 @@
       </c>
       <c r="P314" s="4" t="inlineStr">
         <is>
-          <t>2026-10-19</t>
+          <t>2026-10-26</t>
         </is>
       </c>
       <c r="Q314" s="4" t="n"/>
@@ -24551,7 +24551,7 @@
       </c>
       <c r="P315" s="4" t="inlineStr">
         <is>
-          <t>2026-10-19</t>
+          <t>2026-10-26</t>
         </is>
       </c>
       <c r="Q315" s="4" t="n"/>
@@ -24630,7 +24630,7 @@
       </c>
       <c r="P316" s="4" t="inlineStr">
         <is>
-          <t>2026-10-19</t>
+          <t>2026-10-26</t>
         </is>
       </c>
       <c r="Q316" s="4" t="n"/>
@@ -24709,7 +24709,7 @@
       </c>
       <c r="P317" s="4" t="inlineStr">
         <is>
-          <t>2026-10-19</t>
+          <t>2026-10-26</t>
         </is>
       </c>
       <c r="Q317" s="4" t="n"/>
@@ -24788,7 +24788,7 @@
       </c>
       <c r="P318" s="4" t="inlineStr">
         <is>
-          <t>2026-10-19</t>
+          <t>2026-10-26</t>
         </is>
       </c>
       <c r="Q318" s="4" t="n"/>
@@ -24867,7 +24867,7 @@
       </c>
       <c r="P319" s="4" t="inlineStr">
         <is>
-          <t>2026-10-19</t>
+          <t>2026-10-26</t>
         </is>
       </c>
       <c r="Q319" s="4" t="n"/>
@@ -24946,7 +24946,7 @@
       </c>
       <c r="P320" s="4" t="inlineStr">
         <is>
-          <t>2026-10-19</t>
+          <t>2026-10-26</t>
         </is>
       </c>
       <c r="Q320" s="4" t="n"/>
@@ -25025,7 +25025,7 @@
       </c>
       <c r="P321" s="4" t="inlineStr">
         <is>
-          <t>2026-10-19</t>
+          <t>2026-10-26</t>
         </is>
       </c>
       <c r="Q321" s="4" t="n"/>
@@ -25104,7 +25104,7 @@
       </c>
       <c r="P322" s="4" t="inlineStr">
         <is>
-          <t>2026-10-19</t>
+          <t>2026-10-26</t>
         </is>
       </c>
       <c r="Q322" s="4" t="n"/>
@@ -25183,7 +25183,7 @@
       </c>
       <c r="P323" s="4" t="inlineStr">
         <is>
-          <t>2026-10-19</t>
+          <t>2026-10-26</t>
         </is>
       </c>
       <c r="Q323" s="4" t="n"/>
@@ -25262,7 +25262,7 @@
       </c>
       <c r="P324" s="4" t="inlineStr">
         <is>
-          <t>2026-10-19</t>
+          <t>2026-10-26</t>
         </is>
       </c>
       <c r="Q324" s="4" t="n"/>
@@ -25341,7 +25341,7 @@
       </c>
       <c r="P325" s="4" t="inlineStr">
         <is>
-          <t>2026-10-19</t>
+          <t>2026-10-26</t>
         </is>
       </c>
       <c r="Q325" s="4" t="n"/>
@@ -25420,7 +25420,7 @@
       </c>
       <c r="P326" s="4" t="inlineStr">
         <is>
-          <t>2026-10-19</t>
+          <t>2026-10-26</t>
         </is>
       </c>
       <c r="Q326" s="4" t="n"/>
@@ -25497,7 +25497,7 @@
       </c>
       <c r="P327" s="4" t="inlineStr">
         <is>
-          <t>2026-10-19</t>
+          <t>2026-10-26</t>
         </is>
       </c>
       <c r="Q327" s="4" t="n"/>
@@ -25574,7 +25574,7 @@
       </c>
       <c r="P328" s="4" t="inlineStr">
         <is>
-          <t>2026-10-19</t>
+          <t>2026-10-26</t>
         </is>
       </c>
       <c r="Q328" s="4" t="n"/>
@@ -25651,7 +25651,7 @@
       </c>
       <c r="P329" s="4" t="inlineStr">
         <is>
-          <t>2026-10-19</t>
+          <t>2026-10-26</t>
         </is>
       </c>
       <c r="Q329" s="4" t="n"/>
@@ -25728,7 +25728,7 @@
       </c>
       <c r="P330" s="4" t="inlineStr">
         <is>
-          <t>2026-10-19</t>
+          <t>2026-10-26</t>
         </is>
       </c>
       <c r="Q330" s="4" t="n"/>
@@ -25805,7 +25805,7 @@
       </c>
       <c r="P331" s="4" t="inlineStr">
         <is>
-          <t>2026-10-19</t>
+          <t>2026-10-26</t>
         </is>
       </c>
       <c r="Q331" s="4" t="n"/>
@@ -25882,7 +25882,7 @@
       </c>
       <c r="P332" s="4" t="inlineStr">
         <is>
-          <t>2026-10-19</t>
+          <t>2026-10-26</t>
         </is>
       </c>
       <c r="Q332" s="4" t="n"/>
@@ -25959,7 +25959,7 @@
       </c>
       <c r="P333" s="4" t="inlineStr">
         <is>
-          <t>2026-10-19</t>
+          <t>2026-10-26</t>
         </is>
       </c>
       <c r="Q333" s="4" t="n"/>
@@ -26036,7 +26036,7 @@
       </c>
       <c r="P334" s="4" t="inlineStr">
         <is>
-          <t>2026-10-19</t>
+          <t>2026-10-26</t>
         </is>
       </c>
       <c r="Q334" s="4" t="n"/>
@@ -26113,7 +26113,7 @@
       </c>
       <c r="P335" s="4" t="inlineStr">
         <is>
-          <t>2026-10-19</t>
+          <t>2026-10-26</t>
         </is>
       </c>
       <c r="Q335" s="4" t="n"/>
@@ -26190,7 +26190,7 @@
       </c>
       <c r="P336" s="4" t="inlineStr">
         <is>
-          <t>2026-10-19</t>
+          <t>2026-10-26</t>
         </is>
       </c>
       <c r="Q336" s="4" t="n"/>
@@ -26275,7 +26275,7 @@
       </c>
       <c r="B9" s="4" t="inlineStr">
         <is>
-          <t>2026-10-19</t>
+          <t>2026-10-26</t>
         </is>
       </c>
     </row>
